--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3AC699A-20E8-432A-B58E-79679B708C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47499DE8-75F7-4B90-86B0-8A1E3E528AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -946,6 +946,108 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_009</t>
   </si>
   <si>
@@ -958,30 +1060,6 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_018</t>
   </si>
   <si>
@@ -994,48 +1072,6 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_010</t>
   </si>
   <si>
@@ -1060,42 +1096,6 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1111,61 +1111,109 @@
     <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
   </si>
   <si>
+    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
+  </si>
+  <si>
+    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220</t>
+  </si>
+  <si>
     <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
   </si>
   <si>
-    <t>e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220,e_w669520367-220</t>
-  </si>
-  <si>
     <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
   </si>
   <si>
-    <t>e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
-  </si>
-  <si>
-    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220</t>
-  </si>
-  <si>
     <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
   </si>
   <si>
     <t>e_w1115312336-220,e_KE7-220</t>
   </si>
   <si>
-    <t>e_w563813243-400,e_w669520367-220</t>
-  </si>
-  <si>
     <t>e_w659874569-220,e_w660091166-220</t>
   </si>
   <si>
-    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220</t>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1180,6 +1228,12 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_014</t>
   </si>
   <si>
@@ -1216,28 +1270,34 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wonelc_won_019</t>
@@ -1246,64 +1306,43 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
   </si>
   <si>
     <t>elc_won_011</t>
@@ -1312,6 +1351,9 @@
     <t>elc_won_007</t>
   </si>
   <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
     <t>elc_won_014</t>
   </si>
   <si>
@@ -1342,84 +1384,78 @@
     <t>elc_won_005</t>
   </si>
   <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220</t>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE11-220</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
   </si>
   <si>
     <t>elc_won_019</t>
   </si>
   <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE11-220</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_002</t>
   </si>
   <si>
@@ -1432,82 +1468,46 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
     <t>e_KE15-220</t>
   </si>
   <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220</t>
+  </si>
+  <si>
     <t>elc_wof_007</t>
   </si>
   <si>
     <t>e_w953567827-220</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
     <t>elc_wof_002</t>
   </si>
   <si>
     <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6603,7 +6603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEFEDC32-535A-413C-ADD6-553B63CFED05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72AB880E-11C9-41FF-9B1D-994E8BDF8A97}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6880,13 +6880,13 @@
         <v>392</v>
       </c>
       <c r="AN11" t="s">
-        <v>328</v>
+        <v>393</v>
       </c>
       <c r="AO11">
-        <v>0.98907459074885506</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP11">
-        <v>200.2991696043234</v>
+        <v>118.22451183716133</v>
       </c>
       <c r="AR11" t="s">
         <v>263</v>
@@ -7023,16 +7023,16 @@
         <v>348</v>
       </c>
       <c r="AM12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN12" t="s">
-        <v>333</v>
+        <v>395</v>
       </c>
       <c r="AO12">
-        <v>0.98670016097490887</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP12">
-        <v>243.83038212667131</v>
+        <v>100.3265162100753</v>
       </c>
       <c r="AR12" t="s">
         <v>263</v>
@@ -7065,10 +7065,10 @@
         <v>449</v>
       </c>
       <c r="BC12">
-        <v>0.99264898847830307</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD12">
-        <v>134.76854456444406</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7169,16 +7169,16 @@
         <v>350</v>
       </c>
       <c r="AM13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AN13" t="s">
-        <v>395</v>
+        <v>328</v>
       </c>
       <c r="AO13">
-        <v>0.9934827767968939</v>
+        <v>0.99675250681341587</v>
       </c>
       <c r="AP13">
-        <v>119.4824253902779</v>
+        <v>59.537375087375146</v>
       </c>
       <c r="AR13" t="s">
         <v>263</v>
@@ -7208,13 +7208,13 @@
         <v>450</v>
       </c>
       <c r="BB13" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="BC13">
-        <v>0.99630507039782612</v>
+        <v>0.99264898847830307</v>
       </c>
       <c r="BD13">
-        <v>67.740376039854553</v>
+        <v>134.76854456444406</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7279,16 +7279,16 @@
         <v>272</v>
       </c>
       <c r="Y14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Z14" t="s">
         <v>327</v>
       </c>
       <c r="AA14">
-        <v>0.99594698839866214</v>
+        <v>0.99782085777346563</v>
       </c>
       <c r="AB14">
-        <v>74.305212691194157</v>
+        <v>39.950940819796543</v>
       </c>
       <c r="AD14" t="s">
         <v>263</v>
@@ -7315,16 +7315,16 @@
         <v>352</v>
       </c>
       <c r="AM14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN14" t="s">
-        <v>328</v>
+        <v>398</v>
       </c>
       <c r="AO14">
-        <v>0.99486941977940613</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP14">
-        <v>94.060637377553505</v>
+        <v>151.6999940525175</v>
       </c>
       <c r="AR14" t="s">
         <v>263</v>
@@ -7351,16 +7351,16 @@
         <v>432</v>
       </c>
       <c r="BA14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="BB14" t="s">
-        <v>339</v>
+        <v>449</v>
       </c>
       <c r="BC14">
-        <v>0.99749257613418407</v>
+        <v>0.99417680250918639</v>
       </c>
       <c r="BD14">
-        <v>45.969437539958705</v>
+        <v>106.75862066491723</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7425,16 +7425,16 @@
         <v>274</v>
       </c>
       <c r="Y15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z15" t="s">
         <v>328</v>
       </c>
       <c r="AA15">
-        <v>0.97482112792654896</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB15">
-        <v>461.61265467993644</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD15" t="s">
         <v>263</v>
@@ -7461,16 +7461,16 @@
         <v>354</v>
       </c>
       <c r="AM15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN15" t="s">
-        <v>398</v>
+        <v>328</v>
       </c>
       <c r="AO15">
-        <v>0.98286027536897036</v>
+        <v>0.99228583594785691</v>
       </c>
       <c r="AP15">
-        <v>314.22828490220974</v>
+        <v>141.42634095595602</v>
       </c>
       <c r="AR15" t="s">
         <v>263</v>
@@ -7497,10 +7497,10 @@
         <v>434</v>
       </c>
       <c r="BA15" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="BB15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="BC15">
         <v>0.99790507974591136</v>
@@ -7571,16 +7571,16 @@
         <v>276</v>
       </c>
       <c r="Y16" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="Z16" t="s">
         <v>329</v>
       </c>
       <c r="AA16">
-        <v>0.99782085777346563</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB16">
-        <v>39.950940819796543</v>
+        <v>179.25118814130403</v>
       </c>
       <c r="AD16" t="s">
         <v>263</v>
@@ -7607,16 +7607,16 @@
         <v>356</v>
       </c>
       <c r="AM16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO16">
-        <v>0.99741412098479176</v>
+        <v>0.99740231224454534</v>
       </c>
       <c r="AP16">
-        <v>47.407781945483563</v>
+        <v>47.624275516669421</v>
       </c>
       <c r="AR16" t="s">
         <v>263</v>
@@ -7643,16 +7643,16 @@
         <v>436</v>
       </c>
       <c r="BA16" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="BB16" t="s">
-        <v>453</v>
+        <v>329</v>
       </c>
       <c r="BC16">
-        <v>0.99567841910080701</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD16">
-        <v>79.228983151871589</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7717,16 +7717,16 @@
         <v>278</v>
       </c>
       <c r="Y17" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="Z17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AA17">
-        <v>0.98497581152539015</v>
+        <v>0.99184104324003575</v>
       </c>
       <c r="AB17">
-        <v>275.44345536784743</v>
+        <v>149.58087393267732</v>
       </c>
       <c r="AD17" t="s">
         <v>263</v>
@@ -7753,16 +7753,16 @@
         <v>358</v>
       </c>
       <c r="AM17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN17" t="s">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="AO17">
-        <v>0.98563074303391496</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP17">
-        <v>263.43637771155954</v>
+        <v>199.81501642792259</v>
       </c>
       <c r="AR17" t="s">
         <v>263</v>
@@ -7789,16 +7789,16 @@
         <v>438</v>
       </c>
       <c r="BA17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BB17" t="s">
-        <v>339</v>
+        <v>454</v>
       </c>
       <c r="BC17">
-        <v>0.99660062084319445</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD17">
-        <v>62.321951208100806</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7866,7 +7866,7 @@
         <v>238</v>
       </c>
       <c r="Z18" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA18">
         <v>0.99592595200224132</v>
@@ -7902,13 +7902,13 @@
         <v>403</v>
       </c>
       <c r="AN18" t="s">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="AO18">
-        <v>0.99059324986934494</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP18">
-        <v>172.45708572867548</v>
+        <v>428.87734626058102</v>
       </c>
       <c r="AR18" t="s">
         <v>263</v>
@@ -7935,16 +7935,16 @@
         <v>440</v>
       </c>
       <c r="BA18" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BB18" t="s">
-        <v>457</v>
+        <v>329</v>
       </c>
       <c r="BC18">
-        <v>0.99417680250918639</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD18">
-        <v>106.75862066491723</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8012,7 +8012,7 @@
         <v>258</v>
       </c>
       <c r="Z19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA19">
         <v>0.98069219916089656</v>
@@ -8045,16 +8045,16 @@
         <v>362</v>
       </c>
       <c r="AM19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN19" t="s">
-        <v>405</v>
+        <v>328</v>
       </c>
       <c r="AO19">
-        <v>0.99355139026342754</v>
+        <v>0.98907459074885506</v>
       </c>
       <c r="AP19">
-        <v>118.22451183716133</v>
+        <v>200.2991696043234</v>
       </c>
       <c r="AR19" t="s">
         <v>263</v>
@@ -8084,13 +8084,13 @@
         <v>458</v>
       </c>
       <c r="BB19" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="BC19">
-        <v>0.99722114454285371</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD19">
-        <v>50.94568338101594</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8155,16 +8155,16 @@
         <v>284</v>
       </c>
       <c r="Y20" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="Z20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AA20">
-        <v>0.99327889425386662</v>
+        <v>0.99585076637156988</v>
       </c>
       <c r="AB20">
-        <v>123.22027201244609</v>
+        <v>76.069283187886086</v>
       </c>
       <c r="AD20" t="s">
         <v>263</v>
@@ -8194,13 +8194,13 @@
         <v>406</v>
       </c>
       <c r="AN20" t="s">
-        <v>407</v>
+        <v>330</v>
       </c>
       <c r="AO20">
-        <v>0.99452764457035958</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP20">
-        <v>100.3265162100753</v>
+        <v>243.83038212667131</v>
       </c>
       <c r="AR20" t="s">
         <v>263</v>
@@ -8230,13 +8230,13 @@
         <v>459</v>
       </c>
       <c r="BB20" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="BC20">
-        <v>0.9940284706913598</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD20">
-        <v>109.47803732507046</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8301,16 +8301,16 @@
         <v>286</v>
       </c>
       <c r="Y21" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="Z21" t="s">
         <v>328</v>
       </c>
       <c r="AA21">
-        <v>0.98440782007749728</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB21">
-        <v>285.85663191255094</v>
+        <v>195.2596724360663</v>
       </c>
       <c r="AD21" t="s">
         <v>263</v>
@@ -8337,16 +8337,16 @@
         <v>366</v>
       </c>
       <c r="AM21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AN21" t="s">
         <v>328</v>
       </c>
       <c r="AO21">
-        <v>0.99675250681341587</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP21">
-        <v>59.537375087375146</v>
+        <v>463.38269175414888</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8411,16 +8411,16 @@
         <v>288</v>
       </c>
       <c r="Y22" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="Z22" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA22">
-        <v>0.99184104324003575</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB22">
-        <v>149.58087393267732</v>
+        <v>449.45770041728053</v>
       </c>
       <c r="AD22" t="s">
         <v>263</v>
@@ -8447,16 +8447,16 @@
         <v>368</v>
       </c>
       <c r="AM22" t="s">
+        <v>408</v>
+      </c>
+      <c r="AN22" t="s">
         <v>409</v>
       </c>
-      <c r="AN22" t="s">
-        <v>410</v>
-      </c>
       <c r="AO22">
-        <v>0.99172545486986263</v>
+        <v>0.9934827767968939</v>
       </c>
       <c r="AP22">
-        <v>151.6999940525175</v>
+        <v>119.4824253902779</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8521,16 +8521,16 @@
         <v>290</v>
       </c>
       <c r="Y23" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="Z23" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AA23">
-        <v>0.99515835423076238</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB23">
-        <v>88.763505769357138</v>
+        <v>596.34855668384682</v>
       </c>
       <c r="AD23" t="s">
         <v>263</v>
@@ -8557,16 +8557,16 @@
         <v>370</v>
       </c>
       <c r="AM23" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AN23" t="s">
-        <v>398</v>
+        <v>328</v>
       </c>
       <c r="AO23">
-        <v>0.99330365963041267</v>
+        <v>0.99486941977940613</v>
       </c>
       <c r="AP23">
-        <v>122.76624010910177</v>
+        <v>94.060637377553505</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8631,16 +8631,16 @@
         <v>292</v>
       </c>
       <c r="Y24" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Z24" t="s">
         <v>335</v>
       </c>
       <c r="AA24">
-        <v>0.99312290929392577</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB24">
-        <v>126.07999627802737</v>
+        <v>171.32529124410425</v>
       </c>
       <c r="AD24" t="s">
         <v>263</v>
@@ -8667,16 +8667,16 @@
         <v>372</v>
       </c>
       <c r="AM24" t="s">
+        <v>411</v>
+      </c>
+      <c r="AN24" t="s">
         <v>412</v>
       </c>
-      <c r="AN24" t="s">
-        <v>413</v>
-      </c>
       <c r="AO24">
-        <v>0.99567808239070055</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP24">
-        <v>79.235156170489844</v>
+        <v>314.22828490220974</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8741,16 +8741,16 @@
         <v>294</v>
       </c>
       <c r="Y25" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="Z25" t="s">
         <v>336</v>
       </c>
       <c r="AA25">
-        <v>0.99065498411395791</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB25">
-        <v>171.32529124410425</v>
+        <v>32.188603269438353</v>
       </c>
       <c r="AD25" t="s">
         <v>263</v>
@@ -8777,16 +8777,16 @@
         <v>374</v>
       </c>
       <c r="AM25" t="s">
+        <v>413</v>
+      </c>
+      <c r="AN25" t="s">
         <v>414</v>
       </c>
-      <c r="AN25" t="s">
-        <v>398</v>
-      </c>
       <c r="AO25">
-        <v>0.98870306310272893</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP25">
-        <v>207.11050978330246</v>
+        <v>47.407781945483563</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8851,16 +8851,16 @@
         <v>296</v>
       </c>
       <c r="Y26" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="Z26" t="s">
         <v>337</v>
       </c>
       <c r="AA26">
-        <v>0.99824425800348515</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB26">
-        <v>32.188603269438353</v>
+        <v>135.59158861107267</v>
       </c>
       <c r="AD26" t="s">
         <v>263</v>
@@ -8890,13 +8890,13 @@
         <v>415</v>
       </c>
       <c r="AN26" t="s">
-        <v>324</v>
+        <v>416</v>
       </c>
       <c r="AO26">
-        <v>0.98667278207972509</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP26">
-        <v>244.33232853837262</v>
+        <v>263.43637771155954</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8961,16 +8961,16 @@
         <v>298</v>
       </c>
       <c r="Y27" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z27" t="s">
         <v>338</v>
       </c>
       <c r="AA27">
-        <v>0.99260409516666881</v>
+        <v>0.99515835423076238</v>
       </c>
       <c r="AB27">
-        <v>135.59158861107267</v>
+        <v>88.763505769357138</v>
       </c>
       <c r="AD27" t="s">
         <v>263</v>
@@ -8997,16 +8997,16 @@
         <v>378</v>
       </c>
       <c r="AM27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN27" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO27">
-        <v>0.98615336674947807</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP27">
-        <v>253.85494292623497</v>
+        <v>172.45708572867548</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9071,16 +9071,16 @@
         <v>300</v>
       </c>
       <c r="Y28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Z28" t="s">
         <v>339</v>
       </c>
       <c r="AA28">
-        <v>0.99022266246501978</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB28">
-        <v>179.25118814130403</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD28" t="s">
         <v>263</v>
@@ -9107,16 +9107,16 @@
         <v>380</v>
       </c>
       <c r="AM28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO28">
-        <v>0.99458682795119768</v>
+        <v>0.99567808239070055</v>
       </c>
       <c r="AP28">
-        <v>99.241487561376104</v>
+        <v>79.235156170489844</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9181,16 +9181,16 @@
         <v>302</v>
       </c>
       <c r="Y29" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="Z29" t="s">
         <v>340</v>
       </c>
       <c r="AA29">
-        <v>0.99787844392938518</v>
+        <v>0.98551105518500948</v>
       </c>
       <c r="AB29">
-        <v>38.895194627939205</v>
+        <v>265.63065494149328</v>
       </c>
       <c r="AD29" t="s">
         <v>263</v>
@@ -9217,16 +9217,16 @@
         <v>382</v>
       </c>
       <c r="AM29" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN29" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="AO29">
-        <v>0.99740231224454534</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP29">
-        <v>47.624275516669421</v>
+        <v>207.11050978330246</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9291,16 +9291,16 @@
         <v>304</v>
       </c>
       <c r="Y30" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="Z30" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="AA30">
-        <v>0.99219647908939179</v>
+        <v>0.99326495911353319</v>
       </c>
       <c r="AB30">
-        <v>143.06455002781746</v>
+        <v>123.47574958522414</v>
       </c>
       <c r="AD30" t="s">
         <v>263</v>
@@ -9330,13 +9330,13 @@
         <v>421</v>
       </c>
       <c r="AN30" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AO30">
-        <v>0.97472458044977373</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP30">
-        <v>463.38269175414888</v>
+        <v>244.33232853837262</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9401,16 +9401,16 @@
         <v>306</v>
       </c>
       <c r="Y31" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="Z31" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA31">
-        <v>0.99199432528561049</v>
+        <v>0.99594698839866214</v>
       </c>
       <c r="AB31">
-        <v>146.77070309714048</v>
+        <v>74.305212691194157</v>
       </c>
       <c r="AD31" t="s">
         <v>263</v>
@@ -9443,10 +9443,10 @@
         <v>328</v>
       </c>
       <c r="AO31">
-        <v>0.99228583594785691</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP31">
-        <v>141.42634095595602</v>
+        <v>253.85494292623497</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9511,16 +9511,16 @@
         <v>308</v>
       </c>
       <c r="Y32" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="Z32" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="AA32">
-        <v>0.99686513787774389</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB32">
-        <v>57.472472241362951</v>
+        <v>461.61265467993644</v>
       </c>
       <c r="AD32" t="s">
         <v>263</v>
@@ -9550,13 +9550,13 @@
         <v>423</v>
       </c>
       <c r="AN32" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="AO32">
-        <v>0.98910099910393146</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP32">
-        <v>199.81501642792259</v>
+        <v>99.241487561376104</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9621,16 +9621,16 @@
         <v>310</v>
       </c>
       <c r="Y33" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="Z33" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AA33">
-        <v>0.99585076637156988</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB33">
-        <v>76.069283187886086</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD33" t="s">
         <v>263</v>
@@ -9657,16 +9657,16 @@
         <v>390</v>
       </c>
       <c r="AM33" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN33" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="AO33">
-        <v>0.97660669020396829</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP33">
-        <v>428.87734626058102</v>
+        <v>122.76624010910177</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9731,16 +9731,16 @@
         <v>312</v>
       </c>
       <c r="Y34" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="Z34" t="s">
         <v>328</v>
       </c>
       <c r="AA34">
-        <v>0.9893494724125782</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB34">
-        <v>195.2596724360663</v>
+        <v>285.85663191255094</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9805,16 +9805,16 @@
         <v>314</v>
       </c>
       <c r="Y35" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="Z35" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA35">
-        <v>0.97548412543178475</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB35">
-        <v>449.45770041728053</v>
+        <v>38.895194627939205</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9879,16 +9879,16 @@
         <v>316</v>
       </c>
       <c r="Y36" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="Z36" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="AA36">
-        <v>0.96747189690815383</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB36">
-        <v>596.34855668384682</v>
+        <v>143.06455002781746</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9953,16 +9953,16 @@
         <v>318</v>
       </c>
       <c r="Y37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Z37" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="AA37">
-        <v>0.98551105518500948</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB37">
-        <v>265.63065494149328</v>
+        <v>146.77070309714048</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10027,16 +10027,16 @@
         <v>320</v>
       </c>
       <c r="Y38" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="Z38" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="AA38">
-        <v>0.99326495911353319</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB38">
-        <v>123.47574958522414</v>
+        <v>57.472472241362951</v>
       </c>
     </row>
   </sheetData>
@@ -10045,7 +10045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022FDAF9-B8D4-4367-A0DA-76CD248283CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC4B77A-0C9C-4758-B8F0-B3433BC6FB67}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10157,7 +10157,7 @@
         <v>460</v>
       </c>
       <c r="K11" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10225,7 +10225,7 @@
         <v>462</v>
       </c>
       <c r="K12" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10258,7 +10258,7 @@
         <v>508</v>
       </c>
       <c r="X12" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10293,7 +10293,7 @@
         <v>464</v>
       </c>
       <c r="K13" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="L13">
         <v>1.5817501567892978</v>
@@ -10326,7 +10326,7 @@
         <v>510</v>
       </c>
       <c r="X13" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10361,7 +10361,7 @@
         <v>466</v>
       </c>
       <c r="K14" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10394,7 +10394,7 @@
         <v>512</v>
       </c>
       <c r="X14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10429,7 +10429,7 @@
         <v>468</v>
       </c>
       <c r="K15" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10462,7 +10462,7 @@
         <v>514</v>
       </c>
       <c r="X15" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10497,7 +10497,7 @@
         <v>470</v>
       </c>
       <c r="K16" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10530,7 +10530,7 @@
         <v>516</v>
       </c>
       <c r="X16" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10565,7 +10565,7 @@
         <v>472</v>
       </c>
       <c r="K17" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10598,7 +10598,7 @@
         <v>518</v>
       </c>
       <c r="X17" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Y17">
         <v>2.2530000000000001</v>
@@ -10633,7 +10633,7 @@
         <v>474</v>
       </c>
       <c r="K18" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10666,7 +10666,7 @@
         <v>520</v>
       </c>
       <c r="X18" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="Y18">
         <v>6.1852499999999999</v>
@@ -10701,7 +10701,7 @@
         <v>476</v>
       </c>
       <c r="K19" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10734,7 +10734,7 @@
         <v>522</v>
       </c>
       <c r="X19" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Y19">
         <v>10.093500000000001</v>
@@ -10769,7 +10769,7 @@
         <v>478</v>
       </c>
       <c r="K20" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10837,7 +10837,7 @@
         <v>480</v>
       </c>
       <c r="K21" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="L21">
         <v>15.316017274089829</v>
@@ -10872,7 +10872,7 @@
         <v>482</v>
       </c>
       <c r="K22" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10907,7 +10907,7 @@
         <v>484</v>
       </c>
       <c r="K23" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="L23">
         <v>15.32235174795542</v>
@@ -10942,7 +10942,7 @@
         <v>486</v>
       </c>
       <c r="K24" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="L24">
         <v>4.3876485804695786</v>
@@ -10977,7 +10977,7 @@
         <v>488</v>
       </c>
       <c r="K25" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -11012,7 +11012,7 @@
         <v>490</v>
       </c>
       <c r="K26" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11047,7 +11047,7 @@
         <v>492</v>
       </c>
       <c r="K27" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11082,7 +11082,7 @@
         <v>494</v>
       </c>
       <c r="K28" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11117,7 +11117,7 @@
         <v>496</v>
       </c>
       <c r="K29" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11152,7 +11152,7 @@
         <v>498</v>
       </c>
       <c r="K30" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11187,7 +11187,7 @@
         <v>500</v>
       </c>
       <c r="K31" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11222,7 +11222,7 @@
         <v>502</v>
       </c>
       <c r="K32" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="L32">
         <v>0.91282903432358287</v>
@@ -11257,7 +11257,7 @@
         <v>504</v>
       </c>
       <c r="K33" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11272,7 +11272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E966AF4F-4430-49FB-9743-202BA1EE47A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257556AA-2496-4B3F-99F8-DBC2AB73FFE7}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13089,7 +13089,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C70E4FDC-0B40-400E-80D2-1E901AA979C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0AE4219-5429-497D-B20B-E16CF43329F8}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47499DE8-75F7-4B90-86B0-8A1E3E528AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BDD3D7F-8E31-4E51-9547-6B58BA0655DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -922,40 +922,172 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_004</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_008</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_solelc_spv_028</t>
@@ -964,208 +1096,154 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE7-220</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
     <t>e_w579310367-220,e_w563813243-400</t>
   </si>
   <si>
     <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
   </si>
   <si>
-    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400</t>
+    <t>e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220</t>
   </si>
   <si>
     <t>e_w660091166-220</t>
   </si>
   <si>
-    <t>e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
-  </si>
-  <si>
-    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE7-220</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w660091166-220</t>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_wonelc_won_002</t>
@@ -1174,6 +1252,36 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_020</t>
   </si>
   <si>
@@ -1192,118 +1300,67 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_022</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w579310367-220</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_KE12-400</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
   </si>
   <si>
     <t>elc_won_002</t>
@@ -1312,6 +1369,24 @@
     <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
   </si>
   <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
     <t>elc_won_020</t>
   </si>
   <si>
@@ -1327,85 +1402,34 @@
     <t>e_KE14-400,e_w870818913-220</t>
   </si>
   <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_KE12-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
     <t>elc_won_022</t>
   </si>
   <si>
     <t>e_KE13-400,e_KE11-220</t>
   </si>
   <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wofelc_wof_001</t>
@@ -1420,34 +1444,22 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_010</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_006</t>
@@ -1456,16 +1468,25 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
   </si>
   <si>
     <t>elc_wof_001</t>
@@ -1477,37 +1498,16 @@
     <t>elc_wof_003</t>
   </si>
   <si>
-    <t>e_KE15-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
     <t>elc_wof_010</t>
   </si>
   <si>
-    <t>elc_wof_009</t>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
   </si>
   <si>
     <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6603,7 +6603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72AB880E-11C9-41FF-9B1D-994E8BDF8A97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E44CC1-6EA9-4112-9718-4E993F621EA5}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6841,16 +6841,16 @@
         <v>264</v>
       </c>
       <c r="Y11" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="Z11" t="s">
         <v>324</v>
       </c>
       <c r="AA11">
-        <v>0.99021329006024306</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB11">
-        <v>179.42301556221076</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD11" t="s">
         <v>263</v>
@@ -6880,13 +6880,13 @@
         <v>392</v>
       </c>
       <c r="AN11" t="s">
-        <v>393</v>
+        <v>325</v>
       </c>
       <c r="AO11">
-        <v>0.99355139026342754</v>
+        <v>0.98907459074885506</v>
       </c>
       <c r="AP11">
-        <v>118.22451183716133</v>
+        <v>200.2991696043234</v>
       </c>
       <c r="AR11" t="s">
         <v>263</v>
@@ -6919,10 +6919,10 @@
         <v>447</v>
       </c>
       <c r="BC11">
-        <v>0.99504452373263619</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD11">
-        <v>90.850398235003013</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6987,16 +6987,16 @@
         <v>268</v>
       </c>
       <c r="Y12" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Z12" t="s">
         <v>325</v>
       </c>
       <c r="AA12">
-        <v>0.99117807442989492</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB12">
-        <v>161.73530211859338</v>
+        <v>285.85663191255094</v>
       </c>
       <c r="AD12" t="s">
         <v>263</v>
@@ -7023,16 +7023,16 @@
         <v>348</v>
       </c>
       <c r="AM12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AN12" t="s">
-        <v>395</v>
+        <v>342</v>
       </c>
       <c r="AO12">
-        <v>0.99452764457035958</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP12">
-        <v>100.3265162100753</v>
+        <v>243.83038212667131</v>
       </c>
       <c r="AR12" t="s">
         <v>263</v>
@@ -7065,10 +7065,10 @@
         <v>449</v>
       </c>
       <c r="BC12">
-        <v>0.99722114454285371</v>
+        <v>0.99417680250918639</v>
       </c>
       <c r="BD12">
-        <v>50.94568338101594</v>
+        <v>106.75862066491723</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7133,16 +7133,16 @@
         <v>270</v>
       </c>
       <c r="Y13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Z13" t="s">
         <v>326</v>
       </c>
       <c r="AA13">
-        <v>0.99806216160693018</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB13">
-        <v>35.52703720627968</v>
+        <v>135.59158861107267</v>
       </c>
       <c r="AD13" t="s">
         <v>263</v>
@@ -7169,16 +7169,16 @@
         <v>350</v>
       </c>
       <c r="AM13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AN13" t="s">
-        <v>328</v>
+        <v>395</v>
       </c>
       <c r="AO13">
-        <v>0.99675250681341587</v>
+        <v>0.99740231224454534</v>
       </c>
       <c r="AP13">
-        <v>59.537375087375146</v>
+        <v>47.624275516669421</v>
       </c>
       <c r="AR13" t="s">
         <v>263</v>
@@ -7279,16 +7279,16 @@
         <v>272</v>
       </c>
       <c r="Y14" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Z14" t="s">
         <v>327</v>
       </c>
       <c r="AA14">
-        <v>0.99782085777346563</v>
+        <v>0.99806216160693018</v>
       </c>
       <c r="AB14">
-        <v>39.950940819796543</v>
+        <v>35.52703720627968</v>
       </c>
       <c r="AD14" t="s">
         <v>263</v>
@@ -7315,16 +7315,16 @@
         <v>352</v>
       </c>
       <c r="AM14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN14" t="s">
-        <v>398</v>
+        <v>342</v>
       </c>
       <c r="AO14">
-        <v>0.99172545486986263</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP14">
-        <v>151.6999940525175</v>
+        <v>199.81501642792259</v>
       </c>
       <c r="AR14" t="s">
         <v>263</v>
@@ -7354,13 +7354,13 @@
         <v>452</v>
       </c>
       <c r="BB14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="BC14">
-        <v>0.99417680250918639</v>
+        <v>0.99790507974591136</v>
       </c>
       <c r="BD14">
-        <v>106.75862066491723</v>
+        <v>38.406871324958367</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7425,16 +7425,16 @@
         <v>274</v>
       </c>
       <c r="Y15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Z15" t="s">
         <v>328</v>
       </c>
       <c r="AA15">
-        <v>0.98497581152539015</v>
+        <v>0.99782085777346563</v>
       </c>
       <c r="AB15">
-        <v>275.44345536784743</v>
+        <v>39.950940819796543</v>
       </c>
       <c r="AD15" t="s">
         <v>263</v>
@@ -7461,16 +7461,16 @@
         <v>354</v>
       </c>
       <c r="AM15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AN15" t="s">
-        <v>328</v>
+        <v>398</v>
       </c>
       <c r="AO15">
-        <v>0.99228583594785691</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP15">
-        <v>141.42634095595602</v>
+        <v>428.87734626058102</v>
       </c>
       <c r="AR15" t="s">
         <v>263</v>
@@ -7503,10 +7503,10 @@
         <v>454</v>
       </c>
       <c r="BC15">
-        <v>0.99790507974591136</v>
+        <v>0.99504452373263619</v>
       </c>
       <c r="BD15">
-        <v>38.406871324958367</v>
+        <v>90.850398235003013</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7571,16 +7571,16 @@
         <v>276</v>
       </c>
       <c r="Y16" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="Z16" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="AA16">
-        <v>0.99022266246501978</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB16">
-        <v>179.25118814130403</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD16" t="s">
         <v>263</v>
@@ -7607,16 +7607,16 @@
         <v>356</v>
       </c>
       <c r="AM16" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AN16" t="s">
-        <v>401</v>
+        <v>325</v>
       </c>
       <c r="AO16">
-        <v>0.99740231224454534</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP16">
-        <v>47.624275516669421</v>
+        <v>463.38269175414888</v>
       </c>
       <c r="AR16" t="s">
         <v>263</v>
@@ -7646,13 +7646,13 @@
         <v>455</v>
       </c>
       <c r="BB16" t="s">
-        <v>329</v>
+        <v>449</v>
       </c>
       <c r="BC16">
-        <v>0.99660062084319445</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD16">
-        <v>62.321951208100806</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7717,16 +7717,16 @@
         <v>278</v>
       </c>
       <c r="Y17" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="Z17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AA17">
-        <v>0.99184104324003575</v>
+        <v>0.99585076637156988</v>
       </c>
       <c r="AB17">
-        <v>149.58087393267732</v>
+        <v>76.069283187886086</v>
       </c>
       <c r="AD17" t="s">
         <v>263</v>
@@ -7753,16 +7753,16 @@
         <v>358</v>
       </c>
       <c r="AM17" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AN17" t="s">
-        <v>330</v>
+        <v>401</v>
       </c>
       <c r="AO17">
-        <v>0.98910099910393146</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP17">
-        <v>199.81501642792259</v>
+        <v>314.22828490220974</v>
       </c>
       <c r="AR17" t="s">
         <v>263</v>
@@ -7792,13 +7792,13 @@
         <v>456</v>
       </c>
       <c r="BB17" t="s">
-        <v>454</v>
+        <v>345</v>
       </c>
       <c r="BC17">
-        <v>0.99567841910080701</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD17">
-        <v>79.228983151871589</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7863,16 +7863,16 @@
         <v>280</v>
       </c>
       <c r="Y18" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Z18" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AA18">
-        <v>0.99592595200224132</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB18">
-        <v>74.690879958909605</v>
+        <v>195.2596724360663</v>
       </c>
       <c r="AD18" t="s">
         <v>263</v>
@@ -7899,16 +7899,16 @@
         <v>360</v>
       </c>
       <c r="AM18" t="s">
+        <v>402</v>
+      </c>
+      <c r="AN18" t="s">
         <v>403</v>
       </c>
-      <c r="AN18" t="s">
-        <v>404</v>
-      </c>
       <c r="AO18">
-        <v>0.97660669020396829</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP18">
-        <v>428.87734626058102</v>
+        <v>47.407781945483563</v>
       </c>
       <c r="AR18" t="s">
         <v>263</v>
@@ -7938,13 +7938,13 @@
         <v>457</v>
       </c>
       <c r="BB18" t="s">
-        <v>329</v>
+        <v>454</v>
       </c>
       <c r="BC18">
-        <v>0.9940284706913598</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD18">
-        <v>109.47803732507046</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8009,16 +8009,16 @@
         <v>282</v>
       </c>
       <c r="Y19" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Z19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AA19">
-        <v>0.98069219916089656</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB19">
-        <v>353.97634871689564</v>
+        <v>449.45770041728053</v>
       </c>
       <c r="AD19" t="s">
         <v>263</v>
@@ -8045,16 +8045,16 @@
         <v>362</v>
       </c>
       <c r="AM19" t="s">
+        <v>404</v>
+      </c>
+      <c r="AN19" t="s">
         <v>405</v>
       </c>
-      <c r="AN19" t="s">
-        <v>328</v>
-      </c>
       <c r="AO19">
-        <v>0.98907459074885506</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP19">
-        <v>200.2991696043234</v>
+        <v>263.43637771155954</v>
       </c>
       <c r="AR19" t="s">
         <v>263</v>
@@ -8084,13 +8084,13 @@
         <v>458</v>
       </c>
       <c r="BB19" t="s">
-        <v>447</v>
+        <v>345</v>
       </c>
       <c r="BC19">
-        <v>0.99630507039782612</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD19">
-        <v>67.740376039854553</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8155,16 +8155,16 @@
         <v>284</v>
       </c>
       <c r="Y20" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="Z20" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="AA20">
-        <v>0.99585076637156988</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB20">
-        <v>76.069283187886086</v>
+        <v>596.34855668384682</v>
       </c>
       <c r="AD20" t="s">
         <v>263</v>
@@ -8194,13 +8194,13 @@
         <v>406</v>
       </c>
       <c r="AN20" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="AO20">
-        <v>0.98670016097490887</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP20">
-        <v>243.83038212667131</v>
+        <v>172.45708572867548</v>
       </c>
       <c r="AR20" t="s">
         <v>263</v>
@@ -8230,13 +8230,13 @@
         <v>459</v>
       </c>
       <c r="BB20" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="BC20">
-        <v>0.99749257613418407</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD20">
-        <v>45.969437539958705</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8301,16 +8301,16 @@
         <v>286</v>
       </c>
       <c r="Y21" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Z21" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AA21">
-        <v>0.9893494724125782</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB21">
-        <v>195.2596724360663</v>
+        <v>74.690879958909605</v>
       </c>
       <c r="AD21" t="s">
         <v>263</v>
@@ -8340,13 +8340,13 @@
         <v>407</v>
       </c>
       <c r="AN21" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AO21">
-        <v>0.97472458044977373</v>
+        <v>0.99228583594785691</v>
       </c>
       <c r="AP21">
-        <v>463.38269175414888</v>
+        <v>141.42634095595602</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8411,16 +8411,16 @@
         <v>288</v>
       </c>
       <c r="Y22" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="Z22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AA22">
-        <v>0.97548412543178475</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB22">
-        <v>449.45770041728053</v>
+        <v>353.97634871689564</v>
       </c>
       <c r="AD22" t="s">
         <v>263</v>
@@ -8521,16 +8521,16 @@
         <v>290</v>
       </c>
       <c r="Y23" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="Z23" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AA23">
-        <v>0.96747189690815383</v>
+        <v>0.99594698839866214</v>
       </c>
       <c r="AB23">
-        <v>596.34855668384682</v>
+        <v>74.305212691194157</v>
       </c>
       <c r="AD23" t="s">
         <v>263</v>
@@ -8560,7 +8560,7 @@
         <v>410</v>
       </c>
       <c r="AN23" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AO23">
         <v>0.99486941977940613</v>
@@ -8631,16 +8631,16 @@
         <v>292</v>
       </c>
       <c r="Y24" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="Z24" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="AA24">
-        <v>0.99065498411395791</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB24">
-        <v>171.32529124410425</v>
+        <v>461.61265467993644</v>
       </c>
       <c r="AD24" t="s">
         <v>263</v>
@@ -8673,10 +8673,10 @@
         <v>412</v>
       </c>
       <c r="AO24">
-        <v>0.98286027536897036</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP24">
-        <v>314.22828490220974</v>
+        <v>118.22451183716133</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8741,16 +8741,16 @@
         <v>294</v>
       </c>
       <c r="Y25" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="Z25" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AA25">
-        <v>0.99824425800348515</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB25">
-        <v>32.188603269438353</v>
+        <v>171.32529124410425</v>
       </c>
       <c r="AD25" t="s">
         <v>263</v>
@@ -8780,13 +8780,13 @@
         <v>413</v>
       </c>
       <c r="AN25" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="AO25">
-        <v>0.99741412098479176</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP25">
-        <v>47.407781945483563</v>
+        <v>207.11050978330246</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8851,16 +8851,16 @@
         <v>296</v>
       </c>
       <c r="Y26" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="Z26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA26">
-        <v>0.99260409516666881</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB26">
-        <v>135.59158861107267</v>
+        <v>38.895194627939205</v>
       </c>
       <c r="AD26" t="s">
         <v>263</v>
@@ -8887,16 +8887,16 @@
         <v>376</v>
       </c>
       <c r="AM26" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN26" t="s">
-        <v>416</v>
+        <v>340</v>
       </c>
       <c r="AO26">
-        <v>0.98563074303391496</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP26">
-        <v>263.43637771155954</v>
+        <v>244.33232853837262</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8961,16 +8961,16 @@
         <v>298</v>
       </c>
       <c r="Y27" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="Z27" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AA27">
-        <v>0.99515835423076238</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB27">
-        <v>88.763505769357138</v>
+        <v>143.06455002781746</v>
       </c>
       <c r="AD27" t="s">
         <v>263</v>
@@ -8997,16 +8997,16 @@
         <v>378</v>
       </c>
       <c r="AM27" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AN27" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="AO27">
-        <v>0.99059324986934494</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP27">
-        <v>172.45708572867548</v>
+        <v>253.85494292623497</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9071,16 +9071,16 @@
         <v>300</v>
       </c>
       <c r="Y28" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Z28" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AA28">
-        <v>0.99312290929392577</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB28">
-        <v>126.07999627802737</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD28" t="s">
         <v>263</v>
@@ -9107,16 +9107,16 @@
         <v>380</v>
       </c>
       <c r="AM28" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AN28" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AO28">
-        <v>0.99567808239070055</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP28">
-        <v>79.235156170489844</v>
+        <v>99.241487561376104</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9181,16 +9181,16 @@
         <v>302</v>
       </c>
       <c r="Y29" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Z29" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AA29">
-        <v>0.98551105518500948</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB29">
-        <v>265.63065494149328</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD29" t="s">
         <v>263</v>
@@ -9217,16 +9217,16 @@
         <v>382</v>
       </c>
       <c r="AM29" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AN29" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AO29">
-        <v>0.98870306310272893</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP29">
-        <v>207.11050978330246</v>
+        <v>122.76624010910177</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9291,16 +9291,16 @@
         <v>304</v>
       </c>
       <c r="Y30" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="Z30" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AA30">
-        <v>0.99326495911353319</v>
+        <v>0.99515835423076238</v>
       </c>
       <c r="AB30">
-        <v>123.47574958522414</v>
+        <v>88.763505769357138</v>
       </c>
       <c r="AD30" t="s">
         <v>263</v>
@@ -9327,16 +9327,16 @@
         <v>384</v>
       </c>
       <c r="AM30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AN30" t="s">
-        <v>324</v>
+        <v>420</v>
       </c>
       <c r="AO30">
-        <v>0.98667278207972509</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP30">
-        <v>244.33232853837262</v>
+        <v>100.3265162100753</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9401,16 +9401,16 @@
         <v>306</v>
       </c>
       <c r="Y31" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="Z31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AA31">
-        <v>0.99594698839866214</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB31">
-        <v>74.305212691194157</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD31" t="s">
         <v>263</v>
@@ -9437,16 +9437,16 @@
         <v>386</v>
       </c>
       <c r="AM31" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AN31" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AO31">
-        <v>0.98615336674947807</v>
+        <v>0.99675250681341587</v>
       </c>
       <c r="AP31">
-        <v>253.85494292623497</v>
+        <v>59.537375087375146</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9511,16 +9511,16 @@
         <v>308</v>
       </c>
       <c r="Y32" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="Z32" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="AA32">
-        <v>0.97482112792654896</v>
+        <v>0.99021329006024306</v>
       </c>
       <c r="AB32">
-        <v>461.61265467993644</v>
+        <v>179.42301556221076</v>
       </c>
       <c r="AD32" t="s">
         <v>263</v>
@@ -9547,16 +9547,16 @@
         <v>388</v>
       </c>
       <c r="AM32" t="s">
+        <v>422</v>
+      </c>
+      <c r="AN32" t="s">
         <v>423</v>
       </c>
-      <c r="AN32" t="s">
-        <v>424</v>
-      </c>
       <c r="AO32">
-        <v>0.99458682795119768</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP32">
-        <v>99.241487561376104</v>
+        <v>151.6999940525175</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9621,16 +9621,16 @@
         <v>310</v>
       </c>
       <c r="Y33" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="Z33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA33">
-        <v>0.99327889425386662</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB33">
-        <v>123.22027201244609</v>
+        <v>161.73530211859338</v>
       </c>
       <c r="AD33" t="s">
         <v>263</v>
@@ -9657,16 +9657,16 @@
         <v>390</v>
       </c>
       <c r="AM33" t="s">
+        <v>424</v>
+      </c>
+      <c r="AN33" t="s">
         <v>425</v>
       </c>
-      <c r="AN33" t="s">
-        <v>412</v>
-      </c>
       <c r="AO33">
-        <v>0.99330365963041267</v>
+        <v>0.99567808239070055</v>
       </c>
       <c r="AP33">
-        <v>122.76624010910177</v>
+        <v>79.235156170489844</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9731,16 +9731,16 @@
         <v>312</v>
       </c>
       <c r="Y34" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="Z34" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="AA34">
-        <v>0.98440782007749728</v>
+        <v>0.99184104324003575</v>
       </c>
       <c r="AB34">
-        <v>285.85663191255094</v>
+        <v>149.58087393267732</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9805,16 +9805,16 @@
         <v>314</v>
       </c>
       <c r="Y35" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="Z35" t="s">
         <v>343</v>
       </c>
       <c r="AA35">
-        <v>0.99787844392938518</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB35">
-        <v>38.895194627939205</v>
+        <v>32.188603269438353</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9879,16 +9879,16 @@
         <v>316</v>
       </c>
       <c r="Y36" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="Z36" t="s">
         <v>344</v>
       </c>
       <c r="AA36">
-        <v>0.99219647908939179</v>
+        <v>0.98551105518500948</v>
       </c>
       <c r="AB36">
-        <v>143.06455002781746</v>
+        <v>265.63065494149328</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9953,16 +9953,16 @@
         <v>318</v>
       </c>
       <c r="Y37" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="Z37" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="AA37">
-        <v>0.99199432528561049</v>
+        <v>0.99326495911353319</v>
       </c>
       <c r="AB37">
-        <v>146.77070309714048</v>
+        <v>123.47574958522414</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10027,16 +10027,16 @@
         <v>320</v>
       </c>
       <c r="Y38" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z38" t="s">
         <v>345</v>
       </c>
       <c r="AA38">
-        <v>0.99686513787774389</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB38">
-        <v>57.472472241362951</v>
+        <v>179.25118814130403</v>
       </c>
     </row>
   </sheetData>
@@ -10045,7 +10045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC4B77A-0C9C-4758-B8F0-B3433BC6FB67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33F563A-789E-476F-A5DB-A79944DB4880}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10157,7 +10157,7 @@
         <v>460</v>
       </c>
       <c r="K11" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10190,7 +10190,7 @@
         <v>506</v>
       </c>
       <c r="X11" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="Y11">
         <v>8.3782499999999995</v>
@@ -10225,7 +10225,7 @@
         <v>462</v>
       </c>
       <c r="K12" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10258,7 +10258,7 @@
         <v>508</v>
       </c>
       <c r="X12" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10293,7 +10293,7 @@
         <v>464</v>
       </c>
       <c r="K13" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="L13">
         <v>1.5817501567892978</v>
@@ -10326,7 +10326,7 @@
         <v>510</v>
       </c>
       <c r="X13" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10361,7 +10361,7 @@
         <v>466</v>
       </c>
       <c r="K14" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10394,7 +10394,7 @@
         <v>512</v>
       </c>
       <c r="X14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10429,7 +10429,7 @@
         <v>468</v>
       </c>
       <c r="K15" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10462,7 +10462,7 @@
         <v>514</v>
       </c>
       <c r="X15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10497,7 +10497,7 @@
         <v>470</v>
       </c>
       <c r="K16" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10530,7 +10530,7 @@
         <v>516</v>
       </c>
       <c r="X16" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10565,7 +10565,7 @@
         <v>472</v>
       </c>
       <c r="K17" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10633,7 +10633,7 @@
         <v>474</v>
       </c>
       <c r="K18" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10666,7 +10666,7 @@
         <v>520</v>
       </c>
       <c r="X18" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="Y18">
         <v>6.1852499999999999</v>
@@ -10701,7 +10701,7 @@
         <v>476</v>
       </c>
       <c r="K19" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10734,7 +10734,7 @@
         <v>522</v>
       </c>
       <c r="X19" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="Y19">
         <v>10.093500000000001</v>
@@ -10769,7 +10769,7 @@
         <v>478</v>
       </c>
       <c r="K20" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10802,7 +10802,7 @@
         <v>524</v>
       </c>
       <c r="X20" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10837,7 +10837,7 @@
         <v>480</v>
       </c>
       <c r="K21" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="L21">
         <v>15.316017274089829</v>
@@ -10907,7 +10907,7 @@
         <v>484</v>
       </c>
       <c r="K23" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="L23">
         <v>15.32235174795542</v>
@@ -10977,7 +10977,7 @@
         <v>488</v>
       </c>
       <c r="K25" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -11012,7 +11012,7 @@
         <v>490</v>
       </c>
       <c r="K26" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11047,7 +11047,7 @@
         <v>492</v>
       </c>
       <c r="K27" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11082,7 +11082,7 @@
         <v>494</v>
       </c>
       <c r="K28" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11117,7 +11117,7 @@
         <v>496</v>
       </c>
       <c r="K29" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11152,7 +11152,7 @@
         <v>498</v>
       </c>
       <c r="K30" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11187,7 +11187,7 @@
         <v>500</v>
       </c>
       <c r="K31" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11222,7 +11222,7 @@
         <v>502</v>
       </c>
       <c r="K32" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="L32">
         <v>0.91282903432358287</v>
@@ -11257,7 +11257,7 @@
         <v>504</v>
       </c>
       <c r="K33" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11272,7 +11272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257556AA-2496-4B3F-99F8-DBC2AB73FFE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA49A748-0F38-4A53-9FD2-47DA1FAB87CA}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13089,7 +13089,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0AE4219-5429-497D-B20B-E16CF43329F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604AAA63-E6DD-4142-BAE0-EB6982F75C89}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BDD3D7F-8E31-4E51-9547-6B58BA0655DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1B5AA14-17BF-4659-9F5E-E113591BBA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -922,82 +922,154 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_018</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_014</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_solelc_spv_009</t>
@@ -1012,72 +1084,6 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_023</t>
   </si>
   <si>
@@ -1090,82 +1096,112 @@
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
+  </si>
+  <si>
+    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE7-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
+  </si>
+  <si>
+    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
+  </si>
+  <si>
     <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
   </si>
   <si>
-    <t>e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220,e_w669520367-220</t>
+    <t>e_w669520367-220,e_w563813243-400</t>
   </si>
   <si>
     <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
   </si>
   <si>
-    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE7-220</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
-  </si>
-  <si>
     <t>e_w669520367-220</t>
   </si>
   <si>
-    <t>e_w660091166-220</t>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1180,108 +1216,78 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_003</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_002</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_020</t>
   </si>
   <si>
@@ -1300,10 +1306,34 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w579310367-220</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_KE12-400</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
   </si>
   <si>
     <t>elc_won_011</t>
@@ -1312,81 +1342,57 @@
     <t>elc_won_007</t>
   </si>
   <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE11-220</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
     <t>elc_won_003</t>
   </si>
   <si>
     <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_KE12-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
     <t>elc_won_002</t>
   </si>
   <si>
     <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
   </si>
   <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
     <t>elc_won_020</t>
   </si>
   <si>
@@ -1402,10 +1408,34 @@
     <t>e_KE14-400,e_w870818913-220</t>
   </si>
   <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE11-220</t>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wofelc_wof_009</t>
@@ -1414,42 +1444,12 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_002</t>
   </si>
   <si>
@@ -1468,37 +1468,37 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_KE15-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
     <t>elc_wof_009</t>
   </si>
   <si>
     <t>e_w953567827-220,e_w660091166-220</t>
   </si>
   <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w953567827-220</t>
-  </si>
-  <si>
     <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_KE15-220</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
   </si>
   <si>
     <t>elc_wof_002</t>
@@ -6603,7 +6603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E44CC1-6EA9-4112-9718-4E993F621EA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{205F502F-B890-4626-A7A0-B14121FC7D75}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6841,16 +6841,16 @@
         <v>264</v>
       </c>
       <c r="Y11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z11" t="s">
         <v>324</v>
       </c>
       <c r="AA11">
-        <v>0.99327889425386662</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB11">
-        <v>123.22027201244609</v>
+        <v>135.59158861107267</v>
       </c>
       <c r="AD11" t="s">
         <v>263</v>
@@ -6880,13 +6880,13 @@
         <v>392</v>
       </c>
       <c r="AN11" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="AO11">
-        <v>0.98907459074885506</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP11">
-        <v>200.2991696043234</v>
+        <v>314.22828490220974</v>
       </c>
       <c r="AR11" t="s">
         <v>263</v>
@@ -6919,10 +6919,10 @@
         <v>447</v>
       </c>
       <c r="BC11">
-        <v>0.99567841910080701</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD11">
-        <v>79.228983151871589</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6987,16 +6987,16 @@
         <v>268</v>
       </c>
       <c r="Y12" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="Z12" t="s">
         <v>325</v>
       </c>
       <c r="AA12">
-        <v>0.98440782007749728</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB12">
-        <v>285.85663191255094</v>
+        <v>38.895194627939205</v>
       </c>
       <c r="AD12" t="s">
         <v>263</v>
@@ -7023,16 +7023,16 @@
         <v>348</v>
       </c>
       <c r="AM12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN12" t="s">
-        <v>342</v>
+        <v>395</v>
       </c>
       <c r="AO12">
-        <v>0.98670016097490887</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP12">
-        <v>243.83038212667131</v>
+        <v>47.407781945483563</v>
       </c>
       <c r="AR12" t="s">
         <v>263</v>
@@ -7062,7 +7062,7 @@
         <v>448</v>
       </c>
       <c r="BB12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="BC12">
         <v>0.99417680250918639</v>
@@ -7133,16 +7133,16 @@
         <v>270</v>
       </c>
       <c r="Y13" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="Z13" t="s">
         <v>326</v>
       </c>
       <c r="AA13">
-        <v>0.99260409516666881</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB13">
-        <v>135.59158861107267</v>
+        <v>143.06455002781746</v>
       </c>
       <c r="AD13" t="s">
         <v>263</v>
@@ -7169,16 +7169,16 @@
         <v>350</v>
       </c>
       <c r="AM13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AN13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AO13">
-        <v>0.99740231224454534</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP13">
-        <v>47.624275516669421</v>
+        <v>263.43637771155954</v>
       </c>
       <c r="AR13" t="s">
         <v>263</v>
@@ -7205,16 +7205,16 @@
         <v>430</v>
       </c>
       <c r="BA13" t="s">
+        <v>449</v>
+      </c>
+      <c r="BB13" t="s">
         <v>450</v>
       </c>
-      <c r="BB13" t="s">
-        <v>451</v>
-      </c>
       <c r="BC13">
-        <v>0.99264898847830307</v>
+        <v>0.99504452373263619</v>
       </c>
       <c r="BD13">
-        <v>134.76854456444406</v>
+        <v>90.850398235003013</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7279,16 +7279,16 @@
         <v>272</v>
       </c>
       <c r="Y14" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Z14" t="s">
         <v>327</v>
       </c>
       <c r="AA14">
-        <v>0.99806216160693018</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB14">
-        <v>35.52703720627968</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD14" t="s">
         <v>263</v>
@@ -7315,16 +7315,16 @@
         <v>352</v>
       </c>
       <c r="AM14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AN14" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="AO14">
-        <v>0.98910099910393146</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP14">
-        <v>199.81501642792259</v>
+        <v>172.45708572867548</v>
       </c>
       <c r="AR14" t="s">
         <v>263</v>
@@ -7351,16 +7351,16 @@
         <v>432</v>
       </c>
       <c r="BA14" t="s">
+        <v>451</v>
+      </c>
+      <c r="BB14" t="s">
         <v>452</v>
       </c>
-      <c r="BB14" t="s">
-        <v>447</v>
-      </c>
       <c r="BC14">
-        <v>0.99790507974591136</v>
+        <v>0.99264898847830307</v>
       </c>
       <c r="BD14">
-        <v>38.406871324958367</v>
+        <v>134.76854456444406</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7425,16 +7425,16 @@
         <v>274</v>
       </c>
       <c r="Y15" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="Z15" t="s">
         <v>328</v>
       </c>
       <c r="AA15">
-        <v>0.99782085777346563</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB15">
-        <v>39.950940819796543</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD15" t="s">
         <v>263</v>
@@ -7461,16 +7461,16 @@
         <v>354</v>
       </c>
       <c r="AM15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AO15">
-        <v>0.97660669020396829</v>
+        <v>0.9934827767968939</v>
       </c>
       <c r="AP15">
-        <v>428.87734626058102</v>
+        <v>119.4824253902779</v>
       </c>
       <c r="AR15" t="s">
         <v>263</v>
@@ -7500,13 +7500,13 @@
         <v>453</v>
       </c>
       <c r="BB15" t="s">
-        <v>454</v>
+        <v>333</v>
       </c>
       <c r="BC15">
-        <v>0.99504452373263619</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD15">
-        <v>90.850398235003013</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7571,16 +7571,16 @@
         <v>276</v>
       </c>
       <c r="Y16" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="Z16" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AA16">
-        <v>0.98497581152539015</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB16">
-        <v>275.44345536784743</v>
+        <v>74.690879958909605</v>
       </c>
       <c r="AD16" t="s">
         <v>263</v>
@@ -7607,16 +7607,16 @@
         <v>356</v>
       </c>
       <c r="AM16" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN16" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AO16">
-        <v>0.97472458044977373</v>
+        <v>0.99486941977940613</v>
       </c>
       <c r="AP16">
-        <v>463.38269175414888</v>
+        <v>94.060637377553505</v>
       </c>
       <c r="AR16" t="s">
         <v>263</v>
@@ -7643,16 +7643,16 @@
         <v>436</v>
       </c>
       <c r="BA16" t="s">
+        <v>454</v>
+      </c>
+      <c r="BB16" t="s">
         <v>455</v>
       </c>
-      <c r="BB16" t="s">
-        <v>449</v>
-      </c>
       <c r="BC16">
-        <v>0.99722114454285371</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD16">
-        <v>50.94568338101594</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7717,16 +7717,16 @@
         <v>278</v>
       </c>
       <c r="Y17" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="Z17" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA17">
-        <v>0.99585076637156988</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB17">
-        <v>76.069283187886086</v>
+        <v>353.97634871689564</v>
       </c>
       <c r="AD17" t="s">
         <v>263</v>
@@ -7753,16 +7753,16 @@
         <v>358</v>
       </c>
       <c r="AM17" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN17" t="s">
-        <v>401</v>
+        <v>332</v>
       </c>
       <c r="AO17">
-        <v>0.98286027536897036</v>
+        <v>0.98907459074885506</v>
       </c>
       <c r="AP17">
-        <v>314.22828490220974</v>
+        <v>200.2991696043234</v>
       </c>
       <c r="AR17" t="s">
         <v>263</v>
@@ -7792,13 +7792,13 @@
         <v>456</v>
       </c>
       <c r="BB17" t="s">
-        <v>345</v>
+        <v>455</v>
       </c>
       <c r="BC17">
-        <v>0.99660062084319445</v>
+        <v>0.99790507974591136</v>
       </c>
       <c r="BD17">
-        <v>62.321951208100806</v>
+        <v>38.406871324958367</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7863,16 +7863,16 @@
         <v>280</v>
       </c>
       <c r="Y18" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Z18" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AA18">
-        <v>0.9893494724125782</v>
+        <v>0.99585076637156988</v>
       </c>
       <c r="AB18">
-        <v>195.2596724360663</v>
+        <v>76.069283187886086</v>
       </c>
       <c r="AD18" t="s">
         <v>263</v>
@@ -7899,16 +7899,16 @@
         <v>360</v>
       </c>
       <c r="AM18" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN18" t="s">
-        <v>403</v>
+        <v>343</v>
       </c>
       <c r="AO18">
-        <v>0.99741412098479176</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP18">
-        <v>47.407781945483563</v>
+        <v>243.83038212667131</v>
       </c>
       <c r="AR18" t="s">
         <v>263</v>
@@ -7938,7 +7938,7 @@
         <v>457</v>
       </c>
       <c r="BB18" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="BC18">
         <v>0.99630507039782612</v>
@@ -8009,16 +8009,16 @@
         <v>282</v>
       </c>
       <c r="Y19" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="Z19" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AA19">
-        <v>0.97548412543178475</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB19">
-        <v>449.45770041728053</v>
+        <v>195.2596724360663</v>
       </c>
       <c r="AD19" t="s">
         <v>263</v>
@@ -8048,13 +8048,13 @@
         <v>404</v>
       </c>
       <c r="AN19" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="AO19">
-        <v>0.98563074303391496</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP19">
-        <v>263.43637771155954</v>
+        <v>122.76624010910177</v>
       </c>
       <c r="AR19" t="s">
         <v>263</v>
@@ -8084,7 +8084,7 @@
         <v>458</v>
       </c>
       <c r="BB19" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="BC19">
         <v>0.99749257613418407</v>
@@ -8155,16 +8155,16 @@
         <v>284</v>
       </c>
       <c r="Y20" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="Z20" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AA20">
-        <v>0.96747189690815383</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB20">
-        <v>596.34855668384682</v>
+        <v>449.45770041728053</v>
       </c>
       <c r="AD20" t="s">
         <v>263</v>
@@ -8191,16 +8191,16 @@
         <v>364</v>
       </c>
       <c r="AM20" t="s">
+        <v>405</v>
+      </c>
+      <c r="AN20" t="s">
         <v>406</v>
       </c>
-      <c r="AN20" t="s">
-        <v>345</v>
-      </c>
       <c r="AO20">
-        <v>0.99059324986934494</v>
+        <v>0.99567808239070055</v>
       </c>
       <c r="AP20">
-        <v>172.45708572867548</v>
+        <v>79.235156170489844</v>
       </c>
       <c r="AR20" t="s">
         <v>263</v>
@@ -8230,7 +8230,7 @@
         <v>459</v>
       </c>
       <c r="BB20" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="BC20">
         <v>0.9940284706913598</v>
@@ -8301,16 +8301,16 @@
         <v>286</v>
       </c>
       <c r="Y21" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="Z21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA21">
-        <v>0.99592595200224132</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB21">
-        <v>74.690879958909605</v>
+        <v>596.34855668384682</v>
       </c>
       <c r="AD21" t="s">
         <v>263</v>
@@ -8340,13 +8340,13 @@
         <v>407</v>
       </c>
       <c r="AN21" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AO21">
-        <v>0.99228583594785691</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP21">
-        <v>141.42634095595602</v>
+        <v>463.38269175414888</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8411,16 +8411,16 @@
         <v>288</v>
       </c>
       <c r="Y22" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Z22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AA22">
-        <v>0.98069219916089656</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB22">
-        <v>353.97634871689564</v>
+        <v>179.25118814130403</v>
       </c>
       <c r="AD22" t="s">
         <v>263</v>
@@ -8450,13 +8450,13 @@
         <v>408</v>
       </c>
       <c r="AN22" t="s">
-        <v>409</v>
+        <v>343</v>
       </c>
       <c r="AO22">
-        <v>0.9934827767968939</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP22">
-        <v>119.4824253902779</v>
+        <v>199.81501642792259</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8521,16 +8521,16 @@
         <v>290</v>
       </c>
       <c r="Y23" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="Z23" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA23">
-        <v>0.99594698839866214</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB23">
-        <v>74.305212691194157</v>
+        <v>171.32529124410425</v>
       </c>
       <c r="AD23" t="s">
         <v>263</v>
@@ -8557,16 +8557,16 @@
         <v>370</v>
       </c>
       <c r="AM23" t="s">
+        <v>409</v>
+      </c>
+      <c r="AN23" t="s">
         <v>410</v>
       </c>
-      <c r="AN23" t="s">
-        <v>325</v>
-      </c>
       <c r="AO23">
-        <v>0.99486941977940613</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP23">
-        <v>94.060637377553505</v>
+        <v>428.87734626058102</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8631,16 +8631,16 @@
         <v>292</v>
       </c>
       <c r="Y24" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Z24" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="AA24">
-        <v>0.97482112792654896</v>
+        <v>0.99806216160693018</v>
       </c>
       <c r="AB24">
-        <v>461.61265467993644</v>
+        <v>35.52703720627968</v>
       </c>
       <c r="AD24" t="s">
         <v>263</v>
@@ -8670,13 +8670,13 @@
         <v>411</v>
       </c>
       <c r="AN24" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="AO24">
-        <v>0.99355139026342754</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP24">
-        <v>118.22451183716133</v>
+        <v>207.11050978330246</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8741,16 +8741,16 @@
         <v>294</v>
       </c>
       <c r="Y25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Z25" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA25">
-        <v>0.99065498411395791</v>
+        <v>0.99515835423076238</v>
       </c>
       <c r="AB25">
-        <v>171.32529124410425</v>
+        <v>88.763505769357138</v>
       </c>
       <c r="AD25" t="s">
         <v>263</v>
@@ -8777,16 +8777,16 @@
         <v>374</v>
       </c>
       <c r="AM25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AN25" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="AO25">
-        <v>0.98870306310272893</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP25">
-        <v>207.11050978330246</v>
+        <v>244.33232853837262</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8851,16 +8851,16 @@
         <v>296</v>
       </c>
       <c r="Y26" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="Z26" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AA26">
-        <v>0.99787844392938518</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB26">
-        <v>38.895194627939205</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD26" t="s">
         <v>263</v>
@@ -8887,16 +8887,16 @@
         <v>376</v>
       </c>
       <c r="AM26" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN26" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="AO26">
-        <v>0.98667278207972509</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP26">
-        <v>244.33232853837262</v>
+        <v>253.85494292623497</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8961,16 +8961,16 @@
         <v>298</v>
       </c>
       <c r="Y27" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="Z27" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AA27">
-        <v>0.99219647908939179</v>
+        <v>0.99021329006024306</v>
       </c>
       <c r="AB27">
-        <v>143.06455002781746</v>
+        <v>179.42301556221076</v>
       </c>
       <c r="AD27" t="s">
         <v>263</v>
@@ -8997,16 +8997,16 @@
         <v>378</v>
       </c>
       <c r="AM27" t="s">
+        <v>414</v>
+      </c>
+      <c r="AN27" t="s">
         <v>415</v>
       </c>
-      <c r="AN27" t="s">
-        <v>325</v>
-      </c>
       <c r="AO27">
-        <v>0.98615336674947807</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP27">
-        <v>253.85494292623497</v>
+        <v>99.241487561376104</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9071,16 +9071,16 @@
         <v>300</v>
       </c>
       <c r="Y28" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="Z28" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AA28">
-        <v>0.99199432528561049</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB28">
-        <v>146.77070309714048</v>
+        <v>161.73530211859338</v>
       </c>
       <c r="AD28" t="s">
         <v>263</v>
@@ -9110,13 +9110,13 @@
         <v>416</v>
       </c>
       <c r="AN28" t="s">
-        <v>417</v>
+        <v>332</v>
       </c>
       <c r="AO28">
-        <v>0.99458682795119768</v>
+        <v>0.99228583594785691</v>
       </c>
       <c r="AP28">
-        <v>99.241487561376104</v>
+        <v>141.42634095595602</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9181,16 +9181,16 @@
         <v>302</v>
       </c>
       <c r="Y29" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="Z29" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AA29">
-        <v>0.99686513787774389</v>
+        <v>0.99782085777346563</v>
       </c>
       <c r="AB29">
-        <v>57.472472241362951</v>
+        <v>39.950940819796543</v>
       </c>
       <c r="AD29" t="s">
         <v>263</v>
@@ -9217,16 +9217,16 @@
         <v>382</v>
       </c>
       <c r="AM29" t="s">
+        <v>417</v>
+      </c>
+      <c r="AN29" t="s">
         <v>418</v>
       </c>
-      <c r="AN29" t="s">
-        <v>401</v>
-      </c>
       <c r="AO29">
-        <v>0.99330365963041267</v>
+        <v>0.99740231224454534</v>
       </c>
       <c r="AP29">
-        <v>122.76624010910177</v>
+        <v>47.624275516669421</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9291,16 +9291,16 @@
         <v>304</v>
       </c>
       <c r="Y30" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="Z30" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AA30">
-        <v>0.99515835423076238</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB30">
-        <v>88.763505769357138</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD30" t="s">
         <v>263</v>
@@ -9333,10 +9333,10 @@
         <v>420</v>
       </c>
       <c r="AO30">
-        <v>0.99452764457035958</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP30">
-        <v>100.3265162100753</v>
+        <v>118.22451183716133</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9401,16 +9401,16 @@
         <v>306</v>
       </c>
       <c r="Y31" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="Z31" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AA31">
-        <v>0.99312290929392577</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB31">
-        <v>126.07999627802737</v>
+        <v>32.188603269438353</v>
       </c>
       <c r="AD31" t="s">
         <v>263</v>
@@ -9440,13 +9440,13 @@
         <v>421</v>
       </c>
       <c r="AN31" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="AO31">
-        <v>0.99675250681341587</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP31">
-        <v>59.537375087375146</v>
+        <v>100.3265162100753</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9511,16 +9511,16 @@
         <v>308</v>
       </c>
       <c r="Y32" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="Z32" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AA32">
-        <v>0.99021329006024306</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB32">
-        <v>179.42301556221076</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD32" t="s">
         <v>263</v>
@@ -9547,16 +9547,16 @@
         <v>388</v>
       </c>
       <c r="AM32" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN32" t="s">
-        <v>423</v>
+        <v>332</v>
       </c>
       <c r="AO32">
-        <v>0.99172545486986263</v>
+        <v>0.99675250681341587</v>
       </c>
       <c r="AP32">
-        <v>151.6999940525175</v>
+        <v>59.537375087375146</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9621,16 +9621,16 @@
         <v>310</v>
       </c>
       <c r="Y33" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Z33" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AA33">
-        <v>0.99117807442989492</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB33">
-        <v>161.73530211859338</v>
+        <v>285.85663191255094</v>
       </c>
       <c r="AD33" t="s">
         <v>263</v>
@@ -9663,10 +9663,10 @@
         <v>425</v>
       </c>
       <c r="AO33">
-        <v>0.99567808239070055</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP33">
-        <v>79.235156170489844</v>
+        <v>151.6999940525175</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9734,7 +9734,7 @@
         <v>257</v>
       </c>
       <c r="Z34" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA34">
         <v>0.99184104324003575</v>
@@ -9805,16 +9805,16 @@
         <v>314</v>
       </c>
       <c r="Y35" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Z35" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA35">
-        <v>0.99824425800348515</v>
+        <v>0.99594698839866214</v>
       </c>
       <c r="AB35">
-        <v>32.188603269438353</v>
+        <v>74.305212691194157</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9879,16 +9879,16 @@
         <v>316</v>
       </c>
       <c r="Y36" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="Z36" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="AA36">
-        <v>0.98551105518500948</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB36">
-        <v>265.63065494149328</v>
+        <v>461.61265467993644</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9953,16 +9953,16 @@
         <v>318</v>
       </c>
       <c r="Y37" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="Z37" t="s">
         <v>345</v>
       </c>
       <c r="AA37">
-        <v>0.99326495911353319</v>
+        <v>0.98551105518500948</v>
       </c>
       <c r="AB37">
-        <v>123.47574958522414</v>
+        <v>265.63065494149328</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10027,16 +10027,16 @@
         <v>320</v>
       </c>
       <c r="Y38" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="Z38" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="AA38">
-        <v>0.99022266246501978</v>
+        <v>0.99326495911353319</v>
       </c>
       <c r="AB38">
-        <v>179.25118814130403</v>
+        <v>123.47574958522414</v>
       </c>
     </row>
   </sheetData>
@@ -10045,7 +10045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33F563A-789E-476F-A5DB-A79944DB4880}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B67600-DE3F-44D3-89CE-7C451F0538E5}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10157,7 +10157,7 @@
         <v>460</v>
       </c>
       <c r="K11" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10190,7 +10190,7 @@
         <v>506</v>
       </c>
       <c r="X11" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="Y11">
         <v>8.3782499999999995</v>
@@ -10225,7 +10225,7 @@
         <v>462</v>
       </c>
       <c r="K12" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10293,7 +10293,7 @@
         <v>464</v>
       </c>
       <c r="K13" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="L13">
         <v>1.5817501567892978</v>
@@ -10326,7 +10326,7 @@
         <v>510</v>
       </c>
       <c r="X13" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10361,7 +10361,7 @@
         <v>466</v>
       </c>
       <c r="K14" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10394,7 +10394,7 @@
         <v>512</v>
       </c>
       <c r="X14" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10429,7 +10429,7 @@
         <v>468</v>
       </c>
       <c r="K15" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10497,7 +10497,7 @@
         <v>470</v>
       </c>
       <c r="K16" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10565,7 +10565,7 @@
         <v>472</v>
       </c>
       <c r="K17" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10598,7 +10598,7 @@
         <v>518</v>
       </c>
       <c r="X17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y17">
         <v>2.2530000000000001</v>
@@ -10633,7 +10633,7 @@
         <v>474</v>
       </c>
       <c r="K18" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10701,7 +10701,7 @@
         <v>476</v>
       </c>
       <c r="K19" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10734,7 +10734,7 @@
         <v>522</v>
       </c>
       <c r="X19" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="Y19">
         <v>10.093500000000001</v>
@@ -10769,7 +10769,7 @@
         <v>478</v>
       </c>
       <c r="K20" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10802,7 +10802,7 @@
         <v>524</v>
       </c>
       <c r="X20" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10837,7 +10837,7 @@
         <v>480</v>
       </c>
       <c r="K21" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="L21">
         <v>15.316017274089829</v>
@@ -10872,7 +10872,7 @@
         <v>482</v>
       </c>
       <c r="K22" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10907,7 +10907,7 @@
         <v>484</v>
       </c>
       <c r="K23" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="L23">
         <v>15.32235174795542</v>
@@ -10942,7 +10942,7 @@
         <v>486</v>
       </c>
       <c r="K24" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="L24">
         <v>4.3876485804695786</v>
@@ -10977,7 +10977,7 @@
         <v>488</v>
       </c>
       <c r="K25" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -11012,7 +11012,7 @@
         <v>490</v>
       </c>
       <c r="K26" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11047,7 +11047,7 @@
         <v>492</v>
       </c>
       <c r="K27" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11082,7 +11082,7 @@
         <v>494</v>
       </c>
       <c r="K28" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11117,7 +11117,7 @@
         <v>496</v>
       </c>
       <c r="K29" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11152,7 +11152,7 @@
         <v>498</v>
       </c>
       <c r="K30" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11187,7 +11187,7 @@
         <v>500</v>
       </c>
       <c r="K31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11222,7 +11222,7 @@
         <v>502</v>
       </c>
       <c r="K32" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="L32">
         <v>0.91282903432358287</v>
@@ -11257,7 +11257,7 @@
         <v>504</v>
       </c>
       <c r="K33" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11272,7 +11272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA49A748-0F38-4A53-9FD2-47DA1FAB87CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B58F9A-D0EA-46A0-A3BC-11FE989BE8F1}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13089,7 +13089,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604AAA63-E6DD-4142-BAE0-EB6982F75C89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C830947-EBF4-4862-A61F-1F11075E1A27}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1B5AA14-17BF-4659-9F5E-E113591BBA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52946195-74EB-4C90-8CD8-85BE227A3BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -922,52 +922,154 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_019</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_solelc_spv_007</t>
@@ -994,178 +1096,142 @@
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE7-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220</t>
+  </si>
+  <si>
     <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
   </si>
   <si>
-    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE7-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220,e_w669520367-220</t>
+    <t>e_w579310367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
   </si>
   <si>
     <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
   </si>
   <si>
-    <t>e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w669520367-220</t>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_017</t>
@@ -1192,16 +1258,10 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1222,72 +1282,12 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_013</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_020</t>
   </si>
   <si>
@@ -1306,12 +1306,60 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE11-220</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w579310367-220</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
     <t>elc_won_017</t>
   </si>
   <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
     <t>elc_won_023</t>
   </si>
   <si>
@@ -1327,13 +1375,10 @@
     <t>elc_won_005</t>
   </si>
   <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
   </si>
   <si>
     <t>elc_won_011</t>
@@ -1345,54 +1390,9 @@
     <t>elc_won_019</t>
   </si>
   <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE11-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
     <t>elc_won_013</t>
   </si>
   <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
-  </si>
-  <si>
     <t>elc_won_020</t>
   </si>
   <si>
@@ -1408,22 +1408,52 @@
     <t>e_KE14-400,e_w870818913-220</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wofelc_wof_007</t>
@@ -1432,55 +1462,43 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_KE15-220</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
   </si>
   <si>
     <t>elc_wof_003</t>
   </si>
   <si>
-    <t>e_KE15-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_KE15-220</t>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
   </si>
   <si>
     <t>elc_wof_007</t>
@@ -1489,25 +1507,7 @@
     <t>e_w953567827-220</t>
   </si>
   <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
     <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6603,7 +6603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{205F502F-B890-4626-A7A0-B14121FC7D75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D4564-E8EF-4D23-875F-8FAC158D528B}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6841,16 +6841,16 @@
         <v>264</v>
       </c>
       <c r="Y11" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="Z11" t="s">
         <v>324</v>
       </c>
       <c r="AA11">
-        <v>0.99260409516666881</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB11">
-        <v>135.59158861107267</v>
+        <v>74.690879958909605</v>
       </c>
       <c r="AD11" t="s">
         <v>263</v>
@@ -6880,13 +6880,13 @@
         <v>392</v>
       </c>
       <c r="AN11" t="s">
-        <v>393</v>
+        <v>327</v>
       </c>
       <c r="AO11">
-        <v>0.98286027536897036</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP11">
-        <v>314.22828490220974</v>
+        <v>463.38269175414888</v>
       </c>
       <c r="AR11" t="s">
         <v>263</v>
@@ -6919,10 +6919,10 @@
         <v>447</v>
       </c>
       <c r="BC11">
-        <v>0.99722114454285371</v>
+        <v>0.99504452373263619</v>
       </c>
       <c r="BD11">
-        <v>50.94568338101594</v>
+        <v>90.850398235003013</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6987,16 +6987,16 @@
         <v>268</v>
       </c>
       <c r="Y12" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="Z12" t="s">
         <v>325</v>
       </c>
       <c r="AA12">
-        <v>0.99787844392938518</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB12">
-        <v>38.895194627939205</v>
+        <v>353.97634871689564</v>
       </c>
       <c r="AD12" t="s">
         <v>263</v>
@@ -7023,16 +7023,16 @@
         <v>348</v>
       </c>
       <c r="AM12" t="s">
+        <v>393</v>
+      </c>
+      <c r="AN12" t="s">
         <v>394</v>
       </c>
-      <c r="AN12" t="s">
-        <v>395</v>
-      </c>
       <c r="AO12">
-        <v>0.99741412098479176</v>
+        <v>0.99740231224454534</v>
       </c>
       <c r="AP12">
-        <v>47.407781945483563</v>
+        <v>47.624275516669421</v>
       </c>
       <c r="AR12" t="s">
         <v>263</v>
@@ -7062,7 +7062,7 @@
         <v>448</v>
       </c>
       <c r="BB12" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="BC12">
         <v>0.99417680250918639</v>
@@ -7133,16 +7133,16 @@
         <v>270</v>
       </c>
       <c r="Y13" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="Z13" t="s">
         <v>326</v>
       </c>
       <c r="AA13">
-        <v>0.99219647908939179</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB13">
-        <v>143.06455002781746</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD13" t="s">
         <v>263</v>
@@ -7169,16 +7169,16 @@
         <v>350</v>
       </c>
       <c r="AM13" t="s">
+        <v>395</v>
+      </c>
+      <c r="AN13" t="s">
         <v>396</v>
       </c>
-      <c r="AN13" t="s">
-        <v>397</v>
-      </c>
       <c r="AO13">
-        <v>0.98563074303391496</v>
+        <v>0.99567808239070055</v>
       </c>
       <c r="AP13">
-        <v>263.43637771155954</v>
+        <v>79.235156170489844</v>
       </c>
       <c r="AR13" t="s">
         <v>263</v>
@@ -7205,16 +7205,16 @@
         <v>430</v>
       </c>
       <c r="BA13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="BB13" t="s">
-        <v>450</v>
+        <v>334</v>
       </c>
       <c r="BC13">
-        <v>0.99504452373263619</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD13">
-        <v>90.850398235003013</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7279,16 +7279,16 @@
         <v>272</v>
       </c>
       <c r="Y14" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="Z14" t="s">
         <v>327</v>
       </c>
       <c r="AA14">
-        <v>0.99199432528561049</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB14">
-        <v>146.77070309714048</v>
+        <v>285.85663191255094</v>
       </c>
       <c r="AD14" t="s">
         <v>263</v>
@@ -7315,16 +7315,16 @@
         <v>352</v>
       </c>
       <c r="AM14" t="s">
+        <v>397</v>
+      </c>
+      <c r="AN14" t="s">
         <v>398</v>
       </c>
-      <c r="AN14" t="s">
-        <v>333</v>
-      </c>
       <c r="AO14">
-        <v>0.99059324986934494</v>
+        <v>0.9934827767968939</v>
       </c>
       <c r="AP14">
-        <v>172.45708572867548</v>
+        <v>119.4824253902779</v>
       </c>
       <c r="AR14" t="s">
         <v>263</v>
@@ -7354,13 +7354,13 @@
         <v>451</v>
       </c>
       <c r="BB14" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="BC14">
-        <v>0.99264898847830307</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD14">
-        <v>134.76854456444406</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7425,16 +7425,16 @@
         <v>274</v>
       </c>
       <c r="Y15" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="Z15" t="s">
         <v>328</v>
       </c>
       <c r="AA15">
-        <v>0.99686513787774389</v>
+        <v>0.99782085777346563</v>
       </c>
       <c r="AB15">
-        <v>57.472472241362951</v>
+        <v>39.950940819796543</v>
       </c>
       <c r="AD15" t="s">
         <v>263</v>
@@ -7464,13 +7464,13 @@
         <v>399</v>
       </c>
       <c r="AN15" t="s">
-        <v>400</v>
+        <v>327</v>
       </c>
       <c r="AO15">
-        <v>0.9934827767968939</v>
+        <v>0.99486941977940613</v>
       </c>
       <c r="AP15">
-        <v>119.4824253902779</v>
+        <v>94.060637377553505</v>
       </c>
       <c r="AR15" t="s">
         <v>263</v>
@@ -7497,16 +7497,16 @@
         <v>434</v>
       </c>
       <c r="BA15" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="BB15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="BC15">
-        <v>0.99660062084319445</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD15">
-        <v>62.321951208100806</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7571,16 +7571,16 @@
         <v>276</v>
       </c>
       <c r="Y16" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="Z16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AA16">
-        <v>0.99592595200224132</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB16">
-        <v>74.690879958909605</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD16" t="s">
         <v>263</v>
@@ -7607,16 +7607,16 @@
         <v>356</v>
       </c>
       <c r="AM16" t="s">
+        <v>400</v>
+      </c>
+      <c r="AN16" t="s">
         <v>401</v>
       </c>
-      <c r="AN16" t="s">
-        <v>332</v>
-      </c>
       <c r="AO16">
-        <v>0.99486941977940613</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP16">
-        <v>94.060637377553505</v>
+        <v>207.11050978330246</v>
       </c>
       <c r="AR16" t="s">
         <v>263</v>
@@ -7643,16 +7643,16 @@
         <v>436</v>
       </c>
       <c r="BA16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="BB16" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="BC16">
-        <v>0.99567841910080701</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD16">
-        <v>79.228983151871589</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7717,16 +7717,16 @@
         <v>278</v>
       </c>
       <c r="Y17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AA17">
-        <v>0.98069219916089656</v>
+        <v>0.99184104324003575</v>
       </c>
       <c r="AB17">
-        <v>353.97634871689564</v>
+        <v>149.58087393267732</v>
       </c>
       <c r="AD17" t="s">
         <v>263</v>
@@ -7756,13 +7756,13 @@
         <v>402</v>
       </c>
       <c r="AN17" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AO17">
-        <v>0.98907459074885506</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP17">
-        <v>200.2991696043234</v>
+        <v>244.33232853837262</v>
       </c>
       <c r="AR17" t="s">
         <v>263</v>
@@ -7789,16 +7789,16 @@
         <v>438</v>
       </c>
       <c r="BA17" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="BB17" t="s">
         <v>455</v>
       </c>
       <c r="BC17">
-        <v>0.99790507974591136</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD17">
-        <v>38.406871324958367</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7863,16 +7863,16 @@
         <v>280</v>
       </c>
       <c r="Y18" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Z18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AA18">
-        <v>0.99585076637156988</v>
+        <v>0.99594698839866214</v>
       </c>
       <c r="AB18">
-        <v>76.069283187886086</v>
+        <v>74.305212691194157</v>
       </c>
       <c r="AD18" t="s">
         <v>263</v>
@@ -7902,13 +7902,13 @@
         <v>403</v>
       </c>
       <c r="AN18" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="AO18">
-        <v>0.98670016097490887</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP18">
-        <v>243.83038212667131</v>
+        <v>253.85494292623497</v>
       </c>
       <c r="AR18" t="s">
         <v>263</v>
@@ -7935,16 +7935,16 @@
         <v>440</v>
       </c>
       <c r="BA18" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="BB18" t="s">
-        <v>450</v>
+        <v>334</v>
       </c>
       <c r="BC18">
-        <v>0.99630507039782612</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD18">
-        <v>67.740376039854553</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8009,16 +8009,16 @@
         <v>282</v>
       </c>
       <c r="Y19" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="Z19" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AA19">
-        <v>0.9893494724125782</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB19">
-        <v>195.2596724360663</v>
+        <v>461.61265467993644</v>
       </c>
       <c r="AD19" t="s">
         <v>263</v>
@@ -8048,13 +8048,13 @@
         <v>404</v>
       </c>
       <c r="AN19" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="AO19">
-        <v>0.99330365963041267</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP19">
-        <v>122.76624010910177</v>
+        <v>99.241487561376104</v>
       </c>
       <c r="AR19" t="s">
         <v>263</v>
@@ -8081,16 +8081,16 @@
         <v>442</v>
       </c>
       <c r="BA19" t="s">
+        <v>457</v>
+      </c>
+      <c r="BB19" t="s">
         <v>458</v>
       </c>
-      <c r="BB19" t="s">
-        <v>333</v>
-      </c>
       <c r="BC19">
-        <v>0.99749257613418407</v>
+        <v>0.99264898847830307</v>
       </c>
       <c r="BD19">
-        <v>45.969437539958705</v>
+        <v>134.76854456444406</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8155,16 +8155,16 @@
         <v>284</v>
       </c>
       <c r="Y20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Z20" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AA20">
-        <v>0.97548412543178475</v>
+        <v>0.99806216160693018</v>
       </c>
       <c r="AB20">
-        <v>449.45770041728053</v>
+        <v>35.52703720627968</v>
       </c>
       <c r="AD20" t="s">
         <v>263</v>
@@ -8191,16 +8191,16 @@
         <v>364</v>
       </c>
       <c r="AM20" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN20" t="s">
-        <v>406</v>
+        <v>329</v>
       </c>
       <c r="AO20">
-        <v>0.99567808239070055</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP20">
-        <v>79.235156170489844</v>
+        <v>199.81501642792259</v>
       </c>
       <c r="AR20" t="s">
         <v>263</v>
@@ -8230,13 +8230,13 @@
         <v>459</v>
       </c>
       <c r="BB20" t="s">
-        <v>333</v>
+        <v>455</v>
       </c>
       <c r="BC20">
-        <v>0.9940284706913598</v>
+        <v>0.99790507974591136</v>
       </c>
       <c r="BD20">
-        <v>109.47803732507046</v>
+        <v>38.406871324958367</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8301,16 +8301,16 @@
         <v>286</v>
       </c>
       <c r="Y21" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Z21" t="s">
         <v>332</v>
       </c>
       <c r="AA21">
-        <v>0.96747189690815383</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB21">
-        <v>596.34855668384682</v>
+        <v>32.188603269438353</v>
       </c>
       <c r="AD21" t="s">
         <v>263</v>
@@ -8340,13 +8340,13 @@
         <v>407</v>
       </c>
       <c r="AN21" t="s">
-        <v>332</v>
+        <v>408</v>
       </c>
       <c r="AO21">
-        <v>0.97472458044977373</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP21">
-        <v>463.38269175414888</v>
+        <v>428.87734626058102</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8411,16 +8411,16 @@
         <v>288</v>
       </c>
       <c r="Y22" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="Z22" t="s">
         <v>333</v>
       </c>
       <c r="AA22">
-        <v>0.99022266246501978</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB22">
-        <v>179.25118814130403</v>
+        <v>171.32529124410425</v>
       </c>
       <c r="AD22" t="s">
         <v>263</v>
@@ -8447,16 +8447,16 @@
         <v>368</v>
       </c>
       <c r="AM22" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN22" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="AO22">
-        <v>0.98910099910393146</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP22">
-        <v>199.81501642792259</v>
+        <v>314.22828490220974</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8521,16 +8521,16 @@
         <v>290</v>
       </c>
       <c r="Y23" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s">
         <v>334</v>
       </c>
       <c r="AA23">
-        <v>0.99065498411395791</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB23">
-        <v>171.32529124410425</v>
+        <v>179.25118814130403</v>
       </c>
       <c r="AD23" t="s">
         <v>263</v>
@@ -8557,16 +8557,16 @@
         <v>370</v>
       </c>
       <c r="AM23" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN23" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO23">
-        <v>0.97660669020396829</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP23">
-        <v>428.87734626058102</v>
+        <v>47.407781945483563</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8631,16 +8631,16 @@
         <v>292</v>
       </c>
       <c r="Y24" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s">
         <v>335</v>
       </c>
       <c r="AA24">
-        <v>0.99806216160693018</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB24">
-        <v>35.52703720627968</v>
+        <v>38.895194627939205</v>
       </c>
       <c r="AD24" t="s">
         <v>263</v>
@@ -8667,16 +8667,16 @@
         <v>372</v>
       </c>
       <c r="AM24" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN24" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="AO24">
-        <v>0.98870306310272893</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP24">
-        <v>207.11050978330246</v>
+        <v>263.43637771155954</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8741,16 +8741,16 @@
         <v>294</v>
       </c>
       <c r="Y25" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="Z25" t="s">
         <v>336</v>
       </c>
       <c r="AA25">
-        <v>0.99515835423076238</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB25">
-        <v>88.763505769357138</v>
+        <v>143.06455002781746</v>
       </c>
       <c r="AD25" t="s">
         <v>263</v>
@@ -8777,16 +8777,16 @@
         <v>374</v>
       </c>
       <c r="AM25" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN25" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AO25">
-        <v>0.98667278207972509</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP25">
-        <v>244.33232853837262</v>
+        <v>172.45708572867548</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8851,16 +8851,16 @@
         <v>296</v>
       </c>
       <c r="Y26" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Z26" t="s">
         <v>337</v>
       </c>
       <c r="AA26">
-        <v>0.99312290929392577</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB26">
-        <v>126.07999627802737</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD26" t="s">
         <v>263</v>
@@ -8887,16 +8887,16 @@
         <v>376</v>
       </c>
       <c r="AM26" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN26" t="s">
-        <v>332</v>
+        <v>416</v>
       </c>
       <c r="AO26">
-        <v>0.98615336674947807</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP26">
-        <v>253.85494292623497</v>
+        <v>118.22451183716133</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8961,16 +8961,16 @@
         <v>298</v>
       </c>
       <c r="Y27" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="Z27" t="s">
         <v>338</v>
       </c>
       <c r="AA27">
-        <v>0.99021329006024306</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB27">
-        <v>179.42301556221076</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD27" t="s">
         <v>263</v>
@@ -8997,16 +8997,16 @@
         <v>378</v>
       </c>
       <c r="AM27" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN27" t="s">
-        <v>415</v>
+        <v>327</v>
       </c>
       <c r="AO27">
-        <v>0.99458682795119768</v>
+        <v>0.98907459074885506</v>
       </c>
       <c r="AP27">
-        <v>99.241487561376104</v>
+        <v>200.2991696043234</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9071,16 +9071,16 @@
         <v>300</v>
       </c>
       <c r="Y28" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="Z28" t="s">
         <v>339</v>
       </c>
       <c r="AA28">
-        <v>0.99117807442989492</v>
+        <v>0.99515835423076238</v>
       </c>
       <c r="AB28">
-        <v>161.73530211859338</v>
+        <v>88.763505769357138</v>
       </c>
       <c r="AD28" t="s">
         <v>263</v>
@@ -9107,16 +9107,16 @@
         <v>380</v>
       </c>
       <c r="AM28" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN28" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AO28">
-        <v>0.99228583594785691</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP28">
-        <v>141.42634095595602</v>
+        <v>243.83038212667131</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9181,16 +9181,16 @@
         <v>302</v>
       </c>
       <c r="Y29" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="Z29" t="s">
         <v>340</v>
       </c>
       <c r="AA29">
-        <v>0.99782085777346563</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB29">
-        <v>39.950940819796543</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD29" t="s">
         <v>263</v>
@@ -9217,16 +9217,16 @@
         <v>382</v>
       </c>
       <c r="AM29" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN29" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="AO29">
-        <v>0.99740231224454534</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP29">
-        <v>47.624275516669421</v>
+        <v>122.76624010910177</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9291,16 +9291,16 @@
         <v>304</v>
       </c>
       <c r="Y30" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="Z30" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="AA30">
-        <v>0.98497581152539015</v>
+        <v>0.98551105518500948</v>
       </c>
       <c r="AB30">
-        <v>275.44345536784743</v>
+        <v>265.63065494149328</v>
       </c>
       <c r="AD30" t="s">
         <v>263</v>
@@ -9327,16 +9327,16 @@
         <v>384</v>
       </c>
       <c r="AM30" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN30" t="s">
-        <v>420</v>
+        <v>327</v>
       </c>
       <c r="AO30">
-        <v>0.99355139026342754</v>
+        <v>0.99228583594785691</v>
       </c>
       <c r="AP30">
-        <v>118.22451183716133</v>
+        <v>141.42634095595602</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9401,16 +9401,16 @@
         <v>306</v>
       </c>
       <c r="Y31" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="Z31" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="AA31">
-        <v>0.99824425800348515</v>
+        <v>0.99326495911353319</v>
       </c>
       <c r="AB31">
-        <v>32.188603269438353</v>
+        <v>123.47574958522414</v>
       </c>
       <c r="AD31" t="s">
         <v>263</v>
@@ -9511,16 +9511,16 @@
         <v>308</v>
       </c>
       <c r="Y32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z32" t="s">
         <v>342</v>
       </c>
       <c r="AA32">
-        <v>0.99327889425386662</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB32">
-        <v>123.22027201244609</v>
+        <v>135.59158861107267</v>
       </c>
       <c r="AD32" t="s">
         <v>263</v>
@@ -9550,7 +9550,7 @@
         <v>423</v>
       </c>
       <c r="AN32" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AO32">
         <v>0.99675250681341587</v>
@@ -9621,16 +9621,16 @@
         <v>310</v>
       </c>
       <c r="Y33" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="Z33" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AA33">
-        <v>0.98440782007749728</v>
+        <v>0.99021329006024306</v>
       </c>
       <c r="AB33">
-        <v>285.85663191255094</v>
+        <v>179.42301556221076</v>
       </c>
       <c r="AD33" t="s">
         <v>263</v>
@@ -9731,16 +9731,16 @@
         <v>312</v>
       </c>
       <c r="Y34" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="Z34" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA34">
-        <v>0.99184104324003575</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB34">
-        <v>149.58087393267732</v>
+        <v>161.73530211859338</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9805,16 +9805,16 @@
         <v>314</v>
       </c>
       <c r="Y35" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Z35" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA35">
-        <v>0.99594698839866214</v>
+        <v>0.99585076637156988</v>
       </c>
       <c r="AB35">
-        <v>74.305212691194157</v>
+        <v>76.069283187886086</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9879,16 +9879,16 @@
         <v>316</v>
       </c>
       <c r="Y36" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="Z36" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AA36">
-        <v>0.97482112792654896</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB36">
-        <v>461.61265467993644</v>
+        <v>195.2596724360663</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9953,16 +9953,16 @@
         <v>318</v>
       </c>
       <c r="Y37" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Z37" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AA37">
-        <v>0.98551105518500948</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB37">
-        <v>265.63065494149328</v>
+        <v>449.45770041728053</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10027,16 +10027,16 @@
         <v>320</v>
       </c>
       <c r="Y38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z38" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AA38">
-        <v>0.99326495911353319</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB38">
-        <v>123.47574958522414</v>
+        <v>596.34855668384682</v>
       </c>
     </row>
   </sheetData>
@@ -10045,7 +10045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B67600-DE3F-44D3-89CE-7C451F0538E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3E4FE3-6CF4-40EA-BDB2-2FE4D0ECD92B}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10190,7 +10190,7 @@
         <v>506</v>
       </c>
       <c r="X11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="Y11">
         <v>8.3782499999999995</v>
@@ -10225,7 +10225,7 @@
         <v>462</v>
       </c>
       <c r="K12" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10258,7 +10258,7 @@
         <v>508</v>
       </c>
       <c r="X12" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10293,7 +10293,7 @@
         <v>464</v>
       </c>
       <c r="K13" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="L13">
         <v>1.5817501567892978</v>
@@ -10326,7 +10326,7 @@
         <v>510</v>
       </c>
       <c r="X13" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10361,7 +10361,7 @@
         <v>466</v>
       </c>
       <c r="K14" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10394,7 +10394,7 @@
         <v>512</v>
       </c>
       <c r="X14" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10429,7 +10429,7 @@
         <v>468</v>
       </c>
       <c r="K15" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10462,7 +10462,7 @@
         <v>514</v>
       </c>
       <c r="X15" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10497,7 +10497,7 @@
         <v>470</v>
       </c>
       <c r="K16" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10530,7 +10530,7 @@
         <v>516</v>
       </c>
       <c r="X16" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10565,7 +10565,7 @@
         <v>472</v>
       </c>
       <c r="K17" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10598,7 +10598,7 @@
         <v>518</v>
       </c>
       <c r="X17" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="Y17">
         <v>2.2530000000000001</v>
@@ -10633,7 +10633,7 @@
         <v>474</v>
       </c>
       <c r="K18" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10701,7 +10701,7 @@
         <v>476</v>
       </c>
       <c r="K19" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10769,7 +10769,7 @@
         <v>478</v>
       </c>
       <c r="K20" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10802,7 +10802,7 @@
         <v>524</v>
       </c>
       <c r="X20" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10837,7 +10837,7 @@
         <v>480</v>
       </c>
       <c r="K21" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="L21">
         <v>15.316017274089829</v>
@@ -10872,7 +10872,7 @@
         <v>482</v>
       </c>
       <c r="K22" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10907,7 +10907,7 @@
         <v>484</v>
       </c>
       <c r="K23" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="L23">
         <v>15.32235174795542</v>
@@ -10942,7 +10942,7 @@
         <v>486</v>
       </c>
       <c r="K24" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L24">
         <v>4.3876485804695786</v>
@@ -10977,7 +10977,7 @@
         <v>488</v>
       </c>
       <c r="K25" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -11012,7 +11012,7 @@
         <v>490</v>
       </c>
       <c r="K26" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11047,7 +11047,7 @@
         <v>492</v>
       </c>
       <c r="K27" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11082,7 +11082,7 @@
         <v>494</v>
       </c>
       <c r="K28" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11117,7 +11117,7 @@
         <v>496</v>
       </c>
       <c r="K29" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11222,7 +11222,7 @@
         <v>502</v>
       </c>
       <c r="K32" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="L32">
         <v>0.91282903432358287</v>
@@ -11257,7 +11257,7 @@
         <v>504</v>
       </c>
       <c r="K33" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11272,7 +11272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B58F9A-D0EA-46A0-A3BC-11FE989BE8F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADAD5174-8D2B-4D11-9FFA-7D98BAF40FC8}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13089,7 +13089,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C830947-EBF4-4862-A61F-1F11075E1A27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A836E7-E4D9-4067-A01F-DA1D7701C721}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52946195-74EB-4C90-8CD8-85BE227A3BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C072DA-667F-4187-BAD1-90BC2019EE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="582">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1872,6 +1872,9 @@
   <si>
     <t>Transformer: e_w870818913-220 → e_w870818913-400</t>
   </si>
+  <si>
+    <t>e_KE15-220,e_w660091166-220</t>
+  </si>
 </sst>
 </file>
 
@@ -1885,7 +1888,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2033,15 +2036,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2133,11 +2129,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2352,7 +2343,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2372,9 +2363,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2766,7 +2756,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2786,9 +2775,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="20">
+  <cellStyles count="19">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
-    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -3764,7 +3752,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_KE15-220,e_w660091166-220</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3786,7 +3774,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_KE15-220,e_w660091166-220</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3800,8 +3788,8 @@
       <c r="S28">
         <v>50</v>
       </c>
-      <c r="V28" s="147" t="s">
-        <v>19</v>
+      <c r="V28" t="s">
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -5347,25 +5335,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="147" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="148"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="148" t="s">
+      <c r="G1" s="147"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="147" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="151" t="s">
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="150" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5411,7 +5399,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="152"/>
+      <c r="O2" s="151"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5456,7 +5444,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="152"/>
+      <c r="O3" s="151"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5498,7 +5486,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="153"/>
+      <c r="O4" s="152"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C072DA-667F-4187-BAD1-90BC2019EE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7724E185-9A96-4AFD-A8B7-AA4A34F7485C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="581">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -922,250 +922,352 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_025</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE7-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
+  </si>
+  <si>
     <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
   </si>
   <si>
     <t>e_w660091166-220,e_w669520367-220</t>
   </si>
   <si>
-    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
-  </si>
-  <si>
     <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
   </si>
   <si>
-    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE7-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wonelc_won_009</t>
@@ -1174,18 +1276,6 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_014</t>
   </si>
   <si>
@@ -1198,70 +1288,10 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1276,51 +1306,90 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w579310367-220</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_KE12-400</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE11-220</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
   </si>
   <si>
     <t>elc_won_009</t>
   </si>
   <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE11-220</t>
-  </si>
-  <si>
     <t>elc_won_014</t>
   </si>
   <si>
@@ -1330,55 +1399,7 @@
     <t>elc_won_012</t>
   </si>
   <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_KE12-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
+    <t>elc_won_019</t>
   </si>
   <si>
     <t>elc_won_011</t>
@@ -1387,25 +1408,40 @@
     <t>elc_won_007</t>
   </si>
   <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220</t>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wofelc_wof_001</t>
@@ -1414,18 +1450,6 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_002</t>
   </si>
   <si>
@@ -1438,75 +1462,51 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
     <t>e_KE15-220</t>
   </si>
   <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
     <t>elc_wof_002</t>
   </si>
   <si>
     <t>elc_wof_005</t>
   </si>
   <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w953567827-220</t>
-  </si>
-  <si>
     <t>elc_wof_004</t>
   </si>
   <si>
@@ -1871,9 +1871,6 @@
   </si>
   <si>
     <t>Transformer: e_w870818913-220 → e_w870818913-400</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w660091166-220</t>
   </si>
 </sst>
 </file>
@@ -1888,7 +1885,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2036,8 +2033,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2129,6 +2133,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2343,7 +2352,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2363,8 +2372,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2756,6 +2766,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2775,8 +2786,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -3752,7 +3764,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>e_KE15-220,e_w660091166-220</v>
+        <v>ELC</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3774,7 +3786,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>e_KE15-220,e_w660091166-220</v>
+        <v>ELC</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3788,8 +3800,8 @@
       <c r="S28">
         <v>50</v>
       </c>
-      <c r="V28" t="s">
-        <v>581</v>
+      <c r="V28" s="147" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -5335,25 +5347,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="147" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="150" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5399,7 +5411,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="151"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5444,7 +5456,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="151"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5486,7 +5498,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -6591,7 +6603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D4564-E8EF-4D23-875F-8FAC158D528B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DEE6DB6-F013-4E3E-B5AE-E22C9723415C}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6829,16 +6841,16 @@
         <v>264</v>
       </c>
       <c r="Y11" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Z11" t="s">
         <v>324</v>
       </c>
       <c r="AA11">
-        <v>0.99592595200224132</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB11">
-        <v>74.690879958909605</v>
+        <v>38.895194627939205</v>
       </c>
       <c r="AD11" t="s">
         <v>263</v>
@@ -6868,13 +6880,13 @@
         <v>392</v>
       </c>
       <c r="AN11" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="AO11">
-        <v>0.97472458044977373</v>
+        <v>0.99740231224454534</v>
       </c>
       <c r="AP11">
-        <v>463.38269175414888</v>
+        <v>47.624275516669421</v>
       </c>
       <c r="AR11" t="s">
         <v>263</v>
@@ -6907,10 +6919,10 @@
         <v>447</v>
       </c>
       <c r="BC11">
-        <v>0.99504452373263619</v>
+        <v>0.99417680250918639</v>
       </c>
       <c r="BD11">
-        <v>90.850398235003013</v>
+        <v>106.75862066491723</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6975,16 +6987,16 @@
         <v>268</v>
       </c>
       <c r="Y12" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="Z12" t="s">
         <v>325</v>
       </c>
       <c r="AA12">
-        <v>0.98069219916089656</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB12">
-        <v>353.97634871689564</v>
+        <v>143.06455002781746</v>
       </c>
       <c r="AD12" t="s">
         <v>263</v>
@@ -7011,16 +7023,16 @@
         <v>348</v>
       </c>
       <c r="AM12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN12" t="s">
-        <v>394</v>
+        <v>329</v>
       </c>
       <c r="AO12">
-        <v>0.99740231224454534</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP12">
-        <v>47.624275516669421</v>
+        <v>199.81501642792259</v>
       </c>
       <c r="AR12" t="s">
         <v>263</v>
@@ -7053,10 +7065,10 @@
         <v>449</v>
       </c>
       <c r="BC12">
-        <v>0.99417680250918639</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD12">
-        <v>106.75862066491723</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7121,16 +7133,16 @@
         <v>270</v>
       </c>
       <c r="Y13" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Z13" t="s">
         <v>326</v>
       </c>
       <c r="AA13">
-        <v>0.99327889425386662</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB13">
-        <v>123.22027201244609</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD13" t="s">
         <v>263</v>
@@ -7163,10 +7175,10 @@
         <v>396</v>
       </c>
       <c r="AO13">
-        <v>0.99567808239070055</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP13">
-        <v>79.235156170489844</v>
+        <v>428.87734626058102</v>
       </c>
       <c r="AR13" t="s">
         <v>263</v>
@@ -7196,13 +7208,13 @@
         <v>450</v>
       </c>
       <c r="BB13" t="s">
-        <v>334</v>
+        <v>451</v>
       </c>
       <c r="BC13">
-        <v>0.9940284706913598</v>
+        <v>0.99264898847830307</v>
       </c>
       <c r="BD13">
-        <v>109.47803732507046</v>
+        <v>134.76854456444406</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7267,16 +7279,16 @@
         <v>272</v>
       </c>
       <c r="Y14" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="Z14" t="s">
         <v>327</v>
       </c>
       <c r="AA14">
-        <v>0.98440782007749728</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB14">
-        <v>285.85663191255094</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD14" t="s">
         <v>263</v>
@@ -7309,10 +7321,10 @@
         <v>398</v>
       </c>
       <c r="AO14">
-        <v>0.9934827767968939</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP14">
-        <v>119.4824253902779</v>
+        <v>314.22828490220974</v>
       </c>
       <c r="AR14" t="s">
         <v>263</v>
@@ -7339,16 +7351,16 @@
         <v>432</v>
       </c>
       <c r="BA14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="BB14" t="s">
         <v>447</v>
       </c>
       <c r="BC14">
-        <v>0.99630507039782612</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD14">
-        <v>67.740376039854553</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7413,16 +7425,16 @@
         <v>274</v>
       </c>
       <c r="Y15" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="Z15" t="s">
         <v>328</v>
       </c>
       <c r="AA15">
-        <v>0.99782085777346563</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB15">
-        <v>39.950940819796543</v>
+        <v>171.32529124410425</v>
       </c>
       <c r="AD15" t="s">
         <v>263</v>
@@ -7452,13 +7464,13 @@
         <v>399</v>
       </c>
       <c r="AN15" t="s">
-        <v>327</v>
+        <v>400</v>
       </c>
       <c r="AO15">
-        <v>0.99486941977940613</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP15">
-        <v>94.060637377553505</v>
+        <v>47.407781945483563</v>
       </c>
       <c r="AR15" t="s">
         <v>263</v>
@@ -7485,16 +7497,16 @@
         <v>434</v>
       </c>
       <c r="BA15" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="BB15" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="BC15">
-        <v>0.99749257613418407</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD15">
-        <v>45.969437539958705</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7559,16 +7571,16 @@
         <v>276</v>
       </c>
       <c r="Y16" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="Z16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AA16">
-        <v>0.98497581152539015</v>
+        <v>0.99184104324003575</v>
       </c>
       <c r="AB16">
-        <v>275.44345536784743</v>
+        <v>149.58087393267732</v>
       </c>
       <c r="AD16" t="s">
         <v>263</v>
@@ -7595,16 +7607,16 @@
         <v>356</v>
       </c>
       <c r="AM16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO16">
-        <v>0.98870306310272893</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP16">
-        <v>207.11050978330246</v>
+        <v>263.43637771155954</v>
       </c>
       <c r="AR16" t="s">
         <v>263</v>
@@ -7631,16 +7643,16 @@
         <v>436</v>
       </c>
       <c r="BA16" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="BB16" t="s">
-        <v>449</v>
+        <v>338</v>
       </c>
       <c r="BC16">
-        <v>0.99722114454285371</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD16">
-        <v>50.94568338101594</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7705,16 +7717,16 @@
         <v>278</v>
       </c>
       <c r="Y17" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="Z17" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA17">
-        <v>0.99184104324003575</v>
+        <v>0.99782085777346563</v>
       </c>
       <c r="AB17">
-        <v>149.58087393267732</v>
+        <v>39.950940819796543</v>
       </c>
       <c r="AD17" t="s">
         <v>263</v>
@@ -7741,16 +7753,16 @@
         <v>358</v>
       </c>
       <c r="AM17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN17" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AO17">
-        <v>0.98667278207972509</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP17">
-        <v>244.33232853837262</v>
+        <v>172.45708572867548</v>
       </c>
       <c r="AR17" t="s">
         <v>263</v>
@@ -7777,16 +7789,16 @@
         <v>438</v>
       </c>
       <c r="BA17" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="BB17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BC17">
-        <v>0.99567841910080701</v>
+        <v>0.99504452373263619</v>
       </c>
       <c r="BD17">
-        <v>79.228983151871589</v>
+        <v>90.850398235003013</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7851,16 +7863,16 @@
         <v>280</v>
       </c>
       <c r="Y18" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Z18" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA18">
-        <v>0.99594698839866214</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB18">
-        <v>74.305212691194157</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD18" t="s">
         <v>263</v>
@@ -7887,16 +7899,16 @@
         <v>360</v>
       </c>
       <c r="AM18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN18" t="s">
-        <v>327</v>
+        <v>405</v>
       </c>
       <c r="AO18">
-        <v>0.98615336674947807</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP18">
-        <v>253.85494292623497</v>
+        <v>118.22451183716133</v>
       </c>
       <c r="AR18" t="s">
         <v>263</v>
@@ -7923,16 +7935,16 @@
         <v>440</v>
       </c>
       <c r="BA18" t="s">
+        <v>457</v>
+      </c>
+      <c r="BB18" t="s">
         <v>456</v>
       </c>
-      <c r="BB18" t="s">
-        <v>334</v>
-      </c>
       <c r="BC18">
-        <v>0.99660062084319445</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD18">
-        <v>62.321951208100806</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7997,16 +8009,16 @@
         <v>282</v>
       </c>
       <c r="Y19" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Z19" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AA19">
-        <v>0.97482112792654896</v>
+        <v>0.99515835423076238</v>
       </c>
       <c r="AB19">
-        <v>461.61265467993644</v>
+        <v>88.763505769357138</v>
       </c>
       <c r="AD19" t="s">
         <v>263</v>
@@ -8033,16 +8045,16 @@
         <v>362</v>
       </c>
       <c r="AM19" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN19" t="s">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="AO19">
-        <v>0.99458682795119768</v>
+        <v>0.99228583594785691</v>
       </c>
       <c r="AP19">
-        <v>99.241487561376104</v>
+        <v>141.42634095595602</v>
       </c>
       <c r="AR19" t="s">
         <v>263</v>
@@ -8069,16 +8081,16 @@
         <v>442</v>
       </c>
       <c r="BA19" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BB19" t="s">
-        <v>458</v>
+        <v>338</v>
       </c>
       <c r="BC19">
-        <v>0.99264898847830307</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD19">
-        <v>134.76854456444406</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8143,16 +8155,16 @@
         <v>284</v>
       </c>
       <c r="Y20" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="Z20" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AA20">
-        <v>0.99806216160693018</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB20">
-        <v>35.52703720627968</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD20" t="s">
         <v>263</v>
@@ -8179,16 +8191,16 @@
         <v>364</v>
       </c>
       <c r="AM20" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN20" t="s">
-        <v>329</v>
+        <v>408</v>
       </c>
       <c r="AO20">
-        <v>0.98910099910393146</v>
+        <v>0.99567808239070055</v>
       </c>
       <c r="AP20">
-        <v>199.81501642792259</v>
+        <v>79.235156170489844</v>
       </c>
       <c r="AR20" t="s">
         <v>263</v>
@@ -8218,7 +8230,7 @@
         <v>459</v>
       </c>
       <c r="BB20" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="BC20">
         <v>0.99790507974591136</v>
@@ -8289,16 +8301,16 @@
         <v>286</v>
       </c>
       <c r="Y21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Z21" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AA21">
-        <v>0.99824425800348515</v>
+        <v>0.99021329006024306</v>
       </c>
       <c r="AB21">
-        <v>32.188603269438353</v>
+        <v>179.42301556221076</v>
       </c>
       <c r="AD21" t="s">
         <v>263</v>
@@ -8325,16 +8337,16 @@
         <v>366</v>
       </c>
       <c r="AM21" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AN21" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AO21">
-        <v>0.97660669020396829</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP21">
-        <v>428.87734626058102</v>
+        <v>100.3265162100753</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8399,16 +8411,16 @@
         <v>288</v>
       </c>
       <c r="Y22" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="Z22" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AA22">
-        <v>0.99065498411395791</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB22">
-        <v>171.32529124410425</v>
+        <v>161.73530211859338</v>
       </c>
       <c r="AD22" t="s">
         <v>263</v>
@@ -8435,16 +8447,16 @@
         <v>368</v>
       </c>
       <c r="AM22" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN22" t="s">
-        <v>401</v>
+        <v>331</v>
       </c>
       <c r="AO22">
-        <v>0.98286027536897036</v>
+        <v>0.99675250681341587</v>
       </c>
       <c r="AP22">
-        <v>314.22828490220974</v>
+        <v>59.537375087375146</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8509,16 +8521,16 @@
         <v>290</v>
       </c>
       <c r="Y23" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="Z23" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA23">
-        <v>0.99022266246501978</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB23">
-        <v>179.25118814130403</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD23" t="s">
         <v>263</v>
@@ -8545,16 +8557,16 @@
         <v>370</v>
       </c>
       <c r="AM23" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN23" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO23">
-        <v>0.99741412098479176</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP23">
-        <v>47.407781945483563</v>
+        <v>151.6999940525175</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8619,16 +8631,16 @@
         <v>292</v>
       </c>
       <c r="Y24" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Z24" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AA24">
-        <v>0.99787844392938518</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB24">
-        <v>38.895194627939205</v>
+        <v>285.85663191255094</v>
       </c>
       <c r="AD24" t="s">
         <v>263</v>
@@ -8655,16 +8667,16 @@
         <v>372</v>
       </c>
       <c r="AM24" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN24" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="AO24">
-        <v>0.98563074303391496</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP24">
-        <v>263.43637771155954</v>
+        <v>207.11050978330246</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8729,16 +8741,16 @@
         <v>294</v>
       </c>
       <c r="Y25" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="Z25" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA25">
-        <v>0.99219647908939179</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB25">
-        <v>143.06455002781746</v>
+        <v>135.59158861107267</v>
       </c>
       <c r="AD25" t="s">
         <v>263</v>
@@ -8765,16 +8777,16 @@
         <v>374</v>
       </c>
       <c r="AM25" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN25" t="s">
         <v>334</v>
       </c>
       <c r="AO25">
-        <v>0.99059324986934494</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP25">
-        <v>172.45708572867548</v>
+        <v>244.33232853837262</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8839,16 +8851,16 @@
         <v>296</v>
       </c>
       <c r="Y26" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA26">
-        <v>0.99199432528561049</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB26">
-        <v>146.77070309714048</v>
+        <v>179.25118814130403</v>
       </c>
       <c r="AD26" t="s">
         <v>263</v>
@@ -8875,16 +8887,16 @@
         <v>376</v>
       </c>
       <c r="AM26" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN26" t="s">
-        <v>416</v>
+        <v>331</v>
       </c>
       <c r="AO26">
-        <v>0.99355139026342754</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP26">
-        <v>118.22451183716133</v>
+        <v>253.85494292623497</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8949,16 +8961,16 @@
         <v>298</v>
       </c>
       <c r="Y27" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="Z27" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA27">
-        <v>0.99686513787774389</v>
+        <v>0.99806216160693018</v>
       </c>
       <c r="AB27">
-        <v>57.472472241362951</v>
+        <v>35.52703720627968</v>
       </c>
       <c r="AD27" t="s">
         <v>263</v>
@@ -8988,13 +9000,13 @@
         <v>417</v>
       </c>
       <c r="AN27" t="s">
-        <v>327</v>
+        <v>418</v>
       </c>
       <c r="AO27">
-        <v>0.98907459074885506</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP27">
-        <v>200.2991696043234</v>
+        <v>99.241487561376104</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9059,16 +9071,16 @@
         <v>300</v>
       </c>
       <c r="Y28" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Z28" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA28">
-        <v>0.99515835423076238</v>
+        <v>0.99585076637156988</v>
       </c>
       <c r="AB28">
-        <v>88.763505769357138</v>
+        <v>76.069283187886086</v>
       </c>
       <c r="AD28" t="s">
         <v>263</v>
@@ -9095,16 +9107,16 @@
         <v>380</v>
       </c>
       <c r="AM28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN28" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AO28">
-        <v>0.98670016097490887</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP28">
-        <v>243.83038212667131</v>
+        <v>463.38269175414888</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9169,16 +9181,16 @@
         <v>302</v>
       </c>
       <c r="Y29" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="Z29" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="AA29">
-        <v>0.99312290929392577</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB29">
-        <v>126.07999627802737</v>
+        <v>195.2596724360663</v>
       </c>
       <c r="AD29" t="s">
         <v>263</v>
@@ -9205,16 +9217,16 @@
         <v>382</v>
       </c>
       <c r="AM29" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN29" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="AO29">
-        <v>0.99330365963041267</v>
+        <v>0.9934827767968939</v>
       </c>
       <c r="AP29">
-        <v>122.76624010910177</v>
+        <v>119.4824253902779</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9279,16 +9291,16 @@
         <v>304</v>
       </c>
       <c r="Y30" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Z30" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="AA30">
-        <v>0.98551105518500948</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB30">
-        <v>265.63065494149328</v>
+        <v>449.45770041728053</v>
       </c>
       <c r="AD30" t="s">
         <v>263</v>
@@ -9315,16 +9327,16 @@
         <v>384</v>
       </c>
       <c r="AM30" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AN30" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AO30">
-        <v>0.99228583594785691</v>
+        <v>0.99486941977940613</v>
       </c>
       <c r="AP30">
-        <v>141.42634095595602</v>
+        <v>94.060637377553505</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9389,16 +9401,16 @@
         <v>306</v>
       </c>
       <c r="Y31" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z31" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AA31">
-        <v>0.99326495911353319</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB31">
-        <v>123.47574958522414</v>
+        <v>596.34855668384682</v>
       </c>
       <c r="AD31" t="s">
         <v>263</v>
@@ -9425,16 +9437,16 @@
         <v>386</v>
       </c>
       <c r="AM31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN31" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="AO31">
-        <v>0.99452764457035958</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP31">
-        <v>100.3265162100753</v>
+        <v>122.76624010910177</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9499,16 +9511,16 @@
         <v>308</v>
       </c>
       <c r="Y32" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Z32" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA32">
-        <v>0.99260409516666881</v>
+        <v>0.98551105518500948</v>
       </c>
       <c r="AB32">
-        <v>135.59158861107267</v>
+        <v>265.63065494149328</v>
       </c>
       <c r="AD32" t="s">
         <v>263</v>
@@ -9535,16 +9547,16 @@
         <v>388</v>
       </c>
       <c r="AM32" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN32" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AO32">
-        <v>0.99675250681341587</v>
+        <v>0.98907459074885506</v>
       </c>
       <c r="AP32">
-        <v>59.537375087375146</v>
+        <v>200.2991696043234</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9609,16 +9621,16 @@
         <v>310</v>
       </c>
       <c r="Y33" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Z33" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AA33">
-        <v>0.99021329006024306</v>
+        <v>0.99326495911353319</v>
       </c>
       <c r="AB33">
-        <v>179.42301556221076</v>
+        <v>123.47574958522414</v>
       </c>
       <c r="AD33" t="s">
         <v>263</v>
@@ -9645,16 +9657,16 @@
         <v>390</v>
       </c>
       <c r="AM33" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN33" t="s">
-        <v>425</v>
+        <v>329</v>
       </c>
       <c r="AO33">
-        <v>0.99172545486986263</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP33">
-        <v>151.6999940525175</v>
+        <v>243.83038212667131</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9719,16 +9731,16 @@
         <v>312</v>
       </c>
       <c r="Y34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z34" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AA34">
-        <v>0.99117807442989492</v>
+        <v>0.99594698839866214</v>
       </c>
       <c r="AB34">
-        <v>161.73530211859338</v>
+        <v>74.305212691194157</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9793,16 +9805,16 @@
         <v>314</v>
       </c>
       <c r="Y35" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="Z35" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="AA35">
-        <v>0.99585076637156988</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB35">
-        <v>76.069283187886086</v>
+        <v>461.61265467993644</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9867,16 +9879,16 @@
         <v>316</v>
       </c>
       <c r="Y36" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Z36" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="AA36">
-        <v>0.9893494724125782</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB36">
-        <v>195.2596724360663</v>
+        <v>74.690879958909605</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9941,16 +9953,16 @@
         <v>318</v>
       </c>
       <c r="Y37" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="Z37" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AA37">
-        <v>0.97548412543178475</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB37">
-        <v>449.45770041728053</v>
+        <v>353.97634871689564</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10015,16 +10027,16 @@
         <v>320</v>
       </c>
       <c r="Y38" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Z38" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="AA38">
-        <v>0.96747189690815383</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB38">
-        <v>596.34855668384682</v>
+        <v>32.188603269438353</v>
       </c>
     </row>
   </sheetData>
@@ -10033,7 +10045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3E4FE3-6CF4-40EA-BDB2-2FE4D0ECD92B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B03D1C7-F11B-462B-9056-405766D66A3E}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10145,7 +10157,7 @@
         <v>460</v>
       </c>
       <c r="K11" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10178,7 +10190,7 @@
         <v>506</v>
       </c>
       <c r="X11" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="Y11">
         <v>8.3782499999999995</v>
@@ -10213,7 +10225,7 @@
         <v>462</v>
       </c>
       <c r="K12" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10246,7 +10258,7 @@
         <v>508</v>
       </c>
       <c r="X12" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10281,7 +10293,7 @@
         <v>464</v>
       </c>
       <c r="K13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L13">
         <v>1.5817501567892978</v>
@@ -10314,7 +10326,7 @@
         <v>510</v>
       </c>
       <c r="X13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10349,7 +10361,7 @@
         <v>466</v>
       </c>
       <c r="K14" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10417,7 +10429,7 @@
         <v>468</v>
       </c>
       <c r="K15" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10450,7 +10462,7 @@
         <v>514</v>
       </c>
       <c r="X15" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10485,7 +10497,7 @@
         <v>470</v>
       </c>
       <c r="K16" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10518,7 +10530,7 @@
         <v>516</v>
       </c>
       <c r="X16" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10553,7 +10565,7 @@
         <v>472</v>
       </c>
       <c r="K17" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10586,7 +10598,7 @@
         <v>518</v>
       </c>
       <c r="X17" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="Y17">
         <v>2.2530000000000001</v>
@@ -10621,7 +10633,7 @@
         <v>474</v>
       </c>
       <c r="K18" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10654,7 +10666,7 @@
         <v>520</v>
       </c>
       <c r="X18" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="Y18">
         <v>6.1852499999999999</v>
@@ -10689,7 +10701,7 @@
         <v>476</v>
       </c>
       <c r="K19" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10722,7 +10734,7 @@
         <v>522</v>
       </c>
       <c r="X19" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="Y19">
         <v>10.093500000000001</v>
@@ -10757,7 +10769,7 @@
         <v>478</v>
       </c>
       <c r="K20" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10790,7 +10802,7 @@
         <v>524</v>
       </c>
       <c r="X20" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10825,7 +10837,7 @@
         <v>480</v>
       </c>
       <c r="K21" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="L21">
         <v>15.316017274089829</v>
@@ -10860,7 +10872,7 @@
         <v>482</v>
       </c>
       <c r="K22" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10895,7 +10907,7 @@
         <v>484</v>
       </c>
       <c r="K23" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="L23">
         <v>15.32235174795542</v>
@@ -10930,7 +10942,7 @@
         <v>486</v>
       </c>
       <c r="K24" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="L24">
         <v>4.3876485804695786</v>
@@ -10965,7 +10977,7 @@
         <v>488</v>
       </c>
       <c r="K25" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -11000,7 +11012,7 @@
         <v>490</v>
       </c>
       <c r="K26" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11035,7 +11047,7 @@
         <v>492</v>
       </c>
       <c r="K27" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11070,7 +11082,7 @@
         <v>494</v>
       </c>
       <c r="K28" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11105,7 +11117,7 @@
         <v>496</v>
       </c>
       <c r="K29" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11140,7 +11152,7 @@
         <v>498</v>
       </c>
       <c r="K30" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11175,7 +11187,7 @@
         <v>500</v>
       </c>
       <c r="K31" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11210,7 +11222,7 @@
         <v>502</v>
       </c>
       <c r="K32" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="L32">
         <v>0.91282903432358287</v>
@@ -11245,7 +11257,7 @@
         <v>504</v>
       </c>
       <c r="K33" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11260,7 +11272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADAD5174-8D2B-4D11-9FFA-7D98BAF40FC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E03D65B0-5BD8-4857-8DE4-C8109D309F1B}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13077,7 +13089,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A836E7-E4D9-4067-A01F-DA1D7701C721}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA747722-E703-455C-A4D6-A3BCB0E873D3}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7724E185-9A96-4AFD-A8B7-AA4A34F7485C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CA1305B-812C-4F8E-9CB4-E7233DF963EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="582">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -922,18 +922,84 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_011</t>
   </si>
   <si>
@@ -952,6 +1018,24 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_020</t>
   </si>
   <si>
@@ -964,52 +1048,46 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_solelc_spv_019</t>
@@ -1018,90 +1096,39 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w579310367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
+  </si>
+  <si>
     <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
   </si>
   <si>
@@ -1114,58 +1141,133 @@
     <t>e_w659874569-220,e_w660091166-220</t>
   </si>
   <si>
+    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
+  </si>
+  <si>
     <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
   </si>
   <si>
     <t>e_w669520367-220,e_w563813243-400</t>
   </si>
   <si>
-    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
+    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
   </si>
   <si>
     <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
   </si>
   <si>
-    <t>e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wonelc_won_003</t>
@@ -1174,52 +1276,28 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_022</t>
@@ -1228,82 +1306,79 @@
     <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_w579310367-220</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_KE12-400</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
   </si>
   <si>
     <t>elc_won_003</t>
@@ -1312,43 +1387,19 @@
     <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_KE12-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
   </si>
   <si>
     <t>elc_won_022</t>
@@ -1357,55 +1408,58 @@
     <t>e_KE13-400,e_KE11-220</t>
   </si>
   <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_008</t>
@@ -1414,102 +1468,48 @@
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_KE15-220</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220</t>
   </si>
   <si>
     <t>elc_wof_008</t>
   </si>
   <si>
-    <t>e_KE15-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_KE15-220</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
     <t>e_won_001</t>
   </si>
   <si>
@@ -1871,6 +1871,9 @@
   </si>
   <si>
     <t>Transformer: e_w870818913-220 → e_w870818913-400</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w660091166-220</t>
   </si>
 </sst>
 </file>
@@ -3764,7 +3767,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_KE15-220,e_w660091166-220</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3786,7 +3789,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_KE15-220,e_w660091166-220</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3801,7 +3804,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>19</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -6603,7 +6606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DEE6DB6-F013-4E3E-B5AE-E22C9723415C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C76EFE-51F5-4AC2-9B62-A11389D53311}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6841,16 +6844,16 @@
         <v>264</v>
       </c>
       <c r="Y11" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="Z11" t="s">
         <v>324</v>
       </c>
       <c r="AA11">
-        <v>0.99787844392938518</v>
+        <v>0.99021329006024306</v>
       </c>
       <c r="AB11">
-        <v>38.895194627939205</v>
+        <v>179.42301556221076</v>
       </c>
       <c r="AD11" t="s">
         <v>263</v>
@@ -6883,10 +6886,10 @@
         <v>393</v>
       </c>
       <c r="AO11">
-        <v>0.99740231224454534</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP11">
-        <v>47.624275516669421</v>
+        <v>122.76624010910177</v>
       </c>
       <c r="AR11" t="s">
         <v>263</v>
@@ -6919,10 +6922,10 @@
         <v>447</v>
       </c>
       <c r="BC11">
-        <v>0.99417680250918639</v>
+        <v>0.99504452373263619</v>
       </c>
       <c r="BD11">
-        <v>106.75862066491723</v>
+        <v>90.850398235003013</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6987,16 +6990,16 @@
         <v>268</v>
       </c>
       <c r="Y12" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Z12" t="s">
         <v>325</v>
       </c>
       <c r="AA12">
-        <v>0.99219647908939179</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB12">
-        <v>143.06455002781746</v>
+        <v>161.73530211859338</v>
       </c>
       <c r="AD12" t="s">
         <v>263</v>
@@ -7026,13 +7029,13 @@
         <v>394</v>
       </c>
       <c r="AN12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO12">
-        <v>0.98910099910393146</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP12">
-        <v>199.81501642792259</v>
+        <v>463.38269175414888</v>
       </c>
       <c r="AR12" t="s">
         <v>263</v>
@@ -7133,16 +7136,16 @@
         <v>270</v>
       </c>
       <c r="Y13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Z13" t="s">
         <v>326</v>
       </c>
       <c r="AA13">
-        <v>0.99199432528561049</v>
+        <v>0.99515835423076238</v>
       </c>
       <c r="AB13">
-        <v>146.77070309714048</v>
+        <v>88.763505769357138</v>
       </c>
       <c r="AD13" t="s">
         <v>263</v>
@@ -7172,13 +7175,13 @@
         <v>395</v>
       </c>
       <c r="AN13" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AO13">
-        <v>0.97660669020396829</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP13">
-        <v>428.87734626058102</v>
+        <v>207.11050978330246</v>
       </c>
       <c r="AR13" t="s">
         <v>263</v>
@@ -7279,16 +7282,16 @@
         <v>272</v>
       </c>
       <c r="Y14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Z14" t="s">
         <v>327</v>
       </c>
       <c r="AA14">
-        <v>0.99686513787774389</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB14">
-        <v>57.472472241362951</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD14" t="s">
         <v>263</v>
@@ -7315,16 +7318,16 @@
         <v>352</v>
       </c>
       <c r="AM14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN14" t="s">
-        <v>398</v>
+        <v>324</v>
       </c>
       <c r="AO14">
-        <v>0.98286027536897036</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP14">
-        <v>314.22828490220974</v>
+        <v>244.33232853837262</v>
       </c>
       <c r="AR14" t="s">
         <v>263</v>
@@ -7357,10 +7360,10 @@
         <v>447</v>
       </c>
       <c r="BC14">
-        <v>0.99722114454285371</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD14">
-        <v>50.94568338101594</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7425,16 +7428,16 @@
         <v>274</v>
       </c>
       <c r="Y15" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="Z15" t="s">
         <v>328</v>
       </c>
       <c r="AA15">
-        <v>0.99065498411395791</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB15">
-        <v>171.32529124410425</v>
+        <v>179.25118814130403</v>
       </c>
       <c r="AD15" t="s">
         <v>263</v>
@@ -7461,16 +7464,16 @@
         <v>354</v>
       </c>
       <c r="AM15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AN15" t="s">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="AO15">
-        <v>0.99741412098479176</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP15">
-        <v>47.407781945483563</v>
+        <v>253.85494292623497</v>
       </c>
       <c r="AR15" t="s">
         <v>263</v>
@@ -7500,13 +7503,13 @@
         <v>453</v>
       </c>
       <c r="BB15" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="BC15">
-        <v>0.9940284706913598</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD15">
-        <v>109.47803732507046</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7571,16 +7574,16 @@
         <v>276</v>
       </c>
       <c r="Y16" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="Z16" t="s">
         <v>329</v>
       </c>
       <c r="AA16">
-        <v>0.99184104324003575</v>
+        <v>0.99594698839866214</v>
       </c>
       <c r="AB16">
-        <v>149.58087393267732</v>
+        <v>74.305212691194157</v>
       </c>
       <c r="AD16" t="s">
         <v>263</v>
@@ -7607,16 +7610,16 @@
         <v>356</v>
       </c>
       <c r="AM16" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AN16" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AO16">
-        <v>0.98563074303391496</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP16">
-        <v>263.43637771155954</v>
+        <v>99.241487561376104</v>
       </c>
       <c r="AR16" t="s">
         <v>263</v>
@@ -7646,13 +7649,13 @@
         <v>454</v>
       </c>
       <c r="BB16" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="BC16">
-        <v>0.99660062084319445</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD16">
-        <v>62.321951208100806</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7717,16 +7720,16 @@
         <v>278</v>
       </c>
       <c r="Y17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Z17" t="s">
         <v>330</v>
       </c>
       <c r="AA17">
-        <v>0.99782085777346563</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB17">
-        <v>39.950940819796543</v>
+        <v>461.61265467993644</v>
       </c>
       <c r="AD17" t="s">
         <v>263</v>
@@ -7753,16 +7756,16 @@
         <v>358</v>
       </c>
       <c r="AM17" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AN17" t="s">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="AO17">
-        <v>0.99059324986934494</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP17">
-        <v>172.45708572867548</v>
+        <v>314.22828490220974</v>
       </c>
       <c r="AR17" t="s">
         <v>263</v>
@@ -7792,13 +7795,13 @@
         <v>455</v>
       </c>
       <c r="BB17" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="BC17">
-        <v>0.99504452373263619</v>
+        <v>0.99790507974591136</v>
       </c>
       <c r="BD17">
-        <v>90.850398235003013</v>
+        <v>38.406871324958367</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7863,16 +7866,16 @@
         <v>280</v>
       </c>
       <c r="Y18" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Z18" t="s">
         <v>331</v>
       </c>
       <c r="AA18">
-        <v>0.98497581152539015</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB18">
-        <v>275.44345536784743</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD18" t="s">
         <v>263</v>
@@ -7899,16 +7902,16 @@
         <v>360</v>
       </c>
       <c r="AM18" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AN18" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AO18">
-        <v>0.99355139026342754</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP18">
-        <v>118.22451183716133</v>
+        <v>47.407781945483563</v>
       </c>
       <c r="AR18" t="s">
         <v>263</v>
@@ -7935,16 +7938,16 @@
         <v>440</v>
       </c>
       <c r="BA18" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="BB18" t="s">
-        <v>456</v>
+        <v>328</v>
       </c>
       <c r="BC18">
-        <v>0.99630507039782612</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD18">
-        <v>67.740376039854553</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8009,16 +8012,16 @@
         <v>282</v>
       </c>
       <c r="Y19" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="Z19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AA19">
-        <v>0.99515835423076238</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB19">
-        <v>88.763505769357138</v>
+        <v>285.85663191255094</v>
       </c>
       <c r="AD19" t="s">
         <v>263</v>
@@ -8045,16 +8048,16 @@
         <v>362</v>
       </c>
       <c r="AM19" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AN19" t="s">
-        <v>331</v>
+        <v>404</v>
       </c>
       <c r="AO19">
-        <v>0.99228583594785691</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP19">
-        <v>141.42634095595602</v>
+        <v>263.43637771155954</v>
       </c>
       <c r="AR19" t="s">
         <v>263</v>
@@ -8081,16 +8084,16 @@
         <v>442</v>
       </c>
       <c r="BA19" t="s">
+        <v>457</v>
+      </c>
+      <c r="BB19" t="s">
         <v>458</v>
       </c>
-      <c r="BB19" t="s">
-        <v>338</v>
-      </c>
       <c r="BC19">
-        <v>0.99749257613418407</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD19">
-        <v>45.969437539958705</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8155,16 +8158,16 @@
         <v>284</v>
       </c>
       <c r="Y20" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="Z20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AA20">
-        <v>0.99312290929392577</v>
+        <v>0.99782085777346563</v>
       </c>
       <c r="AB20">
-        <v>126.07999627802737</v>
+        <v>39.950940819796543</v>
       </c>
       <c r="AD20" t="s">
         <v>263</v>
@@ -8191,16 +8194,16 @@
         <v>364</v>
       </c>
       <c r="AM20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AN20" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
       <c r="AO20">
-        <v>0.99567808239070055</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP20">
-        <v>79.235156170489844</v>
+        <v>172.45708572867548</v>
       </c>
       <c r="AR20" t="s">
         <v>263</v>
@@ -8230,13 +8233,13 @@
         <v>459</v>
       </c>
       <c r="BB20" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="BC20">
-        <v>0.99790507974591136</v>
+        <v>0.99417680250918639</v>
       </c>
       <c r="BD20">
-        <v>38.406871324958367</v>
+        <v>106.75862066491723</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8301,16 +8304,16 @@
         <v>286</v>
       </c>
       <c r="Y21" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="Z21" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AA21">
-        <v>0.99021329006024306</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB21">
-        <v>179.42301556221076</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD21" t="s">
         <v>263</v>
@@ -8337,16 +8340,16 @@
         <v>366</v>
       </c>
       <c r="AM21" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AN21" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="AO21">
-        <v>0.99452764457035958</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP21">
-        <v>100.3265162100753</v>
+        <v>199.81501642792259</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8411,16 +8414,16 @@
         <v>288</v>
       </c>
       <c r="Y22" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Z22" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AA22">
-        <v>0.99117807442989492</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB22">
-        <v>161.73530211859338</v>
+        <v>38.895194627939205</v>
       </c>
       <c r="AD22" t="s">
         <v>263</v>
@@ -8447,16 +8450,16 @@
         <v>368</v>
       </c>
       <c r="AM22" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AN22" t="s">
-        <v>331</v>
+        <v>408</v>
       </c>
       <c r="AO22">
-        <v>0.99675250681341587</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP22">
-        <v>59.537375087375146</v>
+        <v>428.87734626058102</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8521,16 +8524,16 @@
         <v>290</v>
       </c>
       <c r="Y23" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="Z23" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AA23">
-        <v>0.99327889425386662</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB23">
-        <v>123.22027201244609</v>
+        <v>143.06455002781746</v>
       </c>
       <c r="AD23" t="s">
         <v>263</v>
@@ -8557,16 +8560,16 @@
         <v>370</v>
       </c>
       <c r="AM23" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AN23" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AO23">
-        <v>0.99172545486986263</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP23">
-        <v>151.6999940525175</v>
+        <v>118.22451183716133</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8631,16 +8634,16 @@
         <v>292</v>
       </c>
       <c r="Y24" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="Z24" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AA24">
-        <v>0.98440782007749728</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB24">
-        <v>285.85663191255094</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD24" t="s">
         <v>263</v>
@@ -8667,16 +8670,16 @@
         <v>372</v>
       </c>
       <c r="AM24" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AN24" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="AO24">
-        <v>0.98870306310272893</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP24">
-        <v>207.11050978330246</v>
+        <v>100.3265162100753</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8741,16 +8744,16 @@
         <v>294</v>
       </c>
       <c r="Y25" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="Z25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AA25">
-        <v>0.99260409516666881</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB25">
-        <v>135.59158861107267</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD25" t="s">
         <v>263</v>
@@ -8777,16 +8780,16 @@
         <v>374</v>
       </c>
       <c r="AM25" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AN25" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AO25">
-        <v>0.98667278207972509</v>
+        <v>0.99675250681341587</v>
       </c>
       <c r="AP25">
-        <v>244.33232853837262</v>
+        <v>59.537375087375146</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8851,16 +8854,16 @@
         <v>296</v>
       </c>
       <c r="Y26" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="Z26" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AA26">
-        <v>0.99022266246501978</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB26">
-        <v>179.25118814130403</v>
+        <v>74.690879958909605</v>
       </c>
       <c r="AD26" t="s">
         <v>263</v>
@@ -8887,16 +8890,16 @@
         <v>376</v>
       </c>
       <c r="AM26" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AN26" t="s">
-        <v>331</v>
+        <v>415</v>
       </c>
       <c r="AO26">
-        <v>0.98615336674947807</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP26">
-        <v>253.85494292623497</v>
+        <v>151.6999940525175</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8961,16 +8964,16 @@
         <v>298</v>
       </c>
       <c r="Y27" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="Z27" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AA27">
-        <v>0.99806216160693018</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB27">
-        <v>35.52703720627968</v>
+        <v>353.97634871689564</v>
       </c>
       <c r="AD27" t="s">
         <v>263</v>
@@ -8997,16 +9000,16 @@
         <v>378</v>
       </c>
       <c r="AM27" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AN27" t="s">
-        <v>418</v>
+        <v>330</v>
       </c>
       <c r="AO27">
-        <v>0.99458682795119768</v>
+        <v>0.99228583594785691</v>
       </c>
       <c r="AP27">
-        <v>99.241487561376104</v>
+        <v>141.42634095595602</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9071,16 +9074,16 @@
         <v>300</v>
       </c>
       <c r="Y28" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="Z28" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AA28">
-        <v>0.99585076637156988</v>
+        <v>0.99806216160693018</v>
       </c>
       <c r="AB28">
-        <v>76.069283187886086</v>
+        <v>35.52703720627968</v>
       </c>
       <c r="AD28" t="s">
         <v>263</v>
@@ -9107,16 +9110,16 @@
         <v>380</v>
       </c>
       <c r="AM28" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AN28" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="AO28">
-        <v>0.97472458044977373</v>
+        <v>0.99740231224454534</v>
       </c>
       <c r="AP28">
-        <v>463.38269175414888</v>
+        <v>47.624275516669421</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9181,16 +9184,16 @@
         <v>302</v>
       </c>
       <c r="Y29" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="Z29" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="AA29">
-        <v>0.9893494724125782</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB29">
-        <v>195.2596724360663</v>
+        <v>171.32529124410425</v>
       </c>
       <c r="AD29" t="s">
         <v>263</v>
@@ -9217,10 +9220,10 @@
         <v>382</v>
       </c>
       <c r="AM29" t="s">
+        <v>419</v>
+      </c>
+      <c r="AN29" t="s">
         <v>420</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>421</v>
       </c>
       <c r="AO29">
         <v>0.9934827767968939</v>
@@ -9291,16 +9294,16 @@
         <v>304</v>
       </c>
       <c r="Y30" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="Z30" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="AA30">
-        <v>0.97548412543178475</v>
+        <v>0.99184104324003575</v>
       </c>
       <c r="AB30">
-        <v>449.45770041728053</v>
+        <v>149.58087393267732</v>
       </c>
       <c r="AD30" t="s">
         <v>263</v>
@@ -9327,10 +9330,10 @@
         <v>384</v>
       </c>
       <c r="AM30" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AN30" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO30">
         <v>0.99486941977940613</v>
@@ -9401,16 +9404,16 @@
         <v>306</v>
       </c>
       <c r="Y31" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Z31" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="AA31">
-        <v>0.96747189690815383</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB31">
-        <v>596.34855668384682</v>
+        <v>32.188603269438353</v>
       </c>
       <c r="AD31" t="s">
         <v>263</v>
@@ -9437,16 +9440,16 @@
         <v>386</v>
       </c>
       <c r="AM31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AN31" t="s">
-        <v>398</v>
+        <v>330</v>
       </c>
       <c r="AO31">
-        <v>0.99330365963041267</v>
+        <v>0.98907459074885506</v>
       </c>
       <c r="AP31">
-        <v>122.76624010910177</v>
+        <v>200.2991696043234</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9514,7 +9517,7 @@
         <v>256</v>
       </c>
       <c r="Z32" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA32">
         <v>0.98551105518500948</v>
@@ -9547,16 +9550,16 @@
         <v>388</v>
       </c>
       <c r="AM32" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AN32" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="AO32">
-        <v>0.98907459074885506</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP32">
-        <v>200.2991696043234</v>
+        <v>243.83038212667131</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9624,7 +9627,7 @@
         <v>235</v>
       </c>
       <c r="Z33" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="AA33">
         <v>0.99326495911353319</v>
@@ -9657,16 +9660,16 @@
         <v>390</v>
       </c>
       <c r="AM33" t="s">
+        <v>424</v>
+      </c>
+      <c r="AN33" t="s">
         <v>425</v>
       </c>
-      <c r="AN33" t="s">
-        <v>329</v>
-      </c>
       <c r="AO33">
-        <v>0.98670016097490887</v>
+        <v>0.99567808239070055</v>
       </c>
       <c r="AP33">
-        <v>243.83038212667131</v>
+        <v>79.235156170489844</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9731,16 +9734,16 @@
         <v>312</v>
       </c>
       <c r="Y34" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Z34" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AA34">
-        <v>0.99594698839866214</v>
+        <v>0.99585076637156988</v>
       </c>
       <c r="AB34">
-        <v>74.305212691194157</v>
+        <v>76.069283187886086</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9805,16 +9808,16 @@
         <v>314</v>
       </c>
       <c r="Y35" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="Z35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AA35">
-        <v>0.97482112792654896</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB35">
-        <v>461.61265467993644</v>
+        <v>195.2596724360663</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9879,16 +9882,16 @@
         <v>316</v>
       </c>
       <c r="Y36" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="Z36" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="AA36">
-        <v>0.99592595200224132</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB36">
-        <v>74.690879958909605</v>
+        <v>449.45770041728053</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9953,16 +9956,16 @@
         <v>318</v>
       </c>
       <c r="Y37" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="Z37" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="AA37">
-        <v>0.98069219916089656</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB37">
-        <v>353.97634871689564</v>
+        <v>596.34855668384682</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10027,16 +10030,16 @@
         <v>320</v>
       </c>
       <c r="Y38" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="Z38" t="s">
         <v>345</v>
       </c>
       <c r="AA38">
-        <v>0.99824425800348515</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB38">
-        <v>32.188603269438353</v>
+        <v>135.59158861107267</v>
       </c>
     </row>
   </sheetData>
@@ -10045,7 +10048,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B03D1C7-F11B-462B-9056-405766D66A3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5766D7-563E-4999-B95A-DC71597597E5}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10157,7 +10160,7 @@
         <v>460</v>
       </c>
       <c r="K11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10190,7 +10193,7 @@
         <v>506</v>
       </c>
       <c r="X11" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="Y11">
         <v>8.3782499999999995</v>
@@ -10225,7 +10228,7 @@
         <v>462</v>
       </c>
       <c r="K12" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10258,7 +10261,7 @@
         <v>508</v>
       </c>
       <c r="X12" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10293,7 +10296,7 @@
         <v>464</v>
       </c>
       <c r="K13" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="L13">
         <v>1.5817501567892978</v>
@@ -10326,7 +10329,7 @@
         <v>510</v>
       </c>
       <c r="X13" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10361,7 +10364,7 @@
         <v>466</v>
       </c>
       <c r="K14" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10394,7 +10397,7 @@
         <v>512</v>
       </c>
       <c r="X14" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10429,7 +10432,7 @@
         <v>468</v>
       </c>
       <c r="K15" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10462,7 +10465,7 @@
         <v>514</v>
       </c>
       <c r="X15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10497,7 +10500,7 @@
         <v>470</v>
       </c>
       <c r="K16" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10530,7 +10533,7 @@
         <v>516</v>
       </c>
       <c r="X16" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10565,7 +10568,7 @@
         <v>472</v>
       </c>
       <c r="K17" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10633,7 +10636,7 @@
         <v>474</v>
       </c>
       <c r="K18" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10666,7 +10669,7 @@
         <v>520</v>
       </c>
       <c r="X18" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="Y18">
         <v>6.1852499999999999</v>
@@ -10701,7 +10704,7 @@
         <v>476</v>
       </c>
       <c r="K19" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10769,7 +10772,7 @@
         <v>478</v>
       </c>
       <c r="K20" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10802,7 +10805,7 @@
         <v>524</v>
       </c>
       <c r="X20" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10837,7 +10840,7 @@
         <v>480</v>
       </c>
       <c r="K21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L21">
         <v>15.316017274089829</v>
@@ -10872,7 +10875,7 @@
         <v>482</v>
       </c>
       <c r="K22" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10907,7 +10910,7 @@
         <v>484</v>
       </c>
       <c r="K23" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="L23">
         <v>15.32235174795542</v>
@@ -10942,7 +10945,7 @@
         <v>486</v>
       </c>
       <c r="K24" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L24">
         <v>4.3876485804695786</v>
@@ -10977,7 +10980,7 @@
         <v>488</v>
       </c>
       <c r="K25" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -11012,7 +11015,7 @@
         <v>490</v>
       </c>
       <c r="K26" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11047,7 +11050,7 @@
         <v>492</v>
       </c>
       <c r="K27" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11082,7 +11085,7 @@
         <v>494</v>
       </c>
       <c r="K28" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11117,7 +11120,7 @@
         <v>496</v>
       </c>
       <c r="K29" t="s">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11152,7 +11155,7 @@
         <v>498</v>
       </c>
       <c r="K30" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11187,7 +11190,7 @@
         <v>500</v>
       </c>
       <c r="K31" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11222,7 +11225,7 @@
         <v>502</v>
       </c>
       <c r="K32" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="L32">
         <v>0.91282903432358287</v>
@@ -11257,7 +11260,7 @@
         <v>504</v>
       </c>
       <c r="K33" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11272,7 +11275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E03D65B0-5BD8-4857-8DE4-C8109D309F1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BF69055-77EA-49E8-933D-4AA3BAC4A4F4}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13089,7 +13092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA747722-E703-455C-A4D6-A3BCB0E873D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A016208B-F00E-4A3B-87C6-306099EC4899}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CA1305B-812C-4F8E-9CB4-E7233DF963EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{341E9D6A-24FD-46D1-BEF7-9C5AC83BD681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="583">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -619,6 +619,9 @@
     <t>wnid offshore potential</t>
   </si>
   <si>
+    <t>ELC_BatIn</t>
+  </si>
+  <si>
     <t>~fi_process</t>
   </si>
   <si>
@@ -922,18 +925,54 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_004</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_008</t>
   </si>
   <si>
@@ -952,6 +991,66 @@
     <t>connecting solar to buses in cluster 26</t>
   </si>
   <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_028</t>
   </si>
   <si>
@@ -970,52 +1069,16 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_solelc_spv_005</t>
@@ -1030,78 +1093,36 @@
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE7-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400</t>
+  </si>
+  <si>
     <t>e_w579310367-220,e_w563813243-400</t>
   </si>
   <si>
@@ -1114,31 +1135,31 @@
     <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
   </si>
   <si>
+    <t>e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w669520367-220</t>
+  </si>
+  <si>
     <t>e_w660091166-220</t>
   </si>
   <si>
+    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
+  </si>
+  <si>
     <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
   </si>
   <si>
-    <t>e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE7-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w660091166-220</t>
+    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
   </si>
   <si>
     <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
@@ -1147,25 +1168,91 @@
     <t>e_w660091166-220,e_w669520367-220</t>
   </si>
   <si>
-    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
     <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
   </si>
   <si>
-    <t>e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wonelc_won_019</t>
@@ -1174,34 +1261,22 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wonelc_won_017</t>
@@ -1228,106 +1303,88 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_002</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w579310367-220</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE11-220</t>
   </si>
   <si>
     <t>elc_won_019</t>
   </si>
   <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
   </si>
   <si>
     <t>elc_won_017</t>
@@ -1348,64 +1405,34 @@
     <t>elc_won_005</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
     <t>elc_won_002</t>
   </si>
   <si>
     <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
   </si>
   <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE11-220</t>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wofelc_wof_001</t>
@@ -1414,16 +1441,10 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wofelc_wof_002</t>
@@ -1444,46 +1465,40 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_008</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
     <t>e_KE15-220</t>
   </si>
   <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w953567827-220</t>
+    <t>elc_wof_004</t>
   </si>
   <si>
     <t>elc_wof_002</t>
@@ -1493,18 +1508,6 @@
   </si>
   <si>
     <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220</t>
   </si>
   <si>
     <t>elc_wof_008</t>
@@ -3804,7 +3807,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -5281,9 +5284,8 @@
     <row r="8" spans="2:25" ht="17.649999999999999">
       <c r="B8" s="20"/>
       <c r="E8" s="26"/>
-      <c r="F8" t="str">
-        <f>C5</f>
-        <v>ELC</v>
+      <c r="F8" t="s">
+        <v>163</v>
       </c>
       <c r="G8" t="str">
         <f>E7</f>
@@ -6606,209 +6608,209 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C76EFE-51F5-4AC2-9B62-A11389D53311}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3059D9-31E7-44EA-8877-86CF7FA16AD5}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:56">
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="X9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AD9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AL9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AR9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AZ9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="2:56">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10" t="s">
+        <v>232</v>
+      </c>
+      <c r="L10" t="s">
+        <v>233</v>
+      </c>
+      <c r="M10" t="s">
+        <v>234</v>
+      </c>
+      <c r="O10" t="s">
         <v>165</v>
       </c>
-      <c r="D10" t="s">
+      <c r="P10" t="s">
         <v>166</v>
       </c>
-      <c r="E10" t="s">
+      <c r="Q10" t="s">
         <v>167</v>
       </c>
-      <c r="F10" t="s">
+      <c r="R10" t="s">
         <v>168</v>
       </c>
-      <c r="G10" t="s">
+      <c r="S10" t="s">
         <v>169</v>
       </c>
-      <c r="H10" t="s">
+      <c r="T10" t="s">
+        <v>263</v>
+      </c>
+      <c r="U10" t="s">
         <v>170</v>
       </c>
-      <c r="J10" t="s">
-        <v>165</v>
-      </c>
-      <c r="K10" t="s">
-        <v>231</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="V10" t="s">
+        <v>171</v>
+      </c>
+      <c r="X10" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>323</v>
+      </c>
+      <c r="Z10" t="s">
         <v>232</v>
-      </c>
-      <c r="M10" t="s">
-        <v>233</v>
-      </c>
-      <c r="O10" t="s">
-        <v>164</v>
-      </c>
-      <c r="P10" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>166</v>
-      </c>
-      <c r="R10" t="s">
-        <v>167</v>
-      </c>
-      <c r="S10" t="s">
-        <v>168</v>
-      </c>
-      <c r="T10" t="s">
-        <v>262</v>
-      </c>
-      <c r="U10" t="s">
-        <v>169</v>
-      </c>
-      <c r="V10" t="s">
-        <v>170</v>
-      </c>
-      <c r="X10" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>322</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>231</v>
       </c>
       <c r="AA10" t="s">
         <v>146</v>
       </c>
       <c r="AB10" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM10" t="s">
         <v>323</v>
       </c>
-      <c r="AD10" t="s">
-        <v>164</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>165</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>167</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>168</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>170</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>165</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>322</v>
-      </c>
       <c r="AN10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO10" t="s">
         <v>146</v>
       </c>
       <c r="AP10" t="s">
+        <v>324</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>165</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>166</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>167</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>169</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>170</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>171</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>166</v>
+      </c>
+      <c r="BA10" t="s">
         <v>323</v>
       </c>
-      <c r="AR10" t="s">
-        <v>164</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>165</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>167</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>168</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>169</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>170</v>
-      </c>
-      <c r="AZ10" t="s">
-        <v>165</v>
-      </c>
-      <c r="BA10" t="s">
-        <v>322</v>
-      </c>
       <c r="BB10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="BC10" t="s">
         <v>146</v>
       </c>
       <c r="BD10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="2:56">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J11" t="s">
         <v>173</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>174</v>
-      </c>
-      <c r="H11" t="s">
-        <v>175</v>
-      </c>
-      <c r="J11" t="s">
-        <v>172</v>
-      </c>
       <c r="K11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L11">
         <v>2.8968976635313326</v>
@@ -6817,144 +6819,144 @@
         <v>0.23486034866280711</v>
       </c>
       <c r="O11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P11" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>266</v>
+      </c>
+      <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s">
+        <v>267</v>
+      </c>
+      <c r="U11" t="s">
+        <v>268</v>
+      </c>
+      <c r="V11" t="s">
+        <v>176</v>
+      </c>
+      <c r="X11" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA11">
+        <v>0.99787844392938518</v>
+      </c>
+      <c r="AB11">
+        <v>38.895194627939205</v>
+      </c>
+      <c r="AD11" t="s">
         <v>264</v>
       </c>
-      <c r="Q11" t="s">
-        <v>265</v>
-      </c>
-      <c r="R11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" t="s">
-        <v>21</v>
-      </c>
-      <c r="T11" t="s">
-        <v>266</v>
-      </c>
-      <c r="U11" t="s">
-        <v>267</v>
-      </c>
-      <c r="V11" t="s">
-        <v>175</v>
-      </c>
-      <c r="X11" t="s">
+      <c r="AE11" t="s">
+        <v>347</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>348</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>347</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>393</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>394</v>
+      </c>
+      <c r="AO11">
+        <v>0.98870306310272893</v>
+      </c>
+      <c r="AP11">
+        <v>207.11050978330246</v>
+      </c>
+      <c r="AR11" t="s">
         <v>264</v>
       </c>
-      <c r="Y11" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>324</v>
-      </c>
-      <c r="AA11">
-        <v>0.99021329006024306</v>
-      </c>
-      <c r="AB11">
-        <v>179.42301556221076</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>263</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>346</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>347</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>346</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>392</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>393</v>
-      </c>
-      <c r="AO11">
-        <v>0.99330365963041267</v>
-      </c>
-      <c r="AP11">
-        <v>122.76624010910177</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>263</v>
-      </c>
       <c r="AS11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AT11" t="s">
+        <v>428</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ11" t="s">
         <v>427</v>
       </c>
-      <c r="AU11" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ11" t="s">
-        <v>426</v>
-      </c>
       <c r="BA11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="BB11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="BC11">
-        <v>0.99504452373263619</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD11">
-        <v>90.850398235003013</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="12" spans="2:56">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" t="s">
         <v>176</v>
       </c>
-      <c r="D12" t="s">
+      <c r="J12" t="s">
         <v>177</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>174</v>
-      </c>
-      <c r="H12" t="s">
-        <v>175</v>
-      </c>
-      <c r="J12" t="s">
-        <v>176</v>
-      </c>
       <c r="K12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L12">
         <v>0.40337662696804566</v>
@@ -6963,144 +6965,144 @@
         <v>0.2412788642829316</v>
       </c>
       <c r="O12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P12" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>270</v>
+      </c>
+      <c r="R12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" t="s">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s">
+        <v>267</v>
+      </c>
+      <c r="U12" t="s">
         <v>268</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="V12" t="s">
+        <v>176</v>
+      </c>
+      <c r="X12" t="s">
         <v>269</v>
       </c>
-      <c r="R12" t="s">
-        <v>10</v>
-      </c>
-      <c r="S12" t="s">
-        <v>21</v>
-      </c>
-      <c r="T12" t="s">
-        <v>266</v>
-      </c>
-      <c r="U12" t="s">
-        <v>267</v>
-      </c>
-      <c r="V12" t="s">
-        <v>175</v>
-      </c>
-      <c r="X12" t="s">
+      <c r="Y12" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>326</v>
+      </c>
+      <c r="AA12">
+        <v>0.99219647908939179</v>
+      </c>
+      <c r="AB12">
+        <v>143.06455002781746</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>264</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>349</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>350</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="s">
         <v>268</v>
       </c>
-      <c r="Y12" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>325</v>
-      </c>
-      <c r="AA12">
-        <v>0.99117807442989492</v>
-      </c>
-      <c r="AB12">
-        <v>161.73530211859338</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>263</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>348</v>
-      </c>
-      <c r="AF12" t="s">
+      <c r="AJ12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL12" t="s">
         <v>349</v>
       </c>
-      <c r="AG12" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>348</v>
-      </c>
       <c r="AM12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO12">
-        <v>0.97472458044977373</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP12">
-        <v>463.38269175414888</v>
+        <v>244.33232853837262</v>
       </c>
       <c r="AR12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AS12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AT12" t="s">
+        <v>430</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ12" t="s">
         <v>429</v>
       </c>
-      <c r="AU12" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>428</v>
-      </c>
       <c r="BA12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="BB12" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="BC12">
-        <v>0.99567841910080701</v>
+        <v>0.99264898847830307</v>
       </c>
       <c r="BD12">
-        <v>79.228983151871589</v>
+        <v>134.76854456444406</v>
       </c>
     </row>
     <row r="13" spans="2:56">
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" t="s">
         <v>179</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H13" t="s">
-        <v>175</v>
-      </c>
-      <c r="J13" t="s">
-        <v>178</v>
-      </c>
       <c r="K13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L13">
         <v>11.689626123166848</v>
@@ -7109,144 +7111,144 @@
         <v>0.2420572787126988</v>
       </c>
       <c r="O13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q13" t="s">
+        <v>272</v>
+      </c>
+      <c r="R13" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s">
+        <v>267</v>
+      </c>
+      <c r="U13" t="s">
+        <v>268</v>
+      </c>
+      <c r="V13" t="s">
+        <v>176</v>
+      </c>
+      <c r="X13" t="s">
         <v>271</v>
       </c>
-      <c r="R13" t="s">
-        <v>10</v>
-      </c>
-      <c r="S13" t="s">
-        <v>21</v>
-      </c>
-      <c r="T13" t="s">
-        <v>266</v>
-      </c>
-      <c r="U13" t="s">
-        <v>267</v>
-      </c>
-      <c r="V13" t="s">
-        <v>175</v>
-      </c>
-      <c r="X13" t="s">
-        <v>270</v>
-      </c>
       <c r="Y13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA13">
-        <v>0.99515835423076238</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB13">
-        <v>88.763505769357138</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AF13" t="s">
+        <v>352</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL13" t="s">
         <v>351</v>
       </c>
-      <c r="AG13" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>350</v>
-      </c>
       <c r="AM13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN13" t="s">
-        <v>393</v>
+        <v>330</v>
       </c>
       <c r="AO13">
-        <v>0.98870306310272893</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP13">
-        <v>207.11050978330246</v>
+        <v>253.85494292623497</v>
       </c>
       <c r="AR13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AS13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AT13" t="s">
+        <v>432</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ13" t="s">
         <v>431</v>
       </c>
-      <c r="AU13" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW13" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ13" t="s">
-        <v>430</v>
-      </c>
       <c r="BA13" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="BB13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="BC13">
-        <v>0.99264898847830307</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD13">
-        <v>134.76854456444406</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="14" spans="2:56">
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
+        <v>182</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" t="s">
+        <v>176</v>
+      </c>
+      <c r="J14" t="s">
         <v>181</v>
       </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" t="s">
-        <v>175</v>
-      </c>
-      <c r="J14" t="s">
-        <v>180</v>
-      </c>
       <c r="K14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L14">
         <v>36.16807762931424</v>
@@ -7255,144 +7257,144 @@
         <v>0.25377483791368649</v>
       </c>
       <c r="O14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q14" t="s">
+        <v>274</v>
+      </c>
+      <c r="R14" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
+        <v>267</v>
+      </c>
+      <c r="U14" t="s">
+        <v>268</v>
+      </c>
+      <c r="V14" t="s">
+        <v>176</v>
+      </c>
+      <c r="X14" t="s">
         <v>273</v>
       </c>
-      <c r="R14" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" t="s">
-        <v>21</v>
-      </c>
-      <c r="T14" t="s">
-        <v>266</v>
-      </c>
-      <c r="U14" t="s">
-        <v>267</v>
-      </c>
-      <c r="V14" t="s">
-        <v>175</v>
-      </c>
-      <c r="X14" t="s">
-        <v>272</v>
-      </c>
       <c r="Y14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Z14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA14">
-        <v>0.99312290929392577</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB14">
-        <v>126.07999627802737</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AF14" t="s">
+        <v>354</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL14" t="s">
         <v>353</v>
       </c>
-      <c r="AG14" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>352</v>
-      </c>
       <c r="AM14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN14" t="s">
-        <v>324</v>
+        <v>398</v>
       </c>
       <c r="AO14">
-        <v>0.98667278207972509</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP14">
-        <v>244.33232853837262</v>
+        <v>99.241487561376104</v>
       </c>
       <c r="AR14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AS14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AT14" t="s">
+        <v>434</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ14" t="s">
         <v>433</v>
       </c>
-      <c r="AU14" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW14" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ14" t="s">
-        <v>432</v>
-      </c>
       <c r="BA14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="BB14" t="s">
-        <v>447</v>
+        <v>337</v>
       </c>
       <c r="BC14">
-        <v>0.99630507039782612</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD14">
-        <v>67.740376039854553</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="15" spans="2:56">
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>176</v>
+      </c>
+      <c r="J15" t="s">
         <v>183</v>
       </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H15" t="s">
-        <v>175</v>
-      </c>
-      <c r="J15" t="s">
-        <v>182</v>
-      </c>
       <c r="K15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L15">
         <v>12.146792968753148</v>
@@ -7401,144 +7403,144 @@
         <v>0.2392671938041559</v>
       </c>
       <c r="O15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q15" t="s">
+        <v>276</v>
+      </c>
+      <c r="R15" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s">
+        <v>267</v>
+      </c>
+      <c r="U15" t="s">
+        <v>268</v>
+      </c>
+      <c r="V15" t="s">
+        <v>176</v>
+      </c>
+      <c r="X15" t="s">
         <v>275</v>
       </c>
-      <c r="R15" t="s">
-        <v>10</v>
-      </c>
-      <c r="S15" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s">
-        <v>266</v>
-      </c>
-      <c r="U15" t="s">
-        <v>267</v>
-      </c>
-      <c r="V15" t="s">
-        <v>175</v>
-      </c>
-      <c r="X15" t="s">
-        <v>274</v>
-      </c>
       <c r="Y15" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="Z15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA15">
-        <v>0.99022266246501978</v>
+        <v>0.99782085777346563</v>
       </c>
       <c r="AB15">
-        <v>179.25118814130403</v>
+        <v>39.950940819796543</v>
       </c>
       <c r="AD15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AF15" t="s">
+        <v>356</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL15" t="s">
         <v>355</v>
       </c>
-      <c r="AG15" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>354</v>
-      </c>
       <c r="AM15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN15" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AO15">
-        <v>0.98615336674947807</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP15">
-        <v>253.85494292623497</v>
+        <v>199.81501642792259</v>
       </c>
       <c r="AR15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AS15" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AT15" t="s">
+        <v>436</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ15" t="s">
         <v>435</v>
       </c>
-      <c r="AU15" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW15" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX15" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ15" t="s">
-        <v>434</v>
-      </c>
       <c r="BA15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="BB15" t="s">
-        <v>328</v>
+        <v>455</v>
       </c>
       <c r="BC15">
-        <v>0.99749257613418407</v>
+        <v>0.99504452373263619</v>
       </c>
       <c r="BD15">
-        <v>45.969437539958705</v>
+        <v>90.850398235003013</v>
       </c>
     </row>
     <row r="16" spans="2:56">
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" t="s">
         <v>185</v>
       </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H16" t="s">
-        <v>175</v>
-      </c>
-      <c r="J16" t="s">
-        <v>184</v>
-      </c>
       <c r="K16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L16">
         <v>7.3042877221233224</v>
@@ -7547,144 +7549,144 @@
         <v>0.22157458702157681</v>
       </c>
       <c r="O16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q16" t="s">
+        <v>278</v>
+      </c>
+      <c r="R16" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s">
+        <v>267</v>
+      </c>
+      <c r="U16" t="s">
+        <v>268</v>
+      </c>
+      <c r="V16" t="s">
+        <v>176</v>
+      </c>
+      <c r="X16" t="s">
         <v>277</v>
       </c>
-      <c r="R16" t="s">
-        <v>10</v>
-      </c>
-      <c r="S16" t="s">
-        <v>21</v>
-      </c>
-      <c r="T16" t="s">
-        <v>266</v>
-      </c>
-      <c r="U16" t="s">
-        <v>267</v>
-      </c>
-      <c r="V16" t="s">
-        <v>175</v>
-      </c>
-      <c r="X16" t="s">
-        <v>276</v>
-      </c>
       <c r="Y16" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Z16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA16">
-        <v>0.99594698839866214</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB16">
-        <v>74.305212691194157</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE16" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AF16" t="s">
+        <v>358</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL16" t="s">
         <v>357</v>
       </c>
-      <c r="AG16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>356</v>
-      </c>
       <c r="AM16" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN16" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO16">
-        <v>0.99458682795119768</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP16">
-        <v>99.241487561376104</v>
+        <v>428.87734626058102</v>
       </c>
       <c r="AR16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AS16" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AT16" t="s">
+        <v>438</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ16" t="s">
         <v>437</v>
       </c>
-      <c r="AU16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW16" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ16" t="s">
-        <v>436</v>
-      </c>
       <c r="BA16" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BB16" t="s">
-        <v>328</v>
+        <v>448</v>
       </c>
       <c r="BC16">
-        <v>0.9940284706913598</v>
+        <v>0.99790507974591136</v>
       </c>
       <c r="BD16">
-        <v>109.47803732507046</v>
+        <v>38.406871324958367</v>
       </c>
     </row>
     <row r="17" spans="2:56">
       <c r="B17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>176</v>
+      </c>
+      <c r="J17" t="s">
         <v>187</v>
       </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s">
-        <v>174</v>
-      </c>
-      <c r="H17" t="s">
-        <v>175</v>
-      </c>
-      <c r="J17" t="s">
-        <v>186</v>
-      </c>
       <c r="K17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L17">
         <v>3.9552307996088447</v>
@@ -7693,144 +7695,144 @@
         <v>0.2301224015067071</v>
       </c>
       <c r="O17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q17" t="s">
+        <v>280</v>
+      </c>
+      <c r="R17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" t="s">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s">
+        <v>267</v>
+      </c>
+      <c r="U17" t="s">
+        <v>268</v>
+      </c>
+      <c r="V17" t="s">
+        <v>176</v>
+      </c>
+      <c r="X17" t="s">
         <v>279</v>
       </c>
-      <c r="R17" t="s">
-        <v>10</v>
-      </c>
-      <c r="S17" t="s">
-        <v>21</v>
-      </c>
-      <c r="T17" t="s">
-        <v>266</v>
-      </c>
-      <c r="U17" t="s">
-        <v>267</v>
-      </c>
-      <c r="V17" t="s">
-        <v>175</v>
-      </c>
-      <c r="X17" t="s">
-        <v>278</v>
-      </c>
       <c r="Y17" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="Z17" t="s">
+        <v>331</v>
+      </c>
+      <c r="AA17">
+        <v>0.99021329006024306</v>
+      </c>
+      <c r="AB17">
+        <v>179.42301556221076</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>264</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>359</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>360</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>359</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>402</v>
+      </c>
+      <c r="AN17" t="s">
         <v>330</v>
       </c>
-      <c r="AA17">
-        <v>0.97482112792654896</v>
-      </c>
-      <c r="AB17">
-        <v>461.61265467993644</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>263</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>358</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>359</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>358</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>400</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>393</v>
-      </c>
       <c r="AO17">
-        <v>0.98286027536897036</v>
+        <v>0.98907459074885506</v>
       </c>
       <c r="AP17">
-        <v>314.22828490220974</v>
+        <v>200.2991696043234</v>
       </c>
       <c r="AR17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AS17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AT17" t="s">
+        <v>440</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ17" t="s">
         <v>439</v>
       </c>
-      <c r="AU17" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW17" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ17" t="s">
-        <v>438</v>
-      </c>
       <c r="BA17" t="s">
+        <v>457</v>
+      </c>
+      <c r="BB17" t="s">
         <v>455</v>
       </c>
-      <c r="BB17" t="s">
-        <v>449</v>
-      </c>
       <c r="BC17">
-        <v>0.99790507974591136</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD17">
-        <v>38.406871324958367</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="18" spans="2:56">
       <c r="B18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" t="s">
         <v>189</v>
       </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>174</v>
-      </c>
-      <c r="H18" t="s">
-        <v>175</v>
-      </c>
-      <c r="J18" t="s">
-        <v>188</v>
-      </c>
       <c r="K18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L18">
         <v>17.329622089430899</v>
@@ -7839,144 +7841,144 @@
         <v>0.2496590287478814</v>
       </c>
       <c r="O18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q18" t="s">
+        <v>282</v>
+      </c>
+      <c r="R18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
+      </c>
+      <c r="T18" t="s">
+        <v>267</v>
+      </c>
+      <c r="U18" t="s">
+        <v>268</v>
+      </c>
+      <c r="V18" t="s">
+        <v>176</v>
+      </c>
+      <c r="X18" t="s">
         <v>281</v>
       </c>
-      <c r="R18" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" t="s">
-        <v>21</v>
-      </c>
-      <c r="T18" t="s">
-        <v>266</v>
-      </c>
-      <c r="U18" t="s">
-        <v>267</v>
-      </c>
-      <c r="V18" t="s">
-        <v>175</v>
-      </c>
-      <c r="X18" t="s">
-        <v>280</v>
-      </c>
       <c r="Y18" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="Z18" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA18">
-        <v>0.99327889425386662</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB18">
-        <v>123.22027201244609</v>
+        <v>161.73530211859338</v>
       </c>
       <c r="AD18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AF18" t="s">
+        <v>362</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL18" t="s">
         <v>361</v>
       </c>
-      <c r="AG18" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>360</v>
-      </c>
       <c r="AM18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AN18" t="s">
-        <v>402</v>
+        <v>335</v>
       </c>
       <c r="AO18">
-        <v>0.99741412098479176</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP18">
-        <v>47.407781945483563</v>
+        <v>243.83038212667131</v>
       </c>
       <c r="AR18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AS18" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AT18" t="s">
+        <v>442</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ18" t="s">
         <v>441</v>
       </c>
-      <c r="AU18" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV18" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW18" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX18" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ18" t="s">
-        <v>440</v>
-      </c>
       <c r="BA18" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="BB18" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="BC18">
-        <v>0.99660062084319445</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD18">
-        <v>62.321951208100806</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="19" spans="2:56">
       <c r="B19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" t="s">
         <v>191</v>
       </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" t="s">
-        <v>174</v>
-      </c>
-      <c r="H19" t="s">
-        <v>175</v>
-      </c>
-      <c r="J19" t="s">
-        <v>190</v>
-      </c>
       <c r="K19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L19">
         <v>11.786576720249853</v>
@@ -7985,144 +7987,144 @@
         <v>0.25369869095953879</v>
       </c>
       <c r="O19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q19" t="s">
+        <v>284</v>
+      </c>
+      <c r="R19" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" t="s">
+        <v>267</v>
+      </c>
+      <c r="U19" t="s">
+        <v>268</v>
+      </c>
+      <c r="V19" t="s">
+        <v>176</v>
+      </c>
+      <c r="X19" t="s">
         <v>283</v>
       </c>
-      <c r="R19" t="s">
-        <v>10</v>
-      </c>
-      <c r="S19" t="s">
-        <v>21</v>
-      </c>
-      <c r="T19" t="s">
-        <v>266</v>
-      </c>
-      <c r="U19" t="s">
-        <v>267</v>
-      </c>
-      <c r="V19" t="s">
-        <v>175</v>
-      </c>
-      <c r="X19" t="s">
-        <v>282</v>
-      </c>
       <c r="Y19" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="Z19" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA19">
+        <v>0.99515835423076238</v>
+      </c>
+      <c r="AB19">
+        <v>88.763505769357138</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>264</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>363</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>364</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>363</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>404</v>
+      </c>
+      <c r="AN19" t="s">
         <v>330</v>
       </c>
-      <c r="AA19">
-        <v>0.98440782007749728</v>
-      </c>
-      <c r="AB19">
-        <v>285.85663191255094</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>263</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>362</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>363</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>362</v>
-      </c>
-      <c r="AM19" t="s">
-        <v>403</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>404</v>
-      </c>
       <c r="AO19">
-        <v>0.98563074303391496</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP19">
-        <v>263.43637771155954</v>
+        <v>463.38269175414888</v>
       </c>
       <c r="AR19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AS19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AT19" t="s">
+        <v>444</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ19" t="s">
         <v>443</v>
       </c>
-      <c r="AU19" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW19" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ19" t="s">
-        <v>442</v>
-      </c>
       <c r="BA19" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BB19" t="s">
-        <v>458</v>
+        <v>337</v>
       </c>
       <c r="BC19">
-        <v>0.99722114454285371</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD19">
-        <v>50.94568338101594</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="20" spans="2:56">
       <c r="B20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" t="s">
         <v>193</v>
       </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" t="s">
-        <v>174</v>
-      </c>
-      <c r="H20" t="s">
-        <v>175</v>
-      </c>
-      <c r="J20" t="s">
-        <v>192</v>
-      </c>
       <c r="K20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L20">
         <v>9.433500569960966</v>
@@ -8131,109 +8133,109 @@
         <v>0.2304230038193946</v>
       </c>
       <c r="O20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q20" t="s">
+        <v>286</v>
+      </c>
+      <c r="R20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" t="s">
+        <v>267</v>
+      </c>
+      <c r="U20" t="s">
+        <v>268</v>
+      </c>
+      <c r="V20" t="s">
+        <v>176</v>
+      </c>
+      <c r="X20" t="s">
         <v>285</v>
       </c>
-      <c r="R20" t="s">
-        <v>10</v>
-      </c>
-      <c r="S20" t="s">
-        <v>21</v>
-      </c>
-      <c r="T20" t="s">
-        <v>266</v>
-      </c>
-      <c r="U20" t="s">
-        <v>267</v>
-      </c>
-      <c r="V20" t="s">
-        <v>175</v>
-      </c>
-      <c r="X20" t="s">
-        <v>284</v>
-      </c>
       <c r="Y20" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="Z20" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AA20">
-        <v>0.99782085777346563</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB20">
-        <v>39.950940819796543</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AF20" t="s">
+        <v>366</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL20" t="s">
         <v>365</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>364</v>
       </c>
       <c r="AM20" t="s">
         <v>405</v>
       </c>
       <c r="AN20" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="AO20">
-        <v>0.99059324986934494</v>
+        <v>0.99740231224454534</v>
       </c>
       <c r="AP20">
-        <v>172.45708572867548</v>
+        <v>47.624275516669421</v>
       </c>
       <c r="AR20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AS20" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AT20" t="s">
+        <v>446</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>176</v>
+      </c>
+      <c r="AZ20" t="s">
         <v>445</v>
       </c>
-      <c r="AU20" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW20" t="s">
-        <v>267</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ20" t="s">
-        <v>444</v>
-      </c>
       <c r="BA20" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="BB20" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="BC20">
         <v>0.99417680250918639</v>
@@ -8244,31 +8246,31 @@
     </row>
     <row r="21" spans="2:56">
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" t="s">
         <v>195</v>
       </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>174</v>
-      </c>
-      <c r="H21" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" t="s">
-        <v>194</v>
-      </c>
       <c r="K21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L21">
         <v>8.8152849300557854</v>
@@ -8277,108 +8279,108 @@
         <v>0.24429475688599259</v>
       </c>
       <c r="O21" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q21" t="s">
+        <v>288</v>
+      </c>
+      <c r="R21" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" t="s">
+        <v>21</v>
+      </c>
+      <c r="T21" t="s">
+        <v>267</v>
+      </c>
+      <c r="U21" t="s">
+        <v>268</v>
+      </c>
+      <c r="V21" t="s">
+        <v>176</v>
+      </c>
+      <c r="X21" t="s">
         <v>287</v>
       </c>
-      <c r="R21" t="s">
-        <v>10</v>
-      </c>
-      <c r="S21" t="s">
-        <v>21</v>
-      </c>
-      <c r="T21" t="s">
-        <v>266</v>
-      </c>
-      <c r="U21" t="s">
-        <v>267</v>
-      </c>
-      <c r="V21" t="s">
-        <v>175</v>
-      </c>
-      <c r="X21" t="s">
-        <v>286</v>
-      </c>
       <c r="Y21" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="Z21" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AA21">
-        <v>0.98497581152539015</v>
+        <v>0.99184104324003575</v>
       </c>
       <c r="AB21">
-        <v>275.44345536784743</v>
+        <v>149.58087393267732</v>
       </c>
       <c r="AD21" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE21" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AF21" t="s">
+        <v>368</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL21" t="s">
         <v>367</v>
       </c>
-      <c r="AG21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL21" t="s">
-        <v>366</v>
-      </c>
       <c r="AM21" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN21" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="AO21">
-        <v>0.98910099910393146</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP21">
-        <v>199.81501642792259</v>
+        <v>100.3265162100753</v>
       </c>
     </row>
     <row r="22" spans="2:56">
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" t="s">
         <v>197</v>
       </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" t="s">
-        <v>174</v>
-      </c>
-      <c r="H22" t="s">
-        <v>175</v>
-      </c>
-      <c r="J22" t="s">
-        <v>196</v>
-      </c>
       <c r="K22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L22">
         <v>14.958068869507889</v>
@@ -8387,108 +8389,108 @@
         <v>0.23354545132238791</v>
       </c>
       <c r="O22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q22" t="s">
+        <v>290</v>
+      </c>
+      <c r="R22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S22" t="s">
+        <v>21</v>
+      </c>
+      <c r="T22" t="s">
+        <v>267</v>
+      </c>
+      <c r="U22" t="s">
+        <v>268</v>
+      </c>
+      <c r="V22" t="s">
+        <v>176</v>
+      </c>
+      <c r="X22" t="s">
         <v>289</v>
       </c>
-      <c r="R22" t="s">
-        <v>10</v>
-      </c>
-      <c r="S22" t="s">
-        <v>21</v>
-      </c>
-      <c r="T22" t="s">
-        <v>266</v>
-      </c>
-      <c r="U22" t="s">
-        <v>267</v>
-      </c>
-      <c r="V22" t="s">
-        <v>175</v>
-      </c>
-      <c r="X22" t="s">
-        <v>288</v>
-      </c>
       <c r="Y22" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="Z22" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AA22">
-        <v>0.99787844392938518</v>
+        <v>0.98551105518500948</v>
       </c>
       <c r="AB22">
-        <v>38.895194627939205</v>
+        <v>265.63065494149328</v>
       </c>
       <c r="AD22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE22" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AF22" t="s">
+        <v>370</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL22" t="s">
         <v>369</v>
       </c>
-      <c r="AG22" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>368</v>
-      </c>
       <c r="AM22" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AN22" t="s">
-        <v>408</v>
+        <v>330</v>
       </c>
       <c r="AO22">
-        <v>0.97660669020396829</v>
+        <v>0.99675250681341587</v>
       </c>
       <c r="AP22">
-        <v>428.87734626058102</v>
+        <v>59.537375087375146</v>
       </c>
     </row>
     <row r="23" spans="2:56">
       <c r="B23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D23" t="s">
+        <v>200</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" t="s">
+        <v>176</v>
+      </c>
+      <c r="J23" t="s">
         <v>199</v>
       </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" t="s">
-        <v>175</v>
-      </c>
-      <c r="J23" t="s">
-        <v>198</v>
-      </c>
       <c r="K23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L23">
         <v>11.43145251014559</v>
@@ -8497,108 +8499,108 @@
         <v>0.22094100918821119</v>
       </c>
       <c r="O23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P23" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q23" t="s">
+        <v>292</v>
+      </c>
+      <c r="R23" t="s">
+        <v>10</v>
+      </c>
+      <c r="S23" t="s">
+        <v>21</v>
+      </c>
+      <c r="T23" t="s">
+        <v>267</v>
+      </c>
+      <c r="U23" t="s">
+        <v>268</v>
+      </c>
+      <c r="V23" t="s">
+        <v>176</v>
+      </c>
+      <c r="X23" t="s">
         <v>291</v>
       </c>
-      <c r="R23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S23" t="s">
-        <v>21</v>
-      </c>
-      <c r="T23" t="s">
-        <v>266</v>
-      </c>
-      <c r="U23" t="s">
-        <v>267</v>
-      </c>
-      <c r="V23" t="s">
-        <v>175</v>
-      </c>
-      <c r="X23" t="s">
-        <v>290</v>
-      </c>
       <c r="Y23" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="Z23" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AA23">
-        <v>0.99219647908939179</v>
+        <v>0.99326495911353319</v>
       </c>
       <c r="AB23">
-        <v>143.06455002781746</v>
+        <v>123.47574958522414</v>
       </c>
       <c r="AD23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE23" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AF23" t="s">
+        <v>372</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL23" t="s">
         <v>371</v>
       </c>
-      <c r="AG23" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL23" t="s">
-        <v>370</v>
-      </c>
       <c r="AM23" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN23" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO23">
-        <v>0.99355139026342754</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP23">
-        <v>118.22451183716133</v>
+        <v>151.6999940525175</v>
       </c>
     </row>
     <row r="24" spans="2:56">
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" t="s">
         <v>201</v>
       </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" t="s">
-        <v>174</v>
-      </c>
-      <c r="H24" t="s">
-        <v>175</v>
-      </c>
-      <c r="J24" t="s">
-        <v>200</v>
-      </c>
       <c r="K24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L24">
         <v>8.8022630868364313</v>
@@ -8607,108 +8609,108 @@
         <v>0.22701719012402771</v>
       </c>
       <c r="O24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q24" t="s">
+        <v>294</v>
+      </c>
+      <c r="R24" t="s">
+        <v>10</v>
+      </c>
+      <c r="S24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T24" t="s">
+        <v>267</v>
+      </c>
+      <c r="U24" t="s">
+        <v>268</v>
+      </c>
+      <c r="V24" t="s">
+        <v>176</v>
+      </c>
+      <c r="X24" t="s">
         <v>293</v>
       </c>
-      <c r="R24" t="s">
-        <v>10</v>
-      </c>
-      <c r="S24" t="s">
-        <v>21</v>
-      </c>
-      <c r="T24" t="s">
-        <v>266</v>
-      </c>
-      <c r="U24" t="s">
-        <v>267</v>
-      </c>
-      <c r="V24" t="s">
-        <v>175</v>
-      </c>
-      <c r="X24" t="s">
-        <v>292</v>
-      </c>
       <c r="Y24" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="Z24" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AA24">
-        <v>0.99199432528561049</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB24">
-        <v>146.77070309714048</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE24" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AF24" t="s">
+        <v>374</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL24" t="s">
         <v>373</v>
       </c>
-      <c r="AG24" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>372</v>
-      </c>
       <c r="AM24" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN24" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO24">
-        <v>0.99452764457035958</v>
+        <v>0.99567808239070055</v>
       </c>
       <c r="AP24">
-        <v>100.3265162100753</v>
+        <v>79.235156170489844</v>
       </c>
     </row>
     <row r="25" spans="2:56">
       <c r="B25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" t="s">
+        <v>176</v>
+      </c>
+      <c r="J25" t="s">
         <v>203</v>
       </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" t="s">
-        <v>202</v>
-      </c>
       <c r="K25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L25">
         <v>25.23431224641401</v>
@@ -8717,108 +8719,108 @@
         <v>0.2208616648568717</v>
       </c>
       <c r="O25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q25" t="s">
+        <v>296</v>
+      </c>
+      <c r="R25" t="s">
+        <v>10</v>
+      </c>
+      <c r="S25" t="s">
+        <v>21</v>
+      </c>
+      <c r="T25" t="s">
+        <v>267</v>
+      </c>
+      <c r="U25" t="s">
+        <v>268</v>
+      </c>
+      <c r="V25" t="s">
+        <v>176</v>
+      </c>
+      <c r="X25" t="s">
         <v>295</v>
       </c>
-      <c r="R25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S25" t="s">
-        <v>21</v>
-      </c>
-      <c r="T25" t="s">
-        <v>266</v>
-      </c>
-      <c r="U25" t="s">
-        <v>267</v>
-      </c>
-      <c r="V25" t="s">
-        <v>175</v>
-      </c>
-      <c r="X25" t="s">
-        <v>294</v>
-      </c>
       <c r="Y25" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AA25">
-        <v>0.99686513787774389</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB25">
-        <v>57.472472241362951</v>
+        <v>285.85663191255094</v>
       </c>
       <c r="AD25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE25" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF25" t="s">
+        <v>376</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL25" t="s">
         <v>375</v>
       </c>
-      <c r="AG25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI25" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>374</v>
-      </c>
       <c r="AM25" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN25" t="s">
-        <v>330</v>
+        <v>394</v>
       </c>
       <c r="AO25">
-        <v>0.99675250681341587</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP25">
-        <v>59.537375087375146</v>
+        <v>122.76624010910177</v>
       </c>
     </row>
     <row r="26" spans="2:56">
       <c r="B26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" t="s">
+        <v>176</v>
+      </c>
+      <c r="J26" t="s">
         <v>205</v>
       </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>174</v>
-      </c>
-      <c r="H26" t="s">
-        <v>175</v>
-      </c>
-      <c r="J26" t="s">
-        <v>204</v>
-      </c>
       <c r="K26" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L26">
         <v>31.037064761761126</v>
@@ -8827,108 +8829,108 @@
         <v>0.22502636726912939</v>
       </c>
       <c r="O26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P26" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q26" t="s">
+        <v>298</v>
+      </c>
+      <c r="R26" t="s">
+        <v>10</v>
+      </c>
+      <c r="S26" t="s">
+        <v>21</v>
+      </c>
+      <c r="T26" t="s">
+        <v>267</v>
+      </c>
+      <c r="U26" t="s">
+        <v>268</v>
+      </c>
+      <c r="V26" t="s">
+        <v>176</v>
+      </c>
+      <c r="X26" t="s">
         <v>297</v>
       </c>
-      <c r="R26" t="s">
-        <v>10</v>
-      </c>
-      <c r="S26" t="s">
-        <v>21</v>
-      </c>
-      <c r="T26" t="s">
-        <v>266</v>
-      </c>
-      <c r="U26" t="s">
-        <v>267</v>
-      </c>
-      <c r="V26" t="s">
-        <v>175</v>
-      </c>
-      <c r="X26" t="s">
-        <v>296</v>
-      </c>
       <c r="Y26" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Z26" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AA26">
-        <v>0.99592595200224132</v>
+        <v>0.99585076637156988</v>
       </c>
       <c r="AB26">
-        <v>74.690879958909605</v>
+        <v>76.069283187886086</v>
       </c>
       <c r="AD26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE26" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF26" t="s">
+        <v>378</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL26" t="s">
         <v>377</v>
       </c>
-      <c r="AG26" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>376</v>
-      </c>
       <c r="AM26" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN26" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO26">
-        <v>0.99172545486986263</v>
+        <v>0.9934827767968939</v>
       </c>
       <c r="AP26">
-        <v>151.6999940525175</v>
+        <v>119.4824253902779</v>
       </c>
     </row>
     <row r="27" spans="2:56">
       <c r="B27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D27" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" t="s">
         <v>207</v>
       </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>174</v>
-      </c>
-      <c r="H27" t="s">
-        <v>175</v>
-      </c>
-      <c r="J27" t="s">
-        <v>206</v>
-      </c>
       <c r="K27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L27">
         <v>3.4722775462637423</v>
@@ -8937,108 +8939,108 @@
         <v>0.22878422375200849</v>
       </c>
       <c r="O27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P27" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q27" t="s">
+        <v>300</v>
+      </c>
+      <c r="R27" t="s">
+        <v>10</v>
+      </c>
+      <c r="S27" t="s">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s">
+        <v>267</v>
+      </c>
+      <c r="U27" t="s">
+        <v>268</v>
+      </c>
+      <c r="V27" t="s">
+        <v>176</v>
+      </c>
+      <c r="X27" t="s">
         <v>299</v>
       </c>
-      <c r="R27" t="s">
-        <v>10</v>
-      </c>
-      <c r="S27" t="s">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s">
-        <v>266</v>
-      </c>
-      <c r="U27" t="s">
-        <v>267</v>
-      </c>
-      <c r="V27" t="s">
-        <v>175</v>
-      </c>
-      <c r="X27" t="s">
-        <v>298</v>
-      </c>
       <c r="Y27" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="Z27" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AA27">
-        <v>0.98069219916089656</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB27">
-        <v>353.97634871689564</v>
+        <v>195.2596724360663</v>
       </c>
       <c r="AD27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE27" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AF27" t="s">
+        <v>380</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL27" t="s">
         <v>379</v>
       </c>
-      <c r="AG27" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL27" t="s">
-        <v>378</v>
-      </c>
       <c r="AM27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN27" t="s">
         <v>330</v>
       </c>
       <c r="AO27">
-        <v>0.99228583594785691</v>
+        <v>0.99486941977940613</v>
       </c>
       <c r="AP27">
-        <v>141.42634095595602</v>
+        <v>94.060637377553505</v>
       </c>
     </row>
     <row r="28" spans="2:56">
       <c r="B28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" t="s">
         <v>209</v>
       </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" t="s">
-        <v>174</v>
-      </c>
-      <c r="H28" t="s">
-        <v>175</v>
-      </c>
-      <c r="J28" t="s">
-        <v>208</v>
-      </c>
       <c r="K28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L28">
         <v>22.602581292198185</v>
@@ -9047,108 +9049,108 @@
         <v>0.22477130876687521</v>
       </c>
       <c r="O28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P28" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q28" t="s">
+        <v>302</v>
+      </c>
+      <c r="R28" t="s">
+        <v>10</v>
+      </c>
+      <c r="S28" t="s">
+        <v>21</v>
+      </c>
+      <c r="T28" t="s">
+        <v>267</v>
+      </c>
+      <c r="U28" t="s">
+        <v>268</v>
+      </c>
+      <c r="V28" t="s">
+        <v>176</v>
+      </c>
+      <c r="X28" t="s">
         <v>301</v>
-      </c>
-      <c r="R28" t="s">
-        <v>10</v>
-      </c>
-      <c r="S28" t="s">
-        <v>21</v>
-      </c>
-      <c r="T28" t="s">
-        <v>266</v>
-      </c>
-      <c r="U28" t="s">
-        <v>267</v>
-      </c>
-      <c r="V28" t="s">
-        <v>175</v>
-      </c>
-      <c r="X28" t="s">
-        <v>300</v>
       </c>
       <c r="Y28" t="s">
         <v>250</v>
       </c>
       <c r="Z28" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="AA28">
-        <v>0.99806216160693018</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB28">
-        <v>35.52703720627968</v>
+        <v>449.45770041728053</v>
       </c>
       <c r="AD28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE28" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AF28" t="s">
+        <v>382</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL28" t="s">
         <v>381</v>
       </c>
-      <c r="AG28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH28" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL28" t="s">
-        <v>380</v>
-      </c>
       <c r="AM28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN28" t="s">
-        <v>418</v>
+        <v>330</v>
       </c>
       <c r="AO28">
-        <v>0.99740231224454534</v>
+        <v>0.99228583594785691</v>
       </c>
       <c r="AP28">
-        <v>47.624275516669421</v>
+        <v>141.42634095595602</v>
       </c>
     </row>
     <row r="29" spans="2:56">
       <c r="B29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D29" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>176</v>
+      </c>
+      <c r="J29" t="s">
         <v>211</v>
       </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" t="s">
-        <v>174</v>
-      </c>
-      <c r="H29" t="s">
-        <v>175</v>
-      </c>
-      <c r="J29" t="s">
-        <v>210</v>
-      </c>
       <c r="K29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L29">
         <v>22.472738272208847</v>
@@ -9157,108 +9159,108 @@
         <v>0.2249101914683718</v>
       </c>
       <c r="O29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P29" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q29" t="s">
+        <v>304</v>
+      </c>
+      <c r="R29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" t="s">
+        <v>21</v>
+      </c>
+      <c r="T29" t="s">
+        <v>267</v>
+      </c>
+      <c r="U29" t="s">
+        <v>268</v>
+      </c>
+      <c r="V29" t="s">
+        <v>176</v>
+      </c>
+      <c r="X29" t="s">
         <v>303</v>
       </c>
-      <c r="R29" t="s">
-        <v>10</v>
-      </c>
-      <c r="S29" t="s">
-        <v>21</v>
-      </c>
-      <c r="T29" t="s">
-        <v>266</v>
-      </c>
-      <c r="U29" t="s">
-        <v>267</v>
-      </c>
-      <c r="V29" t="s">
-        <v>175</v>
-      </c>
-      <c r="X29" t="s">
-        <v>302</v>
-      </c>
       <c r="Y29" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="Z29" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AA29">
-        <v>0.99065498411395791</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB29">
-        <v>171.32529124410425</v>
+        <v>596.34855668384682</v>
       </c>
       <c r="AD29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE29" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AF29" t="s">
+        <v>384</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL29" t="s">
         <v>383</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI29" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ29" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>382</v>
       </c>
       <c r="AM29" t="s">
         <v>419</v>
       </c>
       <c r="AN29" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="AO29">
-        <v>0.9934827767968939</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP29">
-        <v>119.4824253902779</v>
+        <v>314.22828490220974</v>
       </c>
     </row>
     <row r="30" spans="2:56">
       <c r="B30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" t="s">
         <v>213</v>
       </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" t="s">
-        <v>174</v>
-      </c>
-      <c r="H30" t="s">
-        <v>175</v>
-      </c>
-      <c r="J30" t="s">
-        <v>212</v>
-      </c>
       <c r="K30" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L30">
         <v>9.86820378976428</v>
@@ -9267,108 +9269,108 @@
         <v>0.22563358755379659</v>
       </c>
       <c r="O30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q30" t="s">
+        <v>306</v>
+      </c>
+      <c r="R30" t="s">
+        <v>10</v>
+      </c>
+      <c r="S30" t="s">
+        <v>21</v>
+      </c>
+      <c r="T30" t="s">
+        <v>267</v>
+      </c>
+      <c r="U30" t="s">
+        <v>268</v>
+      </c>
+      <c r="V30" t="s">
+        <v>176</v>
+      </c>
+      <c r="X30" t="s">
         <v>305</v>
       </c>
-      <c r="R30" t="s">
-        <v>10</v>
-      </c>
-      <c r="S30" t="s">
-        <v>21</v>
-      </c>
-      <c r="T30" t="s">
-        <v>266</v>
-      </c>
-      <c r="U30" t="s">
-        <v>267</v>
-      </c>
-      <c r="V30" t="s">
-        <v>175</v>
-      </c>
-      <c r="X30" t="s">
-        <v>304</v>
-      </c>
       <c r="Y30" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="Z30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AA30">
-        <v>0.99184104324003575</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB30">
-        <v>149.58087393267732</v>
+        <v>135.59158861107267</v>
       </c>
       <c r="AD30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE30" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AF30" t="s">
+        <v>386</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL30" t="s">
         <v>385</v>
       </c>
-      <c r="AG30" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH30" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI30" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>384</v>
-      </c>
       <c r="AM30" t="s">
+        <v>420</v>
+      </c>
+      <c r="AN30" t="s">
         <v>421</v>
       </c>
-      <c r="AN30" t="s">
-        <v>330</v>
-      </c>
       <c r="AO30">
-        <v>0.99486941977940613</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP30">
-        <v>94.060637377553505</v>
+        <v>47.407781945483563</v>
       </c>
     </row>
     <row r="31" spans="2:56">
       <c r="B31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" t="s">
+        <v>176</v>
+      </c>
+      <c r="J31" t="s">
         <v>215</v>
       </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
-        <v>174</v>
-      </c>
-      <c r="H31" t="s">
-        <v>175</v>
-      </c>
-      <c r="J31" t="s">
-        <v>214</v>
-      </c>
       <c r="K31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L31">
         <v>8.9861448355695916</v>
@@ -9377,108 +9379,108 @@
         <v>0.2255000294564469</v>
       </c>
       <c r="O31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P31" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q31" t="s">
+        <v>308</v>
+      </c>
+      <c r="R31" t="s">
+        <v>10</v>
+      </c>
+      <c r="S31" t="s">
+        <v>21</v>
+      </c>
+      <c r="T31" t="s">
+        <v>267</v>
+      </c>
+      <c r="U31" t="s">
+        <v>268</v>
+      </c>
+      <c r="V31" t="s">
+        <v>176</v>
+      </c>
+      <c r="X31" t="s">
         <v>307</v>
       </c>
-      <c r="R31" t="s">
-        <v>10</v>
-      </c>
-      <c r="S31" t="s">
-        <v>21</v>
-      </c>
-      <c r="T31" t="s">
-        <v>266</v>
-      </c>
-      <c r="U31" t="s">
-        <v>267</v>
-      </c>
-      <c r="V31" t="s">
-        <v>175</v>
-      </c>
-      <c r="X31" t="s">
-        <v>306</v>
-      </c>
       <c r="Y31" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="Z31" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AA31">
-        <v>0.99824425800348515</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB31">
-        <v>32.188603269438353</v>
+        <v>179.25118814130403</v>
       </c>
       <c r="AD31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE31" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AF31" t="s">
+        <v>388</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL31" t="s">
         <v>387</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH31" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI31" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>386</v>
       </c>
       <c r="AM31" t="s">
         <v>422</v>
       </c>
       <c r="AN31" t="s">
-        <v>330</v>
+        <v>423</v>
       </c>
       <c r="AO31">
-        <v>0.98907459074885506</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP31">
-        <v>200.2991696043234</v>
+        <v>263.43637771155954</v>
       </c>
     </row>
     <row r="32" spans="2:56">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" t="s">
         <v>217</v>
       </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" t="s">
-        <v>174</v>
-      </c>
-      <c r="H32" t="s">
-        <v>175</v>
-      </c>
-      <c r="J32" t="s">
-        <v>216</v>
-      </c>
       <c r="K32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L32">
         <v>24.542131316767524</v>
@@ -9487,108 +9489,108 @@
         <v>0.24897163182926521</v>
       </c>
       <c r="O32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P32" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q32" t="s">
+        <v>310</v>
+      </c>
+      <c r="R32" t="s">
+        <v>10</v>
+      </c>
+      <c r="S32" t="s">
+        <v>21</v>
+      </c>
+      <c r="T32" t="s">
+        <v>267</v>
+      </c>
+      <c r="U32" t="s">
+        <v>268</v>
+      </c>
+      <c r="V32" t="s">
+        <v>176</v>
+      </c>
+      <c r="X32" t="s">
         <v>309</v>
       </c>
-      <c r="R32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S32" t="s">
-        <v>21</v>
-      </c>
-      <c r="T32" t="s">
-        <v>266</v>
-      </c>
-      <c r="U32" t="s">
-        <v>267</v>
-      </c>
-      <c r="V32" t="s">
-        <v>175</v>
-      </c>
-      <c r="X32" t="s">
-        <v>308</v>
-      </c>
       <c r="Y32" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Z32" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AA32">
-        <v>0.98551105518500948</v>
+        <v>0.99594698839866214</v>
       </c>
       <c r="AB32">
-        <v>265.63065494149328</v>
+        <v>74.305212691194157</v>
       </c>
       <c r="AD32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE32" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AF32" t="s">
+        <v>390</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL32" t="s">
         <v>389</v>
       </c>
-      <c r="AG32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI32" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>388</v>
-      </c>
       <c r="AM32" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN32" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AO32">
-        <v>0.98670016097490887</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP32">
-        <v>243.83038212667131</v>
+        <v>172.45708572867548</v>
       </c>
     </row>
     <row r="33" spans="2:42">
       <c r="B33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" t="s">
+        <v>176</v>
+      </c>
+      <c r="J33" t="s">
         <v>219</v>
       </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" t="s">
-        <v>174</v>
-      </c>
-      <c r="H33" t="s">
-        <v>175</v>
-      </c>
-      <c r="J33" t="s">
-        <v>218</v>
-      </c>
       <c r="K33" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L33">
         <v>13.40311107600413</v>
@@ -9597,108 +9599,108 @@
         <v>0.2357479849120028</v>
       </c>
       <c r="O33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P33" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q33" t="s">
+        <v>312</v>
+      </c>
+      <c r="R33" t="s">
+        <v>10</v>
+      </c>
+      <c r="S33" t="s">
+        <v>21</v>
+      </c>
+      <c r="T33" t="s">
+        <v>267</v>
+      </c>
+      <c r="U33" t="s">
+        <v>268</v>
+      </c>
+      <c r="V33" t="s">
+        <v>176</v>
+      </c>
+      <c r="X33" t="s">
         <v>311</v>
       </c>
-      <c r="R33" t="s">
-        <v>10</v>
-      </c>
-      <c r="S33" t="s">
-        <v>21</v>
-      </c>
-      <c r="T33" t="s">
-        <v>266</v>
-      </c>
-      <c r="U33" t="s">
-        <v>267</v>
-      </c>
-      <c r="V33" t="s">
-        <v>175</v>
-      </c>
-      <c r="X33" t="s">
-        <v>310</v>
-      </c>
       <c r="Y33" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="Z33" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AA33">
-        <v>0.99326495911353319</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB33">
-        <v>123.47574958522414</v>
+        <v>461.61265467993644</v>
       </c>
       <c r="AD33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE33" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AF33" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL33" t="s">
         <v>391</v>
       </c>
-      <c r="AG33" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH33" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI33" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>390</v>
-      </c>
       <c r="AM33" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN33" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO33">
-        <v>0.99567808239070055</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP33">
-        <v>79.235156170489844</v>
+        <v>118.22451183716133</v>
       </c>
     </row>
     <row r="34" spans="2:42">
       <c r="B34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" t="s">
         <v>221</v>
       </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" t="s">
-        <v>174</v>
-      </c>
-      <c r="H34" t="s">
-        <v>175</v>
-      </c>
-      <c r="J34" t="s">
-        <v>220</v>
-      </c>
       <c r="K34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L34">
         <v>17.135920894226487</v>
@@ -9707,72 +9709,72 @@
         <v>0.24195369464045599</v>
       </c>
       <c r="O34" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P34" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q34" t="s">
+        <v>314</v>
+      </c>
+      <c r="R34" t="s">
+        <v>10</v>
+      </c>
+      <c r="S34" t="s">
+        <v>21</v>
+      </c>
+      <c r="T34" t="s">
+        <v>267</v>
+      </c>
+      <c r="U34" t="s">
+        <v>268</v>
+      </c>
+      <c r="V34" t="s">
+        <v>176</v>
+      </c>
+      <c r="X34" t="s">
         <v>313</v>
       </c>
-      <c r="R34" t="s">
-        <v>10</v>
-      </c>
-      <c r="S34" t="s">
-        <v>21</v>
-      </c>
-      <c r="T34" t="s">
-        <v>266</v>
-      </c>
-      <c r="U34" t="s">
-        <v>267</v>
-      </c>
-      <c r="V34" t="s">
-        <v>175</v>
-      </c>
-      <c r="X34" t="s">
-        <v>312</v>
-      </c>
       <c r="Y34" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="Z34" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AA34">
-        <v>0.99585076637156988</v>
+        <v>0.99806216160693018</v>
       </c>
       <c r="AB34">
-        <v>76.069283187886086</v>
+        <v>35.52703720627968</v>
       </c>
     </row>
     <row r="35" spans="2:42">
       <c r="B35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D35" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
+        <v>175</v>
+      </c>
+      <c r="H35" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" t="s">
         <v>223</v>
       </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" t="s">
-        <v>174</v>
-      </c>
-      <c r="H35" t="s">
-        <v>175</v>
-      </c>
-      <c r="J35" t="s">
-        <v>222</v>
-      </c>
       <c r="K35" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L35">
         <v>16.876925927847243</v>
@@ -9781,72 +9783,72 @@
         <v>0.22830604427963411</v>
       </c>
       <c r="O35" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P35" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q35" t="s">
+        <v>316</v>
+      </c>
+      <c r="R35" t="s">
+        <v>10</v>
+      </c>
+      <c r="S35" t="s">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s">
+        <v>267</v>
+      </c>
+      <c r="U35" t="s">
+        <v>268</v>
+      </c>
+      <c r="V35" t="s">
+        <v>176</v>
+      </c>
+      <c r="X35" t="s">
         <v>315</v>
       </c>
-      <c r="R35" t="s">
-        <v>10</v>
-      </c>
-      <c r="S35" t="s">
-        <v>21</v>
-      </c>
-      <c r="T35" t="s">
-        <v>266</v>
-      </c>
-      <c r="U35" t="s">
-        <v>267</v>
-      </c>
-      <c r="V35" t="s">
-        <v>175</v>
-      </c>
-      <c r="X35" t="s">
-        <v>314</v>
-      </c>
       <c r="Y35" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="Z35" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="AA35">
-        <v>0.9893494724125782</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB35">
-        <v>195.2596724360663</v>
+        <v>171.32529124410425</v>
       </c>
     </row>
     <row r="36" spans="2:42">
       <c r="B36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D36" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" t="s">
         <v>225</v>
       </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" t="s">
-        <v>174</v>
-      </c>
-      <c r="H36" t="s">
-        <v>175</v>
-      </c>
-      <c r="J36" t="s">
-        <v>224</v>
-      </c>
       <c r="K36" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L36">
         <v>16.286751959076469</v>
@@ -9855,72 +9857,72 @@
         <v>0.22435766636713819</v>
       </c>
       <c r="O36" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P36" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q36" t="s">
+        <v>318</v>
+      </c>
+      <c r="R36" t="s">
+        <v>10</v>
+      </c>
+      <c r="S36" t="s">
+        <v>21</v>
+      </c>
+      <c r="T36" t="s">
+        <v>267</v>
+      </c>
+      <c r="U36" t="s">
+        <v>268</v>
+      </c>
+      <c r="V36" t="s">
+        <v>176</v>
+      </c>
+      <c r="X36" t="s">
         <v>317</v>
       </c>
-      <c r="R36" t="s">
-        <v>10</v>
-      </c>
-      <c r="S36" t="s">
-        <v>21</v>
-      </c>
-      <c r="T36" t="s">
-        <v>266</v>
-      </c>
-      <c r="U36" t="s">
-        <v>267</v>
-      </c>
-      <c r="V36" t="s">
-        <v>175</v>
-      </c>
-      <c r="X36" t="s">
-        <v>316</v>
-      </c>
       <c r="Y36" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="Z36" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="AA36">
-        <v>0.97548412543178475</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB36">
-        <v>449.45770041728053</v>
+        <v>74.690879958909605</v>
       </c>
     </row>
     <row r="37" spans="2:42">
       <c r="B37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D37" t="s">
+        <v>228</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" t="s">
+        <v>176</v>
+      </c>
+      <c r="J37" t="s">
         <v>227</v>
       </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" t="s">
-        <v>174</v>
-      </c>
-      <c r="H37" t="s">
-        <v>175</v>
-      </c>
-      <c r="J37" t="s">
-        <v>226</v>
-      </c>
       <c r="K37" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L37">
         <v>3.0341676299481568</v>
@@ -9929,72 +9931,72 @@
         <v>0.22631627354031719</v>
       </c>
       <c r="O37" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P37" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q37" t="s">
+        <v>320</v>
+      </c>
+      <c r="R37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S37" t="s">
+        <v>21</v>
+      </c>
+      <c r="T37" t="s">
+        <v>267</v>
+      </c>
+      <c r="U37" t="s">
+        <v>268</v>
+      </c>
+      <c r="V37" t="s">
+        <v>176</v>
+      </c>
+      <c r="X37" t="s">
         <v>319</v>
       </c>
-      <c r="R37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S37" t="s">
-        <v>21</v>
-      </c>
-      <c r="T37" t="s">
-        <v>266</v>
-      </c>
-      <c r="U37" t="s">
-        <v>267</v>
-      </c>
-      <c r="V37" t="s">
-        <v>175</v>
-      </c>
-      <c r="X37" t="s">
-        <v>318</v>
-      </c>
       <c r="Y37" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="Z37" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="AA37">
-        <v>0.96747189690815383</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB37">
-        <v>596.34855668384682</v>
+        <v>353.97634871689564</v>
       </c>
     </row>
     <row r="38" spans="2:42">
       <c r="B38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" t="s">
+        <v>175</v>
+      </c>
+      <c r="H38" t="s">
+        <v>176</v>
+      </c>
+      <c r="J38" t="s">
         <v>229</v>
       </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" t="s">
-        <v>174</v>
-      </c>
-      <c r="H38" t="s">
-        <v>175</v>
-      </c>
-      <c r="J38" t="s">
-        <v>228</v>
-      </c>
       <c r="K38" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L38">
         <v>8.738095228639077</v>
@@ -10003,43 +10005,43 @@
         <v>0.22637223931889949</v>
       </c>
       <c r="O38" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P38" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q38" t="s">
+        <v>322</v>
+      </c>
+      <c r="R38" t="s">
+        <v>10</v>
+      </c>
+      <c r="S38" t="s">
+        <v>21</v>
+      </c>
+      <c r="T38" t="s">
+        <v>267</v>
+      </c>
+      <c r="U38" t="s">
+        <v>268</v>
+      </c>
+      <c r="V38" t="s">
+        <v>176</v>
+      </c>
+      <c r="X38" t="s">
         <v>321</v>
       </c>
-      <c r="R38" t="s">
-        <v>10</v>
-      </c>
-      <c r="S38" t="s">
-        <v>21</v>
-      </c>
-      <c r="T38" t="s">
-        <v>266</v>
-      </c>
-      <c r="U38" t="s">
-        <v>267</v>
-      </c>
-      <c r="V38" t="s">
-        <v>175</v>
-      </c>
-      <c r="X38" t="s">
-        <v>320</v>
-      </c>
       <c r="Y38" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="Z38" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA38">
-        <v>0.99260409516666881</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB38">
-        <v>135.59158861107267</v>
+        <v>32.188603269438353</v>
       </c>
     </row>
   </sheetData>
@@ -10048,119 +10050,119 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5766D7-563E-4999-B95A-DC71597597E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCA6FEA-1908-4EC7-8DF7-23959AF69E01}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:26">
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="W9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="2:26">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10" t="s">
+        <v>232</v>
+      </c>
+      <c r="L10" t="s">
+        <v>233</v>
+      </c>
+      <c r="M10" t="s">
+        <v>234</v>
+      </c>
+      <c r="O10" t="s">
         <v>165</v>
       </c>
-      <c r="D10" t="s">
+      <c r="P10" t="s">
         <v>166</v>
       </c>
-      <c r="E10" t="s">
+      <c r="Q10" t="s">
         <v>167</v>
       </c>
-      <c r="F10" t="s">
+      <c r="R10" t="s">
         <v>168</v>
       </c>
-      <c r="G10" t="s">
+      <c r="S10" t="s">
         <v>169</v>
       </c>
-      <c r="H10" t="s">
+      <c r="T10" t="s">
         <v>170</v>
       </c>
-      <c r="J10" t="s">
-        <v>165</v>
-      </c>
-      <c r="K10" t="s">
-        <v>231</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="U10" t="s">
+        <v>171</v>
+      </c>
+      <c r="W10" t="s">
+        <v>166</v>
+      </c>
+      <c r="X10" t="s">
         <v>232</v>
       </c>
-      <c r="M10" t="s">
+      <c r="Y10" t="s">
         <v>233</v>
       </c>
-      <c r="O10" t="s">
-        <v>164</v>
-      </c>
-      <c r="P10" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>166</v>
-      </c>
-      <c r="R10" t="s">
-        <v>167</v>
-      </c>
-      <c r="S10" t="s">
-        <v>168</v>
-      </c>
-      <c r="T10" t="s">
-        <v>169</v>
-      </c>
-      <c r="U10" t="s">
-        <v>170</v>
-      </c>
-      <c r="W10" t="s">
-        <v>165</v>
-      </c>
-      <c r="X10" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>232</v>
-      </c>
       <c r="Z10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="2:26">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D11" t="s">
+        <v>462</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J11" t="s">
         <v>461</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>174</v>
-      </c>
-      <c r="H11" t="s">
-        <v>175</v>
-      </c>
-      <c r="J11" t="s">
-        <v>460</v>
-      </c>
       <c r="K11" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10169,31 +10171,31 @@
         <v>0.109836021041595</v>
       </c>
       <c r="O11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Q11" t="s">
+        <v>508</v>
+      </c>
+      <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s">
+        <v>175</v>
+      </c>
+      <c r="U11" t="s">
+        <v>176</v>
+      </c>
+      <c r="W11" t="s">
         <v>507</v>
       </c>
-      <c r="R11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" t="s">
-        <v>21</v>
-      </c>
-      <c r="T11" t="s">
-        <v>174</v>
-      </c>
-      <c r="U11" t="s">
-        <v>175</v>
-      </c>
-      <c r="W11" t="s">
-        <v>506</v>
-      </c>
       <c r="X11" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="Y11">
         <v>8.3782499999999995</v>
@@ -10204,31 +10206,31 @@
     </row>
     <row r="12" spans="2:26">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D12" t="s">
+        <v>464</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" t="s">
         <v>463</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>174</v>
-      </c>
-      <c r="H12" t="s">
-        <v>175</v>
-      </c>
-      <c r="J12" t="s">
-        <v>462</v>
-      </c>
       <c r="K12" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10237,31 +10239,31 @@
         <v>0.2149080559560089</v>
       </c>
       <c r="O12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Q12" t="s">
+        <v>510</v>
+      </c>
+      <c r="R12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" t="s">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s">
+        <v>175</v>
+      </c>
+      <c r="U12" t="s">
+        <v>176</v>
+      </c>
+      <c r="W12" t="s">
         <v>509</v>
       </c>
-      <c r="R12" t="s">
-        <v>10</v>
-      </c>
-      <c r="S12" t="s">
-        <v>21</v>
-      </c>
-      <c r="T12" t="s">
-        <v>174</v>
-      </c>
-      <c r="U12" t="s">
-        <v>175</v>
-      </c>
-      <c r="W12" t="s">
-        <v>508</v>
-      </c>
       <c r="X12" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10272,31 +10274,31 @@
     </row>
     <row r="13" spans="2:26">
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D13" t="s">
+        <v>466</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" t="s">
         <v>465</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H13" t="s">
-        <v>175</v>
-      </c>
-      <c r="J13" t="s">
-        <v>464</v>
-      </c>
       <c r="K13" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="L13">
         <v>1.5817501567892978</v>
@@ -10305,31 +10307,31 @@
         <v>0.33309194745150211</v>
       </c>
       <c r="O13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P13" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Q13" t="s">
+        <v>512</v>
+      </c>
+      <c r="R13" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s">
+        <v>175</v>
+      </c>
+      <c r="U13" t="s">
+        <v>176</v>
+      </c>
+      <c r="W13" t="s">
         <v>511</v>
       </c>
-      <c r="R13" t="s">
-        <v>10</v>
-      </c>
-      <c r="S13" t="s">
-        <v>21</v>
-      </c>
-      <c r="T13" t="s">
-        <v>174</v>
-      </c>
-      <c r="U13" t="s">
-        <v>175</v>
-      </c>
-      <c r="W13" t="s">
-        <v>510</v>
-      </c>
       <c r="X13" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10340,31 +10342,31 @@
     </row>
     <row r="14" spans="2:26">
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D14" t="s">
+        <v>468</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" t="s">
+        <v>176</v>
+      </c>
+      <c r="J14" t="s">
         <v>467</v>
       </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" t="s">
-        <v>175</v>
-      </c>
-      <c r="J14" t="s">
-        <v>466</v>
-      </c>
       <c r="K14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10373,31 +10375,31 @@
         <v>0.2502810608198982</v>
       </c>
       <c r="O14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Q14" t="s">
+        <v>514</v>
+      </c>
+      <c r="R14" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
+        <v>175</v>
+      </c>
+      <c r="U14" t="s">
+        <v>176</v>
+      </c>
+      <c r="W14" t="s">
         <v>513</v>
       </c>
-      <c r="R14" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" t="s">
-        <v>21</v>
-      </c>
-      <c r="T14" t="s">
-        <v>174</v>
-      </c>
-      <c r="U14" t="s">
-        <v>175</v>
-      </c>
-      <c r="W14" t="s">
-        <v>512</v>
-      </c>
       <c r="X14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10408,31 +10410,31 @@
     </row>
     <row r="15" spans="2:26">
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D15" t="s">
+        <v>470</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>176</v>
+      </c>
+      <c r="J15" t="s">
         <v>469</v>
       </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H15" t="s">
-        <v>175</v>
-      </c>
-      <c r="J15" t="s">
-        <v>468</v>
-      </c>
       <c r="K15" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10441,31 +10443,31 @@
         <v>0.2858632512923428</v>
       </c>
       <c r="O15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Q15" t="s">
+        <v>516</v>
+      </c>
+      <c r="R15" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s">
+        <v>175</v>
+      </c>
+      <c r="U15" t="s">
+        <v>176</v>
+      </c>
+      <c r="W15" t="s">
         <v>515</v>
       </c>
-      <c r="R15" t="s">
-        <v>10</v>
-      </c>
-      <c r="S15" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s">
-        <v>174</v>
-      </c>
-      <c r="U15" t="s">
-        <v>175</v>
-      </c>
-      <c r="W15" t="s">
-        <v>514</v>
-      </c>
       <c r="X15" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10476,31 +10478,31 @@
     </row>
     <row r="16" spans="2:26">
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D16" t="s">
+        <v>472</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" t="s">
         <v>471</v>
       </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H16" t="s">
-        <v>175</v>
-      </c>
-      <c r="J16" t="s">
-        <v>470</v>
-      </c>
       <c r="K16" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10509,31 +10511,31 @@
         <v>0.34572608805755811</v>
       </c>
       <c r="O16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P16" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Q16" t="s">
+        <v>518</v>
+      </c>
+      <c r="R16" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s">
+        <v>175</v>
+      </c>
+      <c r="U16" t="s">
+        <v>176</v>
+      </c>
+      <c r="W16" t="s">
         <v>517</v>
       </c>
-      <c r="R16" t="s">
-        <v>10</v>
-      </c>
-      <c r="S16" t="s">
-        <v>21</v>
-      </c>
-      <c r="T16" t="s">
-        <v>174</v>
-      </c>
-      <c r="U16" t="s">
-        <v>175</v>
-      </c>
-      <c r="W16" t="s">
-        <v>516</v>
-      </c>
       <c r="X16" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10544,31 +10546,31 @@
     </row>
     <row r="17" spans="2:26">
       <c r="B17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D17" t="s">
+        <v>474</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>176</v>
+      </c>
+      <c r="J17" t="s">
         <v>473</v>
       </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s">
-        <v>174</v>
-      </c>
-      <c r="H17" t="s">
-        <v>175</v>
-      </c>
-      <c r="J17" t="s">
-        <v>472</v>
-      </c>
       <c r="K17" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10577,31 +10579,31 @@
         <v>0.395906817887822</v>
       </c>
       <c r="O17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Q17" t="s">
+        <v>520</v>
+      </c>
+      <c r="R17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" t="s">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s">
+        <v>175</v>
+      </c>
+      <c r="U17" t="s">
+        <v>176</v>
+      </c>
+      <c r="W17" t="s">
         <v>519</v>
       </c>
-      <c r="R17" t="s">
-        <v>10</v>
-      </c>
-      <c r="S17" t="s">
-        <v>21</v>
-      </c>
-      <c r="T17" t="s">
-        <v>174</v>
-      </c>
-      <c r="U17" t="s">
-        <v>175</v>
-      </c>
-      <c r="W17" t="s">
-        <v>518</v>
-      </c>
       <c r="X17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Y17">
         <v>2.2530000000000001</v>
@@ -10612,31 +10614,31 @@
     </row>
     <row r="18" spans="2:26">
       <c r="B18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D18" t="s">
+        <v>476</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" t="s">
         <v>475</v>
       </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>174</v>
-      </c>
-      <c r="H18" t="s">
-        <v>175</v>
-      </c>
-      <c r="J18" t="s">
-        <v>474</v>
-      </c>
       <c r="K18" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10645,31 +10647,31 @@
         <v>0.33056297534614321</v>
       </c>
       <c r="O18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P18" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q18" t="s">
+        <v>522</v>
+      </c>
+      <c r="R18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
+      </c>
+      <c r="T18" t="s">
+        <v>175</v>
+      </c>
+      <c r="U18" t="s">
+        <v>176</v>
+      </c>
+      <c r="W18" t="s">
         <v>521</v>
       </c>
-      <c r="R18" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" t="s">
-        <v>21</v>
-      </c>
-      <c r="T18" t="s">
-        <v>174</v>
-      </c>
-      <c r="U18" t="s">
-        <v>175</v>
-      </c>
-      <c r="W18" t="s">
-        <v>520</v>
-      </c>
       <c r="X18" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Y18">
         <v>6.1852499999999999</v>
@@ -10680,31 +10682,31 @@
     </row>
     <row r="19" spans="2:26">
       <c r="B19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D19" t="s">
+        <v>478</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" t="s">
         <v>477</v>
       </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" t="s">
-        <v>174</v>
-      </c>
-      <c r="H19" t="s">
-        <v>175</v>
-      </c>
-      <c r="J19" t="s">
-        <v>476</v>
-      </c>
       <c r="K19" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10713,31 +10715,31 @@
         <v>0.27452187627990171</v>
       </c>
       <c r="O19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P19" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Q19" t="s">
+        <v>524</v>
+      </c>
+      <c r="R19" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" t="s">
+        <v>175</v>
+      </c>
+      <c r="U19" t="s">
+        <v>176</v>
+      </c>
+      <c r="W19" t="s">
         <v>523</v>
       </c>
-      <c r="R19" t="s">
-        <v>10</v>
-      </c>
-      <c r="S19" t="s">
-        <v>21</v>
-      </c>
-      <c r="T19" t="s">
-        <v>174</v>
-      </c>
-      <c r="U19" t="s">
-        <v>175</v>
-      </c>
-      <c r="W19" t="s">
-        <v>522</v>
-      </c>
       <c r="X19" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Y19">
         <v>10.093500000000001</v>
@@ -10748,31 +10750,31 @@
     </row>
     <row r="20" spans="2:26">
       <c r="B20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D20" t="s">
+        <v>480</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" t="s">
         <v>479</v>
       </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" t="s">
-        <v>174</v>
-      </c>
-      <c r="H20" t="s">
-        <v>175</v>
-      </c>
-      <c r="J20" t="s">
-        <v>478</v>
-      </c>
       <c r="K20" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10781,31 +10783,31 @@
         <v>0.31186545842804159</v>
       </c>
       <c r="O20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P20" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Q20" t="s">
+        <v>526</v>
+      </c>
+      <c r="R20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" t="s">
+        <v>175</v>
+      </c>
+      <c r="U20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W20" t="s">
         <v>525</v>
       </c>
-      <c r="R20" t="s">
-        <v>10</v>
-      </c>
-      <c r="S20" t="s">
-        <v>21</v>
-      </c>
-      <c r="T20" t="s">
-        <v>174</v>
-      </c>
-      <c r="U20" t="s">
-        <v>175</v>
-      </c>
-      <c r="W20" t="s">
-        <v>524</v>
-      </c>
       <c r="X20" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10816,31 +10818,31 @@
     </row>
     <row r="21" spans="2:26">
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D21" t="s">
+        <v>482</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" t="s">
         <v>481</v>
       </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>174</v>
-      </c>
-      <c r="H21" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" t="s">
-        <v>480</v>
-      </c>
       <c r="K21" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="L21">
         <v>15.316017274089829</v>
@@ -10851,31 +10853,31 @@
     </row>
     <row r="22" spans="2:26">
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D22" t="s">
+        <v>484</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" t="s">
         <v>483</v>
       </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" t="s">
-        <v>174</v>
-      </c>
-      <c r="H22" t="s">
-        <v>175</v>
-      </c>
-      <c r="J22" t="s">
-        <v>482</v>
-      </c>
       <c r="K22" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10886,31 +10888,31 @@
     </row>
     <row r="23" spans="2:26">
       <c r="B23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D23" t="s">
+        <v>486</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" t="s">
+        <v>176</v>
+      </c>
+      <c r="J23" t="s">
         <v>485</v>
       </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" t="s">
-        <v>175</v>
-      </c>
-      <c r="J23" t="s">
-        <v>484</v>
-      </c>
       <c r="K23" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L23">
         <v>15.32235174795542</v>
@@ -10921,31 +10923,31 @@
     </row>
     <row r="24" spans="2:26">
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D24" t="s">
+        <v>488</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" t="s">
         <v>487</v>
       </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" t="s">
-        <v>174</v>
-      </c>
-      <c r="H24" t="s">
-        <v>175</v>
-      </c>
-      <c r="J24" t="s">
-        <v>486</v>
-      </c>
       <c r="K24" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="L24">
         <v>4.3876485804695786</v>
@@ -10956,31 +10958,31 @@
     </row>
     <row r="25" spans="2:26">
       <c r="B25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D25" t="s">
+        <v>490</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" t="s">
+        <v>176</v>
+      </c>
+      <c r="J25" t="s">
         <v>489</v>
       </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" t="s">
-        <v>488</v>
-      </c>
       <c r="K25" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -10991,31 +10993,31 @@
     </row>
     <row r="26" spans="2:26">
       <c r="B26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D26" t="s">
+        <v>492</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" t="s">
+        <v>176</v>
+      </c>
+      <c r="J26" t="s">
         <v>491</v>
       </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>174</v>
-      </c>
-      <c r="H26" t="s">
-        <v>175</v>
-      </c>
-      <c r="J26" t="s">
-        <v>490</v>
-      </c>
       <c r="K26" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11026,31 +11028,31 @@
     </row>
     <row r="27" spans="2:26">
       <c r="B27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D27" t="s">
+        <v>494</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" t="s">
         <v>493</v>
       </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>174</v>
-      </c>
-      <c r="H27" t="s">
-        <v>175</v>
-      </c>
-      <c r="J27" t="s">
-        <v>492</v>
-      </c>
       <c r="K27" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11061,31 +11063,31 @@
     </row>
     <row r="28" spans="2:26">
       <c r="B28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D28" t="s">
+        <v>496</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" t="s">
         <v>495</v>
       </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" t="s">
-        <v>174</v>
-      </c>
-      <c r="H28" t="s">
-        <v>175</v>
-      </c>
-      <c r="J28" t="s">
-        <v>494</v>
-      </c>
       <c r="K28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11096,31 +11098,31 @@
     </row>
     <row r="29" spans="2:26">
       <c r="B29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D29" t="s">
+        <v>498</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>176</v>
+      </c>
+      <c r="J29" t="s">
         <v>497</v>
       </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" t="s">
-        <v>174</v>
-      </c>
-      <c r="H29" t="s">
-        <v>175</v>
-      </c>
-      <c r="J29" t="s">
-        <v>496</v>
-      </c>
       <c r="K29" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11131,31 +11133,31 @@
     </row>
     <row r="30" spans="2:26">
       <c r="B30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D30" t="s">
+        <v>500</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" t="s">
         <v>499</v>
       </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" t="s">
-        <v>174</v>
-      </c>
-      <c r="H30" t="s">
-        <v>175</v>
-      </c>
-      <c r="J30" t="s">
-        <v>498</v>
-      </c>
       <c r="K30" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11166,31 +11168,31 @@
     </row>
     <row r="31" spans="2:26">
       <c r="B31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D31" t="s">
+        <v>502</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" t="s">
+        <v>176</v>
+      </c>
+      <c r="J31" t="s">
         <v>501</v>
       </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
-        <v>174</v>
-      </c>
-      <c r="H31" t="s">
-        <v>175</v>
-      </c>
-      <c r="J31" t="s">
-        <v>500</v>
-      </c>
       <c r="K31" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11201,31 +11203,31 @@
     </row>
     <row r="32" spans="2:26">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D32" t="s">
+        <v>504</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" t="s">
         <v>503</v>
       </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" t="s">
-        <v>174</v>
-      </c>
-      <c r="H32" t="s">
-        <v>175</v>
-      </c>
-      <c r="J32" t="s">
-        <v>502</v>
-      </c>
       <c r="K32" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="L32">
         <v>0.91282903432358287</v>
@@ -11236,31 +11238,31 @@
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D33" t="s">
+        <v>506</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" t="s">
+        <v>176</v>
+      </c>
+      <c r="J33" t="s">
         <v>505</v>
       </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" t="s">
-        <v>174</v>
-      </c>
-      <c r="H33" t="s">
-        <v>175</v>
-      </c>
-      <c r="J33" t="s">
-        <v>504</v>
-      </c>
       <c r="K33" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11275,27 +11277,27 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BF69055-77EA-49E8-933D-4AA3BAC4A4F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC636E1-AC5F-4C01-BCDA-DD05F46E15CB}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -11310,30 +11312,30 @@
         <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -11354,10 +11356,10 @@
         <v>146</v>
       </c>
       <c r="J11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -11366,15 +11368,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -11392,13 +11394,13 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -11407,15 +11409,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P12" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -11433,13 +11435,13 @@
         <v>4400</v>
       </c>
       <c r="H13" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -11448,15 +11450,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -11474,13 +11476,13 @@
         <v>155</v>
       </c>
       <c r="H14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -11489,15 +11491,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P14" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -11515,13 +11517,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -11530,15 +11532,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P15" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -11559,10 +11561,10 @@
         <v>146</v>
       </c>
       <c r="J16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -11571,15 +11573,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P16" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -11597,13 +11599,13 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -11612,15 +11614,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P17" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -11638,13 +11640,13 @@
         <v>2050</v>
       </c>
       <c r="H18" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K18" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -11653,15 +11655,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P18" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -11679,13 +11681,13 @@
         <v>70</v>
       </c>
       <c r="H19" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -11694,15 +11696,15 @@
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P19" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -11720,13 +11722,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -11735,15 +11737,15 @@
         <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P20" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -11764,10 +11766,10 @@
         <v>146</v>
       </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -11776,15 +11778,15 @@
         <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P21" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -11802,13 +11804,13 @@
         <v>700</v>
       </c>
       <c r="H22" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -11817,15 +11819,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P22" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -11843,13 +11845,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -11858,15 +11860,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -11887,10 +11889,10 @@
         <v>146</v>
       </c>
       <c r="J24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -11899,15 +11901,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P24" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -11925,13 +11927,13 @@
         <v>1850</v>
       </c>
       <c r="H25" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -11940,15 +11942,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P25" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -11966,13 +11968,13 @@
         <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -11981,15 +11983,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -12010,10 +12012,10 @@
         <v>146</v>
       </c>
       <c r="J27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -12022,15 +12024,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P27" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -12048,12 +12050,12 @@
         <v>3550</v>
       </c>
       <c r="H28" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -12071,12 +12073,12 @@
         <v>135</v>
       </c>
       <c r="H29" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -12099,7 +12101,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -12117,12 +12119,12 @@
         <v>400</v>
       </c>
       <c r="H31" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -12140,12 +12142,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -12168,7 +12170,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -12186,12 +12188,12 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -12209,12 +12211,12 @@
         <v>2100</v>
       </c>
       <c r="H35" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -12232,12 +12234,12 @@
         <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -12255,12 +12257,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -12283,7 +12285,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -12301,12 +12303,12 @@
         <v>2100</v>
       </c>
       <c r="H39" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -12324,12 +12326,12 @@
         <v>85</v>
       </c>
       <c r="H40" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -12352,7 +12354,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -12370,12 +12372,12 @@
         <v>4200</v>
       </c>
       <c r="H42" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -12393,12 +12395,12 @@
         <v>190</v>
       </c>
       <c r="H43" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -12421,7 +12423,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -12439,12 +12441,12 @@
         <v>4000</v>
       </c>
       <c r="H45" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -12462,12 +12464,12 @@
         <v>170</v>
       </c>
       <c r="H46" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -12490,7 +12492,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -12508,12 +12510,12 @@
         <v>4300</v>
       </c>
       <c r="H48" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -12531,12 +12533,12 @@
         <v>165</v>
       </c>
       <c r="H49" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -12559,7 +12561,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -12577,12 +12579,12 @@
         <v>0.23</v>
       </c>
       <c r="H51" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -12600,12 +12602,12 @@
         <v>550</v>
       </c>
       <c r="H52" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -12623,12 +12625,12 @@
         <v>18</v>
       </c>
       <c r="H53" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -12646,12 +12648,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -12674,7 +12676,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -12692,12 +12694,12 @@
         <v>1300</v>
       </c>
       <c r="H56" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -12715,12 +12717,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -12743,7 +12745,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -12761,12 +12763,12 @@
         <v>1600</v>
       </c>
       <c r="H59" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -12784,12 +12786,12 @@
         <v>55</v>
       </c>
       <c r="H60" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -12812,7 +12814,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -12830,12 +12832,12 @@
         <v>1900</v>
       </c>
       <c r="H62" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -12853,15 +12855,15 @@
         <v>70</v>
       </c>
       <c r="H63" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C64" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -12881,10 +12883,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C65" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -12899,15 +12901,15 @@
         <v>0.43</v>
       </c>
       <c r="H65" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C66" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -12922,15 +12924,15 @@
         <v>2200</v>
       </c>
       <c r="H66" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C67" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -12945,15 +12947,15 @@
         <v>65</v>
       </c>
       <c r="H67" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C68" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -12968,15 +12970,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
+        <v>548</v>
+      </c>
+      <c r="C69" t="s">
         <v>547</v>
-      </c>
-      <c r="C69" t="s">
-        <v>546</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -12996,10 +12998,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
+        <v>548</v>
+      </c>
+      <c r="C70" t="s">
         <v>547</v>
-      </c>
-      <c r="C70" t="s">
-        <v>546</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -13014,15 +13016,15 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H70" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
+        <v>548</v>
+      </c>
+      <c r="C71" t="s">
         <v>547</v>
-      </c>
-      <c r="C71" t="s">
-        <v>546</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -13037,15 +13039,15 @@
         <v>1470</v>
       </c>
       <c r="H71" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
+        <v>548</v>
+      </c>
+      <c r="C72" t="s">
         <v>547</v>
-      </c>
-      <c r="C72" t="s">
-        <v>546</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -13060,15 +13062,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
+        <v>548</v>
+      </c>
+      <c r="C73" t="s">
         <v>547</v>
-      </c>
-      <c r="C73" t="s">
-        <v>546</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -13083,7 +13085,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -13092,71 +13094,71 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A016208B-F00E-4A3B-87C6-306099EC4899}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342F0A77-7A91-42A0-9425-075527803B08}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="2" spans="2:13">
       <c r="B2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="2:13">
       <c r="B3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E3" t="s">
         <v>146</v>
       </c>
       <c r="H3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:13">
       <c r="B4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -13165,30 +13167,30 @@
         <v>10</v>
       </c>
       <c r="M4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
+        <v>553</v>
+      </c>
+      <c r="C5" t="s">
         <v>552</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>551</v>
-      </c>
-      <c r="D5" t="s">
-        <v>550</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
@@ -13197,30 +13199,30 @@
         <v>10</v>
       </c>
       <c r="M5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C6" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -13229,30 +13231,30 @@
         <v>10</v>
       </c>
       <c r="M6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
+        <v>557</v>
+      </c>
+      <c r="C7" t="s">
         <v>556</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>555</v>
-      </c>
-      <c r="D7" t="s">
-        <v>554</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J7" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -13261,30 +13263,30 @@
         <v>10</v>
       </c>
       <c r="M7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D8" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -13293,30 +13295,30 @@
         <v>10</v>
       </c>
       <c r="M8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
+        <v>561</v>
+      </c>
+      <c r="C9" t="s">
         <v>560</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>559</v>
-      </c>
-      <c r="D9" t="s">
-        <v>558</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I9" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J9" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
@@ -13325,30 +13327,30 @@
         <v>10</v>
       </c>
       <c r="M9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C10" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D10" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I10" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -13357,30 +13359,30 @@
         <v>10</v>
       </c>
       <c r="M10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
+        <v>565</v>
+      </c>
+      <c r="C11" t="s">
         <v>564</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>563</v>
-      </c>
-      <c r="D11" t="s">
-        <v>562</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K11" t="s">
         <v>21</v>
@@ -13389,30 +13391,30 @@
         <v>10</v>
       </c>
       <c r="M11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D12" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I12" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -13421,30 +13423,30 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
+        <v>569</v>
+      </c>
+      <c r="C13" t="s">
         <v>568</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>567</v>
-      </c>
-      <c r="D13" t="s">
-        <v>566</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I13" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J13" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K13" t="s">
         <v>21</v>
@@ -13453,7 +13455,7 @@
         <v>10</v>
       </c>
       <c r="M13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{341E9D6A-24FD-46D1-BEF7-9C5AC83BD681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8CE3008-95E4-4F88-A4A1-71324C35A4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -925,18 +925,120 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_011</t>
   </si>
   <si>
@@ -955,40 +1057,34 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_solelc_spv_024</t>
@@ -997,114 +1093,60 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_019</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
     <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
   </si>
   <si>
@@ -1117,58 +1159,88 @@
     <t>e_w659874569-220,e_w660091166-220</t>
   </si>
   <si>
-    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
+    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
   </si>
   <si>
     <t>e_w669520367-220,e_w563813243-400</t>
   </si>
   <si>
-    <t>e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
-  </si>
-  <si>
     <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
   </si>
   <si>
-    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_018</t>
@@ -1195,16 +1267,34 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1219,102 +1309,66 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w579310367-220</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_KE12-400</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
   </si>
   <si>
     <t>elc_won_018</t>
   </si>
   <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
     <t>elc_won_015</t>
   </si>
   <si>
@@ -1327,13 +1381,28 @@
     <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE11-220</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
   </si>
   <si>
     <t>elc_won_011</t>
@@ -1342,73 +1411,34 @@
     <t>elc_won_007</t>
   </si>
   <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE11-220</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_KE12-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wofelc_wof_009</t>
@@ -1417,58 +1447,46 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_KE15-220</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
   </si>
   <si>
     <t>elc_wof_009</t>
@@ -1477,40 +1495,22 @@
     <t>e_w953567827-220,e_w660091166-220</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
     <t>elc_wof_007</t>
   </si>
   <si>
     <t>e_w953567827-220</t>
   </si>
   <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_KE15-220</t>
-  </si>
-  <si>
     <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6608,7 +6608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3059D9-31E7-44EA-8877-86CF7FA16AD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F47AC72-BDE0-433E-BDFF-EA4F2724E736}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6846,16 +6846,16 @@
         <v>265</v>
       </c>
       <c r="Y11" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="Z11" t="s">
         <v>325</v>
       </c>
       <c r="AA11">
-        <v>0.99787844392938518</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB11">
-        <v>38.895194627939205</v>
+        <v>74.690879958909605</v>
       </c>
       <c r="AD11" t="s">
         <v>264</v>
@@ -6885,13 +6885,13 @@
         <v>393</v>
       </c>
       <c r="AN11" t="s">
-        <v>394</v>
+        <v>329</v>
       </c>
       <c r="AO11">
-        <v>0.98870306310272893</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP11">
-        <v>207.11050978330246</v>
+        <v>463.38269175414888</v>
       </c>
       <c r="AR11" t="s">
         <v>264</v>
@@ -6924,10 +6924,10 @@
         <v>448</v>
       </c>
       <c r="BC11">
-        <v>0.99567841910080701</v>
+        <v>0.99504452373263619</v>
       </c>
       <c r="BD11">
-        <v>79.228983151871589</v>
+        <v>90.850398235003013</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6992,16 +6992,16 @@
         <v>269</v>
       </c>
       <c r="Y12" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="Z12" t="s">
         <v>326</v>
       </c>
       <c r="AA12">
-        <v>0.99219647908939179</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB12">
-        <v>143.06455002781746</v>
+        <v>353.97634871689564</v>
       </c>
       <c r="AD12" t="s">
         <v>264</v>
@@ -7028,16 +7028,16 @@
         <v>349</v>
       </c>
       <c r="AM12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AN12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AO12">
-        <v>0.98667278207972509</v>
+        <v>0.99228583594785691</v>
       </c>
       <c r="AP12">
-        <v>244.33232853837262</v>
+        <v>141.42634095595602</v>
       </c>
       <c r="AR12" t="s">
         <v>264</v>
@@ -7067,13 +7067,13 @@
         <v>449</v>
       </c>
       <c r="BB12" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="BC12">
-        <v>0.99264898847830307</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD12">
-        <v>134.76854456444406</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7138,16 +7138,16 @@
         <v>271</v>
       </c>
       <c r="Y13" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Z13" t="s">
         <v>327</v>
       </c>
       <c r="AA13">
-        <v>0.99199432528561049</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB13">
-        <v>146.77070309714048</v>
+        <v>179.25118814130403</v>
       </c>
       <c r="AD13" t="s">
         <v>264</v>
@@ -7174,16 +7174,16 @@
         <v>351</v>
       </c>
       <c r="AM13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AN13" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="AO13">
-        <v>0.98615336674947807</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP13">
-        <v>253.85494292623497</v>
+        <v>199.81501642792259</v>
       </c>
       <c r="AR13" t="s">
         <v>264</v>
@@ -7210,16 +7210,16 @@
         <v>431</v>
       </c>
       <c r="BA13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="BB13" t="s">
-        <v>452</v>
+        <v>327</v>
       </c>
       <c r="BC13">
-        <v>0.99722114454285371</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD13">
-        <v>50.94568338101594</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7284,16 +7284,16 @@
         <v>273</v>
       </c>
       <c r="Y14" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="Z14" t="s">
         <v>328</v>
       </c>
       <c r="AA14">
-        <v>0.99686513787774389</v>
+        <v>0.99782085777346563</v>
       </c>
       <c r="AB14">
-        <v>57.472472241362951</v>
+        <v>39.950940819796543</v>
       </c>
       <c r="AD14" t="s">
         <v>264</v>
@@ -7320,16 +7320,16 @@
         <v>353</v>
       </c>
       <c r="AM14" t="s">
+        <v>396</v>
+      </c>
+      <c r="AN14" t="s">
         <v>397</v>
       </c>
-      <c r="AN14" t="s">
-        <v>398</v>
-      </c>
       <c r="AO14">
-        <v>0.99458682795119768</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP14">
-        <v>99.241487561376104</v>
+        <v>428.87734626058102</v>
       </c>
       <c r="AR14" t="s">
         <v>264</v>
@@ -7356,16 +7356,16 @@
         <v>433</v>
       </c>
       <c r="BA14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="BB14" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="BC14">
-        <v>0.99660062084319445</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD14">
-        <v>62.321951208100806</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7430,16 +7430,16 @@
         <v>275</v>
       </c>
       <c r="Y15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z15" t="s">
         <v>329</v>
       </c>
       <c r="AA15">
-        <v>0.99782085777346563</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB15">
-        <v>39.950940819796543</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD15" t="s">
         <v>264</v>
@@ -7466,16 +7466,16 @@
         <v>355</v>
       </c>
       <c r="AM15" t="s">
+        <v>398</v>
+      </c>
+      <c r="AN15" t="s">
         <v>399</v>
       </c>
-      <c r="AN15" t="s">
-        <v>335</v>
-      </c>
       <c r="AO15">
-        <v>0.98910099910393146</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP15">
-        <v>199.81501642792259</v>
+        <v>314.22828490220974</v>
       </c>
       <c r="AR15" t="s">
         <v>264</v>
@@ -7502,16 +7502,16 @@
         <v>435</v>
       </c>
       <c r="BA15" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="BB15" t="s">
-        <v>455</v>
+        <v>327</v>
       </c>
       <c r="BC15">
-        <v>0.99504452373263619</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD15">
-        <v>90.850398235003013</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7576,16 +7576,16 @@
         <v>277</v>
       </c>
       <c r="Y16" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Z16" t="s">
         <v>330</v>
       </c>
       <c r="AA16">
-        <v>0.98497581152539015</v>
+        <v>0.99806216160693018</v>
       </c>
       <c r="AB16">
-        <v>275.44345536784743</v>
+        <v>35.52703720627968</v>
       </c>
       <c r="AD16" t="s">
         <v>264</v>
@@ -7618,10 +7618,10 @@
         <v>401</v>
       </c>
       <c r="AO16">
-        <v>0.97660669020396829</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP16">
-        <v>428.87734626058102</v>
+        <v>47.407781945483563</v>
       </c>
       <c r="AR16" t="s">
         <v>264</v>
@@ -7648,16 +7648,16 @@
         <v>437</v>
       </c>
       <c r="BA16" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="BB16" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="BC16">
-        <v>0.99790507974591136</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD16">
-        <v>38.406871324958367</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7722,16 +7722,16 @@
         <v>279</v>
       </c>
       <c r="Y17" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Z17" t="s">
         <v>331</v>
       </c>
       <c r="AA17">
-        <v>0.99021329006024306</v>
+        <v>0.99594698839866214</v>
       </c>
       <c r="AB17">
-        <v>179.42301556221076</v>
+        <v>74.305212691194157</v>
       </c>
       <c r="AD17" t="s">
         <v>264</v>
@@ -7761,13 +7761,13 @@
         <v>402</v>
       </c>
       <c r="AN17" t="s">
-        <v>330</v>
+        <v>403</v>
       </c>
       <c r="AO17">
-        <v>0.98907459074885506</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP17">
-        <v>200.2991696043234</v>
+        <v>263.43637771155954</v>
       </c>
       <c r="AR17" t="s">
         <v>264</v>
@@ -7794,16 +7794,16 @@
         <v>439</v>
       </c>
       <c r="BA17" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="BB17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BC17">
-        <v>0.99630507039782612</v>
+        <v>0.99417680250918639</v>
       </c>
       <c r="BD17">
-        <v>67.740376039854553</v>
+        <v>106.75862066491723</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7868,16 +7868,16 @@
         <v>281</v>
       </c>
       <c r="Y18" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="Z18" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AA18">
-        <v>0.99117807442989492</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB18">
-        <v>161.73530211859338</v>
+        <v>461.61265467993644</v>
       </c>
       <c r="AD18" t="s">
         <v>264</v>
@@ -7904,16 +7904,16 @@
         <v>361</v>
       </c>
       <c r="AM18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN18" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AO18">
-        <v>0.98670016097490887</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP18">
-        <v>243.83038212667131</v>
+        <v>172.45708572867548</v>
       </c>
       <c r="AR18" t="s">
         <v>264</v>
@@ -7940,16 +7940,16 @@
         <v>441</v>
       </c>
       <c r="BA18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="BB18" t="s">
-        <v>337</v>
+        <v>456</v>
       </c>
       <c r="BC18">
-        <v>0.99749257613418407</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD18">
-        <v>45.969437539958705</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8017,7 +8017,7 @@
         <v>255</v>
       </c>
       <c r="Z19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AA19">
         <v>0.99515835423076238</v>
@@ -8050,16 +8050,16 @@
         <v>363</v>
       </c>
       <c r="AM19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN19" t="s">
-        <v>330</v>
+        <v>406</v>
       </c>
       <c r="AO19">
-        <v>0.97472458044977373</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP19">
-        <v>463.38269175414888</v>
+        <v>100.3265162100753</v>
       </c>
       <c r="AR19" t="s">
         <v>264</v>
@@ -8086,16 +8086,16 @@
         <v>443</v>
       </c>
       <c r="BA19" t="s">
+        <v>458</v>
+      </c>
+      <c r="BB19" t="s">
         <v>459</v>
       </c>
-      <c r="BB19" t="s">
-        <v>337</v>
-      </c>
       <c r="BC19">
-        <v>0.9940284706913598</v>
+        <v>0.99264898847830307</v>
       </c>
       <c r="BD19">
-        <v>109.47803732507046</v>
+        <v>134.76854456444406</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8163,7 +8163,7 @@
         <v>260</v>
       </c>
       <c r="Z20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AA20">
         <v>0.99312290929392577</v>
@@ -8196,16 +8196,16 @@
         <v>365</v>
       </c>
       <c r="AM20" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AN20" t="s">
-        <v>406</v>
+        <v>329</v>
       </c>
       <c r="AO20">
-        <v>0.99740231224454534</v>
+        <v>0.99675250681341587</v>
       </c>
       <c r="AP20">
-        <v>47.624275516669421</v>
+        <v>59.537375087375146</v>
       </c>
       <c r="AR20" t="s">
         <v>264</v>
@@ -8235,13 +8235,13 @@
         <v>460</v>
       </c>
       <c r="BB20" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BC20">
-        <v>0.99417680250918639</v>
+        <v>0.99790507974591136</v>
       </c>
       <c r="BD20">
-        <v>106.75862066491723</v>
+        <v>38.406871324958367</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8306,16 +8306,16 @@
         <v>287</v>
       </c>
       <c r="Y21" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="Z21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AA21">
-        <v>0.99184104324003575</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB21">
-        <v>149.58087393267732</v>
+        <v>32.188603269438353</v>
       </c>
       <c r="AD21" t="s">
         <v>264</v>
@@ -8342,16 +8342,16 @@
         <v>367</v>
       </c>
       <c r="AM21" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN21" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO21">
-        <v>0.99452764457035958</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP21">
-        <v>100.3265162100753</v>
+        <v>151.6999940525175</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8419,7 +8419,7 @@
         <v>257</v>
       </c>
       <c r="Z22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AA22">
         <v>0.98551105518500948</v>
@@ -8452,16 +8452,16 @@
         <v>369</v>
       </c>
       <c r="AM22" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN22" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="AO22">
-        <v>0.99675250681341587</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP22">
-        <v>59.537375087375146</v>
+        <v>118.22451183716133</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8529,7 +8529,7 @@
         <v>236</v>
       </c>
       <c r="Z23" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="AA23">
         <v>0.99326495911353319</v>
@@ -8562,16 +8562,16 @@
         <v>371</v>
       </c>
       <c r="AM23" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN23" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="AO23">
-        <v>0.99172545486986263</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP23">
-        <v>151.6999940525175</v>
+        <v>207.11050978330246</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8636,16 +8636,16 @@
         <v>293</v>
       </c>
       <c r="Y24" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="Z24" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AA24">
-        <v>0.99327889425386662</v>
+        <v>0.99021329006024306</v>
       </c>
       <c r="AB24">
-        <v>123.22027201244609</v>
+        <v>179.42301556221076</v>
       </c>
       <c r="AD24" t="s">
         <v>264</v>
@@ -8672,16 +8672,16 @@
         <v>373</v>
       </c>
       <c r="AM24" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN24" t="s">
-        <v>413</v>
+        <v>336</v>
       </c>
       <c r="AO24">
-        <v>0.99567808239070055</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP24">
-        <v>79.235156170489844</v>
+        <v>244.33232853837262</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8746,16 +8746,16 @@
         <v>295</v>
       </c>
       <c r="Y25" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="Z25" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AA25">
-        <v>0.98440782007749728</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB25">
-        <v>285.85663191255094</v>
+        <v>161.73530211859338</v>
       </c>
       <c r="AD25" t="s">
         <v>264</v>
@@ -8785,13 +8785,13 @@
         <v>414</v>
       </c>
       <c r="AN25" t="s">
-        <v>394</v>
+        <v>329</v>
       </c>
       <c r="AO25">
-        <v>0.99330365963041267</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP25">
-        <v>122.76624010910177</v>
+        <v>253.85494292623497</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8856,16 +8856,16 @@
         <v>297</v>
       </c>
       <c r="Y26" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="Z26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AA26">
-        <v>0.99585076637156988</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB26">
-        <v>76.069283187886086</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD26" t="s">
         <v>264</v>
@@ -8898,10 +8898,10 @@
         <v>416</v>
       </c>
       <c r="AO26">
-        <v>0.9934827767968939</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP26">
-        <v>119.4824253902779</v>
+        <v>99.241487561376104</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8966,16 +8966,16 @@
         <v>299</v>
       </c>
       <c r="Y27" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="Z27" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AA27">
-        <v>0.9893494724125782</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB27">
-        <v>195.2596724360663</v>
+        <v>285.85663191255094</v>
       </c>
       <c r="AD27" t="s">
         <v>264</v>
@@ -9005,13 +9005,13 @@
         <v>417</v>
       </c>
       <c r="AN27" t="s">
-        <v>330</v>
+        <v>418</v>
       </c>
       <c r="AO27">
-        <v>0.99486941977940613</v>
+        <v>0.99567808239070055</v>
       </c>
       <c r="AP27">
-        <v>94.060637377553505</v>
+        <v>79.235156170489844</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9076,16 +9076,16 @@
         <v>301</v>
       </c>
       <c r="Y28" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="Z28" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="AA28">
-        <v>0.97548412543178475</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB28">
-        <v>449.45770041728053</v>
+        <v>38.895194627939205</v>
       </c>
       <c r="AD28" t="s">
         <v>264</v>
@@ -9112,16 +9112,16 @@
         <v>381</v>
       </c>
       <c r="AM28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN28" t="s">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="AO28">
-        <v>0.99228583594785691</v>
+        <v>0.9934827767968939</v>
       </c>
       <c r="AP28">
-        <v>141.42634095595602</v>
+        <v>119.4824253902779</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9186,16 +9186,16 @@
         <v>303</v>
       </c>
       <c r="Y29" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="Z29" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AA29">
-        <v>0.96747189690815383</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB29">
-        <v>596.34855668384682</v>
+        <v>143.06455002781746</v>
       </c>
       <c r="AD29" t="s">
         <v>264</v>
@@ -9222,16 +9222,16 @@
         <v>383</v>
       </c>
       <c r="AM29" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN29" t="s">
-        <v>394</v>
+        <v>329</v>
       </c>
       <c r="AO29">
-        <v>0.98286027536897036</v>
+        <v>0.99486941977940613</v>
       </c>
       <c r="AP29">
-        <v>314.22828490220974</v>
+        <v>94.060637377553505</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9296,16 +9296,16 @@
         <v>305</v>
       </c>
       <c r="Y30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z30" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA30">
-        <v>0.99260409516666881</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB30">
-        <v>135.59158861107267</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD30" t="s">
         <v>264</v>
@@ -9332,16 +9332,16 @@
         <v>385</v>
       </c>
       <c r="AM30" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AN30" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="AO30">
-        <v>0.99741412098479176</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP30">
-        <v>47.407781945483563</v>
+        <v>122.76624010910177</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9406,16 +9406,16 @@
         <v>307</v>
       </c>
       <c r="Y31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z31" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AA31">
-        <v>0.99022266246501978</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB31">
-        <v>179.25118814130403</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD31" t="s">
         <v>264</v>
@@ -9442,16 +9442,16 @@
         <v>387</v>
       </c>
       <c r="AM31" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN31" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO31">
-        <v>0.98563074303391496</v>
+        <v>0.99740231224454534</v>
       </c>
       <c r="AP31">
-        <v>263.43637771155954</v>
+        <v>47.624275516669421</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9516,16 +9516,16 @@
         <v>309</v>
       </c>
       <c r="Y32" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Z32" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA32">
-        <v>0.99594698839866214</v>
+        <v>0.99585076637156988</v>
       </c>
       <c r="AB32">
-        <v>74.305212691194157</v>
+        <v>76.069283187886086</v>
       </c>
       <c r="AD32" t="s">
         <v>264</v>
@@ -9552,16 +9552,16 @@
         <v>389</v>
       </c>
       <c r="AM32" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN32" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="AO32">
-        <v>0.99059324986934494</v>
+        <v>0.98907459074885506</v>
       </c>
       <c r="AP32">
-        <v>172.45708572867548</v>
+        <v>200.2991696043234</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9626,16 +9626,16 @@
         <v>311</v>
       </c>
       <c r="Y33" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="Z33" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AA33">
-        <v>0.97482112792654896</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB33">
-        <v>461.61265467993644</v>
+        <v>195.2596724360663</v>
       </c>
       <c r="AD33" t="s">
         <v>264</v>
@@ -9662,16 +9662,16 @@
         <v>391</v>
       </c>
       <c r="AM33" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN33" t="s">
-        <v>426</v>
+        <v>345</v>
       </c>
       <c r="AO33">
-        <v>0.99355139026342754</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP33">
-        <v>118.22451183716133</v>
+        <v>243.83038212667131</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9736,16 +9736,16 @@
         <v>313</v>
       </c>
       <c r="Y34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Z34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA34">
-        <v>0.99806216160693018</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB34">
-        <v>35.52703720627968</v>
+        <v>449.45770041728053</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9810,16 +9810,16 @@
         <v>315</v>
       </c>
       <c r="Y35" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="Z35" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="AA35">
-        <v>0.99065498411395791</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB35">
-        <v>171.32529124410425</v>
+        <v>596.34855668384682</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9884,16 +9884,16 @@
         <v>317</v>
       </c>
       <c r="Y36" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="Z36" t="s">
         <v>344</v>
       </c>
       <c r="AA36">
-        <v>0.99592595200224132</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB36">
-        <v>74.690879958909605</v>
+        <v>171.32529124410425</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9958,16 +9958,16 @@
         <v>319</v>
       </c>
       <c r="Y37" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z37" t="s">
         <v>345</v>
       </c>
       <c r="AA37">
-        <v>0.98069219916089656</v>
+        <v>0.99184104324003575</v>
       </c>
       <c r="AB37">
-        <v>353.97634871689564</v>
+        <v>149.58087393267732</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10032,16 +10032,16 @@
         <v>321</v>
       </c>
       <c r="Y38" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="Z38" t="s">
         <v>346</v>
       </c>
       <c r="AA38">
-        <v>0.99824425800348515</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB38">
-        <v>32.188603269438353</v>
+        <v>135.59158861107267</v>
       </c>
     </row>
   </sheetData>
@@ -10050,7 +10050,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCA6FEA-1908-4EC7-8DF7-23959AF69E01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE379407-5312-42FE-BB0E-39B7431E15DA}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10162,7 +10162,7 @@
         <v>461</v>
       </c>
       <c r="K11" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10195,7 +10195,7 @@
         <v>507</v>
       </c>
       <c r="X11" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="Y11">
         <v>8.3782499999999995</v>
@@ -10230,7 +10230,7 @@
         <v>463</v>
       </c>
       <c r="K12" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10263,7 +10263,7 @@
         <v>509</v>
       </c>
       <c r="X12" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10298,7 +10298,7 @@
         <v>465</v>
       </c>
       <c r="K13" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="L13">
         <v>1.5817501567892978</v>
@@ -10331,7 +10331,7 @@
         <v>511</v>
       </c>
       <c r="X13" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10366,7 +10366,7 @@
         <v>467</v>
       </c>
       <c r="K14" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10399,7 +10399,7 @@
         <v>513</v>
       </c>
       <c r="X14" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10434,7 +10434,7 @@
         <v>469</v>
       </c>
       <c r="K15" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10467,7 +10467,7 @@
         <v>515</v>
       </c>
       <c r="X15" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10502,7 +10502,7 @@
         <v>471</v>
       </c>
       <c r="K16" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10535,7 +10535,7 @@
         <v>517</v>
       </c>
       <c r="X16" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10570,7 +10570,7 @@
         <v>473</v>
       </c>
       <c r="K17" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10603,7 +10603,7 @@
         <v>519</v>
       </c>
       <c r="X17" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="Y17">
         <v>2.2530000000000001</v>
@@ -10638,7 +10638,7 @@
         <v>475</v>
       </c>
       <c r="K18" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10671,7 +10671,7 @@
         <v>521</v>
       </c>
       <c r="X18" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="Y18">
         <v>6.1852499999999999</v>
@@ -10706,7 +10706,7 @@
         <v>477</v>
       </c>
       <c r="K19" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10739,7 +10739,7 @@
         <v>523</v>
       </c>
       <c r="X19" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="Y19">
         <v>10.093500000000001</v>
@@ -10774,7 +10774,7 @@
         <v>479</v>
       </c>
       <c r="K20" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10807,7 +10807,7 @@
         <v>525</v>
       </c>
       <c r="X20" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10842,7 +10842,7 @@
         <v>481</v>
       </c>
       <c r="K21" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="L21">
         <v>15.316017274089829</v>
@@ -10877,7 +10877,7 @@
         <v>483</v>
       </c>
       <c r="K22" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10912,7 +10912,7 @@
         <v>485</v>
       </c>
       <c r="K23" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="L23">
         <v>15.32235174795542</v>
@@ -10947,7 +10947,7 @@
         <v>487</v>
       </c>
       <c r="K24" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="L24">
         <v>4.3876485804695786</v>
@@ -10982,7 +10982,7 @@
         <v>489</v>
       </c>
       <c r="K25" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -11017,7 +11017,7 @@
         <v>491</v>
       </c>
       <c r="K26" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11052,7 +11052,7 @@
         <v>493</v>
       </c>
       <c r="K27" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11087,7 +11087,7 @@
         <v>495</v>
       </c>
       <c r="K28" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11122,7 +11122,7 @@
         <v>497</v>
       </c>
       <c r="K29" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11157,7 +11157,7 @@
         <v>499</v>
       </c>
       <c r="K30" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11192,7 +11192,7 @@
         <v>501</v>
       </c>
       <c r="K31" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11227,7 +11227,7 @@
         <v>503</v>
       </c>
       <c r="K32" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="L32">
         <v>0.91282903432358287</v>
@@ -11262,7 +11262,7 @@
         <v>505</v>
       </c>
       <c r="K33" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11277,7 +11277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC636E1-AC5F-4C01-BCDA-DD05F46E15CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D541C4-B5F7-4C08-ABC3-942735393EAB}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13094,7 +13094,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342F0A77-7A91-42A0-9425-075527803B08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E71618F-49E2-40CF-8294-1E14C144E20A}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8CE3008-95E4-4F88-A4A1-71324C35A4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B403CA9-0D78-4998-B409-128C102E9753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -925,18 +925,30 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_025</t>
   </si>
   <si>
@@ -949,6 +961,36 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_012</t>
   </si>
   <si>
@@ -961,6 +1003,42 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_017</t>
   </si>
   <si>
@@ -979,46 +1057,10 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_solelc_spv_018</t>
@@ -1033,30 +1075,6 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_007</t>
   </si>
   <si>
@@ -1081,30 +1099,18 @@
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_KE14-400,e_KE13-400</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
+  </si>
+  <si>
     <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
   </si>
   <si>
@@ -1114,61 +1120,85 @@
     <t>e_w660091166-220</t>
   </si>
   <si>
+    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220,e_KE7-220</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w659874569-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
     <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
   </si>
   <si>
     <t>e_w563813243-400</t>
   </si>
   <si>
+    <t>e_w669520367-220</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
+  </si>
+  <si>
+    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
+  </si>
+  <si>
     <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
   </si>
   <si>
     <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
   </si>
   <si>
-    <t>e_KE14-400,e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
+    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
   </si>
   <si>
     <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
   </si>
   <si>
-    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE7-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
     <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
   </si>
   <si>
-    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_009</t>
@@ -1183,16 +1213,58 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wonelc_won_017</t>
@@ -1219,22 +1291,16 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_002</t>
@@ -1243,70 +1309,28 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_KE14-400,e_w870818913-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
   </si>
   <si>
     <t>elc_won_009</t>
@@ -1315,21 +1339,51 @@
     <t>elc_won_013</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w579310367-220</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_KE13-400,e_KE11-220</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
   </si>
   <si>
     <t>elc_won_017</t>
   </si>
   <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
     <t>elc_won_023</t>
   </si>
   <si>
@@ -1345,19 +1399,10 @@
     <t>elc_won_005</t>
   </si>
   <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220</t>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
   </si>
   <si>
     <t>elc_won_002</t>
@@ -1366,57 +1411,24 @@
     <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
   </si>
   <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE11-220</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_002</t>
   </si>
   <si>
@@ -1429,88 +1441,76 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_010</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
     <t>e_KE15-220</t>
   </si>
   <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w953567827-220</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w953567827-220,e_w660091166-220</t>
+  </si>
+  <si>
     <t>elc_wof_002</t>
   </si>
   <si>
     <t>elc_wof_005</t>
   </si>
   <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220,e_w953567827-220</t>
+  </si>
+  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
     <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6608,7 +6608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F47AC72-BDE0-433E-BDFF-EA4F2724E736}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0574C0-F120-4EB9-9433-2723E5FA8A91}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6846,16 +6846,16 @@
         <v>265</v>
       </c>
       <c r="Y11" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="Z11" t="s">
         <v>325</v>
       </c>
       <c r="AA11">
-        <v>0.99592595200224132</v>
+        <v>0.99515835423076238</v>
       </c>
       <c r="AB11">
-        <v>74.690879958909605</v>
+        <v>88.763505769357138</v>
       </c>
       <c r="AD11" t="s">
         <v>264</v>
@@ -6885,13 +6885,13 @@
         <v>393</v>
       </c>
       <c r="AN11" t="s">
-        <v>329</v>
+        <v>394</v>
       </c>
       <c r="AO11">
-        <v>0.97472458044977373</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP11">
-        <v>463.38269175414888</v>
+        <v>100.3265162100753</v>
       </c>
       <c r="AR11" t="s">
         <v>264</v>
@@ -6992,16 +6992,16 @@
         <v>269</v>
       </c>
       <c r="Y12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z12" t="s">
         <v>326</v>
       </c>
       <c r="AA12">
-        <v>0.98069219916089656</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB12">
-        <v>353.97634871689564</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD12" t="s">
         <v>264</v>
@@ -7028,16 +7028,16 @@
         <v>349</v>
       </c>
       <c r="AM12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN12" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AO12">
-        <v>0.99228583594785691</v>
+        <v>0.99675250681341587</v>
       </c>
       <c r="AP12">
-        <v>141.42634095595602</v>
+        <v>59.537375087375146</v>
       </c>
       <c r="AR12" t="s">
         <v>264</v>
@@ -7067,13 +7067,13 @@
         <v>449</v>
       </c>
       <c r="BB12" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BC12">
-        <v>0.99630507039782612</v>
+        <v>0.99264898847830307</v>
       </c>
       <c r="BD12">
-        <v>67.740376039854553</v>
+        <v>134.76854456444406</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7138,16 +7138,16 @@
         <v>271</v>
       </c>
       <c r="Y13" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="Z13" t="s">
         <v>327</v>
       </c>
       <c r="AA13">
-        <v>0.99022266246501978</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB13">
-        <v>179.25118814130403</v>
+        <v>74.690879958909605</v>
       </c>
       <c r="AD13" t="s">
         <v>264</v>
@@ -7174,16 +7174,16 @@
         <v>351</v>
       </c>
       <c r="AM13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN13" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="AO13">
-        <v>0.98910099910393146</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP13">
-        <v>199.81501642792259</v>
+        <v>151.6999940525175</v>
       </c>
       <c r="AR13" t="s">
         <v>264</v>
@@ -7210,16 +7210,16 @@
         <v>431</v>
       </c>
       <c r="BA13" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="BB13" t="s">
-        <v>327</v>
+        <v>452</v>
       </c>
       <c r="BC13">
-        <v>0.99749257613418407</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD13">
-        <v>45.969437539958705</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7284,16 +7284,16 @@
         <v>273</v>
       </c>
       <c r="Y14" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="Z14" t="s">
         <v>328</v>
       </c>
       <c r="AA14">
-        <v>0.99782085777346563</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB14">
-        <v>39.950940819796543</v>
+        <v>353.97634871689564</v>
       </c>
       <c r="AD14" t="s">
         <v>264</v>
@@ -7320,16 +7320,16 @@
         <v>353</v>
       </c>
       <c r="AM14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AN14" t="s">
-        <v>397</v>
+        <v>334</v>
       </c>
       <c r="AO14">
-        <v>0.97660669020396829</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP14">
-        <v>428.87734626058102</v>
+        <v>199.81501642792259</v>
       </c>
       <c r="AR14" t="s">
         <v>264</v>
@@ -7356,16 +7356,16 @@
         <v>433</v>
       </c>
       <c r="BA14" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BB14" t="s">
-        <v>327</v>
+        <v>448</v>
       </c>
       <c r="BC14">
-        <v>0.9940284706913598</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD14">
-        <v>109.47803732507046</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7430,16 +7430,16 @@
         <v>275</v>
       </c>
       <c r="Y15" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="Z15" t="s">
         <v>329</v>
       </c>
       <c r="AA15">
-        <v>0.98497581152539015</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB15">
-        <v>275.44345536784743</v>
+        <v>179.25118814130403</v>
       </c>
       <c r="AD15" t="s">
         <v>264</v>
@@ -7466,16 +7466,16 @@
         <v>355</v>
       </c>
       <c r="AM15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN15" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO15">
-        <v>0.98286027536897036</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP15">
-        <v>314.22828490220974</v>
+        <v>428.87734626058102</v>
       </c>
       <c r="AR15" t="s">
         <v>264</v>
@@ -7502,16 +7502,16 @@
         <v>435</v>
       </c>
       <c r="BA15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BB15" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BC15">
-        <v>0.99660062084319445</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD15">
-        <v>62.321951208100806</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7576,16 +7576,16 @@
         <v>277</v>
       </c>
       <c r="Y16" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="Z16" t="s">
         <v>330</v>
       </c>
       <c r="AA16">
-        <v>0.99806216160693018</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB16">
-        <v>35.52703720627968</v>
+        <v>38.895194627939205</v>
       </c>
       <c r="AD16" t="s">
         <v>264</v>
@@ -7612,16 +7612,16 @@
         <v>357</v>
       </c>
       <c r="AM16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN16" t="s">
-        <v>401</v>
+        <v>336</v>
       </c>
       <c r="AO16">
-        <v>0.99741412098479176</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP16">
-        <v>47.407781945483563</v>
+        <v>463.38269175414888</v>
       </c>
       <c r="AR16" t="s">
         <v>264</v>
@@ -7648,16 +7648,16 @@
         <v>437</v>
       </c>
       <c r="BA16" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BB16" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BC16">
-        <v>0.99567841910080701</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD16">
-        <v>79.228983151871589</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7722,16 +7722,16 @@
         <v>279</v>
       </c>
       <c r="Y17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Z17" t="s">
         <v>331</v>
       </c>
       <c r="AA17">
-        <v>0.99594698839866214</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB17">
-        <v>74.305212691194157</v>
+        <v>143.06455002781746</v>
       </c>
       <c r="AD17" t="s">
         <v>264</v>
@@ -7761,13 +7761,13 @@
         <v>402</v>
       </c>
       <c r="AN17" t="s">
-        <v>403</v>
+        <v>336</v>
       </c>
       <c r="AO17">
-        <v>0.98563074303391496</v>
+        <v>0.99228583594785691</v>
       </c>
       <c r="AP17">
-        <v>263.43637771155954</v>
+        <v>141.42634095595602</v>
       </c>
       <c r="AR17" t="s">
         <v>264</v>
@@ -7794,16 +7794,16 @@
         <v>439</v>
       </c>
       <c r="BA17" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BB17" t="s">
-        <v>456</v>
+        <v>329</v>
       </c>
       <c r="BC17">
-        <v>0.99417680250918639</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD17">
-        <v>106.75862066491723</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7868,16 +7868,16 @@
         <v>281</v>
       </c>
       <c r="Y18" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="Z18" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AA18">
-        <v>0.97482112792654896</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB18">
-        <v>461.61265467993644</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD18" t="s">
         <v>264</v>
@@ -7904,16 +7904,16 @@
         <v>361</v>
       </c>
       <c r="AM18" t="s">
+        <v>403</v>
+      </c>
+      <c r="AN18" t="s">
         <v>404</v>
       </c>
-      <c r="AN18" t="s">
-        <v>327</v>
-      </c>
       <c r="AO18">
-        <v>0.99059324986934494</v>
+        <v>0.99740231224454534</v>
       </c>
       <c r="AP18">
-        <v>172.45708572867548</v>
+        <v>47.624275516669421</v>
       </c>
       <c r="AR18" t="s">
         <v>264</v>
@@ -7940,16 +7940,16 @@
         <v>441</v>
       </c>
       <c r="BA18" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BB18" t="s">
         <v>456</v>
       </c>
       <c r="BC18">
-        <v>0.99722114454285371</v>
+        <v>0.99417680250918639</v>
       </c>
       <c r="BD18">
-        <v>50.94568338101594</v>
+        <v>106.75862066491723</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8014,16 +8014,16 @@
         <v>283</v>
       </c>
       <c r="Y19" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Z19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AA19">
-        <v>0.99515835423076238</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB19">
-        <v>88.763505769357138</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD19" t="s">
         <v>264</v>
@@ -8056,10 +8056,10 @@
         <v>406</v>
       </c>
       <c r="AO19">
-        <v>0.99452764457035958</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP19">
-        <v>100.3265162100753</v>
+        <v>207.11050978330246</v>
       </c>
       <c r="AR19" t="s">
         <v>264</v>
@@ -8086,16 +8086,16 @@
         <v>443</v>
       </c>
       <c r="BA19" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="BB19" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="BC19">
-        <v>0.99264898847830307</v>
+        <v>0.99790507974591136</v>
       </c>
       <c r="BD19">
-        <v>134.76854456444406</v>
+        <v>38.406871324958367</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8160,16 +8160,16 @@
         <v>285</v>
       </c>
       <c r="Y20" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Z20" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA20">
-        <v>0.99312290929392577</v>
+        <v>0.99184104324003575</v>
       </c>
       <c r="AB20">
-        <v>126.07999627802737</v>
+        <v>149.58087393267732</v>
       </c>
       <c r="AD20" t="s">
         <v>264</v>
@@ -8199,13 +8199,13 @@
         <v>407</v>
       </c>
       <c r="AN20" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AO20">
-        <v>0.99675250681341587</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP20">
-        <v>59.537375087375146</v>
+        <v>244.33232853837262</v>
       </c>
       <c r="AR20" t="s">
         <v>264</v>
@@ -8235,13 +8235,13 @@
         <v>460</v>
       </c>
       <c r="BB20" t="s">
-        <v>454</v>
+        <v>329</v>
       </c>
       <c r="BC20">
-        <v>0.99790507974591136</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD20">
-        <v>38.406871324958367</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8306,16 +8306,16 @@
         <v>287</v>
       </c>
       <c r="Y21" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Z21" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA21">
-        <v>0.99824425800348515</v>
+        <v>0.99782085777346563</v>
       </c>
       <c r="AB21">
-        <v>32.188603269438353</v>
+        <v>39.950940819796543</v>
       </c>
       <c r="AD21" t="s">
         <v>264</v>
@@ -8345,13 +8345,13 @@
         <v>408</v>
       </c>
       <c r="AN21" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="AO21">
-        <v>0.99172545486986263</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP21">
-        <v>151.6999940525175</v>
+        <v>253.85494292623497</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8416,16 +8416,16 @@
         <v>289</v>
       </c>
       <c r="Y22" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="Z22" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA22">
-        <v>0.98551105518500948</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB22">
-        <v>265.63065494149328</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD22" t="s">
         <v>264</v>
@@ -8452,16 +8452,16 @@
         <v>369</v>
       </c>
       <c r="AM22" t="s">
+        <v>409</v>
+      </c>
+      <c r="AN22" t="s">
         <v>410</v>
       </c>
-      <c r="AN22" t="s">
-        <v>411</v>
-      </c>
       <c r="AO22">
-        <v>0.99355139026342754</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP22">
-        <v>118.22451183716133</v>
+        <v>99.241487561376104</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>291</v>
       </c>
       <c r="Y23" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="Z23" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="AA23">
-        <v>0.99326495911353319</v>
+        <v>0.98551105518500948</v>
       </c>
       <c r="AB23">
-        <v>123.47574958522414</v>
+        <v>265.63065494149328</v>
       </c>
       <c r="AD23" t="s">
         <v>264</v>
@@ -8562,16 +8562,16 @@
         <v>371</v>
       </c>
       <c r="AM23" t="s">
+        <v>411</v>
+      </c>
+      <c r="AN23" t="s">
         <v>412</v>
       </c>
-      <c r="AN23" t="s">
-        <v>399</v>
-      </c>
       <c r="AO23">
-        <v>0.98870306310272893</v>
+        <v>0.9934827767968939</v>
       </c>
       <c r="AP23">
-        <v>207.11050978330246</v>
+        <v>119.4824253902779</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8636,16 +8636,16 @@
         <v>293</v>
       </c>
       <c r="Y24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Z24" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="AA24">
-        <v>0.99021329006024306</v>
+        <v>0.99326495911353319</v>
       </c>
       <c r="AB24">
-        <v>179.42301556221076</v>
+        <v>123.47574958522414</v>
       </c>
       <c r="AD24" t="s">
         <v>264</v>
@@ -8678,10 +8678,10 @@
         <v>336</v>
       </c>
       <c r="AO24">
-        <v>0.98667278207972509</v>
+        <v>0.99486941977940613</v>
       </c>
       <c r="AP24">
-        <v>244.33232853837262</v>
+        <v>94.060637377553505</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8746,16 +8746,16 @@
         <v>295</v>
       </c>
       <c r="Y25" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="Z25" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA25">
-        <v>0.99117807442989492</v>
+        <v>0.99021329006024306</v>
       </c>
       <c r="AB25">
-        <v>161.73530211859338</v>
+        <v>179.42301556221076</v>
       </c>
       <c r="AD25" t="s">
         <v>264</v>
@@ -8785,13 +8785,13 @@
         <v>414</v>
       </c>
       <c r="AN25" t="s">
-        <v>329</v>
+        <v>415</v>
       </c>
       <c r="AO25">
-        <v>0.98615336674947807</v>
+        <v>0.99567808239070055</v>
       </c>
       <c r="AP25">
-        <v>253.85494292623497</v>
+        <v>79.235156170489844</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8856,16 +8856,16 @@
         <v>297</v>
       </c>
       <c r="Y26" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="Z26" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA26">
-        <v>0.99327889425386662</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB26">
-        <v>123.22027201244609</v>
+        <v>161.73530211859338</v>
       </c>
       <c r="AD26" t="s">
         <v>264</v>
@@ -8892,16 +8892,16 @@
         <v>377</v>
       </c>
       <c r="AM26" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN26" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="AO26">
-        <v>0.99458682795119768</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP26">
-        <v>99.241487561376104</v>
+        <v>122.76624010910177</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8966,16 +8966,16 @@
         <v>299</v>
       </c>
       <c r="Y27" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="Z27" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="AA27">
-        <v>0.98440782007749728</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB27">
-        <v>285.85663191255094</v>
+        <v>32.188603269438353</v>
       </c>
       <c r="AD27" t="s">
         <v>264</v>
@@ -9005,13 +9005,13 @@
         <v>417</v>
       </c>
       <c r="AN27" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="AO27">
-        <v>0.99567808239070055</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP27">
-        <v>79.235156170489844</v>
+        <v>314.22828490220974</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9076,16 +9076,16 @@
         <v>301</v>
       </c>
       <c r="Y28" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="Z28" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AA28">
-        <v>0.99787844392938518</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB28">
-        <v>38.895194627939205</v>
+        <v>171.32529124410425</v>
       </c>
       <c r="AD28" t="s">
         <v>264</v>
@@ -9112,16 +9112,16 @@
         <v>381</v>
       </c>
       <c r="AM28" t="s">
+        <v>418</v>
+      </c>
+      <c r="AN28" t="s">
         <v>419</v>
       </c>
-      <c r="AN28" t="s">
-        <v>420</v>
-      </c>
       <c r="AO28">
-        <v>0.9934827767968939</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP28">
-        <v>119.4824253902779</v>
+        <v>47.407781945483563</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9186,16 +9186,16 @@
         <v>303</v>
       </c>
       <c r="Y29" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Z29" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AA29">
-        <v>0.99219647908939179</v>
+        <v>0.99806216160693018</v>
       </c>
       <c r="AB29">
-        <v>143.06455002781746</v>
+        <v>35.52703720627968</v>
       </c>
       <c r="AD29" t="s">
         <v>264</v>
@@ -9222,16 +9222,16 @@
         <v>383</v>
       </c>
       <c r="AM29" t="s">
+        <v>420</v>
+      </c>
+      <c r="AN29" t="s">
         <v>421</v>
       </c>
-      <c r="AN29" t="s">
-        <v>329</v>
-      </c>
       <c r="AO29">
-        <v>0.99486941977940613</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP29">
-        <v>94.060637377553505</v>
+        <v>263.43637771155954</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9296,16 +9296,16 @@
         <v>305</v>
       </c>
       <c r="Y30" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Z30" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA30">
-        <v>0.99199432528561049</v>
+        <v>0.99594698839866214</v>
       </c>
       <c r="AB30">
-        <v>146.77070309714048</v>
+        <v>74.305212691194157</v>
       </c>
       <c r="AD30" t="s">
         <v>264</v>
@@ -9335,13 +9335,13 @@
         <v>422</v>
       </c>
       <c r="AN30" t="s">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="AO30">
-        <v>0.99330365963041267</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP30">
-        <v>122.76624010910177</v>
+        <v>172.45708572867548</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9406,16 +9406,16 @@
         <v>307</v>
       </c>
       <c r="Y31" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="Z31" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AA31">
-        <v>0.99686513787774389</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB31">
-        <v>57.472472241362951</v>
+        <v>461.61265467993644</v>
       </c>
       <c r="AD31" t="s">
         <v>264</v>
@@ -9445,13 +9445,13 @@
         <v>423</v>
       </c>
       <c r="AN31" t="s">
-        <v>424</v>
+        <v>336</v>
       </c>
       <c r="AO31">
-        <v>0.99740231224454534</v>
+        <v>0.98907459074885506</v>
       </c>
       <c r="AP31">
-        <v>47.624275516669421</v>
+        <v>200.2991696043234</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9516,16 +9516,16 @@
         <v>309</v>
       </c>
       <c r="Y32" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="Z32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA32">
-        <v>0.99585076637156988</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB32">
-        <v>76.069283187886086</v>
+        <v>135.59158861107267</v>
       </c>
       <c r="AD32" t="s">
         <v>264</v>
@@ -9552,16 +9552,16 @@
         <v>389</v>
       </c>
       <c r="AM32" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AN32" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AO32">
-        <v>0.98907459074885506</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP32">
-        <v>200.2991696043234</v>
+        <v>243.83038212667131</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9626,16 +9626,16 @@
         <v>311</v>
       </c>
       <c r="Y33" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="Z33" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="AA33">
-        <v>0.9893494724125782</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB33">
-        <v>195.2596724360663</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD33" t="s">
         <v>264</v>
@@ -9662,16 +9662,16 @@
         <v>391</v>
       </c>
       <c r="AM33" t="s">
+        <v>425</v>
+      </c>
+      <c r="AN33" t="s">
         <v>426</v>
       </c>
-      <c r="AN33" t="s">
-        <v>345</v>
-      </c>
       <c r="AO33">
-        <v>0.98670016097490887</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP33">
-        <v>243.83038212667131</v>
+        <v>118.22451183716133</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9736,16 +9736,16 @@
         <v>313</v>
       </c>
       <c r="Y34" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="Z34" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AA34">
-        <v>0.97548412543178475</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB34">
-        <v>449.45770041728053</v>
+        <v>285.85663191255094</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9810,16 +9810,16 @@
         <v>315</v>
       </c>
       <c r="Y35" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Z35" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="AA35">
-        <v>0.96747189690815383</v>
+        <v>0.99585076637156988</v>
       </c>
       <c r="AB35">
-        <v>596.34855668384682</v>
+        <v>76.069283187886086</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9884,16 +9884,16 @@
         <v>317</v>
       </c>
       <c r="Y36" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="Z36" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AA36">
-        <v>0.99065498411395791</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB36">
-        <v>171.32529124410425</v>
+        <v>195.2596724360663</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9958,16 +9958,16 @@
         <v>319</v>
       </c>
       <c r="Y37" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="Z37" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="AA37">
-        <v>0.99184104324003575</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB37">
-        <v>149.58087393267732</v>
+        <v>449.45770041728053</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10032,16 +10032,16 @@
         <v>321</v>
       </c>
       <c r="Y38" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="Z38" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AA38">
-        <v>0.99260409516666881</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB38">
-        <v>135.59158861107267</v>
+        <v>596.34855668384682</v>
       </c>
     </row>
   </sheetData>
@@ -10050,7 +10050,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE379407-5312-42FE-BB0E-39B7431E15DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8000A4-91F8-496D-B27D-ABF531258964}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10162,7 +10162,7 @@
         <v>461</v>
       </c>
       <c r="K11" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10230,7 +10230,7 @@
         <v>463</v>
       </c>
       <c r="K12" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10263,7 +10263,7 @@
         <v>509</v>
       </c>
       <c r="X12" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10298,7 +10298,7 @@
         <v>465</v>
       </c>
       <c r="K13" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="L13">
         <v>1.5817501567892978</v>
@@ -10331,7 +10331,7 @@
         <v>511</v>
       </c>
       <c r="X13" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10366,7 +10366,7 @@
         <v>467</v>
       </c>
       <c r="K14" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10399,7 +10399,7 @@
         <v>513</v>
       </c>
       <c r="X14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10434,7 +10434,7 @@
         <v>469</v>
       </c>
       <c r="K15" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10467,7 +10467,7 @@
         <v>515</v>
       </c>
       <c r="X15" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10502,7 +10502,7 @@
         <v>471</v>
       </c>
       <c r="K16" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10535,7 +10535,7 @@
         <v>517</v>
       </c>
       <c r="X16" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10570,7 +10570,7 @@
         <v>473</v>
       </c>
       <c r="K17" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10603,7 +10603,7 @@
         <v>519</v>
       </c>
       <c r="X17" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="Y17">
         <v>2.2530000000000001</v>
@@ -10638,7 +10638,7 @@
         <v>475</v>
       </c>
       <c r="K18" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10671,7 +10671,7 @@
         <v>521</v>
       </c>
       <c r="X18" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="Y18">
         <v>6.1852499999999999</v>
@@ -10706,7 +10706,7 @@
         <v>477</v>
       </c>
       <c r="K19" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10739,7 +10739,7 @@
         <v>523</v>
       </c>
       <c r="X19" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Y19">
         <v>10.093500000000001</v>
@@ -10774,7 +10774,7 @@
         <v>479</v>
       </c>
       <c r="K20" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10807,7 +10807,7 @@
         <v>525</v>
       </c>
       <c r="X20" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10842,7 +10842,7 @@
         <v>481</v>
       </c>
       <c r="K21" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L21">
         <v>15.316017274089829</v>
@@ -10877,7 +10877,7 @@
         <v>483</v>
       </c>
       <c r="K22" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10912,7 +10912,7 @@
         <v>485</v>
       </c>
       <c r="K23" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="L23">
         <v>15.32235174795542</v>
@@ -10947,7 +10947,7 @@
         <v>487</v>
       </c>
       <c r="K24" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="L24">
         <v>4.3876485804695786</v>
@@ -10982,7 +10982,7 @@
         <v>489</v>
       </c>
       <c r="K25" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -11017,7 +11017,7 @@
         <v>491</v>
       </c>
       <c r="K26" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11052,7 +11052,7 @@
         <v>493</v>
       </c>
       <c r="K27" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11087,7 +11087,7 @@
         <v>495</v>
       </c>
       <c r="K28" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11122,7 +11122,7 @@
         <v>497</v>
       </c>
       <c r="K29" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11157,7 +11157,7 @@
         <v>499</v>
       </c>
       <c r="K30" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11192,7 +11192,7 @@
         <v>501</v>
       </c>
       <c r="K31" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11227,7 +11227,7 @@
         <v>503</v>
       </c>
       <c r="K32" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="L32">
         <v>0.91282903432358287</v>
@@ -11262,7 +11262,7 @@
         <v>505</v>
       </c>
       <c r="K33" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11277,7 +11277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D541C4-B5F7-4C08-ABC3-942735393EAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C768E56-14F3-432A-B046-3CDD4A6FA9EE}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13094,7 +13094,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E71618F-49E2-40CF-8294-1E14C144E20A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F5FEBD-8004-4056-8E22-73A4D5C4E48E}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B403CA9-0D78-4998-B409-128C102E9753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC98F1DC-7E14-446D-A66E-7061630A13B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="589">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -649,7 +649,7 @@
     <t>ele</t>
   </si>
   <si>
-    <t>e_spv_001</t>
+    <t>e_spv_KEN_001</t>
   </si>
   <si>
     <t>solar resource in cluster 1</t>
@@ -661,163 +661,163 @@
     <t>no</t>
   </si>
   <si>
-    <t>e_spv_002</t>
+    <t>e_spv_KEN_002</t>
   </si>
   <si>
     <t>solar resource in cluster 2</t>
   </si>
   <si>
-    <t>e_spv_003</t>
+    <t>e_spv_KEN_003</t>
   </si>
   <si>
     <t>solar resource in cluster 3</t>
   </si>
   <si>
-    <t>e_spv_004</t>
+    <t>e_spv_KEN_004</t>
   </si>
   <si>
     <t>solar resource in cluster 4</t>
   </si>
   <si>
-    <t>e_spv_005</t>
+    <t>e_spv_KEN_005</t>
   </si>
   <si>
     <t>solar resource in cluster 5</t>
   </si>
   <si>
-    <t>e_spv_006</t>
+    <t>e_spv_KEN_006</t>
   </si>
   <si>
     <t>solar resource in cluster 6</t>
   </si>
   <si>
-    <t>e_spv_007</t>
+    <t>e_spv_KEN_007</t>
   </si>
   <si>
     <t>solar resource in cluster 7</t>
   </si>
   <si>
-    <t>e_spv_008</t>
+    <t>e_spv_KEN_008</t>
   </si>
   <si>
     <t>solar resource in cluster 8</t>
   </si>
   <si>
-    <t>e_spv_009</t>
+    <t>e_spv_KEN_009</t>
   </si>
   <si>
     <t>solar resource in cluster 9</t>
   </si>
   <si>
-    <t>e_spv_010</t>
+    <t>e_spv_KEN_010</t>
   </si>
   <si>
     <t>solar resource in cluster 10</t>
   </si>
   <si>
-    <t>e_spv_011</t>
+    <t>e_spv_KEN_011</t>
   </si>
   <si>
     <t>solar resource in cluster 11</t>
   </si>
   <si>
-    <t>e_spv_012</t>
+    <t>e_spv_KEN_012</t>
   </si>
   <si>
     <t>solar resource in cluster 12</t>
   </si>
   <si>
-    <t>e_spv_013</t>
+    <t>e_spv_KEN_013</t>
   </si>
   <si>
     <t>solar resource in cluster 13</t>
   </si>
   <si>
-    <t>e_spv_014</t>
+    <t>e_spv_KEN_014</t>
   </si>
   <si>
     <t>solar resource in cluster 14</t>
   </si>
   <si>
-    <t>e_spv_015</t>
+    <t>e_spv_KEN_015</t>
   </si>
   <si>
     <t>solar resource in cluster 15</t>
   </si>
   <si>
-    <t>e_spv_016</t>
+    <t>e_spv_KEN_016</t>
   </si>
   <si>
     <t>solar resource in cluster 16</t>
   </si>
   <si>
-    <t>e_spv_017</t>
+    <t>e_spv_KEN_017</t>
   </si>
   <si>
     <t>solar resource in cluster 17</t>
   </si>
   <si>
-    <t>e_spv_018</t>
+    <t>e_spv_KEN_018</t>
   </si>
   <si>
     <t>solar resource in cluster 18</t>
   </si>
   <si>
-    <t>e_spv_019</t>
+    <t>e_spv_KEN_019</t>
   </si>
   <si>
     <t>solar resource in cluster 19</t>
   </si>
   <si>
-    <t>e_spv_020</t>
+    <t>e_spv_KEN_020</t>
   </si>
   <si>
     <t>solar resource in cluster 20</t>
   </si>
   <si>
-    <t>e_spv_021</t>
+    <t>e_spv_KEN_021</t>
   </si>
   <si>
     <t>solar resource in cluster 21</t>
   </si>
   <si>
-    <t>e_spv_022</t>
+    <t>e_spv_KEN_022</t>
   </si>
   <si>
     <t>solar resource in cluster 22</t>
   </si>
   <si>
-    <t>e_spv_023</t>
+    <t>e_spv_KEN_023</t>
   </si>
   <si>
     <t>solar resource in cluster 23</t>
   </si>
   <si>
-    <t>e_spv_024</t>
+    <t>e_spv_KEN_024</t>
   </si>
   <si>
     <t>solar resource in cluster 24</t>
   </si>
   <si>
-    <t>e_spv_025</t>
+    <t>e_spv_KEN_025</t>
   </si>
   <si>
     <t>solar resource in cluster 25</t>
   </si>
   <si>
-    <t>e_spv_026</t>
+    <t>e_spv_KEN_026</t>
   </si>
   <si>
     <t>solar resource in cluster 26</t>
   </si>
   <si>
-    <t>e_spv_027</t>
+    <t>e_spv_KEN_027</t>
   </si>
   <si>
     <t>solar resource in cluster 27</t>
   </si>
   <si>
-    <t>e_spv_028</t>
+    <t>e_spv_KEN_028</t>
   </si>
   <si>
     <t>solar resource in cluster 28</t>
@@ -835,88 +835,88 @@
     <t>af~fx</t>
   </si>
   <si>
-    <t>elc_spv_001</t>
-  </si>
-  <si>
-    <t>elc_spv_002</t>
-  </si>
-  <si>
-    <t>elc_spv_003</t>
-  </si>
-  <si>
-    <t>elc_spv_004</t>
-  </si>
-  <si>
-    <t>elc_spv_005</t>
-  </si>
-  <si>
-    <t>elc_spv_006</t>
-  </si>
-  <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
-    <t>elc_spv_008</t>
-  </si>
-  <si>
-    <t>elc_spv_009</t>
-  </si>
-  <si>
-    <t>elc_spv_010</t>
-  </si>
-  <si>
-    <t>elc_spv_011</t>
-  </si>
-  <si>
-    <t>elc_spv_012</t>
-  </si>
-  <si>
-    <t>elc_spv_013</t>
-  </si>
-  <si>
-    <t>elc_spv_014</t>
-  </si>
-  <si>
-    <t>elc_spv_015</t>
-  </si>
-  <si>
-    <t>elc_spv_016</t>
-  </si>
-  <si>
-    <t>elc_spv_017</t>
-  </si>
-  <si>
-    <t>elc_spv_018</t>
-  </si>
-  <si>
-    <t>elc_spv_019</t>
-  </si>
-  <si>
-    <t>elc_spv_020</t>
-  </si>
-  <si>
-    <t>elc_spv_021</t>
-  </si>
-  <si>
-    <t>elc_spv_022</t>
-  </si>
-  <si>
-    <t>elc_spv_023</t>
-  </si>
-  <si>
-    <t>elc_spv_024</t>
-  </si>
-  <si>
-    <t>elc_spv_025</t>
-  </si>
-  <si>
-    <t>elc_spv_026</t>
-  </si>
-  <si>
-    <t>elc_spv_027</t>
-  </si>
-  <si>
-    <t>elc_spv_028</t>
+    <t>elc_spv_KEN_001</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_002</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_003</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_004</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_005</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_006</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_007</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_008</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_009</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_010</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_011</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_012</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_013</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_014</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_015</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_016</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_017</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_018</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_019</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_020</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_021</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_022</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_023</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_024</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_025</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_026</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_027</t>
+  </si>
+  <si>
+    <t>elc_spv_KEN_028</t>
   </si>
   <si>
     <t>primarycg</t>
@@ -925,919 +925,940 @@
     <t>pre</t>
   </si>
   <si>
-    <t>distr_solelc_spv_021</t>
+    <t>distr_solelc_spv_KEN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_021</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 21</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
+    <t>distr_solelc_spv_KEN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_028</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
+    <t>distr_solelc_spv_KEN_020</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_KE14-400,e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE12-400,e_w569997185-400,e_w569997185-220,e_w578140339-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_KE2-220,e_KE3-220,e_w696445754-220,e_KE4-220,e_KE1-220</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE7-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220,e_KE2-220,e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w669520367-220</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w457973270-400,e_KE5-220,e_KE1-220,e_w669520367-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_w180021151-220,e_KE11-220,e_KE9-220,e_w220540545-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_KE13-400,e_KE6-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w870818913-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_r14923640-220,e_r14923640-400,e_KE4-220,e_KE1-220,e_w579310367-220,e_w457973270-400,e_KE5-220,e_w563813243-400</t>
-  </si>
-  <si>
-    <t>e_KE6-220,e_w669520367-220,e_w659874569-220</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_w846713577-220,e_w457973270-400,e_KE9-220,e_w220540545-220,e_w669520367-220</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
+    <t>e_KE12-400_KEN,e_w569997185-400_KEN,e_w569997185-220_KEN,e_w578140339-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE6-220_KEN,e_w669520367-220_KEN,e_w659874569-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w563813243-400_KEN,e_w669520367-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE14-400_KEN,e_w870818913-220_KEN,e_w870818913-400_KEN,e_w953567827-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w457973270-400_KEN,e_KE5-220_KEN,e_KE1-220_KEN,e_w669520367-220_KEN,e_w563813243-400_KEN</t>
+  </si>
+  <si>
+    <t>e_KE15-220_KEN,e_w870818913-220_KEN,e_w953567827-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w659874569-220_KEN,e_w669520367-220_KEN,e_w660091166-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w563813243-400_KEN</t>
+  </si>
+  <si>
+    <t>e_KE7-220_KEN,e_w846713577-220_KEN,e_w457973270-400_KEN,e_KE9-220_KEN,e_w220540545-220_KEN,e_w669520367-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w659874569-220_KEN,e_w660091166-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220_KEN,e_KE2-220_KEN,e_r14923640-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE2-220_KEN,e_KE3-220_KEN,e_w696445754-220_KEN,e_KE4-220_KEN,e_KE1-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w669520367-220_KEN,e_w563813243-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w660091166-220_KEN,e_w669520367-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w180021151-220_KEN,e_KE11-220_KEN,e_KE9-220_KEN,e_w220540545-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE14-400_KEN,e_KE13-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w660091166-220_KEN</t>
+  </si>
+  <si>
+    <t>e_r14923640-220_KEN,e_r14923640-400_KEN,e_KE4-220_KEN,e_KE1-220_KEN,e_w579310367-220_KEN,e_w457973270-400_KEN,e_KE5-220_KEN,e_w563813243-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w669520367-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220_KEN,e_KE7-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w579310367-220_KEN,e_w563813243-400_KEN</t>
+  </si>
+  <si>
+    <t>e_KE14-400_KEN,e_KE13-400_KEN,e_KE6-220_KEN,e_w870818913-220_KEN</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_020</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
+    <t>distr_wonelc_won_KEN_009</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
+    <t>distr_wonelc_won_KEN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
+    <t>distr_wonelc_won_KEN_022</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
+    <t>distr_wonelc_won_KEN_005</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w579310367-220,e_w563813243-400,e_KE5-220</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_KE14-400,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400,e_w669520367-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w870818913-220,e_w659874569-220,e_w870818913-400,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_KE7-220,e_KE12-400,e_w569997185-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE11-220</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_KE12-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w669520367-220,e_w659874569-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_KE13-400,e_KE6-220,e_w669520367-220,e_w870818913-220</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
+    <t>elc_won_KEN_016</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_021</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400_KEN,e_w669520367-220_KEN,e_w660091166-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_017</t>
+  </si>
+  <si>
+    <t>e_w579310367-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_011</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_015</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_023</t>
+  </si>
+  <si>
+    <t>e_KE12-400_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_006</t>
+  </si>
+  <si>
+    <t>e_w669520367-220_KEN,e_w659874569-220_KEN,e_w660091166-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_019</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_004</t>
+  </si>
+  <si>
+    <t>e_w870818913-220_KEN,e_w659874569-220_KEN,e_w870818913-400_KEN,e_w953567827-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_013</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_008</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_007</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_014</t>
+  </si>
+  <si>
+    <t>e_KE7-220_KEN,e_KE12-400_KEN,e_w569997185-400_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_002</t>
+  </si>
+  <si>
+    <t>e_KE13-400_KEN,e_KE6-220_KEN,e_w669520367-220_KEN,e_w870818913-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_001</t>
+  </si>
+  <si>
+    <t>e_KE14-400_KEN,e_w870818913-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220_KEN,e_w953567827-220_KEN,e_w660091166-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_020</t>
+  </si>
+  <si>
+    <t>e_w579310367-220_KEN,e_w563813243-400_KEN,e_KE5-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_009</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_012</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_018</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_022</t>
+  </si>
+  <si>
+    <t>e_KE13-400_KEN,e_KE11-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_005</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
+    <t>distr_wofelc_wof_KEN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_009</t>
+    <t>distr_wofelc_wof_KEN_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_KE15-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w953567827-220,e_w660091166-220</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w953567827-220</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_won_001</t>
+    <t>elc_wof_KEN_002</t>
+  </si>
+  <si>
+    <t>e_KE15-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_005</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_006</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_004</t>
+  </si>
+  <si>
+    <t>e_w953567827-220_KEN,e_w660091166-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_003</t>
+  </si>
+  <si>
+    <t>e_KE15-220_KEN,e_w953567827-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_008</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_007</t>
+  </si>
+  <si>
+    <t>e_w953567827-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_009</t>
+  </si>
+  <si>
+    <t>e_won_KEN_001</t>
   </si>
   <si>
     <t>wind resource in cluster 1</t>
   </si>
   <si>
-    <t>e_won_002</t>
+    <t>e_won_KEN_002</t>
   </si>
   <si>
     <t>wind resource in cluster 2</t>
   </si>
   <si>
-    <t>e_won_003</t>
+    <t>e_won_KEN_003</t>
   </si>
   <si>
     <t>wind resource in cluster 3</t>
   </si>
   <si>
-    <t>e_won_004</t>
+    <t>e_won_KEN_004</t>
   </si>
   <si>
     <t>wind resource in cluster 4</t>
   </si>
   <si>
-    <t>e_won_005</t>
+    <t>e_won_KEN_005</t>
   </si>
   <si>
     <t>wind resource in cluster 5</t>
   </si>
   <si>
-    <t>e_won_006</t>
+    <t>e_won_KEN_006</t>
   </si>
   <si>
     <t>wind resource in cluster 6</t>
   </si>
   <si>
-    <t>e_won_007</t>
+    <t>e_won_KEN_007</t>
   </si>
   <si>
     <t>wind resource in cluster 7</t>
   </si>
   <si>
-    <t>e_won_008</t>
+    <t>e_won_KEN_008</t>
   </si>
   <si>
     <t>wind resource in cluster 8</t>
   </si>
   <si>
-    <t>e_won_009</t>
+    <t>e_won_KEN_009</t>
   </si>
   <si>
     <t>wind resource in cluster 9</t>
   </si>
   <si>
-    <t>e_won_010</t>
+    <t>e_won_KEN_010</t>
   </si>
   <si>
     <t>wind resource in cluster 10</t>
   </si>
   <si>
-    <t>e_won_011</t>
+    <t>e_won_KEN_011</t>
   </si>
   <si>
     <t>wind resource in cluster 11</t>
   </si>
   <si>
-    <t>e_won_012</t>
+    <t>e_won_KEN_012</t>
   </si>
   <si>
     <t>wind resource in cluster 12</t>
   </si>
   <si>
-    <t>e_won_013</t>
+    <t>e_won_KEN_013</t>
   </si>
   <si>
     <t>wind resource in cluster 13</t>
   </si>
   <si>
-    <t>e_won_014</t>
+    <t>e_won_KEN_014</t>
   </si>
   <si>
     <t>wind resource in cluster 14</t>
   </si>
   <si>
-    <t>e_won_015</t>
+    <t>e_won_KEN_015</t>
   </si>
   <si>
     <t>wind resource in cluster 15</t>
   </si>
   <si>
-    <t>e_won_016</t>
+    <t>e_won_KEN_016</t>
   </si>
   <si>
     <t>wind resource in cluster 16</t>
   </si>
   <si>
-    <t>e_won_017</t>
+    <t>e_won_KEN_017</t>
   </si>
   <si>
     <t>wind resource in cluster 17</t>
   </si>
   <si>
-    <t>e_won_018</t>
+    <t>e_won_KEN_018</t>
   </si>
   <si>
     <t>wind resource in cluster 18</t>
   </si>
   <si>
-    <t>e_won_019</t>
+    <t>e_won_KEN_019</t>
   </si>
   <si>
     <t>wind resource in cluster 19</t>
   </si>
   <si>
-    <t>e_won_020</t>
+    <t>e_won_KEN_020</t>
   </si>
   <si>
     <t>wind resource in cluster 20</t>
   </si>
   <si>
-    <t>e_won_021</t>
+    <t>e_won_KEN_021</t>
   </si>
   <si>
     <t>wind resource in cluster 21</t>
   </si>
   <si>
-    <t>e_won_022</t>
+    <t>e_won_KEN_022</t>
   </si>
   <si>
     <t>wind resource in cluster 22</t>
   </si>
   <si>
-    <t>e_won_023</t>
+    <t>e_won_KEN_023</t>
   </si>
   <si>
     <t>wind resource in cluster 23</t>
   </si>
   <si>
-    <t>e_wof_001</t>
+    <t>e_wof_KEN_001</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 1</t>
   </si>
   <si>
-    <t>e_wof_002</t>
+    <t>e_wof_KEN_002</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 2</t>
   </si>
   <si>
-    <t>e_wof_003</t>
+    <t>e_wof_KEN_003</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 3</t>
   </si>
   <si>
-    <t>e_wof_004</t>
+    <t>e_wof_KEN_004</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 4</t>
   </si>
   <si>
-    <t>e_wof_005</t>
+    <t>e_wof_KEN_005</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 5</t>
   </si>
   <si>
-    <t>e_wof_006</t>
+    <t>e_wof_KEN_006</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 6</t>
   </si>
   <si>
-    <t>e_wof_007</t>
+    <t>e_wof_KEN_007</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 7</t>
   </si>
   <si>
-    <t>e_wof_008</t>
+    <t>e_wof_KEN_008</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 8</t>
   </si>
   <si>
-    <t>e_wof_009</t>
+    <t>e_wof_KEN_009</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 9</t>
   </si>
   <si>
-    <t>e_wof_010</t>
+    <t>e_wof_KEN_010</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 10</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS</t>
+    <t>en_gas_ccgt</t>
+  </si>
+  <si>
+    <t>ncap_cost</t>
+  </si>
+  <si>
+    <t>ncap_fom</t>
+  </si>
+  <si>
+    <t>act_cost</t>
+  </si>
+  <si>
+    <t>ncap_tlife</t>
+  </si>
+  <si>
+    <t>ncap_iled</t>
+  </si>
+  <si>
+    <t>en_gas_turbine</t>
+  </si>
+  <si>
+    <t>en_gas_chp</t>
+  </si>
+  <si>
+    <t>ELC,HET</t>
+  </si>
+  <si>
+    <t>ncap_chpr</t>
+  </si>
+  <si>
+    <t>en_gas_fuelcell</t>
+  </si>
+  <si>
+    <t>en_gas_ccs</t>
+  </si>
+  <si>
+    <t>ELC,CO2Cap</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical</t>
+  </si>
+  <si>
+    <t>en_coal_igcc</t>
+  </si>
+  <si>
+    <t>en_coal_ccs</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_ccs</t>
+  </si>
+  <si>
+    <t>en_coal_oxyfuel_ccs</t>
+  </si>
+  <si>
+    <t>en_nuclear</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr</t>
+  </si>
+  <si>
+    <t>en_biomass</t>
   </si>
   <si>
     <t>ncap_af</t>
   </si>
   <si>
-    <t>ncap_cost</t>
-  </si>
-  <si>
-    <t>ncap_fom</t>
-  </si>
-  <si>
-    <t>ncap_iled</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit</t>
-  </si>
-  <si>
-    <t>CCGT</t>
-  </si>
-  <si>
-    <t>CCGT + CCS</t>
-  </si>
-  <si>
-    <t>Coal + CCS</t>
-  </si>
-  <si>
-    <t>Gas turbine</t>
-  </si>
-  <si>
-    <t>Hydropower - large-scale unit</t>
-  </si>
-  <si>
-    <t>IGCC</t>
-  </si>
-  <si>
-    <t>IGCC + CCS</t>
-  </si>
-  <si>
-    <t>Nuclear large</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS</t>
-  </si>
-  <si>
-    <t>Solar photovoltaics - Large scale unit</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL</t>
-  </si>
-  <si>
-    <t>Wind offshore</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>Wind onshore</t>
+    <t>en_biomass_cofiring</t>
+  </si>
+  <si>
+    <t>en_biomass_chp</t>
+  </si>
+  <si>
+    <t>en_biomass_ccs</t>
+  </si>
+  <si>
+    <t>en_geothermal</t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
-    <t>stepdown_r14923640_400to220</t>
-  </si>
-  <si>
-    <t>e_r14923640-400</t>
-  </si>
-  <si>
-    <t>e_r14923640-220</t>
-  </si>
-  <si>
-    <t>stepup_r14923640_220to400</t>
-  </si>
-  <si>
-    <t>stepdown_w457973270_400to220</t>
-  </si>
-  <si>
-    <t>e_w457973270-400</t>
-  </si>
-  <si>
-    <t>e_w457973270-220</t>
-  </si>
-  <si>
-    <t>stepup_w457973270_220to400</t>
-  </si>
-  <si>
-    <t>stepdown_w569997185_400to220</t>
-  </si>
-  <si>
-    <t>e_w569997185-400</t>
-  </si>
-  <si>
-    <t>e_w569997185-220</t>
-  </si>
-  <si>
-    <t>stepup_w569997185_220to400</t>
-  </si>
-  <si>
-    <t>stepdown_w578140339_400to220</t>
-  </si>
-  <si>
-    <t>e_w578140339-400</t>
-  </si>
-  <si>
-    <t>e_w578140339-220</t>
-  </si>
-  <si>
-    <t>stepup_w578140339_220to400</t>
-  </si>
-  <si>
-    <t>stepdown_w870818913_400to220</t>
-  </si>
-  <si>
-    <t>e_w870818913-400</t>
-  </si>
-  <si>
-    <t>e_w870818913-220</t>
-  </si>
-  <si>
-    <t>stepup_w870818913_220to400</t>
+    <t>CHP</t>
+  </si>
+  <si>
+    <t>stepdown_r14923640_KEN_400to220</t>
+  </si>
+  <si>
+    <t>e_r14923640-400_KEN</t>
+  </si>
+  <si>
+    <t>e_r14923640-220_KEN</t>
+  </si>
+  <si>
+    <t>stepup_r14923640_KEN_220to400</t>
+  </si>
+  <si>
+    <t>stepdown_w457973270_KEN_400to220</t>
+  </si>
+  <si>
+    <t>e_w457973270-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w457973270-220_KEN</t>
+  </si>
+  <si>
+    <t>stepup_w457973270_KEN_220to400</t>
+  </si>
+  <si>
+    <t>stepdown_w569997185_KEN_400to220</t>
+  </si>
+  <si>
+    <t>e_w569997185-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w569997185-220_KEN</t>
+  </si>
+  <si>
+    <t>stepup_w569997185_KEN_220to400</t>
+  </si>
+  <si>
+    <t>stepdown_w578140339_KEN_400to220</t>
+  </si>
+  <si>
+    <t>e_w578140339-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w578140339-220_KEN</t>
+  </si>
+  <si>
+    <t>stepup_w578140339_KEN_220to400</t>
+  </si>
+  <si>
+    <t>stepdown_w870818913_KEN_400to220</t>
+  </si>
+  <si>
+    <t>e_w870818913-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w870818913-220_KEN</t>
+  </si>
+  <si>
+    <t>stepup_w870818913_KEN_220to400</t>
   </si>
   <si>
     <t>activityunit</t>
@@ -1846,37 +1867,34 @@
     <t>capacityunit</t>
   </si>
   <si>
-    <t>Transformer: e_r14923640-400 → e_r14923640-220</t>
-  </si>
-  <si>
-    <t>Transformer: e_r14923640-220 → e_r14923640-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w457973270-400 → e_w457973270-220</t>
-  </si>
-  <si>
-    <t>Transformer: e_w457973270-220 → e_w457973270-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w569997185-400 → e_w569997185-220</t>
-  </si>
-  <si>
-    <t>Transformer: e_w569997185-220 → e_w569997185-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w578140339-400 → e_w578140339-220</t>
-  </si>
-  <si>
-    <t>Transformer: e_w578140339-220 → e_w578140339-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w870818913-400 → e_w870818913-220</t>
-  </si>
-  <si>
-    <t>Transformer: e_w870818913-220 → e_w870818913-400</t>
-  </si>
-  <si>
-    <t>e_KE15-220,e_w660091166-220</t>
+    <t>Transformer: e_r14923640-400_KEN → e_r14923640-220_KEN</t>
+  </si>
+  <si>
+    <t>Transformer: e_r14923640-220_KEN → e_r14923640-400_KEN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w457973270-400_KEN → e_w457973270-220_KEN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w457973270-220_KEN → e_w457973270-400_KEN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w569997185-400_KEN → e_w569997185-220_KEN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w569997185-220_KEN → e_w569997185-400_KEN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w578140339-400_KEN → e_w578140339-220_KEN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w578140339-220_KEN → e_w578140339-400_KEN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w870818913-400_KEN → e_w870818913-220_KEN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w870818913-220_KEN → e_w870818913-400_KEN</t>
   </si>
 </sst>
 </file>
@@ -2830,6 +2848,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -3770,7 +3791,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>e_KE15-220,e_w660091166-220</v>
+        <v>ELC</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3792,7 +3813,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>e_KE15-220,e_w660091166-220</v>
+        <v>ELC</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3807,7 +3828,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>582</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -6608,7 +6629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0574C0-F120-4EB9-9433-2723E5FA8A91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{289F2EA9-6A06-49FE-BF49-FB40D8C0EE29}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6846,16 +6867,16 @@
         <v>265</v>
       </c>
       <c r="Y11" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="Z11" t="s">
         <v>325</v>
       </c>
       <c r="AA11">
-        <v>0.99515835423076238</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB11">
-        <v>88.763505769357138</v>
+        <v>74.690879958909605</v>
       </c>
       <c r="AD11" t="s">
         <v>264</v>
@@ -6885,13 +6906,13 @@
         <v>393</v>
       </c>
       <c r="AN11" t="s">
-        <v>394</v>
+        <v>332</v>
       </c>
       <c r="AO11">
-        <v>0.99452764457035958</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP11">
-        <v>100.3265162100753</v>
+        <v>253.85494292623497</v>
       </c>
       <c r="AR11" t="s">
         <v>264</v>
@@ -6924,10 +6945,10 @@
         <v>448</v>
       </c>
       <c r="BC11">
-        <v>0.99504452373263619</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD11">
-        <v>90.850398235003013</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6992,16 +7013,16 @@
         <v>269</v>
       </c>
       <c r="Y12" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="Z12" t="s">
         <v>326</v>
       </c>
       <c r="AA12">
-        <v>0.99312290929392577</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB12">
-        <v>126.07999627802737</v>
+        <v>135.59158861107267</v>
       </c>
       <c r="AD12" t="s">
         <v>264</v>
@@ -7028,10 +7049,10 @@
         <v>349</v>
       </c>
       <c r="AM12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AN12" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AO12">
         <v>0.99675250681341587</v>
@@ -7067,13 +7088,13 @@
         <v>449</v>
       </c>
       <c r="BB12" t="s">
-        <v>450</v>
+        <v>341</v>
       </c>
       <c r="BC12">
-        <v>0.99264898847830307</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD12">
-        <v>134.76854456444406</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7138,16 +7159,16 @@
         <v>271</v>
       </c>
       <c r="Y13" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="Z13" t="s">
         <v>327</v>
       </c>
       <c r="AA13">
-        <v>0.99592595200224132</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB13">
-        <v>74.690879958909605</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD13" t="s">
         <v>264</v>
@@ -7174,16 +7195,16 @@
         <v>351</v>
       </c>
       <c r="AM13" t="s">
+        <v>395</v>
+      </c>
+      <c r="AN13" t="s">
         <v>396</v>
       </c>
-      <c r="AN13" t="s">
-        <v>397</v>
-      </c>
       <c r="AO13">
-        <v>0.99172545486986263</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP13">
-        <v>151.6999940525175</v>
+        <v>428.87734626058102</v>
       </c>
       <c r="AR13" t="s">
         <v>264</v>
@@ -7210,16 +7231,16 @@
         <v>431</v>
       </c>
       <c r="BA13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="BB13" t="s">
-        <v>452</v>
+        <v>341</v>
       </c>
       <c r="BC13">
-        <v>0.99567841910080701</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD13">
-        <v>79.228983151871589</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7284,16 +7305,16 @@
         <v>273</v>
       </c>
       <c r="Y14" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="Z14" t="s">
         <v>328</v>
       </c>
       <c r="AA14">
-        <v>0.98069219916089656</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB14">
-        <v>353.97634871689564</v>
+        <v>123.22027201244609</v>
       </c>
       <c r="AD14" t="s">
         <v>264</v>
@@ -7320,16 +7341,16 @@
         <v>353</v>
       </c>
       <c r="AM14" t="s">
+        <v>397</v>
+      </c>
+      <c r="AN14" t="s">
         <v>398</v>
       </c>
-      <c r="AN14" t="s">
-        <v>334</v>
-      </c>
       <c r="AO14">
-        <v>0.98910099910393146</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP14">
-        <v>199.81501642792259</v>
+        <v>314.22828490220974</v>
       </c>
       <c r="AR14" t="s">
         <v>264</v>
@@ -7356,16 +7377,16 @@
         <v>433</v>
       </c>
       <c r="BA14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="BB14" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="BC14">
-        <v>0.99630507039782612</v>
+        <v>0.99790507974591136</v>
       </c>
       <c r="BD14">
-        <v>67.740376039854553</v>
+        <v>38.406871324958367</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7430,16 +7451,16 @@
         <v>275</v>
       </c>
       <c r="Y15" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="Z15" t="s">
         <v>329</v>
       </c>
       <c r="AA15">
-        <v>0.99022266246501978</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB15">
-        <v>179.25118814130403</v>
+        <v>161.73530211859338</v>
       </c>
       <c r="AD15" t="s">
         <v>264</v>
@@ -7469,13 +7490,13 @@
         <v>399</v>
       </c>
       <c r="AN15" t="s">
-        <v>400</v>
+        <v>332</v>
       </c>
       <c r="AO15">
-        <v>0.97660669020396829</v>
+        <v>0.98901431127571227</v>
       </c>
       <c r="AP15">
-        <v>428.87734626058102</v>
+        <v>201.40429327860801</v>
       </c>
       <c r="AR15" t="s">
         <v>264</v>
@@ -7502,16 +7523,16 @@
         <v>435</v>
       </c>
       <c r="BA15" t="s">
+        <v>453</v>
+      </c>
+      <c r="BB15" t="s">
         <v>454</v>
       </c>
-      <c r="BB15" t="s">
-        <v>329</v>
-      </c>
       <c r="BC15">
-        <v>0.99749257613418407</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD15">
-        <v>45.969437539958705</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7576,16 +7597,16 @@
         <v>277</v>
       </c>
       <c r="Y16" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="Z16" t="s">
         <v>330</v>
       </c>
       <c r="AA16">
-        <v>0.99787844392938518</v>
+        <v>0.99806574344338672</v>
       </c>
       <c r="AB16">
-        <v>38.895194627939205</v>
+        <v>35.461370204576532</v>
       </c>
       <c r="AD16" t="s">
         <v>264</v>
@@ -7612,16 +7633,16 @@
         <v>357</v>
       </c>
       <c r="AM16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AN16" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="AO16">
-        <v>0.97472458044977373</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP16">
-        <v>463.38269175414888</v>
+        <v>244.33232853837262</v>
       </c>
       <c r="AR16" t="s">
         <v>264</v>
@@ -7651,13 +7672,13 @@
         <v>455</v>
       </c>
       <c r="BB16" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="BC16">
-        <v>0.99722114454285371</v>
+        <v>0.99504452373263619</v>
       </c>
       <c r="BD16">
-        <v>50.94568338101594</v>
+        <v>90.850398235003013</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7689,10 +7710,10 @@
         <v>241</v>
       </c>
       <c r="L17">
-        <v>3.9552307996088447</v>
+        <v>3.9152307996088447</v>
       </c>
       <c r="M17">
-        <v>0.2301224015067071</v>
+        <v>0.23007356697625059</v>
       </c>
       <c r="O17" t="s">
         <v>264</v>
@@ -7722,16 +7743,16 @@
         <v>279</v>
       </c>
       <c r="Y17" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="Z17" t="s">
         <v>331</v>
       </c>
       <c r="AA17">
-        <v>0.99219647908939179</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB17">
-        <v>143.06455002781746</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD17" t="s">
         <v>264</v>
@@ -7758,16 +7779,16 @@
         <v>359</v>
       </c>
       <c r="AM17" t="s">
+        <v>401</v>
+      </c>
+      <c r="AN17" t="s">
         <v>402</v>
       </c>
-      <c r="AN17" t="s">
-        <v>336</v>
-      </c>
       <c r="AO17">
-        <v>0.99228583594785691</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP17">
-        <v>141.42634095595602</v>
+        <v>47.407781945483563</v>
       </c>
       <c r="AR17" t="s">
         <v>264</v>
@@ -7794,16 +7815,16 @@
         <v>439</v>
       </c>
       <c r="BA17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="BB17" t="s">
-        <v>329</v>
+        <v>454</v>
       </c>
       <c r="BC17">
-        <v>0.9940284706913598</v>
+        <v>0.99417680250918639</v>
       </c>
       <c r="BD17">
-        <v>109.47803732507046</v>
+        <v>106.75862066491723</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7868,16 +7889,16 @@
         <v>281</v>
       </c>
       <c r="Y18" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="Z18" t="s">
         <v>332</v>
       </c>
       <c r="AA18">
-        <v>0.99199432528561049</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB18">
-        <v>146.77070309714048</v>
+        <v>596.34855668384682</v>
       </c>
       <c r="AD18" t="s">
         <v>264</v>
@@ -7910,10 +7931,10 @@
         <v>404</v>
       </c>
       <c r="AO18">
-        <v>0.99740231224454534</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP18">
-        <v>47.624275516669421</v>
+        <v>263.43637771155954</v>
       </c>
       <c r="AR18" t="s">
         <v>264</v>
@@ -7940,16 +7961,16 @@
         <v>441</v>
       </c>
       <c r="BA18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="BB18" t="s">
-        <v>456</v>
+        <v>341</v>
       </c>
       <c r="BC18">
-        <v>0.99417680250918639</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD18">
-        <v>106.75862066491723</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7981,10 +8002,10 @@
         <v>243</v>
       </c>
       <c r="L19">
-        <v>11.786576720249853</v>
+        <v>11.666576720249854</v>
       </c>
       <c r="M19">
-        <v>0.25369869095953879</v>
+        <v>0.25369066917663968</v>
       </c>
       <c r="O19" t="s">
         <v>264</v>
@@ -8014,16 +8035,16 @@
         <v>283</v>
       </c>
       <c r="Y19" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="Z19" t="s">
         <v>333</v>
       </c>
       <c r="AA19">
-        <v>0.99686513787774389</v>
+        <v>0.99585223303701842</v>
       </c>
       <c r="AB19">
-        <v>57.472472241362951</v>
+        <v>76.042394321328146</v>
       </c>
       <c r="AD19" t="s">
         <v>264</v>
@@ -8053,13 +8074,13 @@
         <v>405</v>
       </c>
       <c r="AN19" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AO19">
-        <v>0.98870306310272893</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP19">
-        <v>207.11050978330246</v>
+        <v>122.76624010910177</v>
       </c>
       <c r="AR19" t="s">
         <v>264</v>
@@ -8086,16 +8107,16 @@
         <v>443</v>
       </c>
       <c r="BA19" t="s">
+        <v>458</v>
+      </c>
+      <c r="BB19" t="s">
         <v>459</v>
       </c>
-      <c r="BB19" t="s">
-        <v>452</v>
-      </c>
       <c r="BC19">
-        <v>0.99790507974591136</v>
+        <v>0.99264898847830307</v>
       </c>
       <c r="BD19">
-        <v>38.406871324958367</v>
+        <v>134.76854456444406</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8160,16 +8181,16 @@
         <v>285</v>
       </c>
       <c r="Y20" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Z20" t="s">
         <v>334</v>
       </c>
       <c r="AA20">
-        <v>0.99184104324003575</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB20">
-        <v>149.58087393267732</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD20" t="s">
         <v>264</v>
@@ -8196,16 +8217,16 @@
         <v>365</v>
       </c>
       <c r="AM20" t="s">
+        <v>406</v>
+      </c>
+      <c r="AN20" t="s">
         <v>407</v>
       </c>
-      <c r="AN20" t="s">
-        <v>338</v>
-      </c>
       <c r="AO20">
-        <v>0.98667278207972509</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP20">
-        <v>244.33232853837262</v>
+        <v>99.241487561376104</v>
       </c>
       <c r="AR20" t="s">
         <v>264</v>
@@ -8235,13 +8256,13 @@
         <v>460</v>
       </c>
       <c r="BB20" t="s">
-        <v>329</v>
+        <v>452</v>
       </c>
       <c r="BC20">
-        <v>0.99660062084319445</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD20">
-        <v>62.321951208100806</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8312,10 +8333,10 @@
         <v>335</v>
       </c>
       <c r="AA21">
-        <v>0.99782085777346563</v>
+        <v>0.9978225971936725</v>
       </c>
       <c r="AB21">
-        <v>39.950940819796543</v>
+        <v>39.919051449338276</v>
       </c>
       <c r="AD21" t="s">
         <v>264</v>
@@ -8345,13 +8366,13 @@
         <v>408</v>
       </c>
       <c r="AN21" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AO21">
-        <v>0.98615336674947807</v>
+        <v>0.99218690980150615</v>
       </c>
       <c r="AP21">
-        <v>253.85494292623497</v>
+        <v>143.23998697238727</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8383,10 +8404,10 @@
         <v>246</v>
       </c>
       <c r="L22">
-        <v>14.958068869507889</v>
+        <v>14.907068869507889</v>
       </c>
       <c r="M22">
-        <v>0.23354545132238791</v>
+        <v>0.23351391851419959</v>
       </c>
       <c r="O22" t="s">
         <v>264</v>
@@ -8416,16 +8437,16 @@
         <v>289</v>
       </c>
       <c r="Y22" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Z22" t="s">
         <v>336</v>
       </c>
       <c r="AA22">
-        <v>0.98497581152539015</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB22">
-        <v>275.44345536784743</v>
+        <v>38.895194627939205</v>
       </c>
       <c r="AD22" t="s">
         <v>264</v>
@@ -8455,13 +8476,13 @@
         <v>409</v>
       </c>
       <c r="AN22" t="s">
-        <v>410</v>
+        <v>337</v>
       </c>
       <c r="AO22">
-        <v>0.99458682795119768</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP22">
-        <v>99.241487561376104</v>
+        <v>199.81501642792259</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8526,16 +8547,16 @@
         <v>291</v>
       </c>
       <c r="Y23" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="Z23" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AA23">
-        <v>0.98551105518500948</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB23">
-        <v>265.63065494149328</v>
+        <v>195.2596724360663</v>
       </c>
       <c r="AD23" t="s">
         <v>264</v>
@@ -8562,16 +8583,16 @@
         <v>371</v>
       </c>
       <c r="AM23" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AN23" t="s">
-        <v>412</v>
+        <v>337</v>
       </c>
       <c r="AO23">
-        <v>0.9934827767968939</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP23">
-        <v>119.4824253902779</v>
+        <v>243.83038212667131</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8636,16 +8657,16 @@
         <v>293</v>
       </c>
       <c r="Y24" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="Z24" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="AA24">
-        <v>0.99326495911353319</v>
+        <v>0.99182980512008645</v>
       </c>
       <c r="AB24">
-        <v>123.47574958522414</v>
+        <v>149.78690613174817</v>
       </c>
       <c r="AD24" t="s">
         <v>264</v>
@@ -8672,16 +8693,16 @@
         <v>373</v>
       </c>
       <c r="AM24" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AN24" t="s">
-        <v>336</v>
+        <v>412</v>
       </c>
       <c r="AO24">
-        <v>0.99486941977940613</v>
+        <v>0.9934827767968939</v>
       </c>
       <c r="AP24">
-        <v>94.060637377553505</v>
+        <v>119.4824253902779</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8746,16 +8767,16 @@
         <v>295</v>
       </c>
       <c r="Y25" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="Z25" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AA25">
-        <v>0.99021329006024306</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB25">
-        <v>179.42301556221076</v>
+        <v>461.61265467993644</v>
       </c>
       <c r="AD25" t="s">
         <v>264</v>
@@ -8782,16 +8803,16 @@
         <v>375</v>
       </c>
       <c r="AM25" t="s">
+        <v>413</v>
+      </c>
+      <c r="AN25" t="s">
         <v>414</v>
       </c>
-      <c r="AN25" t="s">
-        <v>415</v>
-      </c>
       <c r="AO25">
-        <v>0.99567808239070055</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP25">
-        <v>79.235156170489844</v>
+        <v>118.22451183716133</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8856,16 +8877,16 @@
         <v>297</v>
       </c>
       <c r="Y26" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="Z26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AA26">
-        <v>0.99117807442989492</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB26">
-        <v>161.73530211859338</v>
+        <v>353.97634871689564</v>
       </c>
       <c r="AD26" t="s">
         <v>264</v>
@@ -8892,16 +8913,16 @@
         <v>377</v>
       </c>
       <c r="AM26" t="s">
+        <v>415</v>
+      </c>
+      <c r="AN26" t="s">
         <v>416</v>
       </c>
-      <c r="AN26" t="s">
-        <v>406</v>
-      </c>
       <c r="AO26">
-        <v>0.99330365963041267</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP26">
-        <v>122.76624010910177</v>
+        <v>151.6999940525175</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8933,10 +8954,10 @@
         <v>251</v>
       </c>
       <c r="L27">
-        <v>3.4722775462637423</v>
+        <v>3.4322775462637423</v>
       </c>
       <c r="M27">
-        <v>0.22878422375200849</v>
+        <v>0.22877912018714369</v>
       </c>
       <c r="O27" t="s">
         <v>264</v>
@@ -8969,7 +8990,7 @@
         <v>240</v>
       </c>
       <c r="Z27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AA27">
         <v>0.99824425800348515</v>
@@ -9005,13 +9026,13 @@
         <v>417</v>
       </c>
       <c r="AN27" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="AO27">
-        <v>0.98286027536897036</v>
+        <v>0.99738740863516284</v>
       </c>
       <c r="AP27">
-        <v>314.22828490220974</v>
+        <v>47.897508355348883</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9076,16 +9097,16 @@
         <v>301</v>
       </c>
       <c r="Y28" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AA28">
-        <v>0.99065498411395791</v>
+        <v>0.99515835423076238</v>
       </c>
       <c r="AB28">
-        <v>171.32529124410425</v>
+        <v>88.763505769357138</v>
       </c>
       <c r="AD28" t="s">
         <v>264</v>
@@ -9112,16 +9133,16 @@
         <v>381</v>
       </c>
       <c r="AM28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO28">
-        <v>0.99741412098479176</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP28">
-        <v>47.407781945483563</v>
+        <v>100.3265162100753</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9186,16 +9207,16 @@
         <v>303</v>
       </c>
       <c r="Y29" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="Z29" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA29">
-        <v>0.99806216160693018</v>
+        <v>0.99326495911353319</v>
       </c>
       <c r="AB29">
-        <v>35.52703720627968</v>
+        <v>123.47574958522414</v>
       </c>
       <c r="AD29" t="s">
         <v>264</v>
@@ -9222,16 +9243,16 @@
         <v>383</v>
       </c>
       <c r="AM29" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN29" t="s">
-        <v>421</v>
+        <v>332</v>
       </c>
       <c r="AO29">
-        <v>0.98563074303391496</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP29">
-        <v>263.43637771155954</v>
+        <v>463.38269175414888</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9299,13 +9320,13 @@
         <v>243</v>
       </c>
       <c r="Z30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA30">
-        <v>0.99594698839866214</v>
+        <v>0.99592997806909844</v>
       </c>
       <c r="AB30">
-        <v>74.305212691194157</v>
+        <v>74.617068733196106</v>
       </c>
       <c r="AD30" t="s">
         <v>264</v>
@@ -9335,13 +9356,13 @@
         <v>422</v>
       </c>
       <c r="AN30" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AO30">
-        <v>0.99059324986934494</v>
+        <v>0.99486941977940613</v>
       </c>
       <c r="AP30">
-        <v>172.45708572867548</v>
+        <v>94.060637377553505</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9406,16 +9427,16 @@
         <v>307</v>
       </c>
       <c r="Y31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Z31" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AA31">
-        <v>0.97482112792654896</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB31">
-        <v>461.61265467993644</v>
+        <v>285.85663191255094</v>
       </c>
       <c r="AD31" t="s">
         <v>264</v>
@@ -9445,13 +9466,13 @@
         <v>423</v>
       </c>
       <c r="AN31" t="s">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="AO31">
-        <v>0.98907459074885506</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP31">
-        <v>200.2991696043234</v>
+        <v>207.11050978330246</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9516,16 +9537,16 @@
         <v>309</v>
       </c>
       <c r="Y32" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="Z32" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="AA32">
-        <v>0.99260409516666881</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB32">
-        <v>135.59158861107267</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD32" t="s">
         <v>264</v>
@@ -9555,13 +9576,13 @@
         <v>424</v>
       </c>
       <c r="AN32" t="s">
-        <v>334</v>
+        <v>425</v>
       </c>
       <c r="AO32">
-        <v>0.98670016097490887</v>
+        <v>0.99495603624977191</v>
       </c>
       <c r="AP32">
-        <v>243.83038212667131</v>
+        <v>92.472668754182365</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9593,10 +9614,10 @@
         <v>257</v>
       </c>
       <c r="L33">
-        <v>13.40311107600413</v>
+        <v>13.34911107600413</v>
       </c>
       <c r="M33">
-        <v>0.2357479849120028</v>
+        <v>0.2357600371105483</v>
       </c>
       <c r="O33" t="s">
         <v>264</v>
@@ -9626,16 +9647,16 @@
         <v>311</v>
       </c>
       <c r="Y33" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Z33" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AA33">
-        <v>0.99327889425386662</v>
+        <v>0.98549080961480506</v>
       </c>
       <c r="AB33">
-        <v>123.22027201244609</v>
+        <v>266.00182372857381</v>
       </c>
       <c r="AD33" t="s">
         <v>264</v>
@@ -9662,16 +9683,16 @@
         <v>391</v>
       </c>
       <c r="AM33" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN33" t="s">
-        <v>426</v>
+        <v>341</v>
       </c>
       <c r="AO33">
-        <v>0.99355139026342754</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP33">
-        <v>118.22451183716133</v>
+        <v>172.45708572867548</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9703,10 +9724,10 @@
         <v>258</v>
       </c>
       <c r="L34">
-        <v>17.135920894226487</v>
+        <v>17.103920894226487</v>
       </c>
       <c r="M34">
-        <v>0.24195369464045599</v>
+        <v>0.2419772556712306</v>
       </c>
       <c r="O34" t="s">
         <v>264</v>
@@ -9736,16 +9757,16 @@
         <v>313</v>
       </c>
       <c r="Y34" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Z34" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AA34">
-        <v>0.98440782007749728</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB34">
-        <v>285.85663191255094</v>
+        <v>143.06455002781746</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9810,16 +9831,16 @@
         <v>315</v>
       </c>
       <c r="Y35" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Z35" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA35">
-        <v>0.99585076637156988</v>
+        <v>0.99021329006024306</v>
       </c>
       <c r="AB35">
-        <v>76.069283187886086</v>
+        <v>179.42301556221076</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9884,16 +9905,16 @@
         <v>317</v>
       </c>
       <c r="Y36" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="Z36" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AA36">
-        <v>0.9893494724125782</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB36">
-        <v>195.2596724360663</v>
+        <v>449.45770041728053</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9958,16 +9979,16 @@
         <v>319</v>
       </c>
       <c r="Y37" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Z37" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="AA37">
-        <v>0.97548412543178475</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB37">
-        <v>449.45770041728053</v>
+        <v>179.25118814130403</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10032,16 +10053,16 @@
         <v>321</v>
       </c>
       <c r="Y38" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="Z38" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AA38">
-        <v>0.96747189690815383</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB38">
-        <v>596.34855668384682</v>
+        <v>171.32529124410425</v>
       </c>
     </row>
   </sheetData>
@@ -10050,7 +10071,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8000A4-91F8-496D-B27D-ABF531258964}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90F5EC30-55E6-49D3-A76E-668985E22549}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10162,7 +10183,7 @@
         <v>461</v>
       </c>
       <c r="K11" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10195,7 +10216,7 @@
         <v>507</v>
       </c>
       <c r="X11" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="Y11">
         <v>8.3782499999999995</v>
@@ -10230,7 +10251,7 @@
         <v>463</v>
       </c>
       <c r="K12" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10263,7 +10284,7 @@
         <v>509</v>
       </c>
       <c r="X12" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10298,13 +10319,13 @@
         <v>465</v>
       </c>
       <c r="K13" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="L13">
-        <v>1.5817501567892978</v>
+        <v>1.5457501567892977</v>
       </c>
       <c r="M13">
-        <v>0.33309194745150211</v>
+        <v>0.33112229530629328</v>
       </c>
       <c r="O13" t="s">
         <v>172</v>
@@ -10331,7 +10352,7 @@
         <v>511</v>
       </c>
       <c r="X13" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10366,7 +10387,7 @@
         <v>467</v>
       </c>
       <c r="K14" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10399,7 +10420,7 @@
         <v>513</v>
       </c>
       <c r="X14" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10434,7 +10455,7 @@
         <v>469</v>
       </c>
       <c r="K15" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10467,7 +10488,7 @@
         <v>515</v>
       </c>
       <c r="X15" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10502,7 +10523,7 @@
         <v>471</v>
       </c>
       <c r="K16" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10535,7 +10556,7 @@
         <v>517</v>
       </c>
       <c r="X16" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10570,7 +10591,7 @@
         <v>473</v>
       </c>
       <c r="K17" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10603,7 +10624,7 @@
         <v>519</v>
       </c>
       <c r="X17" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="Y17">
         <v>2.2530000000000001</v>
@@ -10638,7 +10659,7 @@
         <v>475</v>
       </c>
       <c r="K18" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10671,7 +10692,7 @@
         <v>521</v>
       </c>
       <c r="X18" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Y18">
         <v>6.1852499999999999</v>
@@ -10706,7 +10727,7 @@
         <v>477</v>
       </c>
       <c r="K19" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10739,7 +10760,7 @@
         <v>523</v>
       </c>
       <c r="X19" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="Y19">
         <v>10.093500000000001</v>
@@ -10774,7 +10795,7 @@
         <v>479</v>
       </c>
       <c r="K20" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10807,7 +10828,7 @@
         <v>525</v>
       </c>
       <c r="X20" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10842,13 +10863,13 @@
         <v>481</v>
       </c>
       <c r="K21" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="L21">
-        <v>15.316017274089829</v>
+        <v>15.01601727408983</v>
       </c>
       <c r="M21">
-        <v>0.3404851337933279</v>
+        <v>0.33786342072929448</v>
       </c>
     </row>
     <row r="22" spans="2:26">
@@ -10877,7 +10898,7 @@
         <v>483</v>
       </c>
       <c r="K22" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10912,13 +10933,13 @@
         <v>485</v>
       </c>
       <c r="K23" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="L23">
-        <v>15.32235174795542</v>
+        <v>15.012351747955419</v>
       </c>
       <c r="M23">
-        <v>0.4985435282620107</v>
+        <v>0.49858993991698319</v>
       </c>
     </row>
     <row r="24" spans="2:26">
@@ -10982,7 +11003,7 @@
         <v>489</v>
       </c>
       <c r="K25" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -11017,7 +11038,7 @@
         <v>491</v>
       </c>
       <c r="K26" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -11052,7 +11073,7 @@
         <v>493</v>
       </c>
       <c r="K27" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -11087,7 +11108,7 @@
         <v>495</v>
       </c>
       <c r="K28" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11122,7 +11143,7 @@
         <v>497</v>
       </c>
       <c r="K29" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11157,7 +11178,7 @@
         <v>499</v>
       </c>
       <c r="K30" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11192,7 +11213,7 @@
         <v>501</v>
       </c>
       <c r="K31" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11227,13 +11248,13 @@
         <v>503</v>
       </c>
       <c r="K32" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="L32">
-        <v>0.91282903432358287</v>
+        <v>0.72632903432358276</v>
       </c>
       <c r="M32">
-        <v>9.9312871764815305E-2</v>
+        <v>9.8750472338972398E-2</v>
       </c>
     </row>
     <row r="33" spans="2:13">
@@ -11262,7 +11283,7 @@
         <v>505</v>
       </c>
       <c r="K33" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11277,19 +11298,19 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C768E56-14F3-432A-B046-3CDD4A6FA9EE}">
-  <dimension ref="B9:P73"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{094883D2-0506-40B7-BDC6-3BA19470CB22}">
+  <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:19">
       <c r="B9" t="s">
         <v>231</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:19">
       <c r="B10" t="s">
         <v>166</v>
       </c>
@@ -11300,450 +11321,477 @@
         <v>232</v>
       </c>
       <c r="E10">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F10">
         <v>2030</v>
       </c>
       <c r="G10">
+        <v>2035</v>
+      </c>
+      <c r="H10">
+        <v>2040</v>
+      </c>
+      <c r="I10">
+        <v>2045</v>
+      </c>
+      <c r="J10">
         <v>2050</v>
       </c>
-      <c r="H10" t="s">
+      <c r="K10" t="s">
         <v>54</v>
       </c>
-      <c r="J10" t="s">
+      <c r="M10" t="s">
         <v>165</v>
       </c>
-      <c r="K10" t="s">
+      <c r="N10" t="s">
         <v>166</v>
       </c>
-      <c r="L10" t="s">
+      <c r="O10" t="s">
         <v>167</v>
       </c>
-      <c r="M10" t="s">
+      <c r="P10" t="s">
         <v>168</v>
       </c>
-      <c r="N10" t="s">
+      <c r="Q10" t="s">
         <v>169</v>
       </c>
-      <c r="O10" t="s">
+      <c r="R10" t="s">
         <v>170</v>
       </c>
-      <c r="P10" t="s">
+      <c r="S10" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:19">
       <c r="B11" t="s">
         <v>527</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11">
-        <v>0.30000000000000004</v>
+        <v>700</v>
       </c>
       <c r="F11">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="G11">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="H11" t="s">
-        <v>146</v>
-      </c>
-      <c r="J11" t="s">
+        <v>700</v>
+      </c>
+      <c r="J11">
+        <v>700</v>
+      </c>
+      <c r="K11" t="s">
+        <v>528</v>
+      </c>
+      <c r="M11" t="s">
         <v>172</v>
       </c>
-      <c r="K11" t="s">
+      <c r="N11" t="s">
         <v>527</v>
       </c>
-      <c r="M11" t="s">
-        <v>10</v>
-      </c>
-      <c r="N11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
         <v>268</v>
       </c>
-      <c r="P11" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16">
+      <c r="S11" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
       <c r="B12" t="s">
         <v>527</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
       </c>
       <c r="E12">
-        <v>0.5</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>0.5</v>
-      </c>
-      <c r="G12">
-        <v>0.5</v>
-      </c>
-      <c r="H12" t="s">
-        <v>528</v>
-      </c>
-      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12">
+        <v>25</v>
+      </c>
+      <c r="K12" t="s">
+        <v>529</v>
+      </c>
+      <c r="M12" t="s">
         <v>172</v>
       </c>
-      <c r="K12" t="s">
-        <v>532</v>
-      </c>
-      <c r="M12" t="s">
-        <v>10</v>
-      </c>
       <c r="N12" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" t="s">
+        <v>533</v>
+      </c>
+      <c r="P12" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" t="s">
         <v>268</v>
       </c>
-      <c r="P12" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16">
+      <c r="S12" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
       <c r="B13" t="s">
         <v>527</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
       </c>
       <c r="E13">
-        <v>4900</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="F13">
-        <v>4900</v>
-      </c>
-      <c r="G13">
-        <v>4400</v>
-      </c>
-      <c r="H13" t="s">
-        <v>529</v>
-      </c>
-      <c r="J13" t="s">
-        <v>172</v>
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="J13">
+        <v>0.497</v>
       </c>
       <c r="K13" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="M13" t="s">
-        <v>10</v>
+        <v>556</v>
       </c>
       <c r="N13" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" t="s">
+        <v>534</v>
+      </c>
+      <c r="P13" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" t="s">
         <v>268</v>
       </c>
-      <c r="P13" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16">
+      <c r="S13" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19">
       <c r="B14" t="s">
         <v>527</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
       </c>
       <c r="E14">
-        <v>170</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="F14">
-        <v>170</v>
-      </c>
-      <c r="G14">
-        <v>155</v>
-      </c>
-      <c r="H14" t="s">
-        <v>530</v>
-      </c>
-      <c r="J14" t="s">
+        <v>0.59</v>
+      </c>
+      <c r="J14">
+        <v>0.59</v>
+      </c>
+      <c r="K14" t="s">
+        <v>146</v>
+      </c>
+      <c r="M14" t="s">
         <v>172</v>
       </c>
-      <c r="K14" t="s">
-        <v>534</v>
-      </c>
-      <c r="M14" t="s">
-        <v>10</v>
-      </c>
       <c r="N14" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" t="s">
+        <v>537</v>
+      </c>
+      <c r="P14" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" t="s">
         <v>268</v>
       </c>
-      <c r="P14" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16">
+      <c r="S14" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19">
       <c r="B15" t="s">
         <v>527</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G15">
-        <v>3</v>
-      </c>
-      <c r="H15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15">
+        <v>30</v>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>30</v>
+      </c>
+      <c r="K15" t="s">
         <v>531</v>
       </c>
-      <c r="J15" t="s">
+      <c r="M15" t="s">
         <v>172</v>
       </c>
-      <c r="K15" t="s">
-        <v>535</v>
-      </c>
-      <c r="M15" t="s">
-        <v>10</v>
-      </c>
       <c r="N15" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" t="s">
+        <v>538</v>
+      </c>
+      <c r="P15" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" t="s">
         <v>268</v>
       </c>
-      <c r="P15" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16">
+      <c r="S15" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
       <c r="B16" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
       </c>
       <c r="E16">
-        <v>0.35000000000000003</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>0.35000000000000003</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="H16" t="s">
-        <v>146</v>
-      </c>
-      <c r="J16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>532</v>
+      </c>
+      <c r="M16" t="s">
         <v>172</v>
       </c>
-      <c r="K16" t="s">
-        <v>536</v>
-      </c>
-      <c r="M16" t="s">
-        <v>10</v>
-      </c>
       <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
+        <v>540</v>
+      </c>
+      <c r="P16" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" t="s">
         <v>268</v>
       </c>
-      <c r="P16" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16">
+      <c r="S16" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19">
       <c r="B17" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>400</v>
       </c>
       <c r="F17">
-        <v>0.5</v>
-      </c>
-      <c r="G17">
-        <v>0.5</v>
-      </c>
-      <c r="H17" t="s">
+        <v>400</v>
+      </c>
+      <c r="J17">
+        <v>400</v>
+      </c>
+      <c r="K17" t="s">
         <v>528</v>
       </c>
-      <c r="J17" t="s">
+      <c r="M17" t="s">
         <v>172</v>
       </c>
-      <c r="K17" t="s">
-        <v>537</v>
-      </c>
-      <c r="M17" t="s">
-        <v>10</v>
-      </c>
       <c r="N17" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" t="s">
+        <v>541</v>
+      </c>
+      <c r="P17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" t="s">
         <v>268</v>
       </c>
-      <c r="P17" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16">
+      <c r="S17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
       <c r="B18" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
         <v>19</v>
       </c>
       <c r="E18">
-        <v>2150</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>2100</v>
-      </c>
-      <c r="G18">
-        <v>2050</v>
-      </c>
-      <c r="H18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18">
+        <v>20</v>
+      </c>
+      <c r="K18" t="s">
         <v>529</v>
       </c>
-      <c r="J18" t="s">
+      <c r="M18" t="s">
         <v>172</v>
       </c>
-      <c r="K18" t="s">
-        <v>538</v>
-      </c>
-      <c r="M18" t="s">
-        <v>10</v>
-      </c>
       <c r="N18" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" t="s">
+        <v>542</v>
+      </c>
+      <c r="P18" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>21</v>
+      </c>
+      <c r="R18" t="s">
         <v>268</v>
       </c>
-      <c r="P18" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16">
+      <c r="S18" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19">
       <c r="B19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
         <v>19</v>
       </c>
       <c r="E19">
-        <v>75</v>
+        <v>1.9279999999999999</v>
       </c>
       <c r="F19">
-        <v>75</v>
-      </c>
-      <c r="G19">
-        <v>70</v>
-      </c>
-      <c r="H19" t="s">
+        <v>1.9279999999999999</v>
+      </c>
+      <c r="J19">
+        <v>1.9279999999999999</v>
+      </c>
+      <c r="K19" t="s">
         <v>530</v>
       </c>
-      <c r="J19" t="s">
+      <c r="M19" t="s">
         <v>172</v>
       </c>
-      <c r="K19" t="s">
-        <v>539</v>
-      </c>
-      <c r="M19" t="s">
-        <v>10</v>
-      </c>
       <c r="N19" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" t="s">
+        <v>543</v>
+      </c>
+      <c r="P19" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" t="s">
         <v>268</v>
       </c>
-      <c r="P19" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16">
+      <c r="S19" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19">
       <c r="B20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0.38</v>
       </c>
       <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>531</v>
-      </c>
-      <c r="J20" t="s">
+        <v>0.39</v>
+      </c>
+      <c r="J20">
+        <v>0.41</v>
+      </c>
+      <c r="K20" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" t="s">
         <v>172</v>
       </c>
-      <c r="K20" t="s">
-        <v>540</v>
-      </c>
-      <c r="M20" t="s">
-        <v>10</v>
-      </c>
       <c r="N20" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" t="s">
+        <v>544</v>
+      </c>
+      <c r="P20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" t="s">
         <v>268</v>
       </c>
-      <c r="P20" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16">
+      <c r="S20" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19">
       <c r="B21" t="s">
         <v>533</v>
       </c>
@@ -11754,37 +11802,46 @@
         <v>19</v>
       </c>
       <c r="E21">
-        <v>0.57999999999999996</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>0.59</v>
+        <v>30</v>
       </c>
       <c r="G21">
-        <v>0.59</v>
-      </c>
-      <c r="H21" t="s">
-        <v>146</v>
-      </c>
-      <c r="J21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21">
+        <v>30</v>
+      </c>
+      <c r="I21">
+        <v>30</v>
+      </c>
+      <c r="J21">
+        <v>30</v>
+      </c>
+      <c r="K21" t="s">
+        <v>531</v>
+      </c>
+      <c r="M21" t="s">
         <v>172</v>
       </c>
-      <c r="K21" t="s">
-        <v>541</v>
-      </c>
-      <c r="M21" t="s">
-        <v>10</v>
-      </c>
       <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
+        <v>545</v>
+      </c>
+      <c r="P21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" t="s">
         <v>268</v>
       </c>
-      <c r="P21" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16">
+      <c r="S21" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19">
       <c r="B22" t="s">
         <v>533</v>
       </c>
@@ -11795,78 +11852,87 @@
         <v>19</v>
       </c>
       <c r="E22">
-        <v>700</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>700</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>700</v>
-      </c>
-      <c r="H22" t="s">
-        <v>529</v>
-      </c>
-      <c r="J22" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>532</v>
+      </c>
+      <c r="M22" t="s">
         <v>172</v>
       </c>
-      <c r="K22" t="s">
-        <v>542</v>
-      </c>
-      <c r="M22" t="s">
-        <v>10</v>
-      </c>
       <c r="N22" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" t="s">
+        <v>546</v>
+      </c>
+      <c r="P22" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" t="s">
         <v>268</v>
       </c>
-      <c r="P22" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16">
+      <c r="S22" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19">
       <c r="B23" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>535</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>920</v>
       </c>
       <c r="F23">
-        <v>25</v>
-      </c>
-      <c r="G23">
-        <v>25</v>
-      </c>
-      <c r="H23" t="s">
-        <v>530</v>
-      </c>
-      <c r="J23" t="s">
+        <v>920</v>
+      </c>
+      <c r="J23">
+        <v>920</v>
+      </c>
+      <c r="K23" t="s">
+        <v>528</v>
+      </c>
+      <c r="M23" t="s">
         <v>172</v>
       </c>
-      <c r="K23" t="s">
-        <v>543</v>
-      </c>
-      <c r="M23" t="s">
-        <v>10</v>
-      </c>
       <c r="N23" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" t="s">
+        <v>547</v>
+      </c>
+      <c r="P23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>21</v>
+      </c>
+      <c r="R23" t="s">
         <v>268</v>
       </c>
-      <c r="P23" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16">
+      <c r="S23" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19">
       <c r="B24" t="s">
         <v>534</v>
       </c>
@@ -11874,40 +11940,40 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>535</v>
       </c>
       <c r="E24">
-        <v>0.5</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>0.51</v>
-      </c>
-      <c r="G24">
-        <v>0.51</v>
-      </c>
-      <c r="H24" t="s">
-        <v>146</v>
-      </c>
-      <c r="J24" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24">
+        <v>35</v>
+      </c>
+      <c r="K24" t="s">
+        <v>529</v>
+      </c>
+      <c r="M24" t="s">
         <v>172</v>
       </c>
-      <c r="K24" t="s">
-        <v>544</v>
-      </c>
-      <c r="M24" t="s">
-        <v>10</v>
-      </c>
       <c r="N24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" t="s">
+        <v>548</v>
+      </c>
+      <c r="P24" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" t="s">
         <v>268</v>
       </c>
-      <c r="P24" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16">
+      <c r="S24" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19">
       <c r="B25" t="s">
         <v>534</v>
       </c>
@@ -11915,40 +11981,40 @@
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>535</v>
       </c>
       <c r="E25">
-        <v>2450</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="F25">
-        <v>2450</v>
-      </c>
-      <c r="G25">
-        <v>1850</v>
-      </c>
-      <c r="H25" t="s">
-        <v>529</v>
-      </c>
-      <c r="J25" t="s">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="J25">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="K25" t="s">
+        <v>530</v>
+      </c>
+      <c r="M25" t="s">
         <v>172</v>
       </c>
-      <c r="K25" t="s">
-        <v>545</v>
-      </c>
-      <c r="M25" t="s">
-        <v>10</v>
-      </c>
       <c r="N25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" t="s">
+        <v>549</v>
+      </c>
+      <c r="P25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" t="s">
         <v>268</v>
       </c>
-      <c r="P25" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16">
+      <c r="S25" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19">
       <c r="B26" t="s">
         <v>534</v>
       </c>
@@ -11956,129 +12022,192 @@
         <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>535</v>
       </c>
       <c r="E26">
-        <v>85</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="F26">
-        <v>85</v>
-      </c>
-      <c r="G26">
-        <v>65</v>
-      </c>
-      <c r="H26" t="s">
-        <v>530</v>
-      </c>
-      <c r="J26" t="s">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="J26">
+        <v>0.54</v>
+      </c>
+      <c r="K26" t="s">
+        <v>146</v>
+      </c>
+      <c r="M26" t="s">
         <v>172</v>
       </c>
-      <c r="K26" t="s">
-        <v>546</v>
-      </c>
-      <c r="M26" t="s">
-        <v>10</v>
-      </c>
       <c r="N26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" t="s">
+        <v>551</v>
+      </c>
+      <c r="P26" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" t="s">
         <v>268</v>
       </c>
-      <c r="P26" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16">
+      <c r="S26" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
       <c r="B27" t="s">
+        <v>534</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" t="s">
         <v>535</v>
       </c>
-      <c r="C27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" t="s">
-        <v>19</v>
-      </c>
       <c r="E27">
-        <v>0.32</v>
+        <v>25</v>
       </c>
       <c r="F27">
-        <v>0.33</v>
+        <v>25</v>
       </c>
       <c r="G27">
-        <v>0.33</v>
-      </c>
-      <c r="H27" t="s">
-        <v>146</v>
-      </c>
-      <c r="J27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <v>25</v>
+      </c>
+      <c r="J27">
+        <v>25</v>
+      </c>
+      <c r="K27" t="s">
+        <v>531</v>
+      </c>
+      <c r="M27" t="s">
+        <v>556</v>
+      </c>
+      <c r="N27" t="s">
+        <v>552</v>
+      </c>
+      <c r="P27" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" t="s">
+        <v>268</v>
+      </c>
+      <c r="S27" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19">
+      <c r="B28" t="s">
+        <v>534</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>535</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28" t="s">
+        <v>532</v>
+      </c>
+      <c r="M28" t="s">
         <v>172</v>
       </c>
-      <c r="K27" t="s">
-        <v>548</v>
-      </c>
-      <c r="M27" t="s">
-        <v>10</v>
-      </c>
-      <c r="N27" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="N28" t="s">
+        <v>553</v>
+      </c>
+      <c r="P28" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R28" t="s">
         <v>268</v>
       </c>
-      <c r="P27" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16">
-      <c r="B28" t="s">
+      <c r="S28" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19">
+      <c r="B29" t="s">
+        <v>534</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" t="s">
         <v>535</v>
       </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28">
-        <v>4500</v>
-      </c>
-      <c r="F28">
-        <v>4500</v>
-      </c>
-      <c r="G28">
-        <v>3550</v>
-      </c>
-      <c r="H28" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16">
-      <c r="B29" t="s">
-        <v>535</v>
-      </c>
-      <c r="C29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" t="s">
-        <v>19</v>
-      </c>
       <c r="E29">
-        <v>175</v>
+        <v>0.8</v>
       </c>
       <c r="F29">
-        <v>175</v>
+        <v>0.8</v>
       </c>
       <c r="G29">
-        <v>135</v>
-      </c>
-      <c r="H29" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16">
+        <v>0.8</v>
+      </c>
+      <c r="H29">
+        <v>0.8</v>
+      </c>
+      <c r="I29">
+        <v>0.8</v>
+      </c>
+      <c r="J29">
+        <v>0.8</v>
+      </c>
+      <c r="K29" t="s">
+        <v>536</v>
+      </c>
+      <c r="M29" t="s">
+        <v>172</v>
+      </c>
+      <c r="N29" t="s">
+        <v>554</v>
+      </c>
+      <c r="P29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" t="s">
+        <v>268</v>
+      </c>
+      <c r="S29" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19">
       <c r="B30" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -12087,21 +12216,21 @@
         <v>19</v>
       </c>
       <c r="E30">
-        <v>0.38</v>
+        <v>5000</v>
       </c>
       <c r="F30">
-        <v>0.39</v>
-      </c>
-      <c r="G30">
-        <v>0.41000000000000003</v>
-      </c>
-      <c r="H30" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16">
+        <v>2500</v>
+      </c>
+      <c r="J30">
+        <v>2500</v>
+      </c>
+      <c r="K30" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19">
       <c r="B31" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -12110,21 +12239,21 @@
         <v>19</v>
       </c>
       <c r="E31">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="F31">
-        <v>400</v>
-      </c>
-      <c r="G31">
-        <v>400</v>
-      </c>
-      <c r="H31" t="s">
+        <v>75</v>
+      </c>
+      <c r="J31">
+        <v>75</v>
+      </c>
+      <c r="K31" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="32" spans="2:16">
+    <row r="32" spans="2:19">
       <c r="B32" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -12133,134 +12262,152 @@
         <v>19</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="F32">
-        <v>20</v>
-      </c>
-      <c r="G32">
-        <v>20</v>
-      </c>
-      <c r="H32" t="s">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="J32">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="K32" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:11">
       <c r="B33" t="s">
         <v>537</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
         <v>19</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
+        <v>0.54</v>
+      </c>
+      <c r="J33">
+        <v>0.6</v>
+      </c>
+      <c r="K33" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:11">
       <c r="B34" t="s">
         <v>537</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
       </c>
       <c r="E34">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="F34">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="G34">
-        <v>0.5</v>
-      </c>
-      <c r="H34" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
+        <v>20</v>
+      </c>
+      <c r="H34">
+        <v>20</v>
+      </c>
+      <c r="I34">
+        <v>20</v>
+      </c>
+      <c r="J34">
+        <v>20</v>
+      </c>
+      <c r="K34" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
       <c r="B35" t="s">
         <v>537</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
       </c>
       <c r="E35">
-        <v>2100</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>2100</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>2100</v>
-      </c>
-      <c r="H35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" t="s">
+        <v>538</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" t="s">
+        <v>539</v>
+      </c>
+      <c r="E36">
+        <v>2450</v>
+      </c>
+      <c r="F36">
+        <v>2450</v>
+      </c>
+      <c r="J36">
+        <v>1950</v>
+      </c>
+      <c r="K36" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37" t="s">
+        <v>538</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s">
+        <v>539</v>
+      </c>
+      <c r="E37">
+        <v>85</v>
+      </c>
+      <c r="F37">
+        <v>85</v>
+      </c>
+      <c r="J37">
+        <v>70</v>
+      </c>
+      <c r="K37" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" t="s">
-        <v>537</v>
-      </c>
-      <c r="C36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36">
-        <v>50</v>
-      </c>
-      <c r="F36">
-        <v>50</v>
-      </c>
-      <c r="G36">
-        <v>50</v>
-      </c>
-      <c r="H36" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37" t="s">
-        <v>537</v>
-      </c>
-      <c r="C37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37">
-        <v>4</v>
-      </c>
-      <c r="F37">
-        <v>4</v>
-      </c>
-      <c r="G37">
-        <v>4</v>
-      </c>
-      <c r="H37" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:11">
       <c r="B38" t="s">
         <v>538</v>
       </c>
@@ -12268,22 +12415,22 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>539</v>
       </c>
       <c r="E38">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="F38">
-        <v>0.43</v>
-      </c>
-      <c r="G38">
-        <v>0.45</v>
-      </c>
-      <c r="H38" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8">
+        <v>1.2</v>
+      </c>
+      <c r="J38">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="K38" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
       <c r="B39" t="s">
         <v>538</v>
       </c>
@@ -12291,22 +12438,22 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>539</v>
       </c>
       <c r="E39">
-        <v>2200</v>
+        <v>0.5</v>
       </c>
       <c r="F39">
-        <v>2100</v>
-      </c>
-      <c r="G39">
-        <v>2100</v>
-      </c>
-      <c r="H39" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
+        <v>0.51</v>
+      </c>
+      <c r="J39">
+        <v>0.51</v>
+      </c>
+      <c r="K39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
       <c r="B40" t="s">
         <v>538</v>
       </c>
@@ -12314,47 +12461,65 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>539</v>
       </c>
       <c r="E40">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F40">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="G40">
-        <v>85</v>
-      </c>
-      <c r="H40" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
+        <v>30</v>
+      </c>
+      <c r="H40">
+        <v>30</v>
+      </c>
+      <c r="I40">
+        <v>30</v>
+      </c>
+      <c r="J40">
+        <v>30</v>
+      </c>
+      <c r="K40" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
       <c r="B41" t="s">
+        <v>538</v>
+      </c>
+      <c r="C41" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" t="s">
         <v>539</v>
       </c>
-      <c r="C41" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" t="s">
-        <v>19</v>
-      </c>
       <c r="E41">
-        <v>0.32</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>0.32</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="H41" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8">
+        <v>4</v>
+      </c>
+      <c r="H41">
+        <v>4</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
       <c r="B42" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -12363,21 +12528,21 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>4850</v>
+        <v>1300</v>
       </c>
       <c r="F42">
-        <v>4650</v>
-      </c>
-      <c r="G42">
-        <v>4200</v>
-      </c>
-      <c r="H42" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
+        <v>1300</v>
+      </c>
+      <c r="J42">
+        <v>1300</v>
+      </c>
+      <c r="K42" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
       <c r="B43" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -12386,90 +12551,99 @@
         <v>19</v>
       </c>
       <c r="E43">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="F43">
-        <v>210</v>
-      </c>
-      <c r="G43">
-        <v>190</v>
-      </c>
-      <c r="H43" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8">
+        <v>45</v>
+      </c>
+      <c r="J43">
+        <v>45</v>
+      </c>
+      <c r="K43" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11">
       <c r="B44" t="s">
         <v>540</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
         <v>19</v>
       </c>
       <c r="E44">
-        <v>0.33</v>
+        <v>2.3610000000000002</v>
       </c>
       <c r="F44">
-        <v>0.33</v>
-      </c>
-      <c r="G44">
-        <v>0.33</v>
-      </c>
-      <c r="H44" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="J44">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="K44" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11">
       <c r="B45" t="s">
         <v>540</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D45" t="s">
         <v>19</v>
       </c>
       <c r="E45">
-        <v>4000</v>
+        <v>0.35</v>
       </c>
       <c r="F45">
-        <v>4000</v>
-      </c>
-      <c r="G45">
-        <v>4000</v>
-      </c>
-      <c r="H45" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
+        <v>0.35</v>
+      </c>
+      <c r="J45">
+        <v>0.35</v>
+      </c>
+      <c r="K45" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
       <c r="B46" t="s">
         <v>540</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D46" t="s">
         <v>19</v>
       </c>
       <c r="E46">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="F46">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="G46">
-        <v>170</v>
-      </c>
-      <c r="H46" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
+        <v>40</v>
+      </c>
+      <c r="H46">
+        <v>40</v>
+      </c>
+      <c r="I46">
+        <v>40</v>
+      </c>
+      <c r="J46">
+        <v>40</v>
+      </c>
+      <c r="K46" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
       <c r="B47" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -12478,19 +12652,28 @@
         <v>19</v>
       </c>
       <c r="E47">
-        <v>0.33</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>0.33</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>0.33</v>
-      </c>
-      <c r="H47" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
+        <v>4</v>
+      </c>
+      <c r="H47">
+        <v>4</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+      <c r="K47" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11">
       <c r="B48" t="s">
         <v>541</v>
       </c>
@@ -12501,19 +12684,19 @@
         <v>19</v>
       </c>
       <c r="E48">
-        <v>4800</v>
+        <v>1600</v>
       </c>
       <c r="F48">
-        <v>4800</v>
-      </c>
-      <c r="G48">
-        <v>4300</v>
-      </c>
-      <c r="H48" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
+        <v>1600</v>
+      </c>
+      <c r="J48">
+        <v>1600</v>
+      </c>
+      <c r="K48" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11">
       <c r="B49" t="s">
         <v>541</v>
       </c>
@@ -12524,136 +12707,154 @@
         <v>19</v>
       </c>
       <c r="E49">
-        <v>185</v>
+        <v>55</v>
       </c>
       <c r="F49">
-        <v>185</v>
-      </c>
-      <c r="G49">
-        <v>165</v>
-      </c>
-      <c r="H49" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
+        <v>55</v>
+      </c>
+      <c r="J49">
+        <v>55</v>
+      </c>
+      <c r="K49" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
       <c r="B50" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D50" t="s">
         <v>19</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2.5830000000000002</v>
       </c>
       <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-      <c r="H50" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8">
+        <v>2.4969999999999999</v>
+      </c>
+      <c r="J50">
+        <v>2.3170000000000002</v>
+      </c>
+      <c r="K50" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
       <c r="B51" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D51" t="s">
         <v>19</v>
       </c>
       <c r="E51">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="F51">
-        <v>0.23</v>
-      </c>
-      <c r="G51">
-        <v>0.23</v>
-      </c>
-      <c r="H51" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8">
+        <v>0.39</v>
+      </c>
+      <c r="J51">
+        <v>0.39</v>
+      </c>
+      <c r="K51" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
       <c r="B52" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
         <v>19</v>
       </c>
       <c r="E52">
-        <v>1330</v>
+        <v>40</v>
       </c>
       <c r="F52">
-        <v>820</v>
+        <v>40</v>
       </c>
       <c r="G52">
-        <v>550</v>
-      </c>
-      <c r="H52" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8">
+        <v>40</v>
+      </c>
+      <c r="H52">
+        <v>40</v>
+      </c>
+      <c r="I52">
+        <v>40</v>
+      </c>
+      <c r="J52">
+        <v>40</v>
+      </c>
+      <c r="K52" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
       <c r="B53" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D53" t="s">
         <v>19</v>
       </c>
       <c r="E53">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F53">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G53">
-        <v>18</v>
-      </c>
-      <c r="H53" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8">
+        <v>4</v>
+      </c>
+      <c r="H53">
+        <v>4</v>
+      </c>
+      <c r="I53">
+        <v>4</v>
+      </c>
+      <c r="J53">
+        <v>4</v>
+      </c>
+      <c r="K53" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
       <c r="B54" t="s">
         <v>542</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D54" t="s">
         <v>19</v>
       </c>
       <c r="E54">
-        <v>1.5</v>
+        <v>1900</v>
       </c>
       <c r="F54">
-        <v>1.5</v>
-      </c>
-      <c r="G54">
-        <v>1.5</v>
-      </c>
-      <c r="H54" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8">
+        <v>1900</v>
+      </c>
+      <c r="J54">
+        <v>1900</v>
+      </c>
+      <c r="K54" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11">
       <c r="B55" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -12662,21 +12863,21 @@
         <v>19</v>
       </c>
       <c r="E55">
-        <v>0.35000000000000003</v>
+        <v>70</v>
       </c>
       <c r="F55">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="G55">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="H55" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8">
+        <v>70</v>
+      </c>
+      <c r="J55">
+        <v>70</v>
+      </c>
+      <c r="K55" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11">
       <c r="B56" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -12685,21 +12886,21 @@
         <v>19</v>
       </c>
       <c r="E56">
-        <v>1300</v>
+        <v>2.6389999999999998</v>
       </c>
       <c r="F56">
-        <v>1300</v>
-      </c>
-      <c r="G56">
-        <v>1300</v>
-      </c>
-      <c r="H56" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8">
+        <v>2.6389999999999998</v>
+      </c>
+      <c r="J56">
+        <v>2.6389999999999998</v>
+      </c>
+      <c r="K56" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
       <c r="B57" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -12708,21 +12909,21 @@
         <v>19</v>
       </c>
       <c r="E57">
-        <v>45</v>
+        <v>0.42</v>
       </c>
       <c r="F57">
-        <v>45</v>
-      </c>
-      <c r="G57">
-        <v>45</v>
-      </c>
-      <c r="H57" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8">
+        <v>0.43</v>
+      </c>
+      <c r="J57">
+        <v>0.44</v>
+      </c>
+      <c r="K57" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
       <c r="B58" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -12731,21 +12932,30 @@
         <v>19</v>
       </c>
       <c r="E58">
-        <v>0.39</v>
+        <v>40</v>
       </c>
       <c r="F58">
-        <v>0.39</v>
+        <v>40</v>
       </c>
       <c r="G58">
-        <v>0.39</v>
-      </c>
-      <c r="H58" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
+        <v>40</v>
+      </c>
+      <c r="H58">
+        <v>40</v>
+      </c>
+      <c r="I58">
+        <v>40</v>
+      </c>
+      <c r="J58">
+        <v>40</v>
+      </c>
+      <c r="K58" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -12754,21 +12964,30 @@
         <v>19</v>
       </c>
       <c r="E59">
-        <v>1600</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>1600</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>1600</v>
-      </c>
-      <c r="H59" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>4</v>
+      </c>
+      <c r="J59">
+        <v>4</v>
+      </c>
+      <c r="K59" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
       <c r="B60" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -12777,21 +12996,21 @@
         <v>19</v>
       </c>
       <c r="E60">
-        <v>55</v>
+        <v>2200</v>
       </c>
       <c r="F60">
-        <v>55</v>
-      </c>
-      <c r="G60">
-        <v>55</v>
-      </c>
-      <c r="H60" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8">
+        <v>2100</v>
+      </c>
+      <c r="J60">
+        <v>2100</v>
+      </c>
+      <c r="K60" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
       <c r="B61" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -12800,21 +13019,21 @@
         <v>19</v>
       </c>
       <c r="E61">
-        <v>0.42</v>
+        <v>90</v>
       </c>
       <c r="F61">
-        <v>0.43</v>
-      </c>
-      <c r="G61">
-        <v>0.44</v>
-      </c>
-      <c r="H61" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8">
+        <v>85</v>
+      </c>
+      <c r="J61">
+        <v>85</v>
+      </c>
+      <c r="K61" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
       <c r="B62" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -12823,21 +13042,21 @@
         <v>19</v>
       </c>
       <c r="E62">
-        <v>1900</v>
+        <v>0.4</v>
       </c>
       <c r="F62">
-        <v>1900</v>
-      </c>
-      <c r="G62">
-        <v>1900</v>
-      </c>
-      <c r="H62" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8">
+        <v>0.43</v>
+      </c>
+      <c r="J62">
+        <v>0.45</v>
+      </c>
+      <c r="K62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
       <c r="B63" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -12846,246 +13065,1733 @@
         <v>19</v>
       </c>
       <c r="E63">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F63">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G63">
-        <v>70</v>
-      </c>
-      <c r="H63" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8">
+        <v>40</v>
+      </c>
+      <c r="H63">
+        <v>40</v>
+      </c>
+      <c r="I63">
+        <v>40</v>
+      </c>
+      <c r="J63">
+        <v>40</v>
+      </c>
+      <c r="K63" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
       <c r="B64" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C64" t="s">
-        <v>547</v>
+        <v>32</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
+        <v>4</v>
+      </c>
+      <c r="H64">
+        <v>4</v>
+      </c>
+      <c r="I64">
+        <v>4</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+      <c r="K64" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" t="s">
+        <v>544</v>
+      </c>
+      <c r="C65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65" t="s">
+        <v>539</v>
+      </c>
+      <c r="E65">
+        <v>4500</v>
+      </c>
+      <c r="F65">
+        <v>4500</v>
+      </c>
+      <c r="J65">
+        <v>3650</v>
+      </c>
+      <c r="K65" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" t="s">
+        <v>544</v>
+      </c>
+      <c r="C66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" t="s">
+        <v>539</v>
+      </c>
+      <c r="E66">
+        <v>175</v>
+      </c>
+      <c r="F66">
+        <v>175</v>
+      </c>
+      <c r="J66">
+        <v>140</v>
+      </c>
+      <c r="K66" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" t="s">
+        <v>544</v>
+      </c>
+      <c r="C67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" t="s">
+        <v>539</v>
+      </c>
+      <c r="E67">
+        <v>4.4779999999999998</v>
+      </c>
+      <c r="F67">
+        <v>4.1529999999999996</v>
+      </c>
+      <c r="J67">
+        <v>3.7309999999999999</v>
+      </c>
+      <c r="K67" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" t="s">
+        <v>544</v>
+      </c>
+      <c r="C68" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" t="s">
+        <v>539</v>
+      </c>
+      <c r="E68">
+        <v>0.32</v>
+      </c>
+      <c r="F68">
+        <v>0.33</v>
+      </c>
+      <c r="J68">
+        <v>0.33</v>
+      </c>
+      <c r="K68" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
-      <c r="B65" t="s">
+    <row r="69" spans="2:11">
+      <c r="B69" t="s">
+        <v>544</v>
+      </c>
+      <c r="C69" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" t="s">
+        <v>539</v>
+      </c>
+      <c r="E69">
+        <v>40</v>
+      </c>
+      <c r="F69">
+        <v>40</v>
+      </c>
+      <c r="G69">
+        <v>40</v>
+      </c>
+      <c r="H69">
+        <v>40</v>
+      </c>
+      <c r="I69">
+        <v>40</v>
+      </c>
+      <c r="J69">
+        <v>40</v>
+      </c>
+      <c r="K69" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="B70" t="s">
+        <v>544</v>
+      </c>
+      <c r="C70" t="s">
+        <v>32</v>
+      </c>
+      <c r="D70" t="s">
+        <v>539</v>
+      </c>
+      <c r="E70">
+        <v>5</v>
+      </c>
+      <c r="F70">
+        <v>5</v>
+      </c>
+      <c r="G70">
+        <v>5</v>
+      </c>
+      <c r="H70">
+        <v>5</v>
+      </c>
+      <c r="I70">
+        <v>5</v>
+      </c>
+      <c r="J70">
+        <v>5</v>
+      </c>
+      <c r="K70" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
+      <c r="B71" t="s">
+        <v>545</v>
+      </c>
+      <c r="C71" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" t="s">
+        <v>539</v>
+      </c>
+      <c r="E71">
+        <v>4850</v>
+      </c>
+      <c r="F71">
+        <v>4650</v>
+      </c>
+      <c r="J71">
+        <v>4250</v>
+      </c>
+      <c r="K71" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="B72" t="s">
+        <v>545</v>
+      </c>
+      <c r="C72" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" t="s">
+        <v>539</v>
+      </c>
+      <c r="E72">
+        <v>220</v>
+      </c>
+      <c r="F72">
+        <v>210</v>
+      </c>
+      <c r="J72">
+        <v>190</v>
+      </c>
+      <c r="K72" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
+      <c r="B73" t="s">
+        <v>545</v>
+      </c>
+      <c r="C73" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" t="s">
+        <v>539</v>
+      </c>
+      <c r="E73">
+        <v>4.5830000000000002</v>
+      </c>
+      <c r="F73">
+        <v>4.5830000000000002</v>
+      </c>
+      <c r="J73">
+        <v>4.5830000000000002</v>
+      </c>
+      <c r="K73" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" t="s">
+        <v>545</v>
+      </c>
+      <c r="C74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" t="s">
+        <v>539</v>
+      </c>
+      <c r="E74">
+        <v>0.32</v>
+      </c>
+      <c r="F74">
+        <v>0.32</v>
+      </c>
+      <c r="J74">
+        <v>0.35</v>
+      </c>
+      <c r="K74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="B75" t="s">
+        <v>545</v>
+      </c>
+      <c r="C75" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75" t="s">
+        <v>539</v>
+      </c>
+      <c r="E75">
+        <v>40</v>
+      </c>
+      <c r="F75">
+        <v>40</v>
+      </c>
+      <c r="G75">
+        <v>40</v>
+      </c>
+      <c r="H75">
+        <v>40</v>
+      </c>
+      <c r="I75">
+        <v>40</v>
+      </c>
+      <c r="J75">
+        <v>40</v>
+      </c>
+      <c r="K75" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" t="s">
+        <v>545</v>
+      </c>
+      <c r="C76" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" t="s">
+        <v>539</v>
+      </c>
+      <c r="E76">
+        <v>5</v>
+      </c>
+      <c r="F76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>5</v>
+      </c>
+      <c r="H76">
+        <v>5</v>
+      </c>
+      <c r="I76">
+        <v>5</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
+      <c r="K76" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" t="s">
         <v>546</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C77" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" t="s">
+        <v>539</v>
+      </c>
+      <c r="E77">
+        <v>4800</v>
+      </c>
+      <c r="F77">
+        <v>4800</v>
+      </c>
+      <c r="J77">
+        <v>4350</v>
+      </c>
+      <c r="K77" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" t="s">
+        <v>546</v>
+      </c>
+      <c r="C78" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78" t="s">
+        <v>539</v>
+      </c>
+      <c r="E78">
+        <v>185</v>
+      </c>
+      <c r="F78">
+        <v>185</v>
+      </c>
+      <c r="J78">
+        <v>165</v>
+      </c>
+      <c r="K78" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" t="s">
+        <v>546</v>
+      </c>
+      <c r="C79" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79" t="s">
+        <v>539</v>
+      </c>
+      <c r="E79">
+        <v>4.306</v>
+      </c>
+      <c r="F79">
+        <v>4.306</v>
+      </c>
+      <c r="J79">
+        <v>4.306</v>
+      </c>
+      <c r="K79" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" t="s">
+        <v>546</v>
+      </c>
+      <c r="C80" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80" t="s">
+        <v>539</v>
+      </c>
+      <c r="E80">
+        <v>0.33</v>
+      </c>
+      <c r="F80">
+        <v>0.33</v>
+      </c>
+      <c r="J80">
+        <v>0.33</v>
+      </c>
+      <c r="K80" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" t="s">
+        <v>546</v>
+      </c>
+      <c r="C81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81" t="s">
+        <v>539</v>
+      </c>
+      <c r="E81">
+        <v>40</v>
+      </c>
+      <c r="F81">
+        <v>40</v>
+      </c>
+      <c r="G81">
+        <v>40</v>
+      </c>
+      <c r="H81">
+        <v>40</v>
+      </c>
+      <c r="I81">
+        <v>40</v>
+      </c>
+      <c r="J81">
+        <v>40</v>
+      </c>
+      <c r="K81" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" t="s">
+        <v>546</v>
+      </c>
+      <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" t="s">
+        <v>539</v>
+      </c>
+      <c r="E82">
+        <v>5</v>
+      </c>
+      <c r="F82">
+        <v>5</v>
+      </c>
+      <c r="G82">
+        <v>5</v>
+      </c>
+      <c r="H82">
+        <v>5</v>
+      </c>
+      <c r="I82">
+        <v>5</v>
+      </c>
+      <c r="J82">
+        <v>5</v>
+      </c>
+      <c r="K82" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" t="s">
         <v>547</v>
       </c>
-      <c r="D65" t="s">
+      <c r="C83" t="s">
+        <v>36</v>
+      </c>
+      <c r="D83" t="s">
         <v>19</v>
       </c>
-      <c r="E65">
+      <c r="E83">
+        <v>4000</v>
+      </c>
+      <c r="F83">
+        <v>4000</v>
+      </c>
+      <c r="J83">
+        <v>4000</v>
+      </c>
+      <c r="K83" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" t="s">
+        <v>547</v>
+      </c>
+      <c r="C84" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84">
+        <v>170</v>
+      </c>
+      <c r="F84">
+        <v>170</v>
+      </c>
+      <c r="J84">
+        <v>170</v>
+      </c>
+      <c r="K84" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" t="s">
+        <v>547</v>
+      </c>
+      <c r="C85" t="s">
+        <v>36</v>
+      </c>
+      <c r="D85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="J85">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="K85" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" t="s">
+        <v>547</v>
+      </c>
+      <c r="C86" t="s">
+        <v>36</v>
+      </c>
+      <c r="D86" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86">
+        <v>60</v>
+      </c>
+      <c r="F86">
+        <v>60</v>
+      </c>
+      <c r="G86">
+        <v>60</v>
+      </c>
+      <c r="H86">
+        <v>60</v>
+      </c>
+      <c r="I86">
+        <v>60</v>
+      </c>
+      <c r="J86">
+        <v>60</v>
+      </c>
+      <c r="K86" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" t="s">
+        <v>547</v>
+      </c>
+      <c r="C87" t="s">
+        <v>36</v>
+      </c>
+      <c r="D87" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87">
+        <v>7</v>
+      </c>
+      <c r="F87">
+        <v>7</v>
+      </c>
+      <c r="G87">
+        <v>7</v>
+      </c>
+      <c r="H87">
+        <v>7</v>
+      </c>
+      <c r="I87">
+        <v>7</v>
+      </c>
+      <c r="J87">
+        <v>7</v>
+      </c>
+      <c r="K87" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" t="s">
+        <v>548</v>
+      </c>
+      <c r="C88" t="s">
+        <v>36</v>
+      </c>
+      <c r="D88" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88">
+        <v>8041.7</v>
+      </c>
+      <c r="G88">
+        <v>6989.3</v>
+      </c>
+      <c r="H88">
+        <v>5665.6</v>
+      </c>
+      <c r="I88">
+        <v>4871.3</v>
+      </c>
+      <c r="J88">
+        <v>4341.8999999999996</v>
+      </c>
+      <c r="K88" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" t="s">
+        <v>548</v>
+      </c>
+      <c r="C89" t="s">
+        <v>36</v>
+      </c>
+      <c r="D89" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89">
+        <v>113.3</v>
+      </c>
+      <c r="G89">
+        <v>120.9</v>
+      </c>
+      <c r="H89">
+        <v>120.9</v>
+      </c>
+      <c r="I89">
+        <v>120.9</v>
+      </c>
+      <c r="J89">
+        <v>120.9</v>
+      </c>
+      <c r="K89" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" t="s">
+        <v>548</v>
+      </c>
+      <c r="C90" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="G90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="H90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="I90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="J90">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="K90" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="B91" t="s">
+        <v>548</v>
+      </c>
+      <c r="C91" t="s">
+        <v>36</v>
+      </c>
+      <c r="D91" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91">
+        <v>40</v>
+      </c>
+      <c r="F91">
+        <v>40</v>
+      </c>
+      <c r="G91">
+        <v>40</v>
+      </c>
+      <c r="H91">
+        <v>40</v>
+      </c>
+      <c r="I91">
+        <v>40</v>
+      </c>
+      <c r="J91">
+        <v>40</v>
+      </c>
+      <c r="K91" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="B92" t="s">
+        <v>548</v>
+      </c>
+      <c r="C92" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <v>3</v>
+      </c>
+      <c r="G92">
+        <v>3</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>3</v>
+      </c>
+      <c r="J92">
+        <v>3</v>
+      </c>
+      <c r="K92" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" t="s">
+        <v>549</v>
+      </c>
+      <c r="C93" t="s">
+        <v>31</v>
+      </c>
+      <c r="D93" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93">
+        <v>2150</v>
+      </c>
+      <c r="F93">
+        <v>2100</v>
+      </c>
+      <c r="J93">
+        <v>2000</v>
+      </c>
+      <c r="K93" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" t="s">
+        <v>549</v>
+      </c>
+      <c r="C94" t="s">
+        <v>31</v>
+      </c>
+      <c r="D94" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94">
+        <v>75</v>
+      </c>
+      <c r="F94">
+        <v>75</v>
+      </c>
+      <c r="J94">
+        <v>70</v>
+      </c>
+      <c r="K94" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="B95" t="s">
+        <v>549</v>
+      </c>
+      <c r="C95" t="s">
+        <v>31</v>
+      </c>
+      <c r="D95" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="F95">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="J95">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="K95" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="B96" t="s">
+        <v>549</v>
+      </c>
+      <c r="C96" t="s">
+        <v>31</v>
+      </c>
+      <c r="D96" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96">
+        <v>0.35</v>
+      </c>
+      <c r="F96">
+        <v>0.35</v>
+      </c>
+      <c r="J96">
+        <v>0.35</v>
+      </c>
+      <c r="K96" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11">
+      <c r="B97" t="s">
+        <v>549</v>
+      </c>
+      <c r="C97" t="s">
+        <v>31</v>
+      </c>
+      <c r="D97" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97">
+        <v>0.5</v>
+      </c>
+      <c r="F97">
+        <v>0.5</v>
+      </c>
+      <c r="J97">
+        <v>0.5</v>
+      </c>
+      <c r="K97" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11">
+      <c r="B98" t="s">
+        <v>549</v>
+      </c>
+      <c r="C98" t="s">
+        <v>31</v>
+      </c>
+      <c r="D98" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98">
+        <v>45</v>
+      </c>
+      <c r="F98">
+        <v>45</v>
+      </c>
+      <c r="G98">
+        <v>45</v>
+      </c>
+      <c r="H98">
+        <v>45</v>
+      </c>
+      <c r="I98">
+        <v>45</v>
+      </c>
+      <c r="J98">
+        <v>45</v>
+      </c>
+      <c r="K98" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
+      <c r="B99" t="s">
+        <v>549</v>
+      </c>
+      <c r="C99" t="s">
+        <v>31</v>
+      </c>
+      <c r="D99" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99">
+        <v>3</v>
+      </c>
+      <c r="F99">
+        <v>3</v>
+      </c>
+      <c r="G99">
+        <v>3</v>
+      </c>
+      <c r="H99">
+        <v>3</v>
+      </c>
+      <c r="I99">
+        <v>3</v>
+      </c>
+      <c r="J99">
+        <v>3</v>
+      </c>
+      <c r="K99" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11">
+      <c r="B100" t="s">
+        <v>551</v>
+      </c>
+      <c r="C100" t="s">
+        <v>31</v>
+      </c>
+      <c r="D100" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100">
+        <v>525</v>
+      </c>
+      <c r="F100">
+        <v>500</v>
+      </c>
+      <c r="J100">
+        <v>500</v>
+      </c>
+      <c r="K100" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11">
+      <c r="B101" t="s">
+        <v>551</v>
+      </c>
+      <c r="C101" t="s">
+        <v>31</v>
+      </c>
+      <c r="D101" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101">
+        <v>20</v>
+      </c>
+      <c r="F101">
+        <v>20</v>
+      </c>
+      <c r="J101">
+        <v>20</v>
+      </c>
+      <c r="K101" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11">
+      <c r="B102" t="s">
+        <v>551</v>
+      </c>
+      <c r="C102" t="s">
+        <v>31</v>
+      </c>
+      <c r="D102" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102">
+        <v>1.111</v>
+      </c>
+      <c r="F102">
+        <v>1.111</v>
+      </c>
+      <c r="J102">
+        <v>1.111</v>
+      </c>
+      <c r="K102" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="B103" t="s">
+        <v>551</v>
+      </c>
+      <c r="C103" t="s">
+        <v>31</v>
+      </c>
+      <c r="D103" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103">
         <v>0.37</v>
       </c>
-      <c r="F65">
-        <v>0.39</v>
-      </c>
-      <c r="G65">
-        <v>0.43</v>
-      </c>
-      <c r="H65" t="s">
+      <c r="F103">
+        <v>0.37</v>
+      </c>
+      <c r="J103">
+        <v>0.37</v>
+      </c>
+      <c r="K103" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="B104" t="s">
+        <v>551</v>
+      </c>
+      <c r="C104" t="s">
+        <v>31</v>
+      </c>
+      <c r="D104" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104">
+        <v>0.4</v>
+      </c>
+      <c r="F104">
+        <v>0.4</v>
+      </c>
+      <c r="J104">
+        <v>0.4</v>
+      </c>
+      <c r="K104" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11">
+      <c r="B105" t="s">
+        <v>551</v>
+      </c>
+      <c r="C105" t="s">
+        <v>31</v>
+      </c>
+      <c r="D105" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105">
+        <v>40</v>
+      </c>
+      <c r="F105">
+        <v>40</v>
+      </c>
+      <c r="G105">
+        <v>40</v>
+      </c>
+      <c r="H105">
+        <v>40</v>
+      </c>
+      <c r="I105">
+        <v>40</v>
+      </c>
+      <c r="J105">
+        <v>40</v>
+      </c>
+      <c r="K105" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
+      <c r="B106" t="s">
+        <v>551</v>
+      </c>
+      <c r="C106" t="s">
+        <v>31</v>
+      </c>
+      <c r="D106" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106">
+        <v>2</v>
+      </c>
+      <c r="G106">
+        <v>2</v>
+      </c>
+      <c r="H106">
+        <v>2</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
+      </c>
+      <c r="J106">
+        <v>2</v>
+      </c>
+      <c r="K106" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11">
+      <c r="B107" t="s">
+        <v>552</v>
+      </c>
+      <c r="C107" t="s">
+        <v>31</v>
+      </c>
+      <c r="D107" t="s">
+        <v>535</v>
+      </c>
+      <c r="E107">
+        <v>2850</v>
+      </c>
+      <c r="F107">
+        <v>2750</v>
+      </c>
+      <c r="J107">
+        <v>2650</v>
+      </c>
+      <c r="K107" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="66" spans="2:8">
-      <c r="B66" t="s">
-        <v>546</v>
-      </c>
-      <c r="C66" t="s">
-        <v>547</v>
-      </c>
-      <c r="D66" t="s">
+    <row r="108" spans="2:11">
+      <c r="B108" t="s">
+        <v>552</v>
+      </c>
+      <c r="C108" t="s">
+        <v>31</v>
+      </c>
+      <c r="D108" t="s">
+        <v>535</v>
+      </c>
+      <c r="E108">
+        <v>105</v>
+      </c>
+      <c r="F108">
+        <v>105</v>
+      </c>
+      <c r="J108">
+        <v>100</v>
+      </c>
+      <c r="K108" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11">
+      <c r="B109" t="s">
+        <v>552</v>
+      </c>
+      <c r="C109" t="s">
+        <v>31</v>
+      </c>
+      <c r="D109" t="s">
+        <v>535</v>
+      </c>
+      <c r="E109">
+        <v>1.667</v>
+      </c>
+      <c r="F109">
+        <v>1.667</v>
+      </c>
+      <c r="J109">
+        <v>1.667</v>
+      </c>
+      <c r="K109" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11">
+      <c r="B110" t="s">
+        <v>552</v>
+      </c>
+      <c r="C110" t="s">
+        <v>31</v>
+      </c>
+      <c r="D110" t="s">
+        <v>535</v>
+      </c>
+      <c r="E110">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="F110">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="J110">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="K110" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11">
+      <c r="B111" t="s">
+        <v>552</v>
+      </c>
+      <c r="C111" t="s">
+        <v>31</v>
+      </c>
+      <c r="D111" t="s">
+        <v>535</v>
+      </c>
+      <c r="E111">
+        <v>0.5</v>
+      </c>
+      <c r="F111">
+        <v>0.5</v>
+      </c>
+      <c r="J111">
+        <v>0.5</v>
+      </c>
+      <c r="K111" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11">
+      <c r="B112" t="s">
+        <v>552</v>
+      </c>
+      <c r="C112" t="s">
+        <v>31</v>
+      </c>
+      <c r="D112" t="s">
+        <v>535</v>
+      </c>
+      <c r="E112">
+        <v>25</v>
+      </c>
+      <c r="F112">
+        <v>25</v>
+      </c>
+      <c r="G112">
+        <v>25</v>
+      </c>
+      <c r="H112">
+        <v>25</v>
+      </c>
+      <c r="I112">
+        <v>25</v>
+      </c>
+      <c r="J112">
+        <v>25</v>
+      </c>
+      <c r="K112" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="113" spans="2:11">
+      <c r="B113" t="s">
+        <v>552</v>
+      </c>
+      <c r="C113" t="s">
+        <v>31</v>
+      </c>
+      <c r="D113" t="s">
+        <v>535</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113">
+        <v>2</v>
+      </c>
+      <c r="G113">
+        <v>2</v>
+      </c>
+      <c r="H113">
+        <v>2</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+      <c r="K113" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="114" spans="2:11">
+      <c r="B114" t="s">
+        <v>552</v>
+      </c>
+      <c r="C114" t="s">
+        <v>31</v>
+      </c>
+      <c r="D114" t="s">
+        <v>535</v>
+      </c>
+      <c r="E114">
+        <v>0.8</v>
+      </c>
+      <c r="F114">
+        <v>0.8</v>
+      </c>
+      <c r="G114">
+        <v>0.8</v>
+      </c>
+      <c r="H114">
+        <v>0.8</v>
+      </c>
+      <c r="I114">
+        <v>0.8</v>
+      </c>
+      <c r="J114">
+        <v>0.8</v>
+      </c>
+      <c r="K114" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="115" spans="2:11">
+      <c r="B115" t="s">
+        <v>553</v>
+      </c>
+      <c r="C115" t="s">
+        <v>31</v>
+      </c>
+      <c r="D115" t="s">
+        <v>539</v>
+      </c>
+      <c r="E115">
+        <v>4900</v>
+      </c>
+      <c r="F115">
+        <v>4850</v>
+      </c>
+      <c r="J115">
+        <v>4350</v>
+      </c>
+      <c r="K115" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="116" spans="2:11">
+      <c r="B116" t="s">
+        <v>553</v>
+      </c>
+      <c r="C116" t="s">
+        <v>31</v>
+      </c>
+      <c r="D116" t="s">
+        <v>539</v>
+      </c>
+      <c r="E116">
+        <v>170</v>
+      </c>
+      <c r="F116">
+        <v>170</v>
+      </c>
+      <c r="J116">
+        <v>150</v>
+      </c>
+      <c r="K116" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="117" spans="2:11">
+      <c r="B117" t="s">
+        <v>553</v>
+      </c>
+      <c r="C117" t="s">
+        <v>31</v>
+      </c>
+      <c r="D117" t="s">
+        <v>539</v>
+      </c>
+      <c r="E117">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="F117">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="J117">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="K117" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="118" spans="2:11">
+      <c r="B118" t="s">
+        <v>553</v>
+      </c>
+      <c r="C118" t="s">
+        <v>31</v>
+      </c>
+      <c r="D118" t="s">
+        <v>539</v>
+      </c>
+      <c r="E118">
+        <v>0.3</v>
+      </c>
+      <c r="F118">
+        <v>0.3</v>
+      </c>
+      <c r="J118">
+        <v>0.3</v>
+      </c>
+      <c r="K118" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="119" spans="2:11">
+      <c r="B119" t="s">
+        <v>553</v>
+      </c>
+      <c r="C119" t="s">
+        <v>31</v>
+      </c>
+      <c r="D119" t="s">
+        <v>539</v>
+      </c>
+      <c r="E119">
+        <v>0.5</v>
+      </c>
+      <c r="F119">
+        <v>0.5</v>
+      </c>
+      <c r="J119">
+        <v>0.5</v>
+      </c>
+      <c r="K119" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="120" spans="2:11">
+      <c r="B120" t="s">
+        <v>553</v>
+      </c>
+      <c r="C120" t="s">
+        <v>31</v>
+      </c>
+      <c r="D120" t="s">
+        <v>539</v>
+      </c>
+      <c r="E120">
+        <v>30</v>
+      </c>
+      <c r="F120">
+        <v>30</v>
+      </c>
+      <c r="G120">
+        <v>30</v>
+      </c>
+      <c r="H120">
+        <v>30</v>
+      </c>
+      <c r="I120">
+        <v>30</v>
+      </c>
+      <c r="J120">
+        <v>30</v>
+      </c>
+      <c r="K120" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="121" spans="2:11">
+      <c r="B121" t="s">
+        <v>553</v>
+      </c>
+      <c r="C121" t="s">
+        <v>31</v>
+      </c>
+      <c r="D121" t="s">
+        <v>539</v>
+      </c>
+      <c r="E121">
+        <v>3</v>
+      </c>
+      <c r="F121">
+        <v>3</v>
+      </c>
+      <c r="G121">
+        <v>3</v>
+      </c>
+      <c r="H121">
+        <v>3</v>
+      </c>
+      <c r="I121">
+        <v>3</v>
+      </c>
+      <c r="J121">
+        <v>3</v>
+      </c>
+      <c r="K121" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="122" spans="2:11">
+      <c r="B122" t="s">
+        <v>554</v>
+      </c>
+      <c r="C122" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" t="s">
         <v>19</v>
       </c>
-      <c r="E66">
-        <v>4260</v>
-      </c>
-      <c r="F66">
-        <v>3220</v>
-      </c>
-      <c r="G66">
-        <v>2200</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="E122">
+        <v>3050</v>
+      </c>
+      <c r="F122">
+        <v>2900</v>
+      </c>
+      <c r="J122">
+        <v>2700</v>
+      </c>
+      <c r="K122" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="123" spans="2:11">
+      <c r="B123" t="s">
+        <v>554</v>
+      </c>
+      <c r="C123" t="s">
+        <v>34</v>
+      </c>
+      <c r="D123" t="s">
+        <v>19</v>
+      </c>
+      <c r="E123">
+        <v>60</v>
+      </c>
+      <c r="F123">
+        <v>60</v>
+      </c>
+      <c r="J123">
+        <v>55</v>
+      </c>
+      <c r="K123" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="67" spans="2:8">
-      <c r="B67" t="s">
-        <v>546</v>
-      </c>
-      <c r="C67" t="s">
-        <v>547</v>
-      </c>
-      <c r="D67" t="s">
+    <row r="124" spans="2:11">
+      <c r="B124" t="s">
+        <v>554</v>
+      </c>
+      <c r="C124" t="s">
+        <v>34</v>
+      </c>
+      <c r="D124" t="s">
         <v>19</v>
       </c>
-      <c r="E67">
-        <v>105</v>
-      </c>
-      <c r="F67">
-        <v>85</v>
-      </c>
-      <c r="G67">
-        <v>65</v>
-      </c>
-      <c r="H67" t="s">
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="68" spans="2:8">
-      <c r="B68" t="s">
-        <v>546</v>
-      </c>
-      <c r="C68" t="s">
-        <v>547</v>
-      </c>
-      <c r="D68" t="s">
+    <row r="125" spans="2:11">
+      <c r="B125" t="s">
+        <v>554</v>
+      </c>
+      <c r="C125" t="s">
+        <v>34</v>
+      </c>
+      <c r="D125" t="s">
         <v>19</v>
       </c>
-      <c r="E68">
-        <v>3</v>
-      </c>
-      <c r="F68">
-        <v>3</v>
-      </c>
-      <c r="G68">
-        <v>3</v>
-      </c>
-      <c r="H68" t="s">
+      <c r="E125">
+        <v>0.1</v>
+      </c>
+      <c r="F125">
+        <v>0.1</v>
+      </c>
+      <c r="J125">
+        <v>0.1</v>
+      </c>
+      <c r="K125" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="126" spans="2:11">
+      <c r="B126" t="s">
+        <v>554</v>
+      </c>
+      <c r="C126" t="s">
+        <v>34</v>
+      </c>
+      <c r="D126" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126">
+        <v>0.8</v>
+      </c>
+      <c r="F126">
+        <v>0.8</v>
+      </c>
+      <c r="J126">
+        <v>0.8</v>
+      </c>
+      <c r="K126" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="127" spans="2:11">
+      <c r="B127" t="s">
+        <v>554</v>
+      </c>
+      <c r="C127" t="s">
+        <v>34</v>
+      </c>
+      <c r="D127" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127">
+        <v>30</v>
+      </c>
+      <c r="F127">
+        <v>30</v>
+      </c>
+      <c r="G127">
+        <v>30</v>
+      </c>
+      <c r="H127">
+        <v>30</v>
+      </c>
+      <c r="I127">
+        <v>30</v>
+      </c>
+      <c r="J127">
+        <v>30</v>
+      </c>
+      <c r="K127" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="69" spans="2:8">
-      <c r="B69" t="s">
-        <v>548</v>
-      </c>
-      <c r="C69" t="s">
-        <v>547</v>
-      </c>
-      <c r="D69" t="s">
+    <row r="128" spans="2:11">
+      <c r="B128" t="s">
+        <v>554</v>
+      </c>
+      <c r="C128" t="s">
+        <v>34</v>
+      </c>
+      <c r="D128" t="s">
         <v>19</v>
       </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69">
-        <v>1</v>
-      </c>
-      <c r="H69" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8">
-      <c r="B70" t="s">
-        <v>548</v>
-      </c>
-      <c r="C70" t="s">
-        <v>547</v>
-      </c>
-      <c r="D70" t="s">
-        <v>19</v>
-      </c>
-      <c r="E70">
-        <v>0.32</v>
-      </c>
-      <c r="F70">
-        <v>0.34</v>
-      </c>
-      <c r="G70">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="H70" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8">
-      <c r="B71" t="s">
-        <v>548</v>
-      </c>
-      <c r="C71" t="s">
-        <v>547</v>
-      </c>
-      <c r="D71" t="s">
-        <v>19</v>
-      </c>
-      <c r="E71">
-        <v>1650</v>
-      </c>
-      <c r="F71">
-        <v>1560</v>
-      </c>
-      <c r="G71">
-        <v>1470</v>
-      </c>
-      <c r="H71" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8">
-      <c r="B72" t="s">
-        <v>548</v>
-      </c>
-      <c r="C72" t="s">
-        <v>547</v>
-      </c>
-      <c r="D72" t="s">
-        <v>19</v>
-      </c>
-      <c r="E72">
-        <v>42</v>
-      </c>
-      <c r="F72">
-        <v>40</v>
-      </c>
-      <c r="G72">
-        <v>38</v>
-      </c>
-      <c r="H72" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8">
-      <c r="B73" t="s">
-        <v>548</v>
-      </c>
-      <c r="C73" t="s">
-        <v>547</v>
-      </c>
-      <c r="D73" t="s">
-        <v>19</v>
-      </c>
-      <c r="E73">
-        <v>1.5</v>
-      </c>
-      <c r="F73">
-        <v>1.5</v>
-      </c>
-      <c r="G73">
-        <v>1.5</v>
-      </c>
-      <c r="H73" t="s">
-        <v>531</v>
+      <c r="E128">
+        <v>4</v>
+      </c>
+      <c r="F128">
+        <v>4</v>
+      </c>
+      <c r="G128">
+        <v>4</v>
+      </c>
+      <c r="H128">
+        <v>4</v>
+      </c>
+      <c r="I128">
+        <v>4</v>
+      </c>
+      <c r="J128">
+        <v>4</v>
+      </c>
+      <c r="K128" t="s">
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -13094,7 +14800,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F5FEBD-8004-4056-8E22-73A4D5C4E48E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE480CC-6CB2-40C5-9253-D8B3AB9C7512}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13129,10 +14835,10 @@
         <v>167</v>
       </c>
       <c r="K3" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="L3" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="M3" t="s">
         <v>170</v>
@@ -13140,13 +14846,13 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="C4" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="D4" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -13155,10 +14861,10 @@
         <v>264</v>
       </c>
       <c r="I4" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J4" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -13172,13 +14878,13 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="C5" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="D5" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -13187,10 +14893,10 @@
         <v>264</v>
       </c>
       <c r="I5" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="J5" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
@@ -13204,13 +14910,13 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="C6" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="D6" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -13219,10 +14925,10 @@
         <v>264</v>
       </c>
       <c r="I6" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="J6" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -13236,13 +14942,13 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C7" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="D7" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -13251,10 +14957,10 @@
         <v>264</v>
       </c>
       <c r="I7" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="J7" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -13268,13 +14974,13 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="C8" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="D8" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -13283,10 +14989,10 @@
         <v>264</v>
       </c>
       <c r="I8" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="J8" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -13300,13 +15006,13 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="C9" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D9" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -13315,10 +15021,10 @@
         <v>264</v>
       </c>
       <c r="I9" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="J9" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
@@ -13332,13 +15038,13 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C10" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="D10" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -13347,10 +15053,10 @@
         <v>264</v>
       </c>
       <c r="I10" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="J10" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -13364,13 +15070,13 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="C11" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="D11" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -13379,10 +15085,10 @@
         <v>264</v>
       </c>
       <c r="I11" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="J11" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K11" t="s">
         <v>21</v>
@@ -13396,13 +15102,13 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C12" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="D12" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -13411,10 +15117,10 @@
         <v>264</v>
       </c>
       <c r="I12" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="J12" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -13428,13 +15134,13 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C13" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="D13" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -13443,10 +15149,10 @@
         <v>264</v>
       </c>
       <c r="I13" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="J13" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="K13" t="s">
         <v>21</v>
